--- a/GV_Campaign_NoEmail_20260620.xlsx
+++ b/GV_Campaign_NoEmail_20260620.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GV Campaign (textable)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GV Campaign (randomized)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="95" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>SMS Script</t>
+          <t>SMS Script (unique)</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hi Keelie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10319 Violetlawn St, Detroit, MI 48204; 11701 Winthrop St, Detroit, MI 48227; 14176 Houston Whittier St, Detroit, MI 48205; 14337 Dacosta St, Detroit, MI 48223; 15373 Lamphere St, Detroit, MI 48223; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Keelie. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 10319 Violetlawn St, Detroit, MI 48204; 11701 Winthrop St, Detroit, MI 48227; 14176 Houston Whittier St, Detroit, MI 48205; 14337 Dacosta St, Detroit, MI 48223; 15373 Lamphere St, Detroit, MI 48223; …. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hi Greg, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 125 Deer Hound Trl, Columbia, SC 29223; 145 Angel Garden Way, Columbia, SC 29223; 1731 Cermack St, Columbia, SC 29223; 203 Autumn Run Cir, Columbia, SC 29229; 205 Alderston Way, Columbia, SC 29229; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Greg, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hi Amar, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10504 Olympic St NW, Albuquerque, NM 87114; 2 Package 6509/6513 Arcilla Pl NW, Albuquerque, NM 87120; 2 Prime Lots Volcano Clfs, Albuquerque, NM 87120; 3920 Bryan Ave NW, Albuquerque, NM 87114; 4000 Bryan Ave NW, Albuquerque, NM 87114; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Amar, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hi Tyjuan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 108 Malisa Dr, Columbia, SC 29229; 112 Stanford St, Columbia, SC 29203; 1124 Robin Nest Rd, Columbia, SC 29223; 1700 N Woodstream Rd, Columbia, SC 29212; 2309 Cunningham Rd, Columbia, SC 29210; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Tyjuan — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hi Julie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1146 Castle Pinckney Rd, Columbia, SC 29223; 132 Fairlawn Ct, Columbia, SC 29203; 190 Morningside Dr, Columbia, SC 29210; 218 Gate Post Ln, Columbia, SC 29223; 2584 Cherry St, Columbia, SC 29205; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Julie, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1146 Castle Pinckney Rd, Columbia, SC 29223; 132 Fairlawn Ct, Columbia, SC 29203; 190 Morningside Dr, Columbia, SC 29210; 218 Gate Post Ln, Columbia, SC 29223; 2584 Cherry St, Columbia, SC 29205; …. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hi Jasmine, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13 Gatewood Way, Columbia, SC 29229; 137 Westbridge Rd, Columbia, SC 29223; 29 Wild Iris Ct, Columbia, SC 29209; 4040 Conners St, Columbia, SC 29204; 5802 McMillan Cir, Columbia, SC 29212; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jasmine. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 13 Gatewood Way, Columbia, SC 29229; 137 Westbridge Rd, Columbia, SC 29223; 29 Wild Iris Ct, Columbia, SC 29209; 4040 Conners St, Columbia, SC 29204; 5802 McMillan Cir, Columbia, SC 29212; … — a cash purchase. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hi John, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11718 Coachfield Ln, Houston, TX 77035; 3403 Tidewater Dr, Houston, TX 77045; 5635 Ashburn St, Houston, TX 77033. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>John, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hi Lauren, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1531 Alma Rd, Columbia, SC 29209; 1824 Fairhaven Dr, Columbia, SC 29210; 212 Lake Carolina Blvd, Columbia, SC 29229; 219 Finsbury Rd, Columbia, SC 29212; 2713 Trull St, Columbia, SC 29204; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Lauren. I'm Charles with Paragon Government Solutions, and interested in buying 1531 Alma Rd, Columbia, SC 29209; 1824 Fairhaven Dr, Columbia, SC 29210; 212 Lake Carolina Blvd, Columbia, SC 29229; 219 Finsbury Rd, Columbia, SC 29212; 2713 Trull St, Columbia, SC 29204; … for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hi Tricia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 116 Patio Pl, Columbia, SC 29212; 223 Northwood St, Columbia, SC 29201; 2815 Wesley Dr, Columbia, SC 29204; 38 Cardington Ct, Columbia, SC 29209; 5225 Two Notch Rd, Columbia, SC 29204; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Tricia, hi — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hi Wendy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 117 Lambeth Dr, Columbia, SC 29209; 1331 Boston St, Columbia, SC 29203; 1522 Jerome Dr, Columbia, SC 29203; 3844 Wilmot Ave, Columbia, SC 29205; 40 Brooksby Ct, Columbia, SC 29209; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Wendy, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hi Brad, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1143 Owens Rd, Columbia, SC 29203; 1515 Hatcher Dr, Columbia, SC 29203; 1531 Hatcher Dr, Columbia, SC 29203; 1929 Bluff Rd Unit 115, Columbia, SC 29201; 6930 Monticello Rd, Columbia, SC 29203; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Brad, hi, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1143 Owens Rd, Columbia, SC 29203; 1515 Hatcher Dr, Columbia, SC 29203; 1531 Hatcher Dr, Columbia, SC 29203; 1929 Bluff Rd Unit 115, Columbia, SC 29201; 6930 Monticello Rd, Columbia, SC 29203; … — a cash purchase. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hi Joey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1515 Rushmore Rd, Columbia, SC 29210; 272 Bassett Loop, Columbia, SC 29229; 3408 Belvedere Dr, Columbia, SC 29204; 420 Forest Grove Cir, Columbia, SC 29210; 9429 S Chelsea Rd, Columbia, SC 29223; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Joey, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hi Nina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 106 Rolling Knoll Dr, Columbia, SC 29229; 141 Wincay Rd, Columbia, SC 29223; 1683 Rabon Farms Ln, Columbia, SC 29223; 424 Folkstone Rd, Columbia, SC 29223; 431 Pineneedle Rd, Columbia, SC 29203; …. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Nina, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hi Austin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1246 Rabon Pond Dr, Columbia, SC 29223; 1960 Drexel Lake Dr, Columbia, SC 29223; 3033 Blue Brook Ln, Columbia, SC 29209; 466 Robins Egg Dr, Columbia, SC 29229; 7504 Teague Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Austin. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 1246 Rabon Pond Dr, Columbia, SC 29223; 1960 Drexel Lake Dr, Columbia, SC 29223; 3033 Blue Brook Ln, Columbia, SC 29209; 466 Robins Egg Dr, Columbia, SC 29229; 7504 Teague Rd, Columbia, SC 29209. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hi Bonni, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 145 Patio Pl, Columbia, SC 29212; 1909 Mitchell St, Columbia, SC 29205; 2350 Center St, Columbia, SC 29204; 628 Ridge Trail Dr, Columbia, SC 29229; 9829 Highgate Rd, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Bonni — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hi Daleik, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1163 Atkinson St, Detroit, MI 48202; 1200 S Ethel St, Detroit, MI 48217; 13120 Washburn St, Detroit, MI 48238; 19249 Marx Ave, Detroit, MI 48203; 3948 Minnesota Ave, Detroit, MI 48212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Daleik, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hi Jamila, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 103 Village Way, Columbia, SC 29209; 138 Morningside Dr, Columbia, SC 29210; 3825 Monroe St, Columbia, SC 29205; 407 Sesqui Trl, Columbia, SC 29223; 835 Denny Rd, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jamila, hi, I'm Charles with Paragon Government Solutions. I'm reaching out about 103 Village Way, Columbia, SC 29209; 138 Morningside Dr, Columbia, SC 29210; 3825 Monroe St, Columbia, SC 29205; 407 Sesqui Trl, Columbia, SC 29223; 835 Denny Rd, Columbia, SC 29203 — a cash purchase. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hi Mark, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12717 Indiana St, Detroit, MI 48238; 13166 Montville Pl, Detroit, MI 48238; 14195 Kentfield St, Detroit, MI 48223; 9613 American St, Detroit, MI 48204; 9755 Nardin Dr, Detroit, MI 48204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Mark, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hi Shayla, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 133 Heritage Village Ln, Columbia, SC 29212; 3000 Richfield Dr, Columbia, SC 29201; 398 Fox Squirrel Cir, Columbia, SC 29209; 41 Heritage Village Ln, Columbia, SC 29212; 6 Woodlands Ridge Ct, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Shayla, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 133 Heritage Village Ln, Columbia, SC 29212; 3000 Richfield Dr, Columbia, SC 29201; 398 Fox Squirrel Cir, Columbia, SC 29209; 41 Heritage Village Ln, Columbia, SC 29212; 6 Woodlands Ridge Ct, Columbia, SC 29229. Is the seller open to a cash as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hi Tracy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 126 Burnsdowne Rd, Columbia, SC 29210; 188 Crestland Dr, Columbia, SC 29210; 196 Cottage Lake Way, Columbia, SC 29209; 212 Kendrick Rd, Columbia, SC 29229; 570 Kimpton Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Tracy — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hi Becky, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 115 Mulberry Ln, Columbia, SC 29201; 137 Canterfield Rd, Columbia, SC 29212; 1622 Crestview Ave, Columbia, SC 29223; 923 Huntington Ave, Columbia, SC 29205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Becky, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hi Brandon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13161 Monica St, Detroit, MI 48238; 13595 Wyoming Ave, Detroit, MI 48238; 16093 Liberal St, Detroit, MI 48205; 1956 Monterey St, Detroit, MI 48206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Brandon, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hi Bryant, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1111 Cloister Pl, Columbia, SC 29210; 1158 Cloister Pl, Columbia, SC 29210; 205 Twin Oaks Ln, Columbia, SC 29209; 7604 Edgewater Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Bryant. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 1111 Cloister Pl, Columbia, SC 29210; 1158 Cloister Pl, Columbia, SC 29210; 205 Twin Oaks Ln, Columbia, SC 29209; 7604 Edgewater Dr, Columbia, SC 29223. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hi Jamie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2018 Hallmark Ct, Lakeland, FL 33803; 4119 Sherman Hills Pkwy W, Jacksonville, FL 32210; 541 Linwood Ave, Jacksonville, FL 32206; 857 Benbow St, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jamie, hi. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2018 Hallmark Ct, Lakeland, FL 33803; 4119 Sherman Hills Pkwy W, Jacksonville, FL 32210; 541 Linwood Ave, Jacksonville, FL 32206; 857 Benbow St, Jacksonville, FL 32209. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hi Nadia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1009 Gardendale Dr, Columbia, SC 29210; 1155 Cloister Pl, Columbia, SC 29210; 1522 Hibiscus St, Columbia, SC 29205; 303 Harbor Dr, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Nadia, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hi Renee, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 228 Rolling Rock Rd, Columbia, SC 29212; 400 Green Tree Cir, Columbia, SC 29203; 400 Stanford St, Columbia, SC 29203; 562 Buckhaven Way, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Renee — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hi Sheila, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 124 Farrow Pointe Ln, Columbia, SC 29203; 5666 Middleton Ct, Columbia, SC 29203; E/s Tremont Ave #12, Columbia, SC 29203; E/s Tremont Ave #13, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Sheila, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 124 Farrow Pointe Ln, Columbia, SC 29203; 5666 Middleton Ct, Columbia, SC 29203; E/s Tremont Ave #12, Columbia, SC 29203; E/s Tremont Ave #13, Columbia, SC 29203. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hi Amber, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 314 Leton Dr, Columbia, SC 29210; 316 E Waverly Place Ct, Columbia, SC 29229; 4615 Bluff Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Amber, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hi ANDREA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3736 ROSE Street, Jacksonville, FL 32208; 7316 Parkview Dr, Columbia, SC 29223; 9606 DEVONSHIRE Boulevard, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there ANDREA. Charles here with Paragon Government Solutions, and interested in buying 3736 ROSE Street, Jacksonville, FL 32208; 7316 Parkview Dr, Columbia, SC 29223; 9606 DEVONSHIRE Boulevard, Jacksonville, FL 32208 for cash. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hi Andrew, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10201 S Princeton Ave, Chicago, IL 60628; 2469 E 74th St, Chicago, IL 60649; 7843 S Langley Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Andrew, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hi Angela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1024 Price Ave, Columbia, SC 29201; 277 Piney Grove Rd, Columbia, SC 29210; 953 Texas St, Columbia, SC 29201. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Angela, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hi Anthony, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11439 Ohio St, Detroit, MI 48204; 19614 Charest St, Detroit, MI 48234; 2569 Alter Rd, Detroit, MI 48215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Anthony. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 11439 Ohio St, Detroit, MI 48204; 19614 Charest St, Detroit, MI 48234; 2569 Alter Rd, Detroit, MI 48215. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hi Anya, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12664 Kelly Rd, Detroit, MI 48224; 19187 Gainsborough Rd, Detroit, MI 48223; 5601 Marlborough St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Anya. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 12664 Kelly Rd, Detroit, MI 48224; 19187 Gainsborough Rd, Detroit, MI 48223; 5601 Marlborough St, Detroit, MI 48224. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hi Avia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 205 Parliament Dr, Columbia, SC 29223; 525 Pittsdowne Rd, Columbia, SC 29210; 8416 Little John Dr, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Avia, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 205 Parliament Dr, Columbia, SC 29223; 525 Pittsdowne Rd, Columbia, SC 29210; 8416 Little John Dr, Columbia, SC 29209. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hi Billy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 23 Braiden Manor Rd, Columbia, SC 29209; 231 Gayle Pond Trce, Columbia, SC 29209; 551 Seton Hall Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Billy, Charles here with Paragon Government Solutions. interested in buying 23 Braiden Manor Rd, Columbia, SC 29209; 231 Gayle Pond Trce, Columbia, SC 29209; 551 Seton Hall Dr, Columbia, SC 29223 for cash. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hi Carlina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2027 Leesburg Rd, Columbia, SC 29209; 54 Monmouth Ct, Columbia, SC 29209; 924 Stebondale Rd, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Carlina. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 2027 Leesburg Rd, Columbia, SC 29209; 54 Monmouth Ct, Columbia, SC 29209; 924 Stebondale Rd, Columbia, SC 29203. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hi CHAD, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1169 WOODRUFF Avenue, Jacksonville, FL 32205; 5148 ATTLEBORO Street, Jacksonville, FL 32205; 6116 SUDBURY Avenue S, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey CHAD, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 1169 WOODRUFF Avenue, Jacksonville, FL 32205; 5148 ATTLEBORO Street, Jacksonville, FL 32205; 6116 SUDBURY Avenue S, Jacksonville, FL 32210 for cash. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hi Charles, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 17593 Monica St, Detroit, MI 48221; 5540 Guilford St, Detroit, MI 48224; 7839 Clayburn St, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Charles, hi, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 17593 Monica St, Detroit, MI 48221; 5540 Guilford St, Detroit, MI 48224; 7839 Clayburn St, Detroit, MI 48228 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hi Cody, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 104 Harbor Dr, Columbia, SC 29229; 126 Baysdale Dr, Columbia, SC 29229; 276 Oberlin Rd, Columbia, SC 29212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Cody — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hi Daniel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1257 E 170th St, Cleveland, OH 44110; 3357 W 30th St, Cleveland, OH 44109; 5911 Lexington Ave, Cleveland, OH 44103. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Daniel, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hi DIETCHI, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1007 Anarine Rd, Fayetteville, NC 28303; 1623 Gibson St, Fayetteville, NC 28301; 7314 Hyannis Dr, Fayetteville, NC 28304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi DIETCHI, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hi Heather, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15385 Stansbury St, Detroit, MI 48227; 15862 Stansbury St, Detroit, MI 48227; 20008 Spencer St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Heather — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hi Jamie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2518 Putnam St, Columbia, SC 29204; 509 Ridge Trail Dr, Columbia, SC 29229; 5912 Yorkshire Dr, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Jamie, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hi Kristian, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12140 Wayburn St, Detroit, MI 48224; 19639 Wexford St, Detroit, MI 48234; 9092 Patton St, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Kristian, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hi Mark, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1233 W 73rd Pl, Chicago, IL 60636; 1647 W 59th St, Chicago, IL 60636; 6037 &amp; 6039 S Wood St, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Mark — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hi Melissa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15534 Rocco Dr, Baker, LA 70714; 2128 Clark Ave, Zachary, LA 70791; 2133 Clark Ave, Zachary, LA 70791. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Melissa, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1023 Crow Ct, Grand Prairie, TX 75051; 2666 Kellogg Ave, Dallas, TX 75216; 3644 Kimball Ridge Pl, Dallas, TX 75233. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Michael. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 1023 Crow Ct, Grand Prairie, TX 75051; 2666 Kellogg Ave, Dallas, TX 75216; 3644 Kimball Ridge Pl, Dallas, TX 75233. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hi Nancy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10310 Mills Run Dr, Houston, TX 77070; 17414 Turquoise Stream Dr, Houston, TX 77095; 6527 Gladewell Dr, Houston, TX 77072. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Nancy. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 10310 Mills Run Dr, Houston, TX 77070; 17414 Turquoise Stream Dr, Houston, TX 77095; 6527 Gladewell Dr, Houston, TX 77072. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hi Patrick, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 135 Fox Squirrel Cir, Columbia, SC 29209; 213 Greemount Cir, Columbia, SC 29209; 8206 Bayfield Rd, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Patrick. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 135 Fox Squirrel Cir, Columbia, SC 29209; 213 Greemount Cir, Columbia, SC 29209; 8206 Bayfield Rd, Columbia, SC 29223. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hi Sam, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10799 Worden St, Detroit, MI 48224; 16500 Eastburn St, Detroit, MI 48205; 9205 McKinney St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Sam. I'm Charles with Paragon Government Solutions, and interested in buying 10799 Worden St, Detroit, MI 48224; 16500 Eastburn St, Detroit, MI 48205; 9205 McKinney St, Detroit, MI 48224 for cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hi there, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3700 Ulmer Rd, Columbia, SC 29209; 8 Hampton Oaks Pl, Columbia, SC 29212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day there. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 3700 Ulmer Rd, Columbia, SC 29209; 8 Hampton Oaks Pl, Columbia, SC 29212. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hi Albert, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12717 Riad St, Grosse Pointe, MI 48224; 13892 Bringard Dr, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Albert, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 12717 Riad St, Grosse Pointe, MI 48224; 13892 Bringard Dr, Detroit, MI 48205. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hi Alex, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 201 Sandhurst Rd, Columbia, SC 29210; 2113 Kathleen Dr, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Alex — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hi Alex, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1152 Vinewood St, Detroit, MI 48216; 2905 Putnam St, Detroit, MI 48208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Alex, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hi Alexander, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16321 Stockbridge Ave, Cleveland, OH 44128; 3319 Fulton Rd, Cleveland, OH 44109. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Alexander — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hi Alexandra, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 219 Dixon Dr, Columbia, SC 29203; 7602 Hunt Club Rd APT A104, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Alexandra, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 219 Dixon Dr, Columbia, SC 29203; 7602 Hunt Club Rd APT A104, Columbia, SC 29223. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hi Amber, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9520 Royal Ln #104, Dallas TX 75243; 9520 Royal Ln (#114/#121/#306), Dallas TX 75243. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Amber, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hi Andy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6506 Christie Rd, Columbia, SC 29209; 7818 Exeter Ln, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Andy, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hi Anthony, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1533 S Kilbourn Ave, Chicago, IL 60623; 6914 S Winchester Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Anthony. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 1533 S Kilbourn Ave, Chicago, IL 60623; 6914 S Winchester Ave, Chicago, IL 60636. Open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hi Anthony, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 132 Flora Springs Cir, Columbia, SC 29223; 25 Heatherlaurel Ct, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Anthony. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 132 Flora Springs Cir, Columbia, SC 29223; 25 Heatherlaurel Ct, Columbia, SC 29223. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hi ARTHUR, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1010 KENMORE Street, Jacksonville, FL 32208; 7035 ELWOOD Avenue, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello ARTHUR, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hi Arthur, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1987 W Melvina St, Milwaukee, WI 53206; 3729 N Vel R Phillips Ave, Milwaukee, WI 53212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Arthur, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hi Bobby, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 14941 Littlefield St, Detroit, MI 48227; 15411 Ferguson St, Detroit, MI 48227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Bobby — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hi Brad, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1253 Mosser Dr, Columbia, SC 29203; 9 Twin Oaks Cir, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Brad, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hi Brittany, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2065 Missouri St, Baton Rouge, LA 70802; 2614 Bartlett St, Baton Rouge, LA 70805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Brittany, I'm Charles with Paragon Government Solutions. I'm reaching out about 2065 Missouri St, Baton Rouge, LA 70802; 2614 Bartlett St, Baton Rouge, LA 70805 — a cash purchase. Open to a discounted cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hi Caleb, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 232 Twin Oaks Ln, Columbia, SC 29209; 822 Apache Dr, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Caleb, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hi Cameron, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9175 Everts St, Detroit, MI 48224; 9824 Philip St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Cameron, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 9175 Everts St, Detroit, MI 48224; 9824 Philip St, Detroit, MI 48224. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hi Chachere, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3805 Trotter Rd, Columbia, SC 29209; 808 Kingsbridge Rd, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Chachere. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 3805 Trotter Rd, Columbia, SC 29209; 808 Kingsbridge Rd, Columbia, SC 29210. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hi CHRISTINA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1602 Gardenia Ave, Fayetteville, NC 28311; 1716 Shaw Rd, Fayetteville, NC 28311. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>CHRISTINA, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hi Crystal, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5648 S Sawyer Ave, Chicago, IL 60629; 6100 S Bishop St, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Crystal, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hi Daniella, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 22118 Ulster St, Detroit, MI 48219; 6444 Ashton Ave, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Daniella, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 22118 Ulster St, Detroit, MI 48219; 6444 Ashton Ave, Detroit, MI 48228. Is the seller open to a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hi David, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11532 S Harvard Ave, Chicago, IL 60628; 7629 S Maryland Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey David, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hi Dean, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19760 Rowe St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Dean. Charles here with Paragon Government Solutions, and interested in buying 19760 Rowe St, Detroit, MI 48205 for cash. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hi Delaney, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2 Woodshaw Ct, Columbia, SC 29212; 4604 Ridgewood Ave, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Delaney — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hi DENISE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7330 ELWOOD Avenue, Jacksonville, FL 32208; 8384 DELAWARE Avenue, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello DENISE, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hi Derek, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3814 Hardy St, Houston, TX 77009; 3818 Hardy St, Houston, TX 77009. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Derek, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hi Ejaz, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 14440 Chelsea St, Detroit, MI 48213; 16828 W Chicago St, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Ejaz, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hi Evan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4203 New Orleans St, Houston, TX 77020; 5839 Southurst St, Houston, TX 77033. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Evan, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 4203 New Orleans St, Houston, TX 77020; 5839 Southurst St, Houston, TX 77033. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hi Franco, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13027 Rosemary St, Detroit, MI 48213; 14303 Rosemary St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Franco, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 13027 Rosemary St, Detroit, MI 48213; 14303 Rosemary St, Detroit, MI 48213. Is the seller open to a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hi Gaston, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15470 Mapleridge St, Detroit, MI 48205; 5565 Fairview St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Gaston. Charles Pleasant, Paragon Government Solutions, and interested in buying 15470 Mapleridge St, Detroit, MI 48205; 5565 Fairview St, Detroit, MI 48213 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hi Graciela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2519 Chalk Hill Rd, Dallas, TX 75212; 2522 Wilhurt Ave, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Graciela. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 2519 Chalk Hill Rd, Dallas, TX 75212; 2522 Wilhurt Ave, Dallas, TX 75216. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hi Greg, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20 Shuler Cir, Columbia, SC 29212; 304 Stanford St, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Greg, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 20 Shuler Cir, Columbia, SC 29212; 304 Stanford St, Columbia, SC 29203. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hi Gregory, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4440 Sexton Rd, Cleveland, OH 44105; 8018 Platt Ave, Cleveland, OH 44104. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Gregory — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hi Hassan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20569 Evergreen Rd, Detroit, MI 48219; 6160 Neff Ave, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Hassan, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 20569 Evergreen Rd, Detroit, MI 48219; 6160 Neff Ave, Detroit, MI 48224. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hi JACQUELYN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2371 JAYSON Avenue, Jacksonville, FL 32208; 409 CRYSTAL Street, Jacksonville, FL 32254. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there JACQUELYN — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hi James, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 14045 Sussex St, Detroit, MI 48227; 7638 Stahelin Ave, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>James, hi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 14045 Sussex St, Detroit, MI 48227; 7638 Stahelin Ave, Detroit, MI 48228. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hi JANET, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 412 CHESTNUT Drive, Jacksonville, FL 32208; 5146 SUNDERLAND Road, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey JANET — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hi Jay, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 209 Leago St, Houston, TX 77022; 2818 S Bartell Dr APT 33, Houston, TX 77054. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jay — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hi Jessica, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10066 S Van Vlissingen Rd, Chicago, IL 60617; 4208 S Artesian Ave, Chicago, IL 60632. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Jessica. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 10066 S Van Vlissingen Rd, Chicago, IL 60617; 4208 S Artesian Ave, Chicago, IL 60632. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hi JULIANA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1546 RIVER HILLS Circle W, Jacksonville, FL 32211; 1837 BUCKMAN Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day JULIANA, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1546 RIVER HILLS Circle W, Jacksonville, FL 32211; 1837 BUCKMAN Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hi Kaila, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 17184 Dresden St, Detroit, MI 48205; 19228 Beland St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Kaila. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 17184 Dresden St, Detroit, MI 48205; 19228 Beland St, Detroit, MI 48234 for cash. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hi Kanaan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1018 W 104th Pl, Chicago, IL 60643; 8106 S Burnham Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Kanaan — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hi Kendall, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3819 Uncas St, Baton Rouge, LA 70805; 3851 Uncas St, Baton Rouge, LA 70805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Kendall, hi, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hi Keri, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11000 S Normal Ave, Chicago, IL 60628; 11534 S Princeton Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Keri, this is Charles Pleasant with Paragon Government Solutions. interested in buying 11000 S Normal Ave, Chicago, IL 60628; 11534 S Princeton Ave, Chicago, IL 60628 for cash. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hi KRAVIN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2051 FRANK E Avenue, Jacksonville, FL 32208; 6228 BLUEBIRD Road, Jacksonville, FL 32219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi KRAVIN, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hi Kristie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7604 Edgewater Dr, Columbia, SC 29223; 828 Yellow Swan Ln, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Kristie, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 7604 Edgewater Dr, Columbia, SC 29223; 828 Yellow Swan Ln, Columbia, SC 29210. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hi LaToya, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1253 Rabon Pond Dr, Columbia, SC 29223; 140 Twin Oaks Ln, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi LaToya. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 1253 Rabon Pond Dr, Columbia, SC 29223; 140 Twin Oaks Ln, Columbia, SC 29209. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hi LaTrina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19783 Annott St, Detroit, MI 48205; 7777 W Outer Dr, Detroit, MI 48235. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi LaTrina, Charles Pleasant, Paragon Government Solutions. interested in buying 19783 Annott St, Detroit, MI 48205; 7777 W Outer Dr, Detroit, MI 48235 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hi Leo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3417 Gray St, Detroit, MI 48215; 8127 E Hildale St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Leo — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hi Lisa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1506 Grand Valley Dr, Houston, TX 77090; 4923 Saxon Dr, Houston, TX 77092. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Lisa, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hi Logan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15220 Tacoma St, Detroit, MI 48205; 20485 Helen St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Logan, hi. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 15220 Tacoma St, Detroit, MI 48205; 20485 Helen St, Detroit, MI 48234 for cash. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hi MAIDELYS, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6978 PAUL HOWARD Drive, Jacksonville, FL 32222; 7004 DAYTON Road, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>MAIDELYS, hi, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 6978 PAUL HOWARD Drive, Jacksonville, FL 32222; 7004 DAYTON Road, Jacksonville, FL 32210 for cash. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hi Marcia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 367 Marshdeer Way, Columbia, SC 29229; Nx 1635 Dupont Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Marcia, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 367 Marshdeer Way, Columbia, SC 29229; Nx 1635 Dupont Dr, Columbia, SC 29223. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hi Mary, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 336 Byron Rd, Columbia, SC 29209; 3961 Live Oak St, Columbia, SC 29205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Mary, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hi MATT, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1311 GRANVDIEW Drive, Jacksonville, FL 32211; 6146 BUCKING BRONCO Drive, Jacksonville, FL 32234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi MATT, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hi McCall, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1204 Vickie Ln, Lake Charles, LA 70601; 1802 Rose St, Lake Charles, LA 70601. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello McCall, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hi Medina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1800 Walter St SE, Albuquerque, NM 87102; 314 49th St NW, Albuquerque, NM 87105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Medina, Charles here with Paragon Government Solutions. interested in buying 1800 Walter St SE, Albuquerque, NM 87102; 314 49th St NW, Albuquerque, NM 87105 for cash. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13594 Grandmont Ave, Detroit, MI 48227; 19353 Runyon St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Michael, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hi Minhaz, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19989 Coventry St, Highland Park, MI 48203; 20203 Hull St, Highland Park, MI 48203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Minhaz. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 19989 Coventry St, Highland Park, MI 48203; 20203 Hull St, Highland Park, MI 48203. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hi Mladenka, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5308 W LEWIS Avenue W, Phoenix, AZ 85035; 7630 W AVALON Drive, Phoenix, AZ 85033. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Mladenka, Charles here with Paragon Government Solutions. interested in buying 5308 W LEWIS Avenue W, Phoenix, AZ 85035; 7630 W AVALON Drive, Phoenix, AZ 85033 for cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hi Mo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 125 N Lake Pointe Dr, Columbia, SC 29229; 501 S Edisto Ave, Columbia, SC 29205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Mo, hi — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hi Mohamed, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16610 Collingham Dr, Detroit, MI 48205; 19301 Runyon St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Mohamed. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 16610 Collingham Dr, Detroit, MI 48205; 19301 Runyon St, Detroit, MI 48234 — a cash purchase. Would the owner entertain a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hi Monica, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11548 S Normal Ave, Chicago, IL 60628; 5225 S Wood St, Chicago, IL 60609. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Monica. Charles Pleasant, Paragon Government Solutions, and interested in buying 11548 S Normal Ave, Chicago, IL 60628; 5225 S Wood St, Chicago, IL 60609 for cash. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hi Monika, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2947 Appaloosa Dr, Dallas, TX 75237; 4818 Jesus Maria Ct, Dallas, TX 75236. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Monika, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hi MOSES, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5926 DUNMIRE Avenue, Jacksonville, FL 32219; 6109 STRAWFLOWER Place, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey MOSES. I'm Charles with Paragon Government Solutions, and interested in buying 5926 DUNMIRE Avenue, Jacksonville, FL 32219; 6109 STRAWFLOWER Place, Jacksonville, FL 32209 for cash. Is the seller open to a cash as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hi Nadia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 17206 Fenelon St, Detroit, MI 48212; 7267 Mettetal St, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Nadia, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hi NAJI, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 152 W 10TH Street, Jacksonville, FL 32206; 16228 TISONS BLUFF Road, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello NAJI. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 152 W 10TH Street, Jacksonville, FL 32206; 16228 TISONS BLUFF Road, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hi Nazareth, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2223 Gray St, Detroit, MI 48215; 4827 Gray St, Detroit, MI 48215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Nazareth — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hi Pamela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2912 Chestnut St, Columbia, SC 29204; 3405 Padgett Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Pamela, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hi Rachel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2539 Cherry St, Columbia, SC 29205; W/s Zacks Playhouse Rd, Hollywood, SC 29449. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Rachel, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 2539 Cherry St, Columbia, SC 29205; W/s Zacks Playhouse Rd, Hollywood, SC 29449. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hi Raquel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1513 Dianne Ct SE, Atlanta, GA; 747 Gary Rd NW, Atlanta, GA. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Raquel, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hi RYAN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1711 30TH Street W, Jacksonville, FL 32209; 2820 AUBREY Avenue, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello RYAN. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 1711 30TH Street W, Jacksonville, FL 32209; 2820 AUBREY Avenue, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hi Sam, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1000 Coatesdale Rd, Columbia, SC 29209; 245 Dove Park Rd, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Sam, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 1000 Coatesdale Rd, Columbia, SC 29209; 245 Dove Park Rd, Columbia, SC 29223 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hi Soraida, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 65 W 112th Pl, Chicago, IL 60628; 7521 S Aberdeen St, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Soraida — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hi Starr, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1086 Horne St, Houston, TX 77088; 412 N Bryan St, Houston, TX 77011. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Starr. Charles here with Paragon Government Solutions, and interested in buying 1086 Horne St, Houston, TX 77088; 412 N Bryan St, Houston, TX 77011 for cash. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hi Sydney, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 425 Columbia St, Shreveport, LA 71104; 7045 Elsie St, Shreveport, LA 71108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Sydney, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hi Tarick, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3331 S Liddesdale St, Detroit, MI 48217; 5226 Coplin St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Tarick, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hi Timeka, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2009 Las Cruces Ln, Dallas, TX 75217; 3013 Emmett St, Dallas, TX 75211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Timeka, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hi Timothy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12729 Grandmont Ave, Detroit, MI 48227; 19977 Santa Barbara Dr, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Timothy, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 12729 Grandmont Ave, Detroit, MI 48227; 19977 Santa Barbara Dr, Detroit, MI 48221. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hi Valerie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16 Sand Spur Rd, Columbia, SC 29223; 9505 Puritan Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Valerie, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 16 Sand Spur Rd, Columbia, SC 29223; 9505 Puritan Rd, Columbia, SC 29209. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hi Verdieman, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20209 Stotter St, Detroit, MI 48234; 8229 Carlin St, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Verdieman — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hi Will, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9426 Nyssa St, Houston, TX 77078. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Will, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hi WILLIAM, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 957 ODESSA Drive E, Jacksonville, FL 32254; 9604 WOODLAND Avenue, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day WILLIAM, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hi WILLIAM, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2995 Coleman Rd, Eastover, NC 28312; 6206 Larue Ct, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>WILLIAM, hi, Charles here with Paragon Government Solutions. I'm reaching out about 2995 Coleman Rd, Eastover, NC 28312; 6206 Larue Ct, Fayetteville, NC 28303 — a cash purchase. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hi there, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1700 Grays Inn Rd, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day there, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1700 Grays Inn Rd, Columbia, SC 29210. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hi there, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2412 E MARMORA Street, Phoenix, AZ 85032. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day there, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 2412 E MARMORA Street, Phoenix, AZ 85032. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hi there, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2737 Bristol Pl, New Orleans, LA 70131. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day there, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hi there, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3109 Downes Grove Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>there, hi, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hi there, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 950 W ROMA Avenue, Phoenix, AZ 85013. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day there — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hi Aaron, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7535 S Vernon Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Aaron, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hi Abe, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12621 Hirst Ave, Cleveland, OH 44135. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Abe, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Hi Acencion, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16643 Seawolf Dr, Houston, TX 77062. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Acencion. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 16643 Seawolf Dr, Houston, TX 77062. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hi Adam, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15394 Freeland St, Detroit, MI 48227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Adam, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 15394 Freeland St, Detroit, MI 48227. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hi Adam, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 195 Pomeroy Dr, Shreveport, LA 71115. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Adam, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hi Adekunle, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11722 S Parnell Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Adekunle, hi — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hi Adrian, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2923 SW 11th Ct, Cape Coral, FL 33914. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Adrian — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hi Adrian, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15003 Manor St, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Adrian. I'm Charles with Paragon Government Solutions, and I'm reaching out about 15003 Manor St, Detroit, MI 48238 — a cash purchase. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hi Adrienne, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18402 Revere St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Adrienne, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hi Alana, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4144 E 120th St, Cleveland, OH 44105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Alana, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hi Alannah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1314 Red Ridge Ter, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Alannah, Charles here with Paragon Government Solutions. I'm reaching out about 1314 Red Ridge Ter, Columbia, SC 29203 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hi Albert, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2321 Shadowbrook Dr, Baton Rouge, LA 70816. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Albert — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hi Alejandro, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 919 Christine St, Houston, TX 77017. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Alejandro, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Hi Alex, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3906 Metropolitan Ave, Dallas, TX 75210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Alex, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Hi Alex, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8049 Wetherby St, Detroit, MI 48204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Alex, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 8049 Wetherby St, Detroit, MI 48204. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Hi Alex, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 423 Exchange St, Houston, TX 77020. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Alex — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hi Alexander, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2317 NW 30th Ter, Cape Coral, FL 33993. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Alexander, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hi Alexandria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5981 Arapaho Rd #1607, Dallas TX 75248. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Alexandria — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Hi Alexis, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 17360 Mansfield St, Detroit, MI 48235. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Alexis — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hi Ali, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11718 Plainview Ave, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Ali, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hi Ali, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9030 Plainview Ave, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Ali, this is Charles Pleasant with Paragon Government Solutions. interested in buying 9030 Plainview Ave, Detroit, MI 48228 for cash. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Hi Alicia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4111 Mehalia Dr, Dallas, TX 75241. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Alicia. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 4111 Mehalia Dr, Dallas, TX 75241 — a cash purchase. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Hi Allie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4737 Kildare Ave, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Allie, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Hi Amanda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10323 Sweetbrook Dr, Houston, TX 77038. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Amanda, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 10323 Sweetbrook Dr, Houston, TX 77038 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hi AMANDA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1009 Bugle Call Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi AMANDA, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 1009 Bugle Call Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Hi Amani, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8826 Delilah St, Houston, TX 77033. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Amani — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hi AMBER, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 326 Conifer Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi AMBER, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hi Aminat, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9404 Pinehaven Dr, Dallas, TX 75227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Aminat. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 9404 Pinehaven Dr, Dallas, TX 75227. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hi Amy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1061 Lansing St, Detroit, MI 48209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Amy, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hi Amy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2034 Lakeville Dr, Humble, TX 77339. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Amy, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2034 Lakeville Dr, Humble, TX 77339 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Hi AMY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7092 Pantego Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello AMY. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 7092 Pantego Dr, Fayetteville, NC 28314 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hi Andre, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19447 Sunset St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Andre, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 19447 Sunset St, Detroit, MI 48234. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Hi Andrea, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 121 N 28th Ave, Phoenix, AZ 85009. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Andrea, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hi Angel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7606 Blessing Ave, Austin, TX 78752. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Angel. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 7606 Blessing Ave, Austin, TX 78752. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Hi Angela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16 Carroll St, Trenton, NJ 08609. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Angela, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Hi Angela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7748 S Langley Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Angela, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 7748 S Langley Ave, Chicago, IL 60619. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Hi Angela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15719 Egret Field Ln, Houston, TX 77049. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Angela, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 15719 Egret Field Ln, Houston, TX 77049. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Hi Anthony, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20185 Indiana St, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Anthony — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Hi Anthony, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19189 Appleton St, Detroit, MI 48219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Anthony, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Hi Anthony, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4141 Country Hill Dr, Baton Rouge, LA 70816. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Anthony. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 4141 Country Hill Dr, Baton Rouge, LA 70816. Open to a discounted cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hi ANTHONY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2917 PARR Court E, Jacksonville, FL 32216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there ANTHONY, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Hi Antisha, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3677 Theodore St, Detroit, MI 48211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Antisha, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3677 Theodore St, Detroit, MI 48211 — a cash purchase. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hi ANTOINETTE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9419 SCADLOCKE Road, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello ANTOINETTE, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hi April, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6510 Portsmouth Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day April — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Hi APRYL, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2225 THIERVY Drive, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day APRYL — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Hi Aram, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7407 S May St, Chicago, IL 60621. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Aram, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 7407 S May St, Chicago, IL 60621. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Hi Arianna, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4153 Concord St, Detroit, MI 48207. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Arianna. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 4153 Concord St, Detroit, MI 48207. Could the seller look at a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Hi Arianne, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9823 S Drexel Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Arianne, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 9823 S Drexel Ave, Chicago, IL 60628 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hi Arkadiusz, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2459 E 74th St, Chicago, IL 60649. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Arkadiusz — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Hi ARMANDO, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 153 Knapp Ave, Hamilton, NJ 08610. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day ARMANDO — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Hi Asa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18310 La Salle Ave, Cleveland, OH 44119. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Asa. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 18310 La Salle Ave, Cleveland, OH 44119 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Hi Ashley, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3879 W 21st St, Cleveland, OH 44109. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Ashley, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 3879 W 21st St, Cleveland, OH 44109. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hi Ashley, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 414 Angel Grove Ln, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Ashley — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Hi Ashley, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1008 Walnut Ave, Baltimore, MD 21229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Ashley, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Hi Ashley, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19261 Mitchell St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Ashley, hi, I'm Charles with Paragon Government Solutions. interested in buying 19261 Mitchell St, Detroit, MI 48234 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Hi ATIFA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6819 N PEARL Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello ATIFA — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Hi Austin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4220-22 S Miro St, New Orleans, LA 70125. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Austin, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Hi Babajide, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 317 E 134th St, Chicago, IL 60827. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Babajide, Charles Pleasant, Paragon Government Solutions. interested in buying 317 E 134th St, Chicago, IL 60827 for cash. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Hi Bailee, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11144 Sanford St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Bailee, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 11144 Sanford St, Detroit, MI 48205. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hi Barbara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2336 Albert St, Alexandria, LA 71301. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Barbara, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 2336 Albert St, Alexandria, LA 71301. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Hi BARBARA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1603 W 14TH Street, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello BARBARA. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1603 W 14TH Street, Jacksonville, FL 32209. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Hi BARD, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 651 W 46TH Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there BARD — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Hi Becky, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3830 E LAKEWOOD Parkway E #2057, Phoenix, AZ 85048. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Becky, this is Charles Pleasant with Paragon Government Solutions. interested in buying 3830 E LAKEWOOD Parkway E #2057, Phoenix, AZ 85048 for cash. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Hi Belle, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 413 Seton Hall Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Belle, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Hi Benjamin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1005 Wildwood Ave, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Benjamin. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 1005 Wildwood Ave, Columbia, SC 29203. Would the owner entertain a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Hi Benjamin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15668 Tacoma St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Benjamin, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Hi Bianca, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2609 Foerster Ave, Baltimore, MD 21230. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Bianca — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Hi Blodgie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1215 Oregon St, Bakersfield, CA 93305. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Blodgie, hi — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Hi Brad, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5765 Kleinpeter Rd, Baton Rouge, LA 70811. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Brad, hi. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5765 Kleinpeter Rd, Baton Rouge, LA 70811. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Hi Brandon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4384 Stumberg Ln, Baton Rouge, LA 70816. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Brandon — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Hi Brandon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15237 Carlisle St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Brandon, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 15237 Carlisle St, Detroit, MI 48205. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Hi Brandt, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12610 S Coast Dr, Houston, TX 77047. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Brandt, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Hi Brian, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 30 Ward Ct, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Brian, hi. Charles Pleasant, Paragon Government Solutions, and interested in buying 30 Ward Ct, Columbia, SC 29223 for cash. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Hi Brian, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1648 Tampa Bay Dr, Dallas, TX 75217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Brian, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 1648 Tampa Bay Dr, Dallas, TX 75217. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hi Brianna, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6015 N 32nd Dr, Phoenix, AZ 85017. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Brianna — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hi Bridget, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7522 S Vernon Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Bridget, hi. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 7522 S Vernon Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hi BRIGIDA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 156 Washington St, Trenton, NJ 08611. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there BRIGIDA — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Hi Brittany, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7400 Vanderkloot Ave, New Orleans, LA 70127. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Brittany — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Hi Bryton, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8215 Leather Market St, Houston, TX 77064. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Bryton, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hi Camellia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1141 E 140th St, Cleveland, OH 44110. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Camellia — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Hi Carlton, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 911 S Stadium Rd #A-31, Columbia, SC 29201. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Carlton, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Hi Carly, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10316 Ridge Oak St, Dallas, TX 75227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Carly. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 10316 Ridge Oak St, Dallas, TX 75227. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Hi Carmen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3883 Turtle Creek Blvd #1603, Dallas TX 75219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Carmen. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3883 Turtle Creek Blvd #1603, Dallas TX 75219. Open to a discounted cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Hi Carmen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7216 OAKWOOD Drive, Jacksonville, FL 32211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Carmen — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Hi Carmen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7419 Lake June Rd, Dallas, TX 75217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Carmen. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 7419 Lake June Rd, Dallas, TX 75217 for cash. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Hi Carolinas, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4723 Linden St, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Carolinas — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hi Carolyn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7201 S Vernon Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Carolyn, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 7201 S Vernon Ave, Chicago, IL 60619. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Hi Carolyn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2755 Palmyra St, New Orleans, LA 70119. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Carolyn, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2755 Palmyra St, New Orleans, LA 70119. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Hi Carolyn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6702 Tierwester St, Houston, TX 77021. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Carolyn, hi. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 6702 Tierwester St, Houston, TX 77021. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hi Carrie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1663 W 30th St, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Carrie, this is Charles Pleasant with Paragon Government Solutions. interested in buying 1663 W 30th St, Jacksonville, FL 32209 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hi Carrie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4243 Mandel Dr, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Carrie — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Hi Caryn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10017 Morocco Rd, Houston, TX 77041. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Caryn — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Hi Casey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3414 Maybank St, Columbia, SC 29204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Casey, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 3414 Maybank St, Columbia, SC 29204. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Hi Casey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2610 Brandon St, Dallas, TX 75211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Casey — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hi Cassandra, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 314 Capehill Dr, Webster, TX 77598. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Cassandra. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 314 Capehill Dr, Webster, TX 77598. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hi CATHLEEN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 339 METZ Street, Jacksonville, FL 32211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>CATHLEEN, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Hi CC, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5418 MINOSA Court, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi CC. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 5418 MINOSA Court, Jacksonville, FL 32209 — a cash purchase. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Hi Celia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2530 Marling Dr, Columbia, SC 29204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Celia, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Hi Century, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1033 Glencroft Drive, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Century, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1033 Glencroft Drive, Columbia, SC 29210. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Hi Century, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5411 Cabot Ave, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Century, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Hi Cerita, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 528 1st St SW, Birmingham, AL 35211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Cerita, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 528 1st St SW, Birmingham, AL 35211. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Hi Chad, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2426 Dora Ave NW, Albuquerque, NM 87104. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Chad, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Hi Chad, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4012 Shady Hollow Ln, Dallas, TX 75233. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Chad. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 4012 Shady Hollow Ln, Dallas, TX 75233. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hi CHARLEEN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3821 MIRUELO Circle N, Jacksonville, FL 32217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there CHARLEEN. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3821 MIRUELO Circle N, Jacksonville, FL 32217. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Hi Charles, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 217 Stockmoor Rd, Columbia, SC 29212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Charles — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Hi Charles, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 334 Carver St, Lafayette, LA 70501. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Charles, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 334 Carver St, Lafayette, LA 70501 — a cash purchase. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Hi Cherie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4731 Stokes St, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Cherie, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Hi CHERYL, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9711 SKYDIVE Court, Jacksonville, FL 32221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello CHERYL, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Hi Chip, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 329 Shagbark Ave, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Chip, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Hi Chip, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 329 Shagbark Ave, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Chip, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Hi Chip, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1905 E Kings Hwy, Shreveport, LA 71105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Chip, hi. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 1905 E Kings Hwy, Shreveport, LA 71105. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Hi Chris, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 106 Harbor Dr, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Chris, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Hi Chris, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3405 Gwynns Falls Pkwy, Baltimore, MD 21216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Chris — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hi CHRIS, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2332 BUTTONWOOD Drive, Jacksonville, FL 32216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey CHRIS, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2332 BUTTONWOOD Drive, Jacksonville, FL 32216 — a cash purchase. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Hi Chris, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3804 Park Heights Ave, Baltimore, MD 21215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Chris, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Hi Chris, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8315 Westbourne Dr, Charlotte, NC 28216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Chris, hi. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 8315 Westbourne Dr, Charlotte, NC 28216. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Hi Christina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2776 Prince Charles Ct, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Christina — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Hi Christine, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2633 W Grand Blvd, Detroit, MI 48208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Christine. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 2633 W Grand Blvd, Detroit, MI 48208 — a cash purchase. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hi CHRISTOPHER, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1404 Valencia Dr, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>CHRISTOPHER, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hi Christopher, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7741 S Chappel Ave, Chicago, IL 60649. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Christopher — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hi Chuck, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 711 S Montclair Ave, Dallas, TX 75208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Chuck, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 711 S Montclair Ave, Dallas, TX 75208. Open to a discounted cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Hi Cindy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2237 Kingswood Dr, Columbia, SC 29205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Cindy, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Hi Cindy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11349 S Saint Lawrence Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Cindy, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 11349 S Saint Lawrence Ave, Chicago, IL 60628. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Hi Cindy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1703 Alba Dr, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Cindy — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Hi Cindy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10527 Cayuga Dr, Dallas, TX 75228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Cindy — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Hi Clarence, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7707 Candlegreen Ln, Houston, TX 77071. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Clarence. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 7707 Candlegreen Ln, Houston, TX 77071 — a cash purchase. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Hi Claudia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20495 Mendota St, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Claudia — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Hi Clay, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1522 W Taylor St, Phoenix, AZ 85007. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Clay. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1522 W Taylor St, Phoenix, AZ 85007. Is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Hi Cliff, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11604 Tuscora Ave, Cleveland, OH 44108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Cliff. Charles here with Paragon Government Solutions, and I'm reaching out about 11604 Tuscora Ave, Cleveland, OH 44108 — a cash purchase. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Hi Coby, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5906 Bower Ave, Cleveland, OH 44127. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Coby, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Hi Cody, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6348 S Rhodes Ave, Chicago, IL 60637. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Cody, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Hi Cole, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 417 W Brooklyn Ave, Dallas, TX 75208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Cole. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 417 W Brooklyn Ave, Dallas, TX 75208. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Hi Colleen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3945 Liberty Ave, Pittsburgh, PA 15224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Colleen, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Hi Comeiko, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4971 Brigadoon Ln, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Comeiko. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 4971 Brigadoon Ln, Dallas, TX 75216. Would the owner entertain a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Hi Compass, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1011 Ormewood Ave SE, Atlanta, GA 30316. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Compass, hi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1011 Ormewood Ave SE, Atlanta, GA 30316. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Hi Connie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8133 Cavalier Cir, Dallas TX 75227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Connie — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Hi Conor, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 937 Avenue S, Birmingham, AL 35214. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Conor, Charles here with Paragon Government Solutions. I'm reaching out about 937 Avenue S, Birmingham, AL 35214 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Hi Corey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3503 Oakmont Ave, Baltimore, MD 21215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Corey, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 3503 Oakmont Ave, Baltimore, MD 21215 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Hi Corey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16410 Novara St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Corey, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 16410 Novara St, Detroit, MI 48205 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Hi Cory, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5747 Easthampton Dr Unit D, Houston, TX 77039. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Cory, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5747 Easthampton Dr Unit D, Houston, TX 77039. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Hi Crystal, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4010 Copeland St, Dallas, TX 75210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Crystal. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 4010 Copeland St, Dallas, TX 75210. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Hi Crystal, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5201 W Camelback Rd Lot A174, Phoenix, AZ 85031. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Crystal. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 5201 W Camelback Rd Lot A174, Phoenix, AZ 85031. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Hi CYNDI, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1722 Berriedale Dr, Fayetteville, NC 28304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello CYNDI, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Hi D.R., this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in Ledoux Plan, Trivento, Baker, LA 70714. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello D.R., this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about Ledoux Plan, Trivento, Baker, LA 70714 — a cash purchase. Open to a discounted cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Hi D.R., this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in Ledoux Plan, Zachary Trails at Meadow View, Zachary, LA 70791. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day D.R., Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Hi Daisy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4534 S Honore St, Chicago, IL 60609. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Daisy, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 4534 S Honore St, Chicago, IL 60609. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Hi Dan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1401 Kirby St NE, Albuquerque, NM 87112. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Dan, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Hi DANA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8064 KILWINNING Lane, Jacksonville, FL 32244. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>DANA, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 8064 KILWINNING Lane, Jacksonville, FL 32244 — a cash purchase. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Hi Dana, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11831 Bee Ln, Houston, TX 77067. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Dana — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Hi DANIEL, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5050 SAN JUAN Avenue, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi DANIEL, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5050 SAN JUAN Avenue, Jacksonville, FL 32210. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Hi DANIEL, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 22 MONTE Street, Jacksonville, FL 32254. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>DANIEL, hi. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 22 MONTE Street, Jacksonville, FL 32254. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Hi Daniel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20489 Andover St, Highland Park, MI 48203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Daniel — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Hi DANIELE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1494 8TH Street W, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>DANIELE, hi, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Hi Danielle, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18281 Lancashire St, Detroit, MI 48223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Danielle, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 18281 Lancashire St, Detroit, MI 48223. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Hi DANYELLE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3053 RAY Road, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello DANYELLE, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Hi Darius, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1825 N 17th St, Baton Rouge, LA 70802. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Darius, hi — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Hi Darrin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3507 E SANDRA Terrace, Phoenix, AZ 85032. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Darrin. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3507 E SANDRA Terrace, Phoenix, AZ 85032. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Hi Darryl, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7809 Capitol St, Houston, TX 77012. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Darryl, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 7809 Capitol St, Houston, TX 77012. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Hi Darryl, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19151 Rowe St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Darryl — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Hi Darryl, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 184 Springway Dr, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Darryl, hi — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Hi Darryn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15870 W Parkway St, Detroit, MI 48223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Darryn, hi. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 15870 W Parkway St, Detroit, MI 48223. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Hi Daryl, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20520 Dresden St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Daryl, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Hi David, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 116 Larchwood Dr, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there David, I'm Charles with Paragon Government Solutions. interested in buying 116 Larchwood Dr, Columbia, SC 29203 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Hi David, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11905 Shadeland Ave, Cleveland, OH 44108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>David, hi. I'm Charles with Paragon Government Solutions, and I'm reaching out about 11905 Shadeland Ave, Cleveland, OH 44108 — a cash purchase. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Hi David, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 712 Thaxton Ave SE, Albuquerque, NM 87102. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello David — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Hi David, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6 Crescent Ln, Columbia, SC 29212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi David. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 6 Crescent Ln, Columbia, SC 29212. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Hi David, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 139 Spruce St, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there David, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Hi David, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2631 Mike St, Dallas, TX 75212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey David. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 2631 Mike St, Dallas, TX 75212. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Hi David, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19182 Hickory St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi David. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 19182 Hickory St, Detroit, MI 48205. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Hi DAVID, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 311 Glen Canyon Dr, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>DAVID, hi. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 311 Glen Canyon Dr, Fayetteville, NC 28303. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Hi Dayton, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6338 Firestone Pkwy, San Antonio, TX 78244. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Dayton, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Hi De'Chella, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3309 E 146th St, Cleveland, OH 44120. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>De'Chella, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 3309 E 146th St, Cleveland, OH 44120. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Hi Dean, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3497 W 46th St, Cleveland, OH 44102. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Dean — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Hi Deanna, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1811 Reynoldston Ln, Dallas, TX 75232. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Deanna. I'm Charles with Paragon Government Solutions, and interested in buying 1811 Reynoldston Ln, Dallas, TX 75232 for cash. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Hi Debbie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3508 S Mozart St, Chicago, IL 60632. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Debbie, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Hi Deborah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10147 S State St, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Deborah. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 10147 S State St, Chicago, IL 60628 — a cash purchase. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Hi DEIRDRA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6818 MERRILL Court, Jacksonville, FL 32211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi DEIRDRA, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6818 MERRILL Court, Jacksonville, FL 32211. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Hi Demetria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6511 Brook Ave, Baltimore, MD 21206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Demetria, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Hi Dena, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 301 Squire Rd, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Dena, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 301 Squire Rd, Columbia, SC 29223 — a cash purchase. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Hi Denise, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7613 Parker Rd, Houston, TX 77016. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Denise, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 7613 Parker Rd, Houston, TX 77016. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Hi DENISE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 502 Santa Fe Dr, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello DENISE — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Hi Deven, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7700 S Lowe Ave, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Deven. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 7700 S Lowe Ave, Chicago, IL 60620. Would the owner entertain a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Hi DEXTER, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1145 E 14TH Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello DEXTER, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Hi Dexter, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 639 E 90th Pl, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Dexter. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 639 E 90th Pl, Chicago, IL 60619. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Hi Diana, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18968 E Northlawn St E, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Diana — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Hi Diane, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2024 Elmridge Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Diane. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 2024 Elmridge Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Hi DMITRIY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5527 MAXINE Drive, Jacksonville, FL 32277. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello DMITRIY — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Hi Don, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13159 Todd Ave, Baton Rouge, LA 70815. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Don, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 13159 Todd Ave, Baton Rouge, LA 70815. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Hi Donna, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8529 S May St, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Donna, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Hi Donnie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1778 Jackson Ave, Memphis, TN 38107. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Donnie — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Hi Doreen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3506 Rosedale Rd, Baltimore, MD 21215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Doreen — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Hi Douglas, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7111 Bart Hollow, San Antonio, TX 78250. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Douglas, I'm Charles with Paragon Government Solutions. I'm reaching out about 7111 Bart Hollow, San Antonio, TX 78250 — a cash purchase. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Hi Doxie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 987 E 129th St, Cleveland, OH 44108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Doxie, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 987 E 129th St, Cleveland, OH 44108. Would the owner entertain a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Hi Dr, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7909 Sagebrook Rd, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Dr, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Hi Drew, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4137 W 157th St, Cleveland, OH 44135. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Drew — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Hi Dulcey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18011 Windward Rd, Cleveland, OH 44119. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Dulcey. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 18011 Windward Rd, Cleveland, OH 44119. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Hi Dustin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1861 Torbenson Dr, Cleveland, OH 44112. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Dustin, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Hi DWAYNE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5919 SONORA Drive W, Jacksonville, FL 32244. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there DWAYNE, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Hi Ebony, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3237 W 30th St, Cleveland, OH 44109. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Ebony, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Hi Edgardo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7949 S Manistee Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Edgardo, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 7949 S Manistee Ave, Chicago, IL 60617. Would the owner entertain a cash as-is offer, quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Hi Eduardo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5223 Heathercrest St, Houston, TX 77045. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Eduardo, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5223 Heathercrest St, Houston, TX 77045. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Hi Eduardo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6700 S Stewart Ave, Chicago, IL 60621. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Eduardo, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Hi Edward, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 217 S Shields Rd, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Edward, I'm Charles with Paragon Government Solutions. interested in buying 217 S Shields Rd, Columbia, SC 29223 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Hi Edward, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6633 Sandstone St, Houston, TX 77074. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Edward, hi. Charles here with Paragon Government Solutions, and I'm reaching out about 6633 Sandstone St, Houston, TX 77074 — a cash purchase. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Hi Edward, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13 Winding Way, Trenton, NJ 08620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Edward, hi, Charles here with Paragon Government Solutions. interested in buying 13 Winding Way, Trenton, NJ 08620 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Hi Edwin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19338 Teppert St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Edwin, Charles Pleasant, Paragon Government Solutions. interested in buying 19338 Teppert St, Detroit, MI 48234 for cash. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Hi Eileen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10121 Jasper Ave, Cleveland, OH 44111. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Eileen, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Hi ELISABETH, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2121 EGNER Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there ELISABETH — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Hi Elizabeth, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1356 W 112th St, Cleveland, OH 44102. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Elizabeth, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1356 W 112th St, Cleveland, OH 44102. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Hi Elizabeth, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5308 Foxfire Road, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Elizabeth, hi. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5308 Foxfire Road, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Hi Elizabeth, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2009 NE 13th PL, Cape Coral, FL 33909. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Elizabeth, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Hi ELLEN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5051 LEXINGTON Avenue, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day ELLEN. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5051 LEXINGTON Avenue, Jacksonville, FL 32210. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Hi Elliot, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7901 New York Ave, Cleveland, OH 44105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Elliot. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 7901 New York Ave, Cleveland, OH 44105. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Hi Emil, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8128 S Coles Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Emil, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Hi ERIC, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9324 NORFOLK Boulevard, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi ERIC, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Hi Erick, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18710 McCormick St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Erick, hi — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Hi Esmeralda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 105 Dresden St, Houston, TX 77012. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Esmeralda, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Hi Eve, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11224 S Stewart Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Eve — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Hi EXP, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2012 Bolt Dr, Anderson, SC 29621. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi EXP, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2012 Bolt Dr, Anderson, SC 29621. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Hi Fadie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6324 Annland St, Detroit, MI 48204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Fadie, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 6324 Annland St, Detroit, MI 48204. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Hi Fany, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5935 Glenhurst Dr, Houston, TX 77033. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Fany, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 5935 Glenhurst Dr, Houston, TX 77033 — a cash purchase. Would the seller consider a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Hi Felicia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6953 S Elizabeth St, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Felicia, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6953 S Elizabeth St, Chicago, IL 60636. Open to a discounted cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Hi Floyd, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6525 Palm Island St, Dallas, TX 75241. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Floyd. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 6525 Palm Island St, Dallas, TX 75241. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Hi Francisco, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 921 S 3RD Avenue, Phoenix, AZ 85003. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Francisco. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 921 S 3RD Avenue, Phoenix, AZ 85003. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Hi Francisco, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11432 S Wentworth Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Francisco. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 11432 S Wentworth Ave, Chicago, IL 60628. Is the seller open to a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Hi Francys, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18433 Norwood St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Francys, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 18433 Norwood St, Detroit, MI 48234. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Hi Frank, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10471 Nottingham Rd, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Frank. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 10471 Nottingham Rd, Detroit, MI 48224. Open to a discounted cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Hi Frank, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9137 S Essex Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Frank, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Hi Frank, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7800 S Kimbark Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Frank — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Hi Frederick, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 818 Winters St, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Frederick, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Hi Funmi, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8745 S Euclid Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Funmi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Hi Gabe, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9601 Silk Ave, Cleveland, OH 44102. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Gabe. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 9601 Silk Ave, Cleveland, OH 44102. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Hi GABRIELA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12221 SAND LAKE Court, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there GABRIELA, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Hi Gabrielle, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 203 May Oak Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Gabrielle, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 203 May Oak Rd, Columbia, SC 29229. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Hi GARY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 113 Starhill Ave, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day GARY — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Hi Gaymon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 113 Salusbury Ln, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Gaymon. Charles here with Paragon Government Solutions, and interested in buying 113 Salusbury Ln, Columbia, SC 29229 for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Hi Genaro, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8525 Oak Haven Ln, Dallas, TX 75217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Genaro. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 8525 Oak Haven Ln, Dallas, TX 75217. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Hi Gene, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 192 Dunham Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Gene — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Hi Geraldine, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16779 Greenview Ave, Detroit, MI 48219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Geraldine, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Hi Gerielynn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16770 Greenlawn St, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Gerielynn, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 16770 Greenlawn St, Detroit, MI 48221 — a cash purchase. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Hi Gerilet, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5147 BROKEN ARROW Drive N, Jacksonville, FL 32244. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Gerilet — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Hi Gershon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8005 S Campbell Ave, Chicago, IL 60652. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Gershon — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Hi Gina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2640 Ridgely St, Baltimore, MD 21230. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Gina. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2640 Ridgely St, Baltimore, MD 21230. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Hi Gino, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 78 Liberty St, Trenton, NJ 08611. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Gino, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 78 Liberty St, Trenton, NJ 08611. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Hi Gladys, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 726 Helena Ave, Dallas, TX 75217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Gladys — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Hi Glen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3194 W 95th St, Cleveland, OH 44102. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Glen — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Hi GLEN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8456 BOYSENBERRY Lane W, Jacksonville, FL 32244. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi GLEN. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 8456 BOYSENBERRY Lane W, Jacksonville, FL 32244. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Hi Gonzalo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 725 W SOUTHGATE Avenue W, Phoenix, AZ 85041. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Gonzalo, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Hi Gracie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2628 Marfa Ave, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Gracie, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Hi Gracie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4015 Shadrack Dr, Dallas, TX 75212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Gracie, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Hi Grant, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1709 Jeffrey Bryan Dr, Charlotte, NC 28213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Grant, Charles here with Paragon Government Solutions. interested in buying 1709 Jeffrey Bryan Dr, Charlotte, NC 28213 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Hi Grazyna, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3709 W 66th Pl, Chicago, IL 60629. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Grazyna, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 3709 W 66th Pl, Chicago, IL 60629. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Hi Greg, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1033 Kern St, Bakersfield, CA 93305. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Greg. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1033 Kern St, Bakersfield, CA 93305. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Hi Gregory, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10535 S Peoria St, Chicago, IL 60643. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Gregory, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 10535 S Peoria St, Chicago, IL 60643 for cash. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Hi Gregory, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19358 Teppert St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Gregory, hi. I'm Charles with Paragon Government Solutions, and I'm reaching out about 19358 Teppert St, Detroit, MI 48234 — a cash purchase. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Hi Guillermo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 14810 Walters Rd, Houston, TX 77068. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Guillermo, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 14810 Walters Rd, Houston, TX 77068 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Hi Gwendolyn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 319 Avenue J, Dallas, TX 75203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Gwendolyn, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10372,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Hi HALEY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 174 Bienville Dr, Fayetteville, NC 28311. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi HALEY, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Hi Hannah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 232 Fernview Dr, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Hannah, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 232 Fernview Dr, Columbia, SC 29229. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Hi Hannah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3834 Shelley Blvd, Dallas, TX 75211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Hannah — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Hi Harold, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2012 Lmridge Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Harold, Charles here with Paragon Government Solutions. I'm a cash investor looking at 2012 Lmridge Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Hi Harry, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9432 S Bishop St, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Harry. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 9432 S Bishop St, Chicago, IL 60620. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Hi Hassan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5698 Greenview Ave, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Hassan, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Hi Heather, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2000 Elmridge Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Heather, hi, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Hi Heather, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5235 Cumberland Cove Dr, Baton Rouge, LA 70817. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Heather. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 5235 Cumberland Cove Dr, Baton Rouge, LA 70817. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Hi Heather, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6040 W Perimeter Dr, Baton Rouge, LA 70811. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Heather, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 6040 W Perimeter Dr, Baton Rouge, LA 70811. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Hi Heather, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1802 E Campo Bello Drive #92, Phoenix, AZ 85022. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Heather — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Hi Hector, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8910 N 10TH Street, Phoenix, AZ 85020. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Hector, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Hi HENRY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 27 W 44TH Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>HENRY, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 27 W 44TH Street, Jacksonville, FL 32208 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Hi Henry, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6603 S Oakley Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Henry, hi — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Hi Hermel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13622 Vida Ln, Dallas, TX 75253. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Hermel — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Hi Hilda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1401 El Sereno Dr, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Hilda. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 1401 El Sereno Dr, Bakersfield, CA 93304. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Hi Ian, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19479 Spencer St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Ian, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Hi Ijella, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9627 Scotswood Dr, Baton Rouge, LA 70818. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Ijella, hi — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Hi Ingrid, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 842 Meridian Ave, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Ingrid. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 842 Meridian Ave, Lakeland, FL 33801. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Hi IRAN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2501 DOBY Street, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello IRAN, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2501 DOBY Street, Jacksonville, FL 32209. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Hi Iris, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 189 Mercer St, Hamilton, NJ 08690. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Iris, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 189 Mercer St, Hamilton, NJ 08690 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Hi Isabella, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2304 Pelican Dr, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Isabella, Charles here with Paragon Government Solutions. I'm a cash investor looking at 2304 Pelican Dr, Columbia, SC 29203. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Hi Jack, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 905 Ann Ave, Dallas, TX 75223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jack, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 905 Ann Ave, Dallas, TX 75223. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Hi Jacob, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 17360 Greenlawn St, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Jacob, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 17360 Greenlawn St, Detroit, MI 48221 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Hi JACOBE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2146 LOUISE Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there JACOBE, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Hi Jalisa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3431 Sayers St, Houston, TX 77026. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jalisa, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3431 Sayers St, Houston, TX 77026. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Hi Jamehia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12807 Crystal Cove Dr, Houston, TX 77044. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jamehia — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Hi JAMES, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6528 MITFORD Road, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there JAMES, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 6528 MITFORD Road, Jacksonville, FL 32210. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Hi JAMES, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2203 SHERRINGTON Street, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi JAMES, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Hi James, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9433 S Michigan Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello James — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Hi James, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8350 S Lafayette Ave, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>James, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Hi James, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9261 Camley St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey James — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Hi JAMES, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 736 Tobermory Rd, Fayetteville, NC 28306. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi JAMES, I'm Charles with Paragon Government Solutions. I'm reaching out about 736 Tobermory Rd, Fayetteville, NC 28306 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Hi Jami, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10339 Limestone Dr, Dallas, TX 75217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Jami. Charles here with Paragon Government Solutions, and interested in buying 10339 Limestone Dr, Dallas, TX 75217 for cash. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Hi Jamie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3010 Hartwick Rd, Houston, TX 77093. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Jamie, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 3010 Hartwick Rd, Houston, TX 77093. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Hi Jamie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2229 W 60th St, Indianapolis, IN 46228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jamie. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 2229 W 60th St, Indianapolis, IN 46228 — a cash purchase. Would the owner entertain a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Hi Jamila, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12607 Oakfield Ave, Cleveland, OH 44105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Jamila. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 12607 Oakfield Ave, Cleveland, OH 44105 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Hi Janina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7324 S Blackstone Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Janina — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Hi Jasmin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 240 Mason Ave, Hamilton, NJ 08610. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Jasmin — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Hi Jasmine, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6433 S Talman Ave, Chicago, IL 60629. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jasmine, hi, Charles here with Paragon Government Solutions. I'm reaching out about 6433 S Talman Ave, Chicago, IL 60629 — a cash purchase. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Hi Jason, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1009 Poplar Grove St, Baltimore, MD 21216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jason. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1009 Poplar Grove St, Baltimore, MD 21216. Open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Hi Jason, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5732 Wood Dr SW, Albuquerque, NM 87105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Jason — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Hi Jason, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2600 Brookside Dr APT 41, Bakersfield, CA 93311. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jason. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 2600 Brookside Dr APT 41, Bakersfield, CA 93311. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Hi Jason, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 106 N Briscoe Blvd, Dallas, TX 75211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jason. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 106 N Briscoe Blvd, Dallas, TX 75211. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Hi Jason, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1921 W WHITTON Avenue, Phoenix, AZ 85015. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jason. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1921 W WHITTON Avenue, Phoenix, AZ 85015. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Hi Jay, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19300 Berg Rd, Detroit, MI 48219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jay. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 19300 Berg Rd, Detroit, MI 48219. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Hi Jay, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4909 Falls St, Houston, TX 77026. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Jay, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 4909 Falls St, Houston, TX 77026. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Hi JC, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5009 W Chicago Ave, Chicago, IL 60651. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello JC. I'm Charles with Paragon Government Solutions, and interested in buying 5009 W Chicago Ave, Chicago, IL 60651 for cash. Would the seller consider a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Hi JD, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6810 Satchel Ford Rd, Columbia, SC 29206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there JD. Charles here with Paragon Government Solutions, and interested in buying 6810 Satchel Ford Rd, Columbia, SC 29206 for cash. Is the seller open to a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Hi Jean, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10032 S Calumet Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Jean, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 10032 S Calumet Ave, Chicago, IL 60628. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Hi Jeff, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3218 College St, Slidell, LA 70458. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Jeff, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3218 College St, Slidell, LA 70458 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Hi Jeff, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 116 Clay Ridge Rd, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jeff, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Hi Jeffrey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 109 Kingston Trace Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Jeffrey, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 109 Kingston Trace Rd, Columbia, SC 29229. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Hi Jeffrey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4137 Shorecrest Dr, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Jeffrey, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Hi Jeffrey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8622 Othello St, Houston, TX 77029. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jeffrey, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Hi Jeffrey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3196 W 116th St, Cleveland, OH 44111. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Jeffrey. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 3196 W 116th St, Cleveland, OH 44111. Is the seller open to a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>Hi JELISSA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4173 DAVIE Court, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there JELISSA, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Hi JENNIFER, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9720 STEAD Court, Jacksonville, FL 32221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day JENNIFER, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Hi Jennifer, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 618 E 89th St, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jennifer, hi. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 618 E 89th St, Chicago, IL 60619. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Hi Jenny, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1639 Mustang Canyon Way, Houston, TX 77049. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jenny, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 1639 Mustang Canyon Way, Houston, TX 77049 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Hi Jenya, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1075 Belmont Green Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jenya, hi — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Hi Jerelyn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 409 Sheridan Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jerelyn — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Hi Jerry, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3012 Skyview Dr, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jerry. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 3012 Skyview Dr, Lakeland, FL 33801. Is the seller open to a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Hi Jesse, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1037 Lexington St, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jesse, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1037 Lexington St, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>Hi Jesse, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 33 Heritage Village Ln, Columbia, SC 29212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Jesse — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Hi Jessica, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3929 Trotter Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jessica — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Hi Jessica, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8752 Woodcastle Dr, Dallas, TX 75217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Jessica — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Hi Jessica, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1521 Hamilton Ave, Hamilton, NJ 08629. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jessica. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1521 Hamilton Ave, Hamilton, NJ 08629. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Hi Jessica, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5250 Alter Rd, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jessica, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 5250 Alter Rd, Detroit, MI 48224. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>Hi JESSICA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 994 Wayside Rd, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello JESSICA, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 994 Wayside Rd, Fayetteville, NC 28314. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Hi Jill, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5706 S Columbia Pl, Tulsa, OK 74105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jill, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Hi Jim, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5303 S Winchester Ave, Chicago, IL 60609. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jim, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 5303 S Winchester Ave, Chicago, IL 60609. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>Hi Jimish, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8443 S Manistee Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Jimish — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>Hi Jimmy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8101 Howard Dr, Houston, TX 77017. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Jimmy — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>Hi JoAnn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16503 Wisconsin St, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day JoAnn — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Hi Joe, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in Lots 23-25 Cargill St, Houston, TX 77029. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Joe, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Hi Joel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12126 Garner Mill Ln, Houston, TX 77089. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Joel — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Hi Joel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6502 Leedale St, Houston, TX 77016. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Joel — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Hi Joey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8614 Fringewood Dr, Houston, TX 77028. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Joey, this is Charles Pleasant with Paragon Government Solutions. interested in buying 8614 Fringewood Dr, Houston, TX 77028 for cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Hi John, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15346 Dexter Ave, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello John — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>Hi John, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4386 W 48th St, Cleveland, OH 44144. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello John, I'm Charles with Paragon Government Solutions. interested in buying 4386 W 48th St, Cleveland, OH 44144 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>Hi John, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1002 Prouty Ave, Toledo, OH 43609. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there John — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>Hi John, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10431 Kinslow Dr, Dallas, TX 75217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there John, this is Charles Pleasant with Paragon Government Solutions. interested in buying 10431 Kinslow Dr, Dallas, TX 75217 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Hi John, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 169 Fox Grove Cir, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day John. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 169 Fox Grove Cir, Columbia, SC 29229 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Hi John, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7743 E Canfield St, Detroit, MI 48214. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello John, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Hi John, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in Leadmine Rd, Gaffney, SC 29340. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>John, hi, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on Leadmine Rd, Gaffney, SC 29340. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Hi JOHN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3554 BROCKWAY Road, Jacksonville, FL 32250. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey JOHN, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3554 BROCKWAY Road, Jacksonville, FL 32250. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Hi Johnny, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9016 Harris Ave, Cleveland, OH 44104. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Johnny. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 9016 Harris Ave, Cleveland, OH 44104. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>Hi JON, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3218 PERRY Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello JON — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Hi Jonathan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4329 S Wood St, Chicago, IL 60609. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Jonathan, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 4329 S Wood St, Chicago, IL 60609. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Hi Jonathan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18866 Hull Ave, Detroit, MI 48203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Jonathan, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Hi Jose, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9137 Meyers Rd, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Jose, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Hi Jose, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5921 S Sawyer Ave, Chicago, IL 60629. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Jose, hi, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Hi Jose, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9122 S La Salle St, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Jose — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Hi Joseph, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20505 Hamburg St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Joseph — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Hi JOSEPH, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5250 SANTA MONICA Boulevard S, Jacksonville, FL 32207. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello JOSEPH — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12752,7 +12752,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Hi Joseph, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2856 E 79th St, Chicago, IL 60649. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Joseph, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Hi JOSEPH, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1334 W 32ND Street, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey JOSEPH — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Hi Joshua, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2021 Morninglo Ln, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Joshua. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2021 Morninglo Ln, Columbia, SC 29223. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Hi Joshua, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3403 Alabama Ave, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Joshua — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Hi Joshua, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20017 Hawthorne St, Detroit, MI 48203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Joshua — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Hi Joy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2138 Minnesota St, Baton Rouge, LA 70802. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Joy — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Hi JOYOUS, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5227 BUNCHE Drive, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>JOYOUS, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Hi Ju'Vonne, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1523 E Nevada St, Detroit, MI 48203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Ju'Vonne, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1523 E Nevada St, Detroit, MI 48203 — a cash purchase. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Hi Juanita, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3423 Texas Dr, Dallas, TX 75211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Juanita, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Hi Judith, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12125 Angelus Ave, Cleveland, OH 44105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Judith, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 12125 Angelus Ave, Cleveland, OH 44105. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Hi Judith, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 306 SW 29th St, Cape Coral, FL 33914. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Judith — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Hi Juliana, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 155 Locust Ave W, Hamilton, NJ 08610. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Juliana. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 155 Locust Ave W, Hamilton, NJ 08610 for cash. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Hi Julie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 178 Vermillion Dr, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Julie, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 178 Vermillion Dr, Columbia, SC 29209 — a cash purchase. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13077,7 +13077,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Hi Julio, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5626 Tranquil Cv, San Antonio, TX 78244. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Julio — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>Hi Justin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1246 Junction St, Detroit, MI 48209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Justin — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Hi Justin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4701 Morris St NE APT 2604, Albuquerque, NM 87111. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Justin. I'm Charles with Paragon Government Solutions, and I'm reaching out about 4701 Morris St NE APT 2604, Albuquerque, NM 87111 — a cash purchase. Would the seller consider a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Hi Justine, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3309 Crownover St, Austin, TX 78725. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Justine, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 3309 Crownover St, Austin, TX 78725. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Hi KALICA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2846 YELLOW PINE Drive, Jacksonville, FL 32277. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day KALICA. Charles here with Paragon Government Solutions, and interested in buying 2846 YELLOW PINE Drive, Jacksonville, FL 32277 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Hi Kara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 846 W Carole St, Lakeland, FL 33803. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Kara, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Hi Karelin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4535 W 157th St, Cleveland, OH 44135. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Karelin. I'm Charles with Paragon Government Solutions, and I'm reaching out about 4535 W 157th St, Cleveland, OH 44135 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Hi Karen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 226 Curvewood Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Karen, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Hi Karen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1040 Kentucky St SE, Albuquerque, NM 87108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Karen, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1040 Kentucky St SE, Albuquerque, NM 87108 — a cash purchase. Would the seller consider a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Hi KAREN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6929 ROLLO Road, Jacksonville, FL 32205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello KAREN, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Hi Karina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4030 W MARICOPA Street, Phoenix, AZ 85009. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Karina, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 4030 W MARICOPA Street, Phoenix, AZ 85009. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Hi Karina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7641 Delavan Dr, Houston, TX 77028. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Karina. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 7641 Delavan Dr, Houston, TX 77028 for cash. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Hi Karla, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11827 Gaston Pkwy, Dallas, TX 75218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Karla, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 11827 Gaston Pkwy, Dallas, TX 75218. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Hi Karmen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10210 S Prairie Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Karmen, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 10210 S Prairie Ave, Chicago, IL 60628. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Hi Kashmir, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7305 Tremper St, Houston, TX 77020. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Kashmir, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 7305 Tremper St, Houston, TX 77020 — a cash purchase. Open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Hi Katie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8855 Stout St, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Katie, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Hi Katy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2319 Kathleen Ave, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Katy, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Hi Keith, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 112 Willow Branch Dr, West Monroe, LA 71291. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Keith, hi. Charles here with Paragon Government Solutions, and I'm reaching out about 112 Willow Branch Dr, West Monroe, LA 71291 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Hi KEITH, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4507 TRENTON Drive S, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi KEITH, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13552,7 +13552,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Hi Kelley, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1630 E ADAMS Street, Phoenix, AZ 85034. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Kelley, I'm Charles with Paragon Government Solutions. I'm reaching out about 1630 E ADAMS Street, Phoenix, AZ 85034 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Hi Kelly, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11825 Rosemary St N, Detroit, MI 48213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Kelly — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Hi Keneitra, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 109 Christian St, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Keneitra, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 109 Christian St, Columbia, SC 29203 — a cash purchase. Is the seller open to a cash as-is offer, fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Hi Kenisha, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2324 Alpine Rd, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Kenisha. I'm Charles with Paragon Government Solutions, and I'm reaching out about 2324 Alpine Rd, Columbia, SC 29223 — a cash purchase. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Hi KENNETH, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1113 Branson St, Fayetteville, NC 28305. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there KENNETH, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1113 Branson St, Fayetteville, NC 28305. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>Hi Kerry, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1065 Blanchard Pl, Shreveport, LA 71104. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Kerry. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 1065 Blanchard Pl, Shreveport, LA 71104. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Hi KEVIN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7321 Tollhouse Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey KEVIN — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Hi Kevin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6127 Pontotoc St, Baton Rouge, LA 70812. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Kevin — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>Hi Kevin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1223 Harvey St, Columbia, SC 29201. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Kevin, hi — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Hi Kevin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11632 Laing St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Kevin. Charles Pleasant, Paragon Government Solutions, and interested in buying 11632 Laing St, Detroit, MI 48224 for cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>Hi Khaula, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3718 Barbara Ave, Bakersfield, CA 93309. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Khaula, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Hi Kim, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3428 W Banff Ln, Phoenix, AZ 85053. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Kim. Charles here with Paragon Government Solutions, and I'm reaching out about 3428 W Banff Ln, Phoenix, AZ 85053 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>Hi KIM, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 752 ACOSTA Street, Jacksonville, FL 32204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>KIM, hi, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Hi Kim, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3338 Taylor St, Detroit, MI 48206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Kim. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 3338 Taylor St, Detroit, MI 48206. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Hi Kimberley, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20 Doreen Rd, Hamilton, NJ 08690. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Kimberley. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 20 Doreen Rd, Hamilton, NJ 08690 for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Hi Kimberly, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2056 Persimmon Ct, Cincinnati, OH 45231. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Kimberly, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Hi Kimberly, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 204 Philip St, Detroit, MI 48215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Kimberly, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Hi Kira, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 420 Pitchling Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Kira — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Hi Kodee, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 311 Lockner Rd, Columbia, SC 29212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Kodee, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 311 Lockner Rd, Columbia, SC 29212. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Hi KONT, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4104 LEONARD Circle E, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day KONT — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Hi Koty, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1208 31st St SW, Birmingham, AL 35221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Koty — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Hi Kristen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12018 Texana Cv, San Antonio, TX 78253. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Kristen, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Hi Kristi, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12966 Trail Hollow Dr #2960, Houston, TX 77079. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Kristi, Charles here with Paragon Government Solutions. interested in buying 12966 Trail Hollow Dr #2960, Houston, TX 77079 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Hi Kristian, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4114 Averill St, Houston, TX 77009. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Kristian — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Hi Kristofer, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 602 Lightstone Dr, San Antonio, TX 78258. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Kristofer — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Hi Kya, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5505 Hamlet Ave, Baltimore, MD 21214. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Kya, hi, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Hi KYLE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 725 W 16 Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>KYLE, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 725 W 16 Street, Jacksonville, FL 32206. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Hi Lache, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4103 Sablemist Ct, Houston, TX 77014. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Lache, hi. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 4103 Sablemist Ct, Houston, TX 77014. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Hi LaCretia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 17694 Avon Ave, Detroit, MI 48219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>LaCretia, hi — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Hi Landon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8723 S Eggleston Ave, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Landon. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 8723 S Eggleston Ave, Chicago, IL 60620. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Hi Lara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5003 Gleneagles Ct, Houston, TX 77084. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Lara. Charles here with Paragon Government Solutions, and interested in buying 5003 Gleneagles Ct, Houston, TX 77084 for cash. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Hi Lara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 113 Wescott Pl, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Lara — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Hi LASHAWN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1730 AUDUBON Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello LASHAWN. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1730 AUDUBON Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14377,7 +14377,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Hi LaToya, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16525 Prevost St, Detroit, MI 48235. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey LaToya — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Hi Laura, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2705 Warren Ave, Dallas, TX 75215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Laura, Charles here with Paragon Government Solutions. I'm reaching out about 2705 Warren Ave, Dallas, TX 75215 — a cash purchase. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Hi Laura, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 806 Homestead St, Baltimore, MD 21218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Laura. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 806 Homestead St, Baltimore, MD 21218. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Hi Lauran, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2512 E Stassney Ln, Austin, TX 78744. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Lauran, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Hi Lauren, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2009 Bancroft St, Lake Charles, LA 70607. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Lauren, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 2009 Bancroft St, Lake Charles, LA 70607. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Hi Lauren, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6526 Oak Garden Dr, Baton Rouge, LA 70817. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Lauren — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Hi Lawrence, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6526 Heyden St, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Lawrence, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 6526 Heyden St, Detroit, MI 48228. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14552,7 +14552,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>Hi LEANA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4633 SUFFOLK Avenue, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello LEANA. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 4633 SUFFOLK Avenue, Jacksonville, FL 32208. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Hi Lee, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9 Vicky Ct, Hamilton, NJ 08610. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Lee, hi, Charles here with Paragon Government Solutions. I'm reaching out about 9 Vicky Ct, Hamilton, NJ 08610 — a cash purchase. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Hi Leilani, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10712 Grantwood Ave, Cleveland, OH 44108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Leilani, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>Hi Leonel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 903 Cameron Ave, Dallas, TX 75223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Leonel — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Hi Leontra, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11981 Whitehill St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Leontra, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14677,7 +14677,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>Hi Lesa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 146 Dunham Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Lesa, I'm Charles with Paragon Government Solutions. I'm reaching out about 146 Dunham Rd, Columbia, SC 29209 — a cash purchase. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>Hi Lesa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2054 Elmridge Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Lesa, Charles here with Paragon Government Solutions. I'm reaching out about 2054 Elmridge Rd, Columbia, SC 29209 — a cash purchase. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>Hi LeTanya, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2043 Parker Ranch Rd SE, Atlanta, GA 30316. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi LeTanya. I'm Charles with Paragon Government Solutions, and I'm reaching out about 2043 Parker Ranch Rd SE, Atlanta, GA 30316 — a cash purchase. Is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>Hi LETICIA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3072 BESSENT Road, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>LETICIA, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Hi Liliana, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 530 Utah St SE Trailer 14A, Albuquerque, NM 87108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Liliana, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 530 Utah St SE Trailer 14A, Albuquerque, NM 87108. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>Hi Lily, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1027 Hollywood Ave, Dallas, TX 75208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Lily, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 1027 Hollywood Ave, Dallas, TX 75208. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>Hi Linda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15779 Wabash St, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Linda, hi, I'm Charles with Paragon Government Solutions. I'm reaching out about 15779 Wabash St, Detroit, MI 48238 — a cash purchase. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>Hi LINDA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4815 LYNBROOK Drive, Jacksonville, FL 32207. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>LINDA, hi, Charles Pleasant, Paragon Government Solutions. interested in buying 4815 LYNBROOK Drive, Jacksonville, FL 32207 for cash. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Hi Linda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10 Stacey Ave, Trenton, NJ 08618. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Linda, hi — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Hi Lindsey, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5525 E THOMAS Road #R9, Phoenix, AZ 85018. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Lindsey, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Hi Lisa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 131 Elm Rd, Pittsburgh, PA 15237. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Lisa, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 131 Elm Rd, Pittsburgh, PA 15237. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Hi Lisa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1910 Greenoaks Rd APT A, Columbia, SC 29206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Lisa, hi. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 1910 Greenoaks Rd APT A, Columbia, SC 29206. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Hi Liz, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1200 Bluff Rd #198, Columbia, SC 29201. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Liz — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Hi Liz, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1607 Elrino St, Baltimore, MD 21224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Liz — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Hi Lora, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2434 Paxton St, Columbia, SC 29204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Lora, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Hi Lori, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12346 Elmdale St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Lori — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Hi Louis, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 600 Stirrup Ave, Bakersfield, CA 93307. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Louis, hi, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 600 Stirrup Ave, Bakersfield, CA 93307. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Hi LOURDES, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 72 E 32 Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>LOURDES, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Hi Luan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3220 Plymouth Pl, New Orleans, LA 70131. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Luan, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Hi Luciano, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5930 Guadalupe St, Houston, TX 77016. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Luciano, hi. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 5930 Guadalupe St, Houston, TX 77016. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Hi LUCIE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 162 E 54TH Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day LUCIE, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 162 E 54TH Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Hi Luis, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 342 Creekwood Run, Lakeland, FL 33809. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Luis — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Hi Lydia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13515 S Baltimore Ave, Chicago, IL 60633. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Lydia — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Hi MAE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1412 Morganton Rd, Fayetteville, NC 28305. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi MAE. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 1412 Morganton Rd, Fayetteville, NC 28305. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Hi Maico, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1638 W MOHAVE Street, Phoenix, AZ 85007. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Maico, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1638 W MOHAVE Street, Phoenix, AZ 85007. Would the seller consider a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Hi Makia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8357 Navy St, Detroit, MI 48209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Makia, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Hi Malaka, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10731 Roxbury St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Malaka. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 10731 Roxbury St, Detroit, MI 48224. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Hi Malwina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8252 S Marshfield Ave, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Malwina. I'm Charles with Paragon Government Solutions, and interested in buying 8252 S Marshfield Ave, Chicago, IL 60620 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Hi Mamie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 216 W 10th St, Lakeland, FL 33805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Mamie. Charles Pleasant, Paragon Government Solutions, and interested in buying 216 W 10th St, Lakeland, FL 33805 for cash. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Hi Marc, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6003 Glenoak Ave, Baltimore, MD 21214. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Marc, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6003 Glenoak Ave, Baltimore, MD 21214. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Hi Marc, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3010 NE 6th Place Cpe, Coral, FL 33909. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Marc, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Hi Marc, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2744 Briarhurst Dr APT 51, Houston, TX 77057. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Marc — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Hi Marc, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8313 S Wabash Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Marc, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Hi Marcela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3712 W Cold Spring Ln, Baltimore, MD 21215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Marcela — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15527,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Hi Marcelo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1918 Michigan Ave, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Marcelo, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Hi Marcia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 90 Grandview Ave, Hamilton, NJ 08620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Marcia, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 90 Grandview Ave, Hamilton, NJ 08620. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Hi Marcia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2627 Carmel St, Houston, TX 77091. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Marcia, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 2627 Carmel St, Houston, TX 77091. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Hi Marcy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1115 Belmont Green Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Marcy, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 1115 Belmont Green Rd, Columbia, SC 29209. Is the seller open to a cash as-is offer, close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Hi Margarita, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2526 Exline St, Dallas, TX 75215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Margarita, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2526 Exline St, Dallas, TX 75215 for cash. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Hi Maria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1250 W 49th Pl, Chicago, IL 60609. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Maria, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Hi Maria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4541 S Laporte Ave, Chicago, IL 60638. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Maria — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Hi Maria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1015 Barelas St SW, Albuquerque, NM 87102. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Maria — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Hi Maria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 618 Dolores St, Bakersfield, CA 93305. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Maria, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 618 Dolores St, Bakersfield, CA 93305. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Hi Maria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19355 Alcoy St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Maria. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 19355 Alcoy St, Detroit, MI 48205. Would the owner entertain a cash as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Hi MARIA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5974 CHARLES D EVERS Drive, Jacksonville, FL 32219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello MARIA, Charles here with Paragon Government Solutions. I'm reaching out about 5974 CHARLES D EVERS Drive, Jacksonville, FL 32219 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Hi Mariah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9042 S Ellis Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Mariah, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Hi Maribel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16560 La Salle Ave, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Maribel, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 16560 La Salle Ave, Detroit, MI 48221. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Hi Maricela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15008 Strathmoor St, Detroit, MI 48227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Maricela — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Hi Maricela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 124 Harriet Dr, San Antonio, TX 78216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Maricela. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 124 Harriet Dr, San Antonio, TX 78216. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Hi Maricela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7667 Ellsworth St, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Maricela, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Hi Marie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11927 Horse Canyon, San Antonio, TX 78254. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Marie — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Hi Marisela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5819 S Fairfield Ave, Chicago, IL 60629. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Marisela, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Hi Mariusz, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8153 S Stewart Ave, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Mariusz. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 8153 S Stewart Ave, Chicago, IL 60620. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16002,7 +16002,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>Hi Mark, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7039 Sheffield Dr, Lakeland, FL 33810. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Mark, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Hi Mark, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1010 N 18TH Street, Phoenix, AZ 85006. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Mark — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Hi Marketta, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16241 E State Fair St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Marketta, Charles here with Paragon Government Solutions. I'm reaching out about 16241 E State Fair St, Detroit, MI 48205 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Hi Marshon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11841 S Union Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Marshon — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Hi Martha, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10356 Shelburne Dr, Dallas, TX 75227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Martha. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 10356 Shelburne Dr, Dallas, TX 75227. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Hi Martha, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4403 Allen St, Houston, TX 77007. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Martha, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>Hi Martina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6826 Larkstone St, Houston, TX 77028. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Martina, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 6826 Larkstone St, Houston, TX 77028. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Hi Mary, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1803 Cermack St, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Mary, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Hi Mary, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 511 Solar Dr, San Antonio, TX 78227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Mary. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 511 Solar Dr, San Antonio, TX 78227. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Hi Matt, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 24 Merrymount Rd, Baltimore, MD 21210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Matt, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 24 Merrymount Rd, Baltimore, MD 21210. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Hi Matthew, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1816 N 37th Avenue, Phoenix, AZ 85009. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Matthew, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1816 N 37th Avenue, Phoenix, AZ 85009. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>Hi MATTHEW, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4840 COLONIAL Avenue, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello MATTHEW, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Hi Mauricio, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3523 Edgewood St, Dallas, TX 75215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Mauricio. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3523 Edgewood St, Dallas, TX 75215. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Hi Mauricio, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5242 W Monroe St, Chicago, IL 60644. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Mauricio, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5242 W Monroe St, Chicago, IL 60644. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Hi Maya, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5936 Hillcrest St, Detroit, MI 48236. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Maya. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 5936 Hillcrest St, Detroit, MI 48236 — a cash purchase. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Hi MELISSA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2007 LAMBERT Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey MELISSA, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 2007 LAMBERT Street, Jacksonville, FL 32206. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Hi Melody, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 353 E 90th St, Chicago, IL 60619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Melody — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Hi Meredith, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8511 Little River Rd, Houston, TX 77064. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Meredith, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 8511 Little River Rd, Houston, TX 77064. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16452,7 +16452,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6463 Crane St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Michael, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 6463 Crane St, Detroit, MI 48213. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 120 Curvewood Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Michael, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 120 Curvewood Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Hi MICHAEL, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1204 Patrick Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>MICHAEL, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1204 Patrick Dr, Fayetteville, NC 28314 — a cash purchase. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7939 S Kingston Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Michael — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 228 Haybert Ct, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Michael, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2637 Marbella Ln, Dallas, TX 75228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 2637 Marbella Ln, Dallas, TX 75228. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5950 S Marshfield Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Michael, hi — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10318 Hammerly Blvd #172, Houston, TX 77043. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Michael, hi — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9960 S Van Vlissingen Rd, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Michael, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Hi Michelle, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5601 Howell St, Houston, TX 77032. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Michelle, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Hi Michelle, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16438 Vermillion Dr, Baton Rouge, LA 70819. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Michelle — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Hi Michelle, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16438 Vermillion Dr, Baton Rouge, LA 70819. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Michelle, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 16438 Vermillion Dr, Baton Rouge, LA 70819. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Hi Michelle, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13350 Tacoma St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Michelle, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 13350 Tacoma St, Detroit, MI 48205. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Hi Mike, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3065 Noble St, Houston, TX 77026. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Mike, hi, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3065 Noble St, Houston, TX 77026. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>Hi MIKE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1928 Crestview Dr, Fayetteville, NC 28304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there MIKE, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1928 Crestview Dr, Fayetteville, NC 28304 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Hi Mike, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4337 Algonquin St, Detroit, MI 48215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Mike, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 4337 Algonquin St, Detroit, MI 48215 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Hi Mike, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8243 N 34TH Drive, Phoenix, AZ 85051. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Mike, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 8243 N 34TH Drive, Phoenix, AZ 85051. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Hi MILDRED, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10460 GAILWOOD Circle E, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello MILDRED. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 10460 GAILWOOD Circle E, Jacksonville, FL 32218. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>Hi Milton, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10707 Carvel Ln, Houston, TX 77072. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Milton, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 10707 Carvel Ln, Houston, TX 77072 — a cash purchase. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Hi Milton, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1038 Canal Dr W, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Milton — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>Hi Milton, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 628 E 131st St, Cleveland, OH 44108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Milton — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>Hi MINNA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9852 OLIVIA Street, Jacksonville, FL 32219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there MINNA — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>Hi Mitchell, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 342 Ishmeal St, Houston, TX 77091. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Mitchell, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Hi MITZIE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1912 Blake St, Fayetteville, NC 28301. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi MITZIE, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1912 Blake St, Fayetteville, NC 28301. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Hi Moe, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11409 Manor St, Detroit, MI 48204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Moe, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 11409 Manor St, Detroit, MI 48204. Would the seller consider a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Hi Mohammad, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3502 Goodhope St, Houston, TX 77021. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Mohammad, hi, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3502 Goodhope St, Houston, TX 77021. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>Hi MORGAN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 525 W 66TH Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day MORGAN, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 525 W 66TH Street, Jacksonville, FL 32208. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Hi Mr., this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 131 Hoffman Ave, Trenton, NJ 08618. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Mr.. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 131 Hoffman Ave, Trenton, NJ 08618. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Hi Ms, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 635 Marilyn Dr, Baton Rouge, LA 70815. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Ms — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>Hi Mwood, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 18982 Joann St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Mwood, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 18982 Joann St, Detroit, MI 48205. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Hi Nader, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12400 Lansdowne St, Grosse Pointe, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Nader. Charles here with Paragon Government Solutions, and I'm reaching out about 12400 Lansdowne St, Grosse Pointe, MI 48224 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Hi Nadia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1333 W 71st St, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Nadia — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Hi Najah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 17160 Northlawn St, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Najah, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 17160 Northlawn St, Detroit, MI 48221 for cash. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17277,7 +17277,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Hi Nakashia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9937 Golden Gate Ave, Baton Rouge, LA 70818. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Nakashia — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Hi Nameer, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2510 Sturtevant St, Detroit, MI 48206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Nameer. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2510 Sturtevant St, Detroit, MI 48206. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Hi Nanci, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4500 Norfolk Ave, Baltimore, MD 21216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Nanci — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>Hi Nancy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4217 NW 32nd Ter, Cape Coral, FL 33993. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Nancy, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 4217 NW 32nd Ter, Cape Coral, FL 33993. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Hi Nancy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4903 Canal St, Houston, TX 77011. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Nancy — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Hi Nardu, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3250 Elm Dr, Baton Rouge, LA 70805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Nardu, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3250 Elm Dr, Baton Rouge, LA 70805 — a cash purchase. Is the seller open to a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Hi NARENDRA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7007 LUCKY Drive E, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi NARENDRA, Charles Pleasant, Paragon Government Solutions. interested in buying 7007 LUCKY Drive E, Jacksonville, FL 32208 for cash. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Hi Natalie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4009 W ORANGE Drive #36, Phoenix, AZ 85019. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Natalie — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Hi Nataly, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20260 Dean St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Nataly, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Hi Neeta, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19024 Riverview St, Detroit, MI 48219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Neeta. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 19024 Riverview St, Detroit, MI 48219. Is the seller open to a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Hi Nelly, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 315 Gober St, Houston, TX 77017. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Nelly, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 315 Gober St, Houston, TX 77017 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Hi Nichol, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 125 Cedar Glen Ln, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Nichol, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>Hi Nicholas, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3952 Bluehill St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Nicholas, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>Hi Nick, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 129 Pond Oak Ln, Columbia, SC 29212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Nick. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 129 Pond Oak Ln, Columbia, SC 29212. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Hi Nick, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2407 E Cold Spring Ln, Baltimore, MD 21214. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Nick, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Hi NICOLE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 322 E 6TH Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey NICOLE. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 322 E 6TH Street, Jacksonville, FL 32206. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17677,7 +17677,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Hi Nikhil, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 408 Longfellow Blvd, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Nikhil, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>Hi Nikole, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3450 Minnesota Ave, St. Louis, MO 63118. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Nikole. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 3450 Minnesota Ave, St. Louis, MO 63118. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17727,7 +17727,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Hi Nilsa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 703 Monterey Ave, Cape Coral, FL 33904. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Nilsa, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 703 Monterey Ave, Cape Coral, FL 33904. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>Hi Nima, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 409 Wilkes Rd, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Nima — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>Hi NM, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3809 Santa Anita Rd SW, Albuquerque, NM 87105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey NM — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>Hi Noah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16574 Westbrook St, Detroit, MI 48219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Noah — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17827,7 +17827,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Hi Norma, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1810 Atlas Dr, Dallas, TX 75216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Norma, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 1810 Atlas Dr, Dallas, TX 75216. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Hi Norma, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11326 S Union Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Norma, this is Charles Pleasant with Paragon Government Solutions. interested in buying 11326 S Union Ave, Chicago, IL 60628 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17877,7 +17877,7 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Hi Olivia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1434 N Leamington Ave, Chicago, IL 60651. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Olivia, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1434 N Leamington Ave, Chicago, IL 60651. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Hi Orlando, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13420 Chico Rd NE, Albuquerque, NM 87123. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Orlando, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Hi Oscar, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10939 S Avenue F, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Oscar — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17952,7 +17952,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Hi Otis, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7221 S Bennett Ave, Chicago, IL 60649. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Otis. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 7221 S Bennett Ave, Chicago, IL 60649. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Hi Pablo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 213 Hogan St, Houston, TX 77009. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Pablo, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 213 Hogan St, Houston, TX 77009. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Hi PAIGE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3821 OLYMPIC Lane, Jacksonville, FL 32223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey PAIGE, this is Charles Pleasant with Paragon Government Solutions. interested in buying 3821 OLYMPIC Lane, Jacksonville, FL 32223 for cash. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Hi Pamela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 520 W CLARENDON Avenue #C3, Phoenix, AZ 85013. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Pamela, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 520 W CLARENDON Avenue #C3, Phoenix, AZ 85013. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18052,7 +18052,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Hi Pamela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11401 S Morgan St, Chicago, IL 60643. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Pamela, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 11401 S Morgan St, Chicago, IL 60643. Open to a discounted cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>Hi Pamela, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3714 Hydrangea St, Columbia, SC 29205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Pamela, I'm Charles with Paragon Government Solutions. interested in buying 3714 Hydrangea St, Columbia, SC 29205 for cash. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Hi Patricia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 109 Oakley Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Patricia, hi — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18127,7 +18127,7 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>Hi PATRICIA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1934 N Pearl St, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>PATRICIA, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 1934 N Pearl St, Fayetteville, NC 28303. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Hi Patrick, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 609 Chestnut Ave, Trenton, NJ 08611. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Patrick, I'm Charles with Paragon Government Solutions. interested in buying 609 Chestnut Ave, Trenton, NJ 08611 for cash. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Hi Patti, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 218 Florien St, Pittsburgh, PA 15204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Patti, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>Hi Paul, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4629 Larkspur St, Houston, TX 77051. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Paul, I'm Charles with Paragon Government Solutions. I'm reaching out about 4629 Larkspur St, Houston, TX 77051 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>Hi PEPPER, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2185 MOREHOUSE Road, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>PEPPER, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18252,7 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>Hi PETER, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 919 OBSERVATORY Parkway, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi PETER. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 919 OBSERVATORY Parkway, Jacksonville, FL 32218 — a cash purchase. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Hi Phil, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 245 Piney Grove Rd, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Phil, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18302,7 +18302,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Hi Phyllis, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 847 Glenmore Ave, Baton Rouge, LA 70806. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Phyllis, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Hi Ponce, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12 Sea Hawk Ct, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Ponce, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 12 Sea Hawk Ct, Columbia, SC 29203 for cash. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>Hi QUINNEICE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1921 Ashridge Dr, Fayetteville, NC 28304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>QUINNEICE, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Hi Rachel, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 330 Klamath Dr, Pittsburgh, PA 15205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Rachel, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Hi Rae, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7720 Smart St, Detroit, MI 48210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Rae, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 7720 Smart St, Detroit, MI 48210 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Hi Randal, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1644 Pincushion Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Randal — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Hi Ray, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6627 Eastwood St, Houston, TX 77021. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Ray, hi, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Hi Re/Max, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1720 Morninghill Dr, Columbia, SC 29210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Re/Max — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Hi Rebecca, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6408 Macroom Meadows Ln, Houston, TX 77048. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Rebecca, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 6408 Macroom Meadows Ln, Houston, TX 77048. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>Hi Regina, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6036 Central St, Detroit, MI 48210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Regina. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 6036 Central St, Detroit, MI 48210. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>Hi Reid, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6224 Highland Hills Dr, Dallas, TX 75241. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Reid — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Hi Rene, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7331 S Peoria St, Chicago, IL 60621. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Rene, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 7331 S Peoria St, Chicago, IL 60621. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Hi Reva, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8451 Greenview Ave, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Reva, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 8451 Greenview Ave, Detroit, MI 48228. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18627,7 +18627,7 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>Hi Rhonda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 37985 Falcon Wood Dr, Denham Springs, LA 70706. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Rhonda — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Hi Rhonda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2802 W Mosher St, Baltimore, MD 21216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Rhonda, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 2802 W Mosher St, Baltimore, MD 21216. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>Hi Ricardo, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10243 Mills Run Dr, Houston, TX 77070. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Ricardo, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>Hi Richard, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8327 Lou Gehrig St, San Antonio, TX 78240. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Richard, hi. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 8327 Lou Gehrig St, San Antonio, TX 78240. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>Hi Robbie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 33870 Perkins Crossing Rd, Walker, LA 70785. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Robbie, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>Hi Robert, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8410 N 32ND Avenue, Phoenix, AZ 85051. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Robert. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 8410 N 32ND Avenue, Phoenix, AZ 85051. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>Hi ROBERT, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 784 Yardville Hamilton Sq, Trenton, NJ 08691. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello ROBERT, this is Charles Pleasant with Paragon Government Solutions. interested in buying 784 Yardville Hamilton Sq, Trenton, NJ 08691 for cash. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>Hi Robert, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 321 Crawford Rd, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Robert. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 321 Crawford Rd, Columbia, SC 29203. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>Hi Robert, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6235 Leaf Arbor Dr, Houston, TX 77092. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Robert, Charles here with Paragon Government Solutions. I'm a cash investor looking at 6235 Leaf Arbor Dr, Houston, TX 77092. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>Hi Roberto, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11881 Saint Patrick St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Roberto. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 11881 Saint Patrick St, Detroit, MI 48205 — a cash purchase. Would the owner entertain a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>Hi Roberto, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3226 Decatur Ave, Lakeland, FL 33805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Roberto. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3226 Decatur Ave, Lakeland, FL 33805. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>Hi Robin, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 17003 Tireman St, Detroit, MI 48228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Robin. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 17003 Tireman St, Detroit, MI 48228. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>Hi Robyn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15212 Crystal Dr, Pride, LA 70770. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Robyn — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>Hi Rodney, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 14035 Kentfield St, Detroit, MI 48223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Rodney — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>Hi Rohn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1614 Kayouche St, Lake Charles, LA 70601. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Rohn, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1614 Kayouche St, Lake Charles, LA 70601. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>Hi Ross, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2507 Parktrail Rd, Baltimore, MD 21234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Ross, this is Charles Pleasant with Paragon Government Solutions. interested in buying 2507 Parktrail Rd, Baltimore, MD 21234 for cash. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19027,7 +19027,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>Hi Rosy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 205 Thelma Ln, Lake Charles, LA 70601. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Rosy — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>Hi Roxanne, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1316 E Applegate Dr, Austin, TX 78753. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Roxanne, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>Hi Rubi, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4600 Ireland St, Houston, TX 77016. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Rubi — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19102,7 +19102,7 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>Hi Ryan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1613 S 5th St, Phoenix, AZ 85004. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Ryan, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>Hi RYAN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3318 NOLAN Street, Jacksonville, FL 32254. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello RYAN. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 3318 NOLAN Street, Jacksonville, FL 32254. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>Hi Ryan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4630 Thrush Dr, Indianapolis, IN 46222. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Ryan — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>Hi Ryan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2258 Hawthorne Ave, Pittsburgh, PA 15218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Ryan. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 2258 Hawthorne Ave, Pittsburgh, PA 15218. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>Hi S., this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12828 Strathmoor St, Detroit, MI 48227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day S. — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>Hi Samantha, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6159 Lyndhurst Dr, Houston, TX 77033. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Samantha, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19252,7 +19252,7 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>Hi Sara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6537 S 15th Dr, Phoenix, AZ 85041. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Sara, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>Hi Sarah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5953 S Throop St, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Sarah. I'm Charles with Paragon Government Solutions, and interested in buying 5953 S Throop St, Chicago, IL 60636 for cash. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19302,7 +19302,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>Hi Schlanda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1319 Reynes St, New Orleans, LA 70117. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Schlanda, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>Hi Schylbea, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13123 Indiana St, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Schylbea — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19352,7 +19352,7 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>Hi Scott, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7607 Dobel St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Scott. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 7607 Dobel St, Detroit, MI 48234. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>Hi Scott, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6104 Franklin Villas Way, Indianapolis, IN 46237. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Scott, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>Hi SCOTT, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6711 CAVALIER Road, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello SCOTT, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>Hi Scott, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1021 E TAYLOR Street, Phoenix, AZ 85006. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Scott, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>Hi Sean, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8605 Fireside Dr, Austin, TX 78757. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Sean, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>Hi Sean, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8506 McDade St, Houston, TX 77080. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Sean. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 8506 McDade St, Houston, TX 77080. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>Hi Sebastian, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5730 S Hoyne Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Sebastian, hi. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5730 S Hoyne Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>Hi Sergio, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16203 Barbarossa Dr, Houston, TX 77083. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Sergio. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 16203 Barbarossa Dr, Houston, TX 77083. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>Hi Sergio, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10841 S Vernon Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Sergio, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>Hi SETH, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2837 LIPPIA Road, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello SETH, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>Hi Shakena, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 130 Brandon Hall Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Shakena. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 130 Brandon Hall Rd, Columbia, SC 29229. Is the seller open to a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>Hi Shane, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 889 E 128th St, Cleveland, OH 44108. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Shane. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 889 E 128th St, Cleveland, OH 44108. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>Hi Shannon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8710 Files St, Dallas, TX 75217. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Shannon, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 8710 Files St, Dallas, TX 75217. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>Hi Shannon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 134 Palmetto Park Cir, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Shannon — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>Hi Sharon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 516 Lakeside Ave, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Sharon — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>Hi Sharon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 515 W Main St, Gonzales, LA 70737. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Sharon, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 515 W Main St, Gonzales, LA 70737. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>Hi Shauntell, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 337 W 110th Pl, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Shauntell, hi — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>Hi SHAWANA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8342 BARRACUDA Road, Jacksonville, FL 32244. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day SHAWANA — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>Hi Shawn, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5404 Dixie Ln, Alexandria, LA 71301. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Shawn, Charles here with Paragon Government Solutions. interested in buying 5404 Dixie Ln, Alexandria, LA 71301 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>Hi SHAWN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3862 ORLANDO Circle W, Jacksonville, FL 32207. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey SHAWN. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3862 ORLANDO Circle W, Jacksonville, FL 32207. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>Hi Shay, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 180 Crestmere Pl, Memphis, TN 38112. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Shay — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>Hi Shelby, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4235 Elmwood St, Houston, TX 77051. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Shelby, hi, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19902,7 +19902,7 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>Hi Shelly, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4500 Blossom Valley Ln, Bakersfield, CA 93313. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Shelly — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>Hi Shemika, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2764 Dalton St, Baton Rouge, LA 70805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Shemika — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>Hi Shemika, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2764 Dalton St, Baton Rouge, LA 70805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Shemika — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>Hi Sherrease, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 14216 Kentucky St, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Sherrease, Charles here with Paragon Government Solutions. I'm reaching out about 14216 Kentucky St, Detroit, MI 48238 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20002,7 +20002,7 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>Hi Sherri, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2108 Blake Ave, Dallas, TX 75228. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Sherri, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20027,7 +20027,7 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>Hi Sherri, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8091 Kenney St, Detroit, MI 48234. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Sherri, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 8091 Kenney St, Detroit, MI 48234. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20052,7 +20052,7 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>Hi SHINESHA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 235 Whitney Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>SHINESHA, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>Hi Shirley, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3815 Webb Ct, Columbia, SC 29204. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Shirley, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>Hi Shoaib, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5093 Garland St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Shoaib, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5093 Garland St, Detroit, MI 48213. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>Hi Shoaib, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5330 Longmeadow St, Houston, TX 77033. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Shoaib — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>Hi Shon, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2091 Yulee St, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Shon, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>Hi Shonda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 218 Sanhican Dr, Trenton, NJ 08618. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Shonda. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 218 Sanhican Dr, Trenton, NJ 08618. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>Hi Sidra, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7106 Tierwester St, Houston, TX 77021. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Sidra — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>Hi Sonia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 514 L St, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Sonia, this is Charles Pleasant with Paragon Government Solutions. interested in buying 514 L St, Bakersfield, CA 93304 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>Hi Sonia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11315 Raincove Dr, Houston, TX 77016. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Sonia — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>Hi STACEY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6811 LANGFORD Street, Jacksonville, FL 32219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi STACEY, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>Hi Stacie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4400 Norfolk Ave, Baltimore, MD 21216. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Stacie, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 4400 Norfolk Ave, Baltimore, MD 21216. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20327,7 +20327,7 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>Hi Stacy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11833 Beachberry Dr, Houston, TX 77034. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Stacy — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6541 W OSBORN Road, Phoenix, AZ 85033. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5135 S May St, Chicago, IL 60609. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Stephanie, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20402,7 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1404 SE 34th Ter, Cape Coral, FL 33904. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Stephanie, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>Hi STEPHANIE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2205 COMMONWEALTH Avenue, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>STEPHANIE, hi — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20452,7 +20452,7 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>Hi STEPHANIE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 115 Brookwood Ave, Fayetteville, NC 28301. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey STEPHANIE — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6106 Sandy Creek Ln, Zachary, LA 70791. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Stephanie, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 6106 Sandy Creek Ln, Zachary, LA 70791. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16127 Long Rd, Houston, TX 77044. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Stephanie, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20527,7 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>Hi STEPHEN, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4222 Woodlea Ave, Baltimore, MD 21206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey STEPHEN — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20552,7 +20552,7 @@
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>Hi Steve, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6831 S Emerald Ave, Chicago, IL 60621. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Steve — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>Hi Steve, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2666 Olympia Ave, North Charleston, SC 29405. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Steve, hi. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 2666 Olympia Ave, North Charleston, SC 29405 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>Hi Steven, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2514 W Ramsey Ave, Milwaukee, WI 53221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Steven, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20627,7 +20627,7 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>Hi Steven, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 408 W Montana Ave, Dallas, TX 75224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Steven, Charles here with Paragon Government Solutions. I'm a cash investor looking at 408 W Montana Ave, Dallas, TX 75224. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20652,7 +20652,7 @@
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>Hi Steven, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12008 Vista Nogal St, San Antonio, TX 78213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Steven, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 12008 Vista Nogal St, San Antonio, TX 78213 — a cash purchase. Would the owner entertain a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20677,7 +20677,7 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>Hi Steven, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3061 Horse Ranch Rd, San Antonio, TX 78264. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Steven, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3061 Horse Ranch Rd, San Antonio, TX 78264. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>Hi Summer, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1201 Willow Dr, Lake Charles, LA 70611. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Summer — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>Hi Susan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3419 SE 5th Ave, Cape Coral, FL 33904. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Susan, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 3419 SE 5th Ave, Cape Coral, FL 33904. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>Hi Susan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12244 Woodmont Ave, Detroit, MI 48227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Susan — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>Hi Suzy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 13050 N 19TH Street #50, Phoenix, AZ 85022. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Suzy. I'm Charles with Paragon Government Solutions, and I'm reaching out about 13050 N 19TH Street #50, Phoenix, AZ 85022 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>Hi Sylvia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4401 Hughes Ln Space 200, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Sylvia, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20832,7 +20832,7 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>Hi T'Keyah, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in your listing. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there T'Keyah, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>Hi Tai, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7219 Avocet Ln, Houston, TX 77040. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Tai, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20882,7 +20882,7 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>Hi Tal, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2166 W 93rd St, Cleveland, OH 44102. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Tal, Charles Pleasant, Paragon Government Solutions. interested in buying 2166 W 93rd St, Cleveland, OH 44102 for cash. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>Hi Tamara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5151 S Denley Dr, Dallas, TX 75241. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Tamara, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20932,7 +20932,7 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>Hi Tamara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1991 Lawrence St, Detroit, MI 48206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Tamara, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20957,7 +20957,7 @@
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>Hi Tamara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3846 W 84th Pl, Chicago, IL 60652. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Tamara, hi — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>Hi Tamesha, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12323 Misty Laurel Dr, Houston, TX 77014. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Tamesha. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 12323 Misty Laurel Dr, Houston, TX 77014. Would the seller consider a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Hi Tami, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6243 S 31st West Ave, Tulsa, OK 74132. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Tami. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 6243 S 31st West Ave, Tulsa, OK 74132 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21032,7 +21032,7 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Hi Tamie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 24 Evans Ave, Trenton, NJ 08638. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Tamie — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21057,7 +21057,7 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>Hi Tamika, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10118 S Luella Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Tamika, hi. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 10118 S Luella Ave, Chicago, IL 60617. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21082,7 +21082,7 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Hi Tammi, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 323 Belle Winds Ct, Shreveport, LA 71106. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Tammi, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21107,7 +21107,7 @@
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Hi Tammy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12011 Doubleday Dr, Houston, TX 77089. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Tammy, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>Hi TANA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2425 HOLMES Street, Jacksonville, FL 32207. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there TANA. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2425 HOLMES Street, Jacksonville, FL 32207. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>Hi Tanisha, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19953 Hull St, Detroit, MI 48203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Tanisha, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 19953 Hull St, Detroit, MI 48203. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>Hi Tara, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1430 Dahlia Rd, Columbia, SC 29205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Tara, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>Hi TASHELE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9656 FLECHETTE Avenue, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>TASHELE, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 9656 FLECHETTE Avenue, Jacksonville, FL 32208 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>Hi Tashia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2433 W Tonto St, Phoenix, AZ 85009. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Tashia — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>Hi Tawanda, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4410 Greenwood Ln, Baker, LA 70714. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Tawanda, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 4410 Greenwood Ln, Baker, LA 70714. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21282,7 +21282,7 @@
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>Hi Taz, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10615 Kirkdale Dr, Houston, TX 77089. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Taz, Charles here with Paragon Government Solutions. I'm reaching out about 10615 Kirkdale Dr, Houston, TX 77089 — a cash purchase. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>Hi Teal, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2831 Lawrence St, Denver, CO 80205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Teal, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>Hi Tene', this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6845 S Chappel Ave, Chicago, IL 60649. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Tene', Charles here with Paragon Government Solutions. I'm a cash investor looking at 6845 S Chappel Ave, Chicago, IL 60649. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>Hi Tera, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2222 Detroit Ave APT 504, Cleveland, OH 44113. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Tera, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2222 Detroit Ave APT 504, Cleveland, OH 44113. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>Hi Terence, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 389 Northwood St, Columbia, SC 29201. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Terence — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21407,7 +21407,7 @@
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>Hi Teresa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 189 Regina Ave, Hamilton, NJ 08619. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Teresa — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>Hi Teresa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2602 Falls Dr, Dallas, TX 75211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Teresa. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2602 Falls Dr, Dallas, TX 75211. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>Hi Terry, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 609 Lufkin Circle, Fayetteville, NC 28311. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Terry. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 609 Lufkin Circle, Fayetteville, NC 28311. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>Hi Terry, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5214 Quarter Ln, Baton Rouge, LA 70809. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Terry — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>Hi Thalia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12699 Greenlawn St, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Thalia, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 12699 Greenlawn St, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>Hi Thao, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1263 James St, Baltimore, MD 21223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Thao, hi — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21557,7 +21557,7 @@
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>Hi Thao, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9303 Kingsflower Cir, Houston, TX 77075. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Thao. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 9303 Kingsflower Cir, Houston, TX 77075. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>Hi Thomas, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8656 &amp; 8560 Farmbrook St, Detroit, MI 48224. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Thomas, I'm Charles with Paragon Government Solutions. I'm reaching out about 8656 &amp; 8560 Farmbrook St, Detroit, MI 48224 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>Hi THOMAS, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1232 RENSSELAER Avenue, Jacksonville, FL 32205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there THOMAS, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21632,7 @@
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>Hi TIER, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 621 Ashboro St, Fayetteville, NC 28311. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey TIER, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 621 Ashboro St, Fayetteville, NC 28311. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>Hi Tiffany, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10320 S Indiana Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Tiffany. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 10320 S Indiana Ave, Chicago, IL 60628. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>Hi Tiffany, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11744 Wade St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Tiffany, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 11744 Wade St, Detroit, MI 48213. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21707,7 +21707,7 @@
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>Hi TIM, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7940 EATON Avenue, Jacksonville, FL 32211. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi TIM. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 7940 EATON Avenue, Jacksonville, FL 32211. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21732,7 +21732,7 @@
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>Hi Timothy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 230 Sterling Rd, Bakersfield, CA 93307. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Timothy, I'm Charles with Paragon Government Solutions. I'm reaching out about 230 Sterling Rd, Bakersfield, CA 93307 — a cash purchase. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21757,7 +21757,7 @@
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>Hi Timothy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20260 Patton St, Detroit, MI 48219. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Timothy, hi, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>Hi TJ, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1809 Manteo St, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>TJ, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21807,7 +21807,7 @@
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>Hi TLeice, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2684 Iroquois St, Baton Rouge, LA 70805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello TLeice — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>Hi TLeice, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2684 Iroquois St, Baton Rouge, LA 70805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>TLeice, hi, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>Hi Tom, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 83 Bryn Mawr Ave, Trenton, NJ 08618. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Tom, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 83 Bryn Mawr Ave, Trenton, NJ 08618. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>Hi TONY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3252 THOMAS Street, Jacksonville, FL 32254. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>TONY, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 3252 THOMAS Street, Jacksonville, FL 32254. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>Hi TONYA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5466 Maplewood Ct, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey TONYA, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21932,7 +21932,7 @@
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>Hi Tonya, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 12746 Woodland Dr, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Tonya. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 12746 Woodland Dr, Jacksonville, FL 32218 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21957,7 +21957,7 @@
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>Hi TORANIQUE, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1354 Worstead Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi TORANIQUE. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1354 Worstead Dr, Fayetteville, NC 28314 — a cash purchase. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21982,7 +21982,7 @@
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>Hi Tosh, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1735 N Sherwood Forest Dr, Baton Rouge, LA 70814. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Tosh, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>Hi TRACEY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1181 Torrey Dr, Fayetteville, NC 28301. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey TRACEY — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>Hi Transit, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 699 Gladiolus Dr, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Transit, hi — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22057,7 +22057,7 @@
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>Hi Tricia, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 129 Kings Parish Ct, Columbia, SC 29209. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Tricia, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22082,7 +22082,7 @@
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>Hi Trinh, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 255 Sorrel Tree Dr, Columbia, SC 29223. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Trinh. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 255 Sorrel Tree Dr, Columbia, SC 29223. Open to a discounted cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>Hi TRINITY, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6559 Amanda Cir, Fayetteville, NC 28304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi TRINITY. Charles here with Paragon Government Solutions, and I'm reaching out about 6559 Amanda Cir, Fayetteville, NC 28304 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22132,7 +22132,7 @@
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>Hi Tucker, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4538 Larkspur St, Houston, TX 77051. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Tucker, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 4538 Larkspur St, Houston, TX 77051. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>Hi Tyjuan, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 29 Battery Walk Ct, Columbia, SC 29212. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Tyjuan, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 29 Battery Walk Ct, Columbia, SC 29212. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22182,7 +22182,7 @@
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>Hi Tyler, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 338 Bowling Ave, Columbia, SC 29203. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Tyler, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22207,7 +22207,7 @@
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>Hi Tyreeta, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3628 W 83rd St, Chicago, IL 60652. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Tyreeta, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>Hi Tyrone, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7137 S Winchester Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Tyrone, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 7137 S Winchester Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22257,7 +22257,7 @@
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>Hi Valerie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3698 Menlo Rd, Shaker Heights, OH 44120. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Valerie, hi. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 3698 Menlo Rd, Shaker Heights, OH 44120. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22282,7 +22282,7 @@
       </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>Hi Vanessa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15560 Tiger Bend Rd, Baton Rouge, LA 70817. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Vanessa, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22307,7 +22307,7 @@
       </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>Hi Vanessa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2248 Cooper St, Dallas, TX 75215. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Vanessa, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 2248 Cooper St, Dallas, TX 75215. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>Hi Vanessa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8043 Wier Dr, Houston, TX 77017. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Vanessa. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 8043 Wier Dr, Houston, TX 77017. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>Hi Vanessa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 133 Cornwall Ave, Trenton, NJ 08618. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Vanessa, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 133 Cornwall Ave, Trenton, NJ 08618. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22382,7 @@
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>Hi Vanessa, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 11265 S May St, Chicago, IL 60643. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Vanessa, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 11265 S May St, Chicago, IL 60643 — a cash purchase. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>Hi VANETTA, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 4022 TYNDALE Drive, Jacksonville, FL 32210. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi VANETTA — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>Hi Vanity, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8926 S Lowe Ave, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Vanity, hi — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>Hi Veronica, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 213 T St, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Veronica — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>Hi Vickie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in your listing. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Vickie. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in your listing. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>Hi Victoria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2127 Coelum Ct, Dallas TX 75253. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Victoria, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22532,7 +22532,7 @@
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>Hi Victoria, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 7538 Bywood St, Houston, TX 77028. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Victoria, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 7538 Bywood St, Houston, TX 77028. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>Hi Vince, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 517 Windjammer Ln, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Vince — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>Hi Vinh, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2503 Highland Ave, Shreveport, LA 71104. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Vinh, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22607,7 +22607,7 @@
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>Hi Viveka, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8028 S Ada St, Chicago, IL 60620. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi Viveka. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 8028 S Ada St, Chicago, IL 60620 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>Hi Wally, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 5604 Creekmore Dr, Oklahoma City, OK 73179. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Wally, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 5604 Creekmore Dr, Oklahoma City, OK 73179. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22657,7 +22657,7 @@
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>Hi Wayne, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2011 Lake Carolina Dr, Columbia, SC 29229. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day Wayne, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>Hi WELCOME, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 603 Faison Ave, Fayetteville, NC 28304. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi WELCOME, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 603 Faison Ave, Fayetteville, NC 28304. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>Hi Wendy, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 16878 Lilac St, Detroit, MI 48221. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Wendy, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 16878 Lilac St, Detroit, MI 48221. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22732,7 +22732,7 @@
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>Hi Wes, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 1013 N Ruth Ave, Lakeland, FL 33805. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Wes. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 1013 N Ruth Ave, Lakeland, FL 33805. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>Hi William, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3713 Mary Ave, Baltimore, MD 21206. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there William — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22782,7 +22782,7 @@
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>Hi William, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 6211 Fullerton Ave, Cleveland, OH 44105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>William, hi — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22807,7 +22807,7 @@
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>Hi WILLIAM, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 10592 HAVERFORD Road, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi WILLIAM, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22832,7 +22832,7 @@
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>Hi William, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 14711 Lappin St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey William, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 14711 Lappin St, Detroit, MI 48205 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>Hi William, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2640 Cypress Ave, Dallas, TX 75227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Good day William. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 2640 Cypress Ave, Dallas, TX 75227. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>Hi Willie, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 8367 Howton St #A/B, Houston, TX 77028. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Willie, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>Hi Xiaochen, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 20315 Goulburn St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hello Xiaochen. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 20315 Goulburn St, Detroit, MI 48205. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22932,7 +22932,7 @@
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>Hi Yu, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 19408 Goulburn St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Yu, hi, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22957,7 +22957,7 @@
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>Hi Yurika, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 9551 Gonzales Dr, Dallas, TX 75227. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hi there Yurika, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>Hi Yvette, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 3078 Benny Rd SW, Albuquerque, NM 87105. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Yvette, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>Hi Zachary, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 2937 Seyburn St, Detroit, MI 48214. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Zachary, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23032,7 @@
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>Hi Zena, this is Charles Pleasant with Paragon Government Solutions - I'm a cash buyer interested in 15801 E State Fair St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, quick close, short inspection? I can send written terms today - what's the best email to send it to? Thanks!</t>
+          <t>Hey Zena, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>

--- a/GV_Campaign_NoEmail_20260620.xlsx
+++ b/GV_Campaign_NoEmail_20260620.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GV Campaign (randomized)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GV Campaign" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="95" customWidth="1" min="6" max="6"/>
   </cols>
@@ -472,7 +472,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10319 Violetlawn St, Detroit, MI 48204; 11701 Winthrop St, Detroit, MI 48227; 14176 Houston Whittier St, Detroit, MI 48205; 14337 Dacosta St, Detroit, MI 48223; 15373 Lamphere St, Detroit, MI 48223; …</t>
+          <t>10319 Violetlawn St, Detroit, MI 48204</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Good day Keelie. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 10319 Violetlawn St, Detroit, MI 48204; 11701 Winthrop St, Detroit, MI 48227; 14176 Houston Whittier St, Detroit, MI 48205; 14337 Dacosta St, Detroit, MI 48223; 15373 Lamphere St, Detroit, MI 48223; …. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
+          <t>Hi Keelie — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -502,12 +502,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>125 Deer Hound Trl, Columbia, SC 29223; 145 Angel Garden Way, Columbia, SC 29223; 1731 Cermack St, Columbia, SC 29223; 203 Autumn Run Cir, Columbia, SC 29229; 205 Alderston Way, Columbia, SC 29229; …</t>
+          <t>125 Deer Hound Trl, Columbia, SC 29223</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hello Greg, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hi there Greg, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10504 Olympic St NW, Albuquerque, NM 87114; 2 Package 6509/6513 Arcilla Pl NW, Albuquerque, NM 87120; 2 Prime Lots Volcano Clfs, Albuquerque, NM 87120; 3920 Bryan Ave NW, Albuquerque, NM 87114; 4000 Bryan Ave NW, Albuquerque, NM 87114; …</t>
+          <t>10504 Olympic St NW, Albuquerque, NM 87114</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hello Amar, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there Amar — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>108 Malisa Dr, Columbia, SC 29229; 112 Stanford St, Columbia, SC 29203; 1124 Robin Nest Rd, Columbia, SC 29223; 1700 N Woodstream Rd, Columbia, SC 29212; 2309 Cunningham Rd, Columbia, SC 29210; …</t>
+          <t>108 Malisa Dr, Columbia, SC 29229</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hey Tyjuan — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
+          <t>Good day Tyjuan — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1146 Castle Pinckney Rd, Columbia, SC 29223; 132 Fairlawn Ct, Columbia, SC 29203; 190 Morningside Dr, Columbia, SC 29210; 218 Gate Post Ln, Columbia, SC 29223; 2584 Cherry St, Columbia, SC 29205; …</t>
+          <t>1146 Castle Pinckney Rd, Columbia, SC 29223</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hey Julie, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1146 Castle Pinckney Rd, Columbia, SC 29223; 132 Fairlawn Ct, Columbia, SC 29203; 190 Morningside Dr, Columbia, SC 29210; 218 Gate Post Ln, Columbia, SC 29223; 2584 Cherry St, Columbia, SC 29205; …. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Hi Julie, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1146 Castle Pinckney Rd, Columbia, SC 29223. Could the seller look at a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13 Gatewood Way, Columbia, SC 29229; 137 Westbridge Rd, Columbia, SC 29223; 29 Wild Iris Ct, Columbia, SC 29209; 4040 Conners St, Columbia, SC 29204; 5802 McMillan Cir, Columbia, SC 29212; …</t>
+          <t>13 Gatewood Way, Columbia, SC 29229</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hi Jasmine. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 13 Gatewood Way, Columbia, SC 29229; 137 Westbridge Rd, Columbia, SC 29223; 29 Wild Iris Ct, Columbia, SC 29209; 4040 Conners St, Columbia, SC 29204; 5802 McMillan Cir, Columbia, SC 29212; … — a cash purchase. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
+          <t>Hello Jasmine — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11718 Coachfield Ln, Houston, TX 77035; 3403 Tidewater Dr, Houston, TX 77045; 5635 Ashburn St, Houston, TX 77033</t>
+          <t>11718 Coachfield Ln, Houston, TX 77035</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>John, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello John. Charles Pleasant, Paragon Government Solutions, and interested in buying 11718 Coachfield Ln, Houston, TX 77035 for cash. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1531 Alma Rd, Columbia, SC 29209; 1824 Fairhaven Dr, Columbia, SC 29210; 212 Lake Carolina Blvd, Columbia, SC 29229; 219 Finsbury Rd, Columbia, SC 29212; 2713 Trull St, Columbia, SC 29204; …</t>
+          <t>1531 Alma Rd, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hi Lauren. I'm Charles with Paragon Government Solutions, and interested in buying 1531 Alma Rd, Columbia, SC 29209; 1824 Fairhaven Dr, Columbia, SC 29210; 212 Lake Carolina Blvd, Columbia, SC 29229; 219 Finsbury Rd, Columbia, SC 29212; 2713 Trull St, Columbia, SC 29204; … for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Lauren — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>116 Patio Pl, Columbia, SC 29212; 223 Northwood St, Columbia, SC 29201; 2815 Wesley Dr, Columbia, SC 29204; 38 Cardington Ct, Columbia, SC 29209; 5225 Two Notch Rd, Columbia, SC 29204; …</t>
+          <t>116 Patio Pl, Columbia, SC 29212</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tricia, hi — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day Tricia, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>117 Lambeth Dr, Columbia, SC 29209; 1331 Boston St, Columbia, SC 29203; 1522 Jerome Dr, Columbia, SC 29203; 3844 Wilmot Ave, Columbia, SC 29205; 40 Brooksby Ct, Columbia, SC 29209; …</t>
+          <t>117 Lambeth Dr, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hello Wendy, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hello Wendy — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1143 Owens Rd, Columbia, SC 29203; 1515 Hatcher Dr, Columbia, SC 29203; 1531 Hatcher Dr, Columbia, SC 29203; 1929 Bluff Rd Unit 115, Columbia, SC 29201; 6930 Monticello Rd, Columbia, SC 29203; …</t>
+          <t>1143 Owens Rd, Columbia, SC 29203</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brad, hi, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1143 Owens Rd, Columbia, SC 29203; 1515 Hatcher Dr, Columbia, SC 29203; 1531 Hatcher Dr, Columbia, SC 29203; 1929 Bluff Rd Unit 115, Columbia, SC 29201; 6930 Monticello Rd, Columbia, SC 29203; … — a cash purchase. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
+          <t>Good day Brad, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1515 Rushmore Rd, Columbia, SC 29210; 272 Bassett Loop, Columbia, SC 29229; 3408 Belvedere Dr, Columbia, SC 29204; 420 Forest Grove Cir, Columbia, SC 29210; 9429 S Chelsea Rd, Columbia, SC 29223; …</t>
+          <t>1515 Rushmore Rd, Columbia, SC 29210</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hi there Joey, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hey Joey. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 1515 Rushmore Rd, Columbia, SC 29210. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>106 Rolling Knoll Dr, Columbia, SC 29229; 141 Wincay Rd, Columbia, SC 29223; 1683 Rabon Farms Ln, Columbia, SC 29223; 424 Folkstone Rd, Columbia, SC 29223; 431 Pineneedle Rd, Columbia, SC 29203; …</t>
+          <t>106 Rolling Knoll Dr, Columbia, SC 29229</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hi Nina, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Good day Nina. Charles here with Paragon Government Solutions, and I'm reaching out about 106 Rolling Knoll Dr, Columbia, SC 29229 — a cash purchase. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1246 Rabon Pond Dr, Columbia, SC 29223; 1960 Drexel Lake Dr, Columbia, SC 29223; 3033 Blue Brook Ln, Columbia, SC 29209; 466 Robins Egg Dr, Columbia, SC 29229; 7504 Teague Rd, Columbia, SC 29209</t>
+          <t>1246 Rabon Pond Dr, Columbia, SC 29223</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Good day Austin. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 1246 Rabon Pond Dr, Columbia, SC 29223; 1960 Drexel Lake Dr, Columbia, SC 29223; 3033 Blue Brook Ln, Columbia, SC 29209; 466 Robins Egg Dr, Columbia, SC 29229; 7504 Teague Rd, Columbia, SC 29209. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
+          <t>Hi Austin. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 1246 Rabon Pond Dr, Columbia, SC 29223. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>145 Patio Pl, Columbia, SC 29212; 1909 Mitchell St, Columbia, SC 29205; 2350 Center St, Columbia, SC 29204; 628 Ridge Trail Dr, Columbia, SC 29229; 9829 Highgate Rd, Columbia, SC 29223</t>
+          <t>145 Patio Pl, Columbia, SC 29212</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hey Bonni — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
+          <t>Good day Bonni, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1163 Atkinson St, Detroit, MI 48202; 1200 S Ethel St, Detroit, MI 48217; 13120 Washburn St, Detroit, MI 48238; 19249 Marx Ave, Detroit, MI 48203; 3948 Minnesota Ave, Detroit, MI 48212</t>
+          <t>1163 Atkinson St, Detroit, MI 48202</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Good day Daleik, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Hey Daleik — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>103 Village Way, Columbia, SC 29209; 138 Morningside Dr, Columbia, SC 29210; 3825 Monroe St, Columbia, SC 29205; 407 Sesqui Trl, Columbia, SC 29223; 835 Denny Rd, Columbia, SC 29203</t>
+          <t>103 Village Way, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jamila, hi, I'm Charles with Paragon Government Solutions. I'm reaching out about 103 Village Way, Columbia, SC 29209; 138 Morningside Dr, Columbia, SC 29210; 3825 Monroe St, Columbia, SC 29205; 407 Sesqui Trl, Columbia, SC 29223; 835 Denny Rd, Columbia, SC 29203 — a cash purchase. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Hey Jamila. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 103 Village Way, Columbia, SC 29209. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12717 Indiana St, Detroit, MI 48238; 13166 Montville Pl, Detroit, MI 48238; 14195 Kentfield St, Detroit, MI 48223; 9613 American St, Detroit, MI 48204; 9755 Nardin Dr, Detroit, MI 48204</t>
+          <t>12717 Indiana St, Detroit, MI 48238</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Good day Mark, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Mark. Charles Pleasant, Paragon Government Solutions, and interested in buying 12717 Indiana St, Detroit, MI 48238 for cash. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>133 Heritage Village Ln, Columbia, SC 29212; 3000 Richfield Dr, Columbia, SC 29201; 398 Fox Squirrel Cir, Columbia, SC 29209; 41 Heritage Village Ln, Columbia, SC 29212; 6 Woodlands Ridge Ct, Columbia, SC 29229</t>
+          <t>133 Heritage Village Ln, Columbia, SC 29212</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shayla, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 133 Heritage Village Ln, Columbia, SC 29212; 3000 Richfield Dr, Columbia, SC 29201; 398 Fox Squirrel Cir, Columbia, SC 29209; 41 Heritage Village Ln, Columbia, SC 29212; 6 Woodlands Ridge Ct, Columbia, SC 29229. Is the seller open to a cash as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Shayla — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>126 Burnsdowne Rd, Columbia, SC 29210; 188 Crestland Dr, Columbia, SC 29210; 196 Cottage Lake Way, Columbia, SC 29209; 212 Kendrick Rd, Columbia, SC 29229; 570 Kimpton Dr, Columbia, SC 29223</t>
+          <t>126 Burnsdowne Rd, Columbia, SC 29210</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hey Tracy — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Tracy, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>115 Mulberry Ln, Columbia, SC 29201; 137 Canterfield Rd, Columbia, SC 29212; 1622 Crestview Ave, Columbia, SC 29223; 923 Huntington Ave, Columbia, SC 29205</t>
+          <t>115 Mulberry Ln, Columbia, SC 29201</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Good day Becky, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hi Becky. I'm Charles with Paragon Government Solutions, and interested in buying 115 Mulberry Ln, Columbia, SC 29201 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13161 Monica St, Detroit, MI 48238; 13595 Wyoming Ave, Detroit, MI 48238; 16093 Liberal St, Detroit, MI 48205; 1956 Monterey St, Detroit, MI 48206</t>
+          <t>13161 Monica St, Detroit, MI 48238</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hello Brandon, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Hey Brandon, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1111 Cloister Pl, Columbia, SC 29210; 1158 Cloister Pl, Columbia, SC 29210; 205 Twin Oaks Ln, Columbia, SC 29209; 7604 Edgewater Dr, Columbia, SC 29223</t>
+          <t>1111 Cloister Pl, Columbia, SC 29210</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hey Bryant. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 1111 Cloister Pl, Columbia, SC 29210; 1158 Cloister Pl, Columbia, SC 29210; 205 Twin Oaks Ln, Columbia, SC 29209; 7604 Edgewater Dr, Columbia, SC 29223. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi there Bryant, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1111 Cloister Pl, Columbia, SC 29210. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2018 Hallmark Ct, Lakeland, FL 33803; 4119 Sherman Hills Pkwy W, Jacksonville, FL 32210; 541 Linwood Ave, Jacksonville, FL 32206; 857 Benbow St, Jacksonville, FL 32209</t>
+          <t>2018 Hallmark Ct, Lakeland, FL 33803</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jamie, hi. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2018 Hallmark Ct, Lakeland, FL 33803; 4119 Sherman Hills Pkwy W, Jacksonville, FL 32210; 541 Linwood Ave, Jacksonville, FL 32206; 857 Benbow St, Jacksonville, FL 32209. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hey Jamie. I'm Charles with Paragon Government Solutions, and interested in buying 2018 Hallmark Ct, Lakeland, FL 33803 for cash. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1009 Gardendale Dr, Columbia, SC 29210; 1155 Cloister Pl, Columbia, SC 29210; 1522 Hibiscus St, Columbia, SC 29205; 303 Harbor Dr, Columbia, SC 29229</t>
+          <t>1009 Gardendale Dr, Columbia, SC 29210</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hello Nadia, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Hi there Nadia — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>228 Rolling Rock Rd, Columbia, SC 29212; 400 Green Tree Cir, Columbia, SC 29203; 400 Stanford St, Columbia, SC 29203; 562 Buckhaven Way, Columbia, SC 29229</t>
+          <t>228 Rolling Rock Rd, Columbia, SC 29212</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hello Renee — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
+          <t>Renee, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>124 Farrow Pointe Ln, Columbia, SC 29203; 5666 Middleton Ct, Columbia, SC 29203; E/s Tremont Ave #12, Columbia, SC 29203; E/s Tremont Ave #13, Columbia, SC 29203</t>
+          <t>124 Farrow Pointe Ln, Columbia, SC 29203</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hi there Sheila, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 124 Farrow Pointe Ln, Columbia, SC 29203; 5666 Middleton Ct, Columbia, SC 29203; E/s Tremont Ave #12, Columbia, SC 29203; E/s Tremont Ave #13, Columbia, SC 29203. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
+          <t>Good day Sheila. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 124 Farrow Pointe Ln, Columbia, SC 29203 — a cash purchase. Is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>314 Leton Dr, Columbia, SC 29210; 316 E Waverly Place Ct, Columbia, SC 29229; 4615 Bluff Rd, Columbia, SC 29209</t>
+          <t>314 Leton Dr, Columbia, SC 29210</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hi there Amber, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Amber, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3736 ROSE Street, Jacksonville, FL 32208; 7316 Parkview Dr, Columbia, SC 29223; 9606 DEVONSHIRE Boulevard, Jacksonville, FL 32208</t>
+          <t>3736 ROSE Street, Jacksonville, FL 32208</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hi there ANDREA. Charles here with Paragon Government Solutions, and interested in buying 3736 ROSE Street, Jacksonville, FL 32208; 7316 Parkview Dr, Columbia, SC 29223; 9606 DEVONSHIRE Boulevard, Jacksonville, FL 32208 for cash. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
+          <t>Hey ANDREA. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 3736 ROSE Street, Jacksonville, FL 32208. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10201 S Princeton Ave, Chicago, IL 60628; 2469 E 74th St, Chicago, IL 60649; 7843 S Langley Ave, Chicago, IL 60619</t>
+          <t>10201 S Princeton Ave, Chicago, IL 60628</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hi Andrew, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Andrew, I'm Charles with Paragon Government Solutions. I'm reaching out about 10201 S Princeton Ave, Chicago, IL 60628 — a cash purchase. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1024 Price Ave, Columbia, SC 29201; 277 Piney Grove Rd, Columbia, SC 29210; 953 Texas St, Columbia, SC 29201</t>
+          <t>1024 Price Ave, Columbia, SC 29201</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hi Angela, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day Angela, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11439 Ohio St, Detroit, MI 48204; 19614 Charest St, Detroit, MI 48234; 2569 Alter Rd, Detroit, MI 48215</t>
+          <t>11439 Ohio St, Detroit, MI 48204</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hi Anthony. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 11439 Ohio St, Detroit, MI 48204; 19614 Charest St, Detroit, MI 48234; 2569 Alter Rd, Detroit, MI 48215. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
+          <t>Anthony, hi. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 11439 Ohio St, Detroit, MI 48204. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12664 Kelly Rd, Detroit, MI 48224; 19187 Gainsborough Rd, Detroit, MI 48223; 5601 Marlborough St, Detroit, MI 48224</t>
+          <t>12664 Kelly Rd, Detroit, MI 48224</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hi Anya. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 12664 Kelly Rd, Detroit, MI 48224; 19187 Gainsborough Rd, Detroit, MI 48223; 5601 Marlborough St, Detroit, MI 48224. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
+          <t>Hello Anya, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 12664 Kelly Rd, Detroit, MI 48224 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>205 Parliament Dr, Columbia, SC 29223; 525 Pittsdowne Rd, Columbia, SC 29210; 8416 Little John Dr, Columbia, SC 29209</t>
+          <t>205 Parliament Dr, Columbia, SC 29223</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hi there Avia, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 205 Parliament Dr, Columbia, SC 29223; 525 Pittsdowne Rd, Columbia, SC 29210; 8416 Little John Dr, Columbia, SC 29209. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
+          <t>Hey Avia — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>23 Braiden Manor Rd, Columbia, SC 29209; 231 Gayle Pond Trce, Columbia, SC 29209; 551 Seton Hall Dr, Columbia, SC 29223</t>
+          <t>23 Braiden Manor Rd, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hi there Billy, Charles here with Paragon Government Solutions. interested in buying 23 Braiden Manor Rd, Columbia, SC 29209; 231 Gayle Pond Trce, Columbia, SC 29209; 551 Seton Hall Dr, Columbia, SC 29223 for cash. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
+          <t>Hey Billy, Charles Pleasant, Paragon Government Solutions. interested in buying 23 Braiden Manor Rd, Columbia, SC 29209 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2027 Leesburg Rd, Columbia, SC 29209; 54 Monmouth Ct, Columbia, SC 29209; 924 Stebondale Rd, Columbia, SC 29203</t>
+          <t>2027 Leesburg Rd, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hi there Carlina. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 2027 Leesburg Rd, Columbia, SC 29209; 54 Monmouth Ct, Columbia, SC 29209; 924 Stebondale Rd, Columbia, SC 29203. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
+          <t>Hi Carlina — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1169 WOODRUFF Avenue, Jacksonville, FL 32205; 5148 ATTLEBORO Street, Jacksonville, FL 32205; 6116 SUDBURY Avenue S, Jacksonville, FL 32210</t>
+          <t>1169 WOODRUFF Avenue, Jacksonville, FL 32205</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hey CHAD, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 1169 WOODRUFF Avenue, Jacksonville, FL 32205; 5148 ATTLEBORO Street, Jacksonville, FL 32205; 6116 SUDBURY Avenue S, Jacksonville, FL 32210 for cash. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi there CHAD, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 1169 WOODRUFF Avenue, Jacksonville, FL 32205 for cash. Is the seller open to a cash as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17593 Monica St, Detroit, MI 48221; 5540 Guilford St, Detroit, MI 48224; 7839 Clayburn St, Detroit, MI 48228</t>
+          <t>17593 Monica St, Detroit, MI 48221</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charles, hi, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 17593 Monica St, Detroit, MI 48221; 5540 Guilford St, Detroit, MI 48224; 7839 Clayburn St, Detroit, MI 48228 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks so much!</t>
+          <t>Good day Charles, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>104 Harbor Dr, Columbia, SC 29229; 126 Baysdale Dr, Columbia, SC 29229; 276 Oberlin Rd, Columbia, SC 29212</t>
+          <t>104 Harbor Dr, Columbia, SC 29229</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hey Cody — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
+          <t>Good day Cody, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1257 E 170th St, Cleveland, OH 44110; 3357 W 30th St, Cleveland, OH 44109; 5911 Lexington Ave, Cleveland, OH 44103</t>
+          <t>1257 E 170th St, Cleveland, OH 44110</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Daniel, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there Daniel, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1007 Anarine Rd, Fayetteville, NC 28303; 1623 Gibson St, Fayetteville, NC 28301; 7314 Hyannis Dr, Fayetteville, NC 28304</t>
+          <t>1007 Anarine Rd, Fayetteville, NC 28303</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hi DIETCHI, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
+          <t>Hey DIETCHI, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15385 Stansbury St, Detroit, MI 48227; 15862 Stansbury St, Detroit, MI 48227; 20008 Spencer St, Detroit, MI 48234</t>
+          <t>15385 Stansbury St, Detroit, MI 48227</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hello Heather — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
+          <t>Heather, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 15385 Stansbury St, Detroit, MI 48227 — a cash purchase. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2518 Putnam St, Columbia, SC 29204; 509 Ridge Trail Dr, Columbia, SC 29229; 5912 Yorkshire Dr, Columbia, SC 29209</t>
+          <t>2518 Putnam St, Columbia, SC 29204</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hello Jamie, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hey Jamie, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12140 Wayburn St, Detroit, MI 48224; 19639 Wexford St, Detroit, MI 48234; 9092 Patton St, Detroit, MI 48228</t>
+          <t>12140 Wayburn St, Detroit, MI 48224</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hello Kristian, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hello Kristian, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 12140 Wayburn St, Detroit, MI 48224. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1233 W 73rd Pl, Chicago, IL 60636; 1647 W 59th St, Chicago, IL 60636; 6037 &amp; 6039 S Wood St, Chicago, IL 60636</t>
+          <t>1233 W 73rd Pl, Chicago, IL 60636</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hi Mark — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Mark — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15534 Rocco Dr, Baker, LA 70714; 2128 Clark Ave, Zachary, LA 70791; 2133 Clark Ave, Zachary, LA 70791</t>
+          <t>15534 Rocco Dr, Baker, LA 70714</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hello Melissa, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Melissa — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1023 Crow Ct, Grand Prairie, TX 75051; 2666 Kellogg Ave, Dallas, TX 75216; 3644 Kimball Ridge Pl, Dallas, TX 75233</t>
+          <t>1023 Crow Ct, Grand Prairie, TX 75051</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hi there Michael. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 1023 Crow Ct, Grand Prairie, TX 75051; 2666 Kellogg Ave, Dallas, TX 75216; 3644 Kimball Ridge Pl, Dallas, TX 75233. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
+          <t>Michael, hi, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10310 Mills Run Dr, Houston, TX 77070; 17414 Turquoise Stream Dr, Houston, TX 77095; 6527 Gladewell Dr, Houston, TX 77072</t>
+          <t>10310 Mills Run Dr, Houston, TX 77070</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hi there Nancy. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 10310 Mills Run Dr, Houston, TX 77070; 17414 Turquoise Stream Dr, Houston, TX 77095; 6527 Gladewell Dr, Houston, TX 77072. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey Nancy, this is Charles Pleasant with Paragon Government Solutions. interested in buying 10310 Mills Run Dr, Houston, TX 77070 for cash. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>135 Fox Squirrel Cir, Columbia, SC 29209; 213 Greemount Cir, Columbia, SC 29209; 8206 Bayfield Rd, Columbia, SC 29223</t>
+          <t>135 Fox Squirrel Cir, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Good day Patrick. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 135 Fox Squirrel Cir, Columbia, SC 29209; 213 Greemount Cir, Columbia, SC 29209; 8206 Bayfield Rd, Columbia, SC 29223. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
+          <t>Patrick, hi — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10799 Worden St, Detroit, MI 48224; 16500 Eastburn St, Detroit, MI 48205; 9205 McKinney St, Detroit, MI 48224</t>
+          <t>10799 Worden St, Detroit, MI 48224</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hello Sam. I'm Charles with Paragon Government Solutions, and interested in buying 10799 Worden St, Detroit, MI 48224; 16500 Eastburn St, Detroit, MI 48205; 9205 McKinney St, Detroit, MI 48224 for cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Sam, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3700 Ulmer Rd, Columbia, SC 29209; 8 Hampton Oaks Pl, Columbia, SC 29212</t>
+          <t>3700 Ulmer Rd, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Good day there. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 3700 Ulmer Rd, Columbia, SC 29209; 8 Hampton Oaks Pl, Columbia, SC 29212. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi there, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3700 Ulmer Rd, Columbia, SC 29209. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12717 Riad St, Grosse Pointe, MI 48224; 13892 Bringard Dr, Detroit, MI 48205</t>
+          <t>12717 Riad St, Grosse Pointe, MI 48224</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hi there Albert, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 12717 Riad St, Grosse Pointe, MI 48224; 13892 Bringard Dr, Detroit, MI 48205. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Albert, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>201 Sandhurst Rd, Columbia, SC 29210; 2113 Kathleen Dr, Columbia, SC 29210</t>
+          <t>201 Sandhurst Rd, Columbia, SC 29210</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hi Alex — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Alex, Charles Pleasant, Paragon Government Solutions. interested in buying 201 Sandhurst Rd, Columbia, SC 29210 for cash. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1152 Vinewood St, Detroit, MI 48216; 2905 Putnam St, Detroit, MI 48208</t>
+          <t>1152 Vinewood St, Detroit, MI 48216</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hello Alex, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Alex, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>16321 Stockbridge Ave, Cleveland, OH 44128; 3319 Fulton Rd, Cleveland, OH 44109</t>
+          <t>16321 Stockbridge Ave, Cleveland, OH 44128</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hi Alexander — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi Alexander — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>219 Dixon Dr, Columbia, SC 29203; 7602 Hunt Club Rd APT A104, Columbia, SC 29223</t>
+          <t>219 Dixon Dr, Columbia, SC 29203</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Good day Alexandra, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 219 Dixon Dr, Columbia, SC 29203; 7602 Hunt Club Rd APT A104, Columbia, SC 29223. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi Alexandra, this is Charles Pleasant with Paragon Government Solutions. interested in buying 219 Dixon Dr, Columbia, SC 29203 for cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9520 Royal Ln #104, Dallas TX 75243; 9520 Royal Ln (#114/#121/#306), Dallas TX 75243</t>
+          <t>9520 Royal Ln #104, Dallas TX 75243</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Amber, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks much!</t>
+          <t>Hello Amber, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6506 Christie Rd, Columbia, SC 29209; 7818 Exeter Ln, Columbia, SC 29223</t>
+          <t>6506 Christie Rd, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hey Andy, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Andy — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1533 S Kilbourn Ave, Chicago, IL 60623; 6914 S Winchester Ave, Chicago, IL 60636</t>
+          <t>1533 S Kilbourn Ave, Chicago, IL 60623</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hello Anthony. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 1533 S Kilbourn Ave, Chicago, IL 60623; 6914 S Winchester Ave, Chicago, IL 60636. Open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Anthony, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>132 Flora Springs Cir, Columbia, SC 29223; 25 Heatherlaurel Ct, Columbia, SC 29223</t>
+          <t>132 Flora Springs Cir, Columbia, SC 29223</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hello Anthony. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 132 Flora Springs Cir, Columbia, SC 29223; 25 Heatherlaurel Ct, Columbia, SC 29223. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
+          <t>Anthony, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 132 Flora Springs Cir, Columbia, SC 29223. Is the seller open to a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1010 KENMORE Street, Jacksonville, FL 32208; 7035 ELWOOD Avenue, Jacksonville, FL 32208</t>
+          <t>1010 KENMORE Street, Jacksonville, FL 32208</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hello ARTHUR, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>ARTHUR, hi, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 1010 KENMORE Street, Jacksonville, FL 32208. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1987 W Melvina St, Milwaukee, WI 53206; 3729 N Vel R Phillips Ave, Milwaukee, WI 53212</t>
+          <t>1987 W Melvina St, Milwaukee, WI 53206</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hi there Arthur, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Hi Arthur, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14941 Littlefield St, Detroit, MI 48227; 15411 Ferguson St, Detroit, MI 48227</t>
+          <t>14941 Littlefield St, Detroit, MI 48227</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hey Bobby — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Bobby, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1253 Mosser Dr, Columbia, SC 29203; 9 Twin Oaks Cir, Columbia, SC 29209</t>
+          <t>1253 Mosser Dr, Columbia, SC 29203</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hi Brad, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Brad, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1253 Mosser Dr, Columbia, SC 29203. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2065 Missouri St, Baton Rouge, LA 70802; 2614 Bartlett St, Baton Rouge, LA 70805</t>
+          <t>2065 Missouri St, Baton Rouge, LA 70802</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hey Brittany, I'm Charles with Paragon Government Solutions. I'm reaching out about 2065 Missouri St, Baton Rouge, LA 70802; 2614 Bartlett St, Baton Rouge, LA 70805 — a cash purchase. Open to a discounted cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
+          <t>Hi there Brittany — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>232 Twin Oaks Ln, Columbia, SC 29209; 822 Apache Dr, Columbia, SC 29203</t>
+          <t>232 Twin Oaks Ln, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hi there Caleb, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Caleb, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>9175 Everts St, Detroit, MI 48224; 9824 Philip St, Detroit, MI 48224</t>
+          <t>9175 Everts St, Detroit, MI 48224</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cameron, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 9175 Everts St, Detroit, MI 48224; 9824 Philip St, Detroit, MI 48224. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
+          <t>Cameron, hi — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3805 Trotter Rd, Columbia, SC 29209; 808 Kingsbridge Rd, Columbia, SC 29210</t>
+          <t>3805 Trotter Rd, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Good day Chachere. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 3805 Trotter Rd, Columbia, SC 29209; 808 Kingsbridge Rd, Columbia, SC 29210. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
+          <t>Hi there Chachere, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1602 Gardenia Ave, Fayetteville, NC 28311; 1716 Shaw Rd, Fayetteville, NC 28311</t>
+          <t>1602 Gardenia Ave, Fayetteville, NC 28311</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CHRISTINA, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks so much!</t>
+          <t>Hello CHRISTINA, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5648 S Sawyer Ave, Chicago, IL 60629; 6100 S Bishop St, Chicago, IL 60636</t>
+          <t>5648 S Sawyer Ave, Chicago, IL 60629</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hi Crystal, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hello Crystal, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 5648 S Sawyer Ave, Chicago, IL 60629 — a cash purchase. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22118 Ulster St, Detroit, MI 48219; 6444 Ashton Ave, Detroit, MI 48228</t>
+          <t>22118 Ulster St, Detroit, MI 48219</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hi there Daniella, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 22118 Ulster St, Detroit, MI 48219; 6444 Ashton Ave, Detroit, MI 48228. Is the seller open to a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Daniella — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11532 S Harvard Ave, Chicago, IL 60628; 7629 S Maryland Ave, Chicago, IL 60619</t>
+          <t>11532 S Harvard Ave, Chicago, IL 60628</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hey David, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hey David. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 11532 S Harvard Ave, Chicago, IL 60628 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hi Dean. Charles here with Paragon Government Solutions, and interested in buying 19760 Rowe St, Detroit, MI 48205 for cash. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Dean, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2 Woodshaw Ct, Columbia, SC 29212; 4604 Ridgewood Ave, Columbia, SC 29203</t>
+          <t>2 Woodshaw Ct, Columbia, SC 29212</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hi Delaney — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there Delaney, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2 Woodshaw Ct, Columbia, SC 29212 — a cash purchase. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7330 ELWOOD Avenue, Jacksonville, FL 32208; 8384 DELAWARE Avenue, Jacksonville, FL 32208</t>
+          <t>7330 ELWOOD Avenue, Jacksonville, FL 32208</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hello DENISE, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi there DENISE. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 7330 ELWOOD Avenue, Jacksonville, FL 32208. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3814 Hardy St, Houston, TX 77009; 3818 Hardy St, Houston, TX 77009</t>
+          <t>3814 Hardy St, Houston, TX 77009</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Good day Derek, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Hey Derek, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>14440 Chelsea St, Detroit, MI 48213; 16828 W Chicago St, Detroit, MI 48228</t>
+          <t>14440 Chelsea St, Detroit, MI 48213</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ejaz, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi Ejaz, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2407,12 +2407,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4203 New Orleans St, Houston, TX 77020; 5839 Southurst St, Houston, TX 77033</t>
+          <t>4203 New Orleans St, Houston, TX 77020</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hi Evan, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 4203 New Orleans St, Houston, TX 77020; 5839 Southurst St, Houston, TX 77033. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks!</t>
+          <t>Good day Evan — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>13027 Rosemary St, Detroit, MI 48213; 14303 Rosemary St, Detroit, MI 48213</t>
+          <t>13027 Rosemary St, Detroit, MI 48213</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hi Franco, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 13027 Rosemary St, Detroit, MI 48213; 14303 Rosemary St, Detroit, MI 48213. Is the seller open to a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
+          <t>Franco, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 13027 Rosemary St, Detroit, MI 48213. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15470 Mapleridge St, Detroit, MI 48205; 5565 Fairview St, Detroit, MI 48213</t>
+          <t>15470 Mapleridge St, Detroit, MI 48205</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hi Gaston. Charles Pleasant, Paragon Government Solutions, and interested in buying 15470 Mapleridge St, Detroit, MI 48205; 5565 Fairview St, Detroit, MI 48213 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there Gaston. I'm Charles with Paragon Government Solutions, and interested in buying 15470 Mapleridge St, Detroit, MI 48205 for cash. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2519 Chalk Hill Rd, Dallas, TX 75212; 2522 Wilhurt Ave, Dallas, TX 75216</t>
+          <t>2519 Chalk Hill Rd, Dallas, TX 75212</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hi there Graciela. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 2519 Chalk Hill Rd, Dallas, TX 75212; 2522 Wilhurt Ave, Dallas, TX 75216. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Graciela, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2507,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20 Shuler Cir, Columbia, SC 29212; 304 Stanford St, Columbia, SC 29203</t>
+          <t>20 Shuler Cir, Columbia, SC 29212</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hi there Greg, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 20 Shuler Cir, Columbia, SC 29212; 304 Stanford St, Columbia, SC 29203. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there Greg, Charles here with Paragon Government Solutions. interested in buying 20 Shuler Cir, Columbia, SC 29212 for cash. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4440 Sexton Rd, Cleveland, OH 44105; 8018 Platt Ave, Cleveland, OH 44104</t>
+          <t>4440 Sexton Rd, Cleveland, OH 44105</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hi Gregory — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
+          <t>Good day Gregory — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20569 Evergreen Rd, Detroit, MI 48219; 6160 Neff Ave, Detroit, MI 48224</t>
+          <t>20569 Evergreen Rd, Detroit, MI 48219</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Good day Hassan, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 20569 Evergreen Rd, Detroit, MI 48219; 6160 Neff Ave, Detroit, MI 48224. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Hi there Hassan — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2371 JAYSON Avenue, Jacksonville, FL 32208; 409 CRYSTAL Street, Jacksonville, FL 32254</t>
+          <t>2371 JAYSON Avenue, Jacksonville, FL 32208</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hi there JACQUELYN — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks much!</t>
+          <t>Hey JACQUELYN, this is Charles Pleasant with Paragon Government Solutions. interested in buying 2371 JAYSON Avenue, Jacksonville, FL 32208 for cash. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>14045 Sussex St, Detroit, MI 48227; 7638 Stahelin Ave, Detroit, MI 48228</t>
+          <t>14045 Sussex St, Detroit, MI 48227</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>James, hi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 14045 Sussex St, Detroit, MI 48227; 7638 Stahelin Ave, Detroit, MI 48228. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi there James, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 14045 Sussex St, Detroit, MI 48227. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>412 CHESTNUT Drive, Jacksonville, FL 32208; 5146 SUNDERLAND Road, Jacksonville, FL 32210</t>
+          <t>412 CHESTNUT Drive, Jacksonville, FL 32208</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hey JANET — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks!</t>
+          <t>JANET, hi, I'm Charles with Paragon Government Solutions. I'm reaching out about 412 CHESTNUT Drive, Jacksonville, FL 32208 — a cash purchase. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>209 Leago St, Houston, TX 77022; 2818 S Bartell Dr APT 33, Houston, TX 77054</t>
+          <t>209 Leago St, Houston, TX 77022</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hey Jay — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks!</t>
+          <t>Hi Jay — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>10066 S Van Vlissingen Rd, Chicago, IL 60617; 4208 S Artesian Ave, Chicago, IL 60632</t>
+          <t>10066 S Van Vlissingen Rd, Chicago, IL 60617</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hello Jessica. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 10066 S Van Vlissingen Rd, Chicago, IL 60617; 4208 S Artesian Ave, Chicago, IL 60632. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
+          <t>Hi Jessica, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 10066 S Van Vlissingen Rd, Chicago, IL 60617 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1546 RIVER HILLS Circle W, Jacksonville, FL 32211; 1837 BUCKMAN Street, Jacksonville, FL 32206</t>
+          <t>1546 RIVER HILLS Circle W, Jacksonville, FL 32211</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Good day JULIANA, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1546 RIVER HILLS Circle W, Jacksonville, FL 32211; 1837 BUCKMAN Street, Jacksonville, FL 32206. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
+          <t>Hey JULIANA, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>17184 Dresden St, Detroit, MI 48205; 19228 Beland St, Detroit, MI 48234</t>
+          <t>17184 Dresden St, Detroit, MI 48205</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Good day Kaila. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 17184 Dresden St, Detroit, MI 48205; 19228 Beland St, Detroit, MI 48234 for cash. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Kaila. I'm Charles with Paragon Government Solutions, and interested in buying 17184 Dresden St, Detroit, MI 48205 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1018 W 104th Pl, Chicago, IL 60643; 8106 S Burnham Ave, Chicago, IL 60617</t>
+          <t>1018 W 104th Pl, Chicago, IL 60643</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Good day Kanaan — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Kanaan. Charles here with Paragon Government Solutions, and interested in buying 1018 W 104th Pl, Chicago, IL 60643 for cash. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3819 Uncas St, Baton Rouge, LA 70805; 3851 Uncas St, Baton Rouge, LA 70805</t>
+          <t>3819 Uncas St, Baton Rouge, LA 70805</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kendall, hi, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey Kendall, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3819 Uncas St, Baton Rouge, LA 70805 — a cash purchase. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>11000 S Normal Ave, Chicago, IL 60628; 11534 S Princeton Ave, Chicago, IL 60628</t>
+          <t>11000 S Normal Ave, Chicago, IL 60628</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Good day Keri, this is Charles Pleasant with Paragon Government Solutions. interested in buying 11000 S Normal Ave, Chicago, IL 60628; 11534 S Princeton Ave, Chicago, IL 60628 for cash. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey Keri, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2051 FRANK E Avenue, Jacksonville, FL 32208; 6228 BLUEBIRD Road, Jacksonville, FL 32219</t>
+          <t>2051 FRANK E Avenue, Jacksonville, FL 32208</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hi KRAVIN, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hello KRAVIN, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>7604 Edgewater Dr, Columbia, SC 29223; 828 Yellow Swan Ln, Columbia, SC 29210</t>
+          <t>7604 Edgewater Dr, Columbia, SC 29223</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Good day Kristie, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 7604 Edgewater Dr, Columbia, SC 29223; 828 Yellow Swan Ln, Columbia, SC 29210. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
+          <t>Good day Kristie — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1253 Rabon Pond Dr, Columbia, SC 29223; 140 Twin Oaks Ln, Columbia, SC 29209</t>
+          <t>1253 Rabon Pond Dr, Columbia, SC 29223</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hi LaToya. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 1253 Rabon Pond Dr, Columbia, SC 29223; 140 Twin Oaks Ln, Columbia, SC 29209. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Good day LaToya, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>19783 Annott St, Detroit, MI 48205; 7777 W Outer Dr, Detroit, MI 48235</t>
+          <t>19783 Annott St, Detroit, MI 48205</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hi LaTrina, Charles Pleasant, Paragon Government Solutions. interested in buying 19783 Annott St, Detroit, MI 48205; 7777 W Outer Dr, Detroit, MI 48235 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
+          <t>Good day LaTrina, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3417 Gray St, Detroit, MI 48215; 8127 E Hildale St, Detroit, MI 48234</t>
+          <t>3417 Gray St, Detroit, MI 48215</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Good day Leo — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
+          <t>Hello Leo — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1506 Grand Valley Dr, Houston, TX 77090; 4923 Saxon Dr, Houston, TX 77092</t>
+          <t>1506 Grand Valley Dr, Houston, TX 77090</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hey Lisa, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Lisa, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>15220 Tacoma St, Detroit, MI 48205; 20485 Helen St, Detroit, MI 48234</t>
+          <t>15220 Tacoma St, Detroit, MI 48205</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Logan, hi. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 15220 Tacoma St, Detroit, MI 48205; 20485 Helen St, Detroit, MI 48234 for cash. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Logan, hi. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 15220 Tacoma St, Detroit, MI 48205. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6978 PAUL HOWARD Drive, Jacksonville, FL 32222; 7004 DAYTON Road, Jacksonville, FL 32210</t>
+          <t>6978 PAUL HOWARD Drive, Jacksonville, FL 32222</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MAIDELYS, hi, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 6978 PAUL HOWARD Drive, Jacksonville, FL 32222; 7004 DAYTON Road, Jacksonville, FL 32210 for cash. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>MAIDELYS, hi — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>367 Marshdeer Way, Columbia, SC 29229; Nx 1635 Dupont Dr, Columbia, SC 29223</t>
+          <t>367 Marshdeer Way, Columbia, SC 29229</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Good day Marcia, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 367 Marshdeer Way, Columbia, SC 29229; Nx 1635 Dupont Dr, Columbia, SC 29223. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello Marcia — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3062,12 +3062,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>336 Byron Rd, Columbia, SC 29209; 3961 Live Oak St, Columbia, SC 29205</t>
+          <t>336 Byron Rd, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hi there Mary, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks!</t>
+          <t>Hey Mary — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1311 GRANVDIEW Drive, Jacksonville, FL 32211; 6146 BUCKING BRONCO Drive, Jacksonville, FL 32234</t>
+          <t>1311 GRANVDIEW Drive, Jacksonville, FL 32211</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hi MATT, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there MATT, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3112,12 +3112,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1204 Vickie Ln, Lake Charles, LA 70601; 1802 Rose St, Lake Charles, LA 70601</t>
+          <t>1204 Vickie Ln, Lake Charles, LA 70601</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hello McCall, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there McCall, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 1204 Vickie Ln, Lake Charles, LA 70601. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1800 Walter St SE, Albuquerque, NM 87102; 314 49th St NW, Albuquerque, NM 87105</t>
+          <t>1800 Walter St SE, Albuquerque, NM 87102</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hi Medina, Charles here with Paragon Government Solutions. interested in buying 1800 Walter St SE, Albuquerque, NM 87102; 314 49th St NW, Albuquerque, NM 87105 for cash. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Medina, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1800 Walter St SE, Albuquerque, NM 87102. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>13594 Grandmont Ave, Detroit, MI 48227; 19353 Runyon St, Detroit, MI 48234</t>
+          <t>13594 Grandmont Ave, Detroit, MI 48227</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Michael, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Michael, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>19989 Coventry St, Highland Park, MI 48203; 20203 Hull St, Highland Park, MI 48203</t>
+          <t>19989 Coventry St, Highland Park, MI 48203</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hi there Minhaz. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 19989 Coventry St, Highland Park, MI 48203; 20203 Hull St, Highland Park, MI 48203. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Good day Minhaz. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 19989 Coventry St, Highland Park, MI 48203. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3212,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5308 W LEWIS Avenue W, Phoenix, AZ 85035; 7630 W AVALON Drive, Phoenix, AZ 85033</t>
+          <t>5308 W LEWIS Avenue W, Phoenix, AZ 85035</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Good day Mladenka, Charles here with Paragon Government Solutions. interested in buying 5308 W LEWIS Avenue W, Phoenix, AZ 85035; 7630 W AVALON Drive, Phoenix, AZ 85033 for cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi Mladenka, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5308 W LEWIS Avenue W, Phoenix, AZ 85035. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>125 N Lake Pointe Dr, Columbia, SC 29229; 501 S Edisto Ave, Columbia, SC 29205</t>
+          <t>125 N Lake Pointe Dr, Columbia, SC 29229</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mo, hi — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
+          <t>Hey Mo, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>16610 Collingham Dr, Detroit, MI 48205; 19301 Runyon St, Detroit, MI 48234</t>
+          <t>16610 Collingham Dr, Detroit, MI 48205</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hey Mohamed. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 16610 Collingham Dr, Detroit, MI 48205; 19301 Runyon St, Detroit, MI 48234 — a cash purchase. Would the owner entertain a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
+          <t>Mohamed, hi, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>11548 S Normal Ave, Chicago, IL 60628; 5225 S Wood St, Chicago, IL 60609</t>
+          <t>11548 S Normal Ave, Chicago, IL 60628</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hi there Monica. Charles Pleasant, Paragon Government Solutions, and interested in buying 11548 S Normal Ave, Chicago, IL 60628; 5225 S Wood St, Chicago, IL 60609 for cash. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thank you!</t>
+          <t>Hey Monica. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 11548 S Normal Ave, Chicago, IL 60628. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2947 Appaloosa Dr, Dallas, TX 75237; 4818 Jesus Maria Ct, Dallas, TX 75236</t>
+          <t>2947 Appaloosa Dr, Dallas, TX 75237</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hi Monika, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day Monika. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2947 Appaloosa Dr, Dallas, TX 75237. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5926 DUNMIRE Avenue, Jacksonville, FL 32219; 6109 STRAWFLOWER Place, Jacksonville, FL 32209</t>
+          <t>5926 DUNMIRE Avenue, Jacksonville, FL 32219</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hey MOSES. I'm Charles with Paragon Government Solutions, and interested in buying 5926 DUNMIRE Avenue, Jacksonville, FL 32219; 6109 STRAWFLOWER Place, Jacksonville, FL 32209 for cash. Is the seller open to a cash as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello MOSES, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 5926 DUNMIRE Avenue, Jacksonville, FL 32219. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>17206 Fenelon St, Detroit, MI 48212; 7267 Mettetal St, Detroit, MI 48228</t>
+          <t>17206 Fenelon St, Detroit, MI 48212</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hey Nadia, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Nadia, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3387,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>152 W 10TH Street, Jacksonville, FL 32206; 16228 TISONS BLUFF Road, Jacksonville, FL 32218</t>
+          <t>152 W 10TH Street, Jacksonville, FL 32206</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hello NAJI. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 152 W 10TH Street, Jacksonville, FL 32206; 16228 TISONS BLUFF Road, Jacksonville, FL 32218. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello NAJI — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2223 Gray St, Detroit, MI 48215; 4827 Gray St, Detroit, MI 48215</t>
+          <t>2223 Gray St, Detroit, MI 48215</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hi there Nazareth — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Nazareth, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 2223 Gray St, Detroit, MI 48215. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2912 Chestnut St, Columbia, SC 29204; 3405 Padgett Rd, Columbia, SC 29209</t>
+          <t>2912 Chestnut St, Columbia, SC 29204</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hi Pamela, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Good day Pamela — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2539 Cherry St, Columbia, SC 29205; W/s Zacks Playhouse Rd, Hollywood, SC 29449</t>
+          <t>2539 Cherry St, Columbia, SC 29205</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hello Rachel, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 2539 Cherry St, Columbia, SC 29205; W/s Zacks Playhouse Rd, Hollywood, SC 29449. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Rachel, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2539 Cherry St, Columbia, SC 29205 — a cash purchase. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>1513 Dianne Ct SE, Atlanta, GA; 747 Gary Rd NW, Atlanta, GA</t>
+          <t>1513 Dianne Ct SE, Atlanta, GA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Good day Raquel, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Raquel, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3512,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1711 30TH Street W, Jacksonville, FL 32209; 2820 AUBREY Avenue, Jacksonville, FL 32208</t>
+          <t>1711 30TH Street W, Jacksonville, FL 32209</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hello RYAN. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 1711 30TH Street W, Jacksonville, FL 32209; 2820 AUBREY Avenue, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
+          <t>Hey RYAN, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>1000 Coatesdale Rd, Columbia, SC 29209; 245 Dove Park Rd, Columbia, SC 29223</t>
+          <t>1000 Coatesdale Rd, Columbia, SC 29209</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hey Sam, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 1000 Coatesdale Rd, Columbia, SC 29209; 245 Dove Park Rd, Columbia, SC 29223 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
+          <t>Hi Sam. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1000 Coatesdale Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>65 W 112th Pl, Chicago, IL 60628; 7521 S Aberdeen St, Chicago, IL 60620</t>
+          <t>65 W 112th Pl, Chicago, IL 60628</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hello Soraida — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
+          <t>Hello Soraida. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 65 W 112th Pl, Chicago, IL 60628. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3592,12 +3592,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>1086 Horne St, Houston, TX 77088; 412 N Bryan St, Houston, TX 77011</t>
+          <t>1086 Horne St, Houston, TX 77088</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hello Starr. Charles here with Paragon Government Solutions, and interested in buying 1086 Horne St, Houston, TX 77088; 412 N Bryan St, Houston, TX 77011 for cash. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
+          <t>Hi Starr, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1086 Horne St, Houston, TX 77088. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3617,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>425 Columbia St, Shreveport, LA 71104; 7045 Elsie St, Shreveport, LA 71108</t>
+          <t>425 Columbia St, Shreveport, LA 71104</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hi Sydney, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Hi there Sydney. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 425 Columbia St, Shreveport, LA 71104. Open to a discounted cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3331 S Liddesdale St, Detroit, MI 48217; 5226 Coplin St, Detroit, MI 48213</t>
+          <t>3331 S Liddesdale St, Detroit, MI 48217</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hi there Tarick, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Tarick, Charles here with Paragon Government Solutions. I'm a cash investor looking at 3331 S Liddesdale St, Detroit, MI 48217. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2009 Las Cruces Ln, Dallas, TX 75217; 3013 Emmett St, Dallas, TX 75211</t>
+          <t>2009 Las Cruces Ln, Dallas, TX 75217</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hello Timeka, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Timeka, hi, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>12729 Grandmont Ave, Detroit, MI 48227; 19977 Santa Barbara Dr, Detroit, MI 48221</t>
+          <t>12729 Grandmont Ave, Detroit, MI 48227</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Timothy, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 12729 Grandmont Ave, Detroit, MI 48227; 19977 Santa Barbara Dr, Detroit, MI 48221. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey Timothy. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 12729 Grandmont Ave, Detroit, MI 48227 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>16 Sand Spur Rd, Columbia, SC 29223; 9505 Puritan Rd, Columbia, SC 29209</t>
+          <t>16 Sand Spur Rd, Columbia, SC 29223</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hi there Valerie, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 16 Sand Spur Rd, Columbia, SC 29223; 9505 Puritan Rd, Columbia, SC 29209. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there Valerie — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20209 Stotter St, Detroit, MI 48234; 8229 Carlin St, Detroit, MI 48228</t>
+          <t>20209 Stotter St, Detroit, MI 48234</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hey Verdieman — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
+          <t>Hi there Verdieman, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Will, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Will — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>957 ODESSA Drive E, Jacksonville, FL 32254; 9604 WOODLAND Avenue, Jacksonville, FL 32208</t>
+          <t>957 ODESSA Drive E, Jacksonville, FL 32254</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Good day WILLIAM, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi there WILLIAM, Charles here with Paragon Government Solutions. I'm reaching out about 957 ODESSA Drive E, Jacksonville, FL 32254 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3817,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2995 Coleman Rd, Eastover, NC 28312; 6206 Larue Ct, Fayetteville, NC 28303</t>
+          <t>2995 Coleman Rd, Eastover, NC 28312</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>WILLIAM, hi, Charles here with Paragon Government Solutions. I'm reaching out about 2995 Coleman Rd, Eastover, NC 28312; 6206 Larue Ct, Fayetteville, NC 28303 — a cash purchase. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
+          <t>Hello WILLIAM. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2995 Coleman Rd, Eastover, NC 28312. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Good day there, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1700 Grays Inn Rd, Columbia, SC 29210. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day there. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1700 Grays Inn Rd, Columbia, SC 29210 — a cash purchase. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Good day there, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 2412 E MARMORA Street, Phoenix, AZ 85032. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Good day there, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks much!</t>
+          <t>Hey there. Charles here with Paragon Government Solutions, and I'm reaching out about 2737 Bristol Pl, New Orleans, LA 70131 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>there, hi, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
+          <t>Hi there, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Good day there — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
+          <t>Hey there — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hi Aaron, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thank you!</t>
+          <t>Aaron, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 7535 S Vernon Ave, Chicago, IL 60619. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hi there Abe, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Abe, hi, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 12621 Hirst Ave, Cleveland, OH 44135. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Good day Acencion. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 16643 Seawolf Dr, Houston, TX 77062. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi Acencion — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hello Adam, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 15394 Freeland St, Detroit, MI 48227. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Adam, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hey Adam, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Adam, hi — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Adekunle, hi — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
+          <t>Good day Adekunle — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hello Adrian — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Adrian, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hi there Adrian. I'm Charles with Paragon Government Solutions, and I'm reaching out about 15003 Manor St, Detroit, MI 48238 — a cash purchase. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Hey Adrian, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 15003 Manor St, Detroit, MI 48238. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hi Adrienne, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi there Adrienne. Charles here with Paragon Government Solutions, and I'm reaching out about 18402 Revere St, Detroit, MI 48234 — a cash purchase. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hey Alana, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there Alana, this is Charles Pleasant with Paragon Government Solutions. interested in buying 4144 E 120th St, Cleveland, OH 44105 for cash. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hi there Alannah, Charles here with Paragon Government Solutions. I'm reaching out about 1314 Red Ridge Ter, Columbia, SC 29203 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
+          <t>Good day Alannah — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Good day Albert — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Albert, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Good day Alejandro, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Hi Alejandro. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 919 Christine St, Houston, TX 77017. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Hi there Alex, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Alex, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Hello Alex, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 8049 Wetherby St, Detroit, MI 48204. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Alex. I'm Charles with Paragon Government Solutions, and interested in buying 8049 Wetherby St, Detroit, MI 48204 for cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Hello Alex — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi Alex, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hey Alexander, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Alexander, I'm Charles with Paragon Government Solutions. I'm reaching out about 2317 NW 30th Ter, Cape Coral, FL 33993 — a cash purchase. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hey Alexandria — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
+          <t>Alexandria, hi — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Hello Alexis — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Alexis, this is Charles Pleasant with Paragon Government Solutions. interested in buying 17360 Mansfield St, Detroit, MI 48235 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hey Ali, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hey Ali, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hello Ali, this is Charles Pleasant with Paragon Government Solutions. interested in buying 9030 Plainview Ave, Detroit, MI 48228 for cash. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi there Ali, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Hi Alicia. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 4111 Mehalia Dr, Dallas, TX 75241 — a cash purchase. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Alicia. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 4111 Mehalia Dr, Dallas, TX 75241 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Hi there Allie, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hello Allie, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 4737 Kildare Ave, Dallas, TX 75216. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Hi Amanda, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 10323 Sweetbrook Dr, Houston, TX 77038 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
+          <t>Good day Amanda. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 10323 Sweetbrook Dr, Houston, TX 77038. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hi AMANDA, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 1009 Bugle Call Dr, Fayetteville, NC 28314. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
+          <t>Good day AMANDA. I'm Charles with Paragon Government Solutions, and I'm reaching out about 1009 Bugle Call Dr, Fayetteville, NC 28314 — a cash purchase. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Hi there Amani — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Appreciate it!</t>
+          <t>Good day Amani. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 8826 Delilah St, Houston, TX 77033. Could the seller look at a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hi AMBER, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
+          <t>Good day AMBER. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 326 Conifer Dr, Fayetteville, NC 28314. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hi Aminat. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 9404 Pinehaven Dr, Dallas, TX 75227. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
+          <t>Hi there Aminat — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hello Amy, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Hi Amy — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hi there Amy, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2034 Lakeville Dr, Humble, TX 77339 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there Amy, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Hello AMY. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 7092 Pantego Dr, Fayetteville, NC 28314 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
+          <t>AMY, hi. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 7092 Pantego Dr, Fayetteville, NC 28314 for cash. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hi Andre, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 19447 Sunset St, Detroit, MI 48234. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
+          <t>Andre, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 19447 Sunset St, Detroit, MI 48234. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Hey Andrea, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Andrea, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hi there Angel. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 7606 Blessing Ave, Austin, TX 78752. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
+          <t>Hello Angel. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 7606 Blessing Ave, Austin, TX 78752. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Good day Angela, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Angela, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 16 Carroll St, Trenton, NJ 08609 for cash. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Hi there Angela, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 7748 S Langley Ave, Chicago, IL 60619. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi there Angela. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 7748 S Langley Ave, Chicago, IL 60619. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Hello Angela, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 15719 Egret Field Ln, Houston, TX 77049. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Hello Angela. Charles Pleasant, Paragon Government Solutions, and interested in buying 15719 Egret Field Ln, Houston, TX 77049 for cash. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Hey Anthony — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks!</t>
+          <t>Good day Anthony. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 20185 Indiana St, Detroit, MI 48221. Is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Hello Anthony, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Hello Anthony, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Good day Anthony. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 4141 Country Hill Dr, Baton Rouge, LA 70816. Open to a discounted cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
+          <t>Hello Anthony, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 4141 Country Hill Dr, Baton Rouge, LA 70816 — a cash purchase. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hi there ANTHONY, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi there ANTHONY. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 2917 PARR Court E, Jacksonville, FL 32216. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Hello Antisha, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3677 Theodore St, Detroit, MI 48211 — a cash purchase. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
+          <t>Antisha, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 3677 Theodore St, Detroit, MI 48211. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hello ANTOINETTE, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
+          <t>Good day ANTOINETTE — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Good day April — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Much appreciated!</t>
+          <t>Hey April, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 6510 Portsmouth Dr, Fayetteville, NC 28314. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Good day APRYL — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
+          <t>APRYL, hi, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Hello Aram, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 7407 S May St, Chicago, IL 60621. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day Aram, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Hi there Arianna. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 4153 Concord St, Detroit, MI 48207. Could the seller look at a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
+          <t>Hi Arianna, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Hi there Arianne, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 9823 S Drexel Ave, Chicago, IL 60628 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Hi there Arianne, I'm Charles with Paragon Government Solutions. interested in buying 9823 S Drexel Ave, Chicago, IL 60628 for cash. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hi Arkadiusz — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks!</t>
+          <t>Hi Arkadiusz — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Good day ARMANDO — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
+          <t>ARMANDO, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 153 Knapp Ave, Hamilton, NJ 08610. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Hello Asa. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 18310 La Salle Ave, Cleveland, OH 44119 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hello Asa. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 18310 La Salle Ave, Cleveland, OH 44119. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Hey Ashley, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 3879 W 21st St, Cleveland, OH 44109. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Ashley, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3879 W 21st St, Cleveland, OH 44109. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hi Ashley — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Ashley — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Hi there Ashley, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi Ashley — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ashley, hi, I'm Charles with Paragon Government Solutions. interested in buying 19261 Mitchell St, Detroit, MI 48234 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there Ashley, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 19261 Mitchell St, Detroit, MI 48234. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Hello ATIFA — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
+          <t>ATIFA, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Hi Austin, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Austin, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Good day Babajide, Charles Pleasant, Paragon Government Solutions. interested in buying 317 E 134th St, Chicago, IL 60827 for cash. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
+          <t>Hello Babajide, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bailee, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 11144 Sanford St, Detroit, MI 48205. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Appreciate it!</t>
+          <t>Good day Bailee, Charles here with Paragon Government Solutions. I'm reaching out about 11144 Sanford St, Detroit, MI 48205 — a cash purchase. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hello Barbara, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 2336 Albert St, Alexandria, LA 71301. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Hi there Barbara, I'm Charles with Paragon Government Solutions. interested in buying 2336 Albert St, Alexandria, LA 71301 for cash. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Hello BARBARA. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1603 W 14TH Street, Jacksonville, FL 32209. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi BARBARA, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 1603 W 14TH Street, Jacksonville, FL 32209. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Hi there BARD — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thank you!</t>
+          <t>Hello BARD, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 651 W 46TH Street, Jacksonville, FL 32208. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Hi there Becky, this is Charles Pleasant with Paragon Government Solutions. interested in buying 3830 E LAKEWOOD Parkway E #2057, Phoenix, AZ 85048 for cash. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thank you!</t>
+          <t>Hi Becky, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Hey Belle, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day Belle. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 413 Seton Hall Dr, Columbia, SC 29223 — a cash purchase. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Hi Benjamin. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 1005 Wildwood Ave, Columbia, SC 29203. Would the owner entertain a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi there Benjamin. I'm Charles with Paragon Government Solutions, and I'm reaching out about 1005 Wildwood Ave, Columbia, SC 29203 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Hi there Benjamin, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Benjamin — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Hi there Bianca — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thank you!</t>
+          <t>Good day Bianca. I'm Charles with Paragon Government Solutions, and interested in buying 2609 Foerster Ave, Baltimore, MD 21230 for cash. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Blodgie, hi — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks!</t>
+          <t>Blodgie, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Brad, hi. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5765 Kleinpeter Rd, Baton Rouge, LA 70811. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Brad, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Good day Brandon — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks!</t>
+          <t>Good day Brandon, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Hi there Brandon, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 15237 Carlisle St, Detroit, MI 48205. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
+          <t>Brandon, hi. Charles Pleasant, Paragon Government Solutions, and interested in buying 15237 Carlisle St, Detroit, MI 48205 for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Hi Brandt, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Brandt, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Brian, hi. Charles Pleasant, Paragon Government Solutions, and interested in buying 30 Ward Ct, Columbia, SC 29223 for cash. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
+          <t>Hey Brian, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Hi Brian, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 1648 Tampa Bay Dr, Dallas, TX 75217. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
+          <t>Hi there Brian — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hey Brianna — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi Brianna. Charles here with Paragon Government Solutions, and I'm reaching out about 6015 N 32nd Dr, Phoenix, AZ 85017 — a cash purchase. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bridget, hi. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 7522 S Vernon Ave, Chicago, IL 60619. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks so much!</t>
+          <t>Hi Bridget — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hi there BRIGIDA — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day BRIGIDA. Charles Pleasant, Paragon Government Solutions, and interested in buying 156 Washington St, Trenton, NJ 08611 for cash. Open to a discounted cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Good day Brittany — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Brittany, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 7400 Vanderkloot Ave, New Orleans, LA 70127. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Good day Bryton, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Bryton, Charles here with Paragon Government Solutions. I'm a cash investor looking at 8215 Leather Market St, Houston, TX 77064. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hello Camellia — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Camellia, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Hi Carlton, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Hi there Carlton, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Hi there Carly. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 10316 Ridge Oak St, Dallas, TX 75227. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Carly, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 10316 Ridge Oak St, Dallas, TX 75227. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Good day Carmen. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3883 Turtle Creek Blvd #1603, Dallas TX 75219. Open to a discounted cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thank you!</t>
+          <t>Hello Carmen — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Good day Carmen — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
+          <t>Carmen, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Hey Carmen. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 7419 Lake June Rd, Dallas, TX 75217 for cash. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
+          <t>Good day Carmen. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 7419 Lake June Rd, Dallas, TX 75217 — a cash purchase. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Hello Carolinas — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
+          <t>Good day Carolinas, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 4723 Linden St, Columbia, SC 29203. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hi there Carolyn, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 7201 S Vernon Ave, Chicago, IL 60619. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks!</t>
+          <t>Good day Carolyn, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Carolyn, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2755 Palmyra St, New Orleans, LA 70119. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
+          <t>Hello Carolyn, I'm Charles with Paragon Government Solutions. interested in buying 2755 Palmyra St, New Orleans, LA 70119 for cash. Would the owner entertain a cash as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Carolyn, hi. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 6702 Tierwester St, Houston, TX 77021. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day Carolyn, Charles here with Paragon Government Solutions. I'm a cash investor looking at 6702 Tierwester St, Houston, TX 77021. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hey Carrie, this is Charles Pleasant with Paragon Government Solutions. interested in buying 1663 W 30th St, Jacksonville, FL 32209 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi there Carrie — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hello Carrie — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
+          <t>Carrie, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 4243 Mandel Dr, Columbia, SC 29210 — a cash purchase. Is the seller open to a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Hey Caryn — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
+          <t>Caryn, hi, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Hey Casey, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 3414 Maybank St, Columbia, SC 29204. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi there Casey. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 3414 Maybank St, Columbia, SC 29204. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Hi there Casey — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
+          <t>Hey Casey, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 2610 Brandon St, Dallas, TX 75211 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Good day Cassandra. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 314 Capehill Dr, Webster, TX 77598. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Cassandra. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 314 Capehill Dr, Webster, TX 77598. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CATHLEEN, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hello CATHLEEN, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 339 METZ Street, Jacksonville, FL 32211. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Hi CC. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 5418 MINOSA Court, Jacksonville, FL 32209 — a cash purchase. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey CC, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Hello Celia, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Celia — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Hi there Century, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1033 Glencroft Drive, Columbia, SC 29210. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Century. I'm Charles with Paragon Government Solutions, and interested in buying 1033 Glencroft Drive, Columbia, SC 29210 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Hi there Century, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Century — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Cerita, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 528 1st St SW, Birmingham, AL 35211. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Good day Cerita, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 528 1st St SW, Birmingham, AL 35211. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Chad, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Chad, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Hi there Chad. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 4012 Shady Hollow Ln, Dallas, TX 75233. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Chad, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hi there CHARLEEN. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3821 MIRUELO Circle N, Jacksonville, FL 32217. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Hi there CHARLEEN, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Hey Charles — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
+          <t>Hi there Charles, this is Charles Pleasant with Paragon Government Solutions. interested in buying 217 Stockmoor Rd, Columbia, SC 29212 for cash. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Hi Charles, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 334 Carver St, Lafayette, LA 70501 — a cash purchase. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
+          <t>Hi Charles, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 334 Carver St, Lafayette, LA 70501. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Hi there Cherie, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Cherie, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 4731 Stokes St, Dallas, TX 75216 for cash. Could the seller look at a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Hello CHERYL, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hey CHERYL, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Chip, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Chip, Charles Pleasant, Paragon Government Solutions. interested in buying 329 Shagbark Ave, Columbia, SC 29209 for cash. Is the seller open to a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Hey Chip, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Chip — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Chip, hi. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 1905 E Kings Hwy, Shreveport, LA 71105. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
+          <t>Hello Chip — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Hi there Chris, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hello Chris — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Hey Chris — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Much appreciated!</t>
+          <t>Chris, hi — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hey CHRIS, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2332 BUTTONWOOD Drive, Jacksonville, FL 32216 — a cash purchase. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi CHRIS, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Hi Chris, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Good day Chris, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Chris, hi. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 8315 Westbourne Dr, Charlotte, NC 28216. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi Chris. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 8315 Westbourne Dr, Charlotte, NC 28216. Would the owner entertain a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Good day Christina — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Christina, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Hello Christine. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 2633 W Grand Blvd, Detroit, MI 48208 — a cash purchase. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
+          <t>Hi there Christine. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2633 W Grand Blvd, Detroit, MI 48208. Open to a discounted cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CHRISTOPHER, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
+          <t>Hello CHRISTOPHER — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hey Christopher — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Christopher, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 7741 S Chappel Ave, Chicago, IL 60649 for cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Good day Chuck, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 711 S Montclair Ave, Dallas, TX 75208. Open to a discounted cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
+          <t>Hello Chuck. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 711 S Montclair Ave, Dallas, TX 75208. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Cindy, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Cindy — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Cindy, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 11349 S Saint Lawrence Ave, Chicago, IL 60628. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks!</t>
+          <t>Hi Cindy — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Good day Cindy — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello Cindy, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 1703 Alba Dr, Columbia, SC 29209. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Hello Cindy — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Cindy, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 10527 Cayuga Dr, Dallas, TX 75228. Open to a discounted cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Hi Clarence. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 7707 Candlegreen Ln, Houston, TX 77071 — a cash purchase. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Clarence, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Good day Claudia — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Claudia. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 20495 Mendota St, Detroit, MI 48221. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Hello Clay. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1522 W Taylor St, Phoenix, AZ 85007. Is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thank you!</t>
+          <t>Hi there Clay. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1522 W Taylor St, Phoenix, AZ 85007. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Hey Cliff. Charles here with Paragon Government Solutions, and I'm reaching out about 11604 Tuscora Ave, Cleveland, OH 44108 — a cash purchase. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
+          <t>Cliff, hi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 11604 Tuscora Ave, Cleveland, OH 44108. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Good day Coby, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Coby, hi. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 5906 Bower Ave, Cleveland, OH 44127. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Hey Cody, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day Cody, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6348 S Rhodes Ave, Chicago, IL 60637. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Good day Cole. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 417 W Brooklyn Ave, Dallas, TX 75208. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Cole. I'm Charles with Paragon Government Solutions, and interested in buying 417 W Brooklyn Ave, Dallas, TX 75208 for cash. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Hello Colleen, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi Colleen. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3945 Liberty Ave, Pittsburgh, PA 15224. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Hi there Comeiko. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 4971 Brigadoon Ln, Dallas, TX 75216. Would the owner entertain a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello Comeiko, this is Charles Pleasant with Paragon Government Solutions. interested in buying 4971 Brigadoon Ln, Dallas, TX 75216 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Compass, hi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1011 Ormewood Ave SE, Atlanta, GA 30316. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Hi there Compass. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 1011 Ormewood Ave SE, Atlanta, GA 30316. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Hey Connie — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Connie — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Good day Conor, Charles here with Paragon Government Solutions. I'm reaching out about 937 Avenue S, Birmingham, AL 35214 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
+          <t>Conor, hi, Charles here with Paragon Government Solutions. I'm a cash investor looking at 937 Avenue S, Birmingham, AL 35214. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Hi there Corey, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 3503 Oakmont Ave, Baltimore, MD 21215 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi there Corey, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Corey, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 16410 Novara St, Detroit, MI 48205 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thank you!</t>
+          <t>Hey Corey. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 16410 Novara St, Detroit, MI 48205. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Hello Cory, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5747 Easthampton Dr Unit D, Houston, TX 77039. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Cory, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 5747 Easthampton Dr Unit D, Houston, TX 77039. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Hey Crystal. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 4010 Copeland St, Dallas, TX 75210. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello Crystal. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 4010 Copeland St, Dallas, TX 75210. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Hello Crystal. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 5201 W Camelback Rd Lot A174, Phoenix, AZ 85031. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
+          <t>Hey Crystal, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 5201 W Camelback Rd Lot A174, Phoenix, AZ 85031. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Hello CYNDI, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>CYNDI, hi. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1722 Berriedale Dr, Fayetteville, NC 28304. Is the seller open to a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Hello D.R., this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about Ledoux Plan, Trivento, Baker, LA 70714 — a cash purchase. Open to a discounted cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day D.R. — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Good day D.R., Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day D.R., my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Daisy, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 4534 S Honore St, Chicago, IL 60609. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Daisy, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dan, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Hello Dan, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1401 Kirby St NE, Albuquerque, NM 87112 — a cash purchase. Is the seller open to a cash as-is offer, close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>DANA, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 8064 KILWINNING Lane, Jacksonville, FL 32244 — a cash purchase. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi DANA, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Good day Dana — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks!</t>
+          <t>Good day Dana. I'm Charles with Paragon Government Solutions, and interested in buying 11831 Bee Ln, Houston, TX 77067 for cash. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Hi DANIEL, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5050 SAN JUAN Avenue, Jacksonville, FL 32210. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
+          <t>DANIEL, hi — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>DANIEL, hi. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 22 MONTE Street, Jacksonville, FL 32254. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
+          <t>DANIEL, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Hey Daniel — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
+          <t>Daniel, hi, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>DANIELE, hi, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi DANIELE. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1494 8TH Street W, Jacksonville, FL 32209 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Hi Danielle, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 18281 Lancashire St, Detroit, MI 48223. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Danielle. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 18281 Lancashire St, Detroit, MI 48223 — a cash purchase. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Hello DANYELLE, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Hi there DANYELLE, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Darius, hi — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Darius, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1825 N 17th St, Baton Rouge, LA 70802. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Hey Darrin. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3507 E SANDRA Terrace, Phoenix, AZ 85032. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Hi there Darrin, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Hey Darryl, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 7809 Capitol St, Houston, TX 77012. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi there Darryl, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Good day Darryl — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks so much!</t>
+          <t>Hello Darryl, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 19151 Rowe St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Darryl, hi — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
+          <t>Darryl, hi — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Darryn, hi. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 15870 W Parkway St, Detroit, MI 48223. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
+          <t>Good day Darryn — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Daryl, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Daryl. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 20520 Dresden St, Detroit, MI 48205. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Hi there David, I'm Charles with Paragon Government Solutions. interested in buying 116 Larchwood Dr, Columbia, SC 29203 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks so much!</t>
+          <t>Good day David. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 116 Larchwood Dr, Columbia, SC 29203. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>David, hi. I'm Charles with Paragon Government Solutions, and I'm reaching out about 11905 Shadeland Ave, Cleveland, OH 44108 — a cash purchase. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Good day David. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 11905 Shadeland Ave, Cleveland, OH 44108. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Hello David — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
+          <t>Hello David — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Hi David. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 6 Crescent Ln, Columbia, SC 29212. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
+          <t>Hi there David — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Hi there David, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Hi David, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Hey David. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 2631 Mike St, Dallas, TX 75212. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there David — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Hi David. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 19182 Hickory St, Detroit, MI 48205. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there David, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>DAVID, hi. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 311 Glen Canyon Dr, Fayetteville, NC 28303. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>Good day DAVID — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Good day Dayton, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Dayton, hi. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 6338 Firestone Pkwy, San Antonio, TX 78244. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>De'Chella, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 3309 E 146th St, Cleveland, OH 44120. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
+          <t>Hey De'Chella, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3309 E 146th St, Cleveland, OH 44120. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Hi Dean — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Dean — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Hi Deanna. I'm Charles with Paragon Government Solutions, and interested in buying 1811 Reynoldston Ln, Dallas, TX 75232 for cash. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Deanna, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1811 Reynoldston Ln, Dallas, TX 75232. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Hello Debbie, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi Debbie — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Hello Deborah. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 10147 S State St, Chicago, IL 60628 — a cash purchase. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
+          <t>Deborah, hi — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Hi DEIRDRA, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6818 MERRILL Court, Jacksonville, FL 32211. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi DEIRDRA, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 6818 MERRILL Court, Jacksonville, FL 32211. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Good day Demetria, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi Demetria, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Hey Dena, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 301 Squire Rd, Columbia, SC 29223 — a cash purchase. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
+          <t>Hey Dena, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Hey Denise, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 7613 Parker Rd, Houston, TX 77016. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
+          <t>Hey Denise, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Hello DENISE — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
+          <t>Hi there DENISE — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Good day Deven. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 7700 S Lowe Ave, Chicago, IL 60620. Would the owner entertain a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
+          <t>Good day Deven, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Hello DEXTER, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
+          <t>Good day DEXTER, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Hey Dexter. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 639 E 90th Pl, Chicago, IL 60619. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
+          <t>Hi Dexter, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 639 E 90th Pl, Chicago, IL 60619. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Hey Diana — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thank you!</t>
+          <t>Good day Diana, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Hi Diane. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 2024 Elmridge Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Hello Diane. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2024 Elmridge Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Hello DMITRIY — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
+          <t>DMITRIY, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Hi there Don, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 13159 Todd Ave, Baton Rouge, LA 70815. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day Don, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 13159 Todd Ave, Baton Rouge, LA 70815. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Hello Donna, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hey Donna, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 8529 S May St, Chicago, IL 60620. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Hi there Donnie — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Donnie — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Good day Doreen — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
+          <t>Hello Doreen, this is Charles Pleasant with Paragon Government Solutions. interested in buying 3506 Rosedale Rd, Baltimore, MD 21215 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Hi Douglas, I'm Charles with Paragon Government Solutions. I'm reaching out about 7111 Bart Hollow, San Antonio, TX 78250 — a cash purchase. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Douglas — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Doxie, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 987 E 129th St, Cleveland, OH 44108. Would the owner entertain a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Doxie — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Hi there Dr, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Dr. Charles Pleasant, Paragon Government Solutions, and interested in buying 7909 Sagebrook Rd, Columbia, SC 29223 for cash. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Hey Drew — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
+          <t>Good day Drew, I'm Charles with Paragon Government Solutions. interested in buying 4137 W 157th St, Cleveland, OH 44135 for cash. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Hi Dulcey. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 18011 Windward Rd, Cleveland, OH 44119. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi there Dulcey. I'm Charles with Paragon Government Solutions, and I'm reaching out about 18011 Windward Rd, Cleveland, OH 44119 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Hi Dustin, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Dustin, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Hi there DWAYNE, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day DWAYNE. Charles here with Paragon Government Solutions, and interested in buying 5919 SONORA Drive W, Jacksonville, FL 32244 for cash. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Hey Ebony, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Good day Ebony. Charles here with Paragon Government Solutions, and interested in buying 3237 W 30th St, Cleveland, OH 44109 for cash. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Edgardo, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 7949 S Manistee Ave, Chicago, IL 60617. Would the owner entertain a cash as-is offer, quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hey Edgardo, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 7949 S Manistee Ave, Chicago, IL 60617 — a cash purchase. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Hello Eduardo, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5223 Heathercrest St, Houston, TX 77045. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
+          <t>Eduardo, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 5223 Heathercrest St, Houston, TX 77045. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Hello Eduardo, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hello Eduardo — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Good day Edward, I'm Charles with Paragon Government Solutions. interested in buying 217 S Shields Rd, Columbia, SC 29223 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
+          <t>Hello Edward. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 217 S Shields Rd, Columbia, SC 29223 — a cash purchase. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Edward, hi. Charles here with Paragon Government Solutions, and I'm reaching out about 6633 Sandstone St, Houston, TX 77074 — a cash purchase. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>Good day Edward, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 6633 Sandstone St, Houston, TX 77074. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Edward, hi, Charles here with Paragon Government Solutions. interested in buying 13 Winding Way, Trenton, NJ 08620 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
+          <t>Edward, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 13 Winding Way, Trenton, NJ 08620. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Hey Edwin, Charles Pleasant, Paragon Government Solutions. interested in buying 19338 Teppert St, Detroit, MI 48234 for cash. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
+          <t>Hi Edwin. Charles here with Paragon Government Solutions, and interested in buying 19338 Teppert St, Detroit, MI 48234 for cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Hello Eileen, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Eileen, hi — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Hi there ELISABETH — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
+          <t>Hey ELISABETH, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Hey Elizabeth, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1356 W 112th St, Cleveland, OH 44102. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
+          <t>Good day Elizabeth, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Elizabeth, hi. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5308 Foxfire Road, Fayetteville, NC 28303. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
+          <t>Hi Elizabeth — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Hey Elizabeth, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Elizabeth — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Good day ELLEN. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5051 LEXINGTON Avenue, Jacksonville, FL 32210. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there ELLEN, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Hi there Elliot. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 7901 New York Ave, Cleveland, OH 44105. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks!</t>
+          <t>Hi there Elliot. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 7901 New York Ave, Cleveland, OH 44105. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Hello Emil, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hey Emil — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Hi ERIC, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>ERIC, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Erick, hi — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Erick. Charles here with Paragon Government Solutions, and interested in buying 18710 McCormick St, Detroit, MI 48224 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Esmeralda, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there Esmeralda — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Good day Eve — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Appreciate it!</t>
+          <t>Hey Eve. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 11224 S Stewart Ave, Chicago, IL 60628. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Hi EXP, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2012 Bolt Dr, Anderson, SC 29621. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there EXP, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 2012 Bolt Dr, Anderson, SC 29621. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Fadie, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 6324 Annland St, Detroit, MI 48204. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there Fadie — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Fany, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 5935 Glenhurst Dr, Houston, TX 77033 — a cash purchase. Would the seller consider a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thank you!</t>
+          <t>Hey Fany — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Hello Felicia, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6953 S Elizabeth St, Chicago, IL 60636. Open to a discounted cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Good day Felicia — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Good day Floyd. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 6525 Palm Island St, Dallas, TX 75241. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
+          <t>Hello Floyd, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 6525 Palm Island St, Dallas, TX 75241. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Hi there Francisco. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 921 S 3RD Avenue, Phoenix, AZ 85003. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Francisco, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 921 S 3RD Avenue, Phoenix, AZ 85003. Is the seller open to a cash as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Hey Francisco. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 11432 S Wentworth Ave, Chicago, IL 60628. Is the seller open to a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Francisco, hi. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 11432 S Wentworth Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Good day Francys, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 18433 Norwood St, Detroit, MI 48234. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thank you!</t>
+          <t>Hi Francys. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 18433 Norwood St, Detroit, MI 48234. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Hey Frank. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 10471 Nottingham Rd, Detroit, MI 48224. Open to a discounted cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there Frank, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Hello Frank, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hello Frank, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Hey Frank — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks!</t>
+          <t>Hey Frank. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 7800 S Kimbark Ave, Chicago, IL 60619. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Hello Frederick, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks!</t>
+          <t>Frederick, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 818 Winters St, Dallas, TX 75216. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Hey Funmi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Funmi, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 8745 S Euclid Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Hi Gabe. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 9601 Silk Ave, Cleveland, OH 44102. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Hey Gabe — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Hi there GABRIELA, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
+          <t>Good day GABRIELA, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Hi there Gabrielle, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 203 May Oak Rd, Columbia, SC 29229. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi there Gabrielle, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 203 May Oak Rd, Columbia, SC 29229. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Good day GARY — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
+          <t>Hey GARY, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Good day Gaymon. Charles here with Paragon Government Solutions, and interested in buying 113 Salusbury Ln, Columbia, SC 29229 for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
+          <t>Gaymon, hi, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 113 Salusbury Ln, Columbia, SC 29229. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Hey Genaro. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 8525 Oak Haven Ln, Dallas, TX 75217. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
+          <t>Hey Genaro — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Hi Gene — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Gene. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 192 Dunham Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Hey Geraldine, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Geraldine. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 16779 Greenview Ave, Detroit, MI 48219 — a cash purchase. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Gerielynn, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 16770 Greenlawn St, Detroit, MI 48221 — a cash purchase. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Appreciate it!</t>
+          <t>Gerielynn, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 16770 Greenlawn St, Detroit, MI 48221. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Good day Gerilet — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
+          <t>Hi Gerilet. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 5147 BROKEN ARROW Drive N, Jacksonville, FL 32244. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Hello Gershon — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
+          <t>Hi there Gershon, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Hi Gina. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2640 Ridgely St, Baltimore, MD 21230. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
+          <t>Gina, hi, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 2640 Ridgely St, Baltimore, MD 21230. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Good day Gino, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 78 Liberty St, Trenton, NJ 08611. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Gino, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Hi there Gladys — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Gladys — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Hello Glen — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day Glen. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 3194 W 95th St, Cleveland, OH 44102. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Hi GLEN. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 8456 BOYSENBERRY Lane W, Jacksonville, FL 32244. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey GLEN. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 8456 BOYSENBERRY Lane W, Jacksonville, FL 32244. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Hi there Gonzalo, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Gonzalo — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Hey Gracie, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Gracie, hi. Charles Pleasant, Paragon Government Solutions, and interested in buying 2628 Marfa Ave, Dallas, TX 75216 for cash. Open to a discounted cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Hi there Gracie, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hey Gracie, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 4015 Shadrack Dr, Dallas, TX 75212. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Hello Grant, Charles here with Paragon Government Solutions. interested in buying 1709 Jeffrey Bryan Dr, Charlotte, NC 28213 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
+          <t>Hi there Grant, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1709 Jeffrey Bryan Dr, Charlotte, NC 28213. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Hey Grazyna, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 3709 W 66th Pl, Chicago, IL 60629. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Good day Grazyna. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3709 W 66th Pl, Chicago, IL 60629. Could the seller look at a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Hi Greg. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1033 Kern St, Bakersfield, CA 93305. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi Greg, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1033 Kern St, Bakersfield, CA 93305. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Gregory, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 10535 S Peoria St, Chicago, IL 60643 for cash. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
+          <t>Hey Gregory — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Gregory, hi. I'm Charles with Paragon Government Solutions, and I'm reaching out about 19358 Teppert St, Detroit, MI 48234 — a cash purchase. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hello Gregory, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 19358 Teppert St, Detroit, MI 48234. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Hello Guillermo, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 14810 Walters Rd, Houston, TX 77068 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
+          <t>Hi there Guillermo, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 14810 Walters Rd, Houston, TX 77068. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Gwendolyn, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Gwendolyn — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10372,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Hi HALEY, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
+          <t>HALEY, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Hi Hannah, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 232 Fernview Dr, Columbia, SC 29229. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hannah, hi, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Hi there Hannah — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi there Hannah. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 3834 Shelley Blvd, Dallas, TX 75211. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Hey Harold, Charles here with Paragon Government Solutions. I'm a cash investor looking at 2012 Lmridge Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Harold — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Hey Harry. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 9432 S Bishop St, Chicago, IL 60620. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Harry. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 9432 S Bishop St, Chicago, IL 60620. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Hey Hassan, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hassan, hi, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Heather, hi, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Heather, hi, Charles here with Paragon Government Solutions. I'm a cash investor looking at 2000 Elmridge Rd, Columbia, SC 29209. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Hi there Heather. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 5235 Cumberland Cove Dr, Baton Rouge, LA 70817. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hey Heather, Charles here with Paragon Government Solutions. interested in buying 5235 Cumberland Cove Dr, Baton Rouge, LA 70817 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Hi Heather, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 6040 W Perimeter Dr, Baton Rouge, LA 70811. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Heather, hi. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 6040 W Perimeter Dr, Baton Rouge, LA 70811. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Hey Heather — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Heather — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Hey Hector, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hector, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 8910 N 10TH Street, Phoenix, AZ 85020. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>HENRY, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 27 W 44TH Street, Jacksonville, FL 32208 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there HENRY, Charles Pleasant, Paragon Government Solutions. interested in buying 27 W 44TH Street, Jacksonville, FL 32208 for cash. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Henry, hi — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi Henry, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Hey Hermel — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
+          <t>Hello Hermel, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Hi Hilda. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 1401 El Sereno Dr, Bakersfield, CA 93304. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey Hilda, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1401 El Sereno Dr, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Good day Ian, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Hello Ian, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Ijella, hi — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
+          <t>Hi there Ijella — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Hello Ingrid. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 842 Meridian Ave, Lakeland, FL 33801. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
+          <t>Hi there Ingrid — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Hello IRAN, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2501 DOBY Street, Jacksonville, FL 32209. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there IRAN — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Good day Iris, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 189 Mercer St, Hamilton, NJ 08690 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day Iris — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Hello Isabella, Charles here with Paragon Government Solutions. I'm a cash investor looking at 2304 Pelican Dr, Columbia, SC 29203. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
+          <t>Good day Isabella, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Hey Jack, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 905 Ann Ave, Dallas, TX 75223. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks!</t>
+          <t>Hello Jack, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Hi there Jacob, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 17360 Greenlawn St, Detroit, MI 48221 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
+          <t>Jacob, hi, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 17360 Greenlawn St, Detroit, MI 48221 for cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Hi there JACOBE, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi JACOBE, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 2146 LOUISE Street, Jacksonville, FL 32206. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Hi Jalisa, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3431 Sayers St, Houston, TX 77026. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thank you!</t>
+          <t>Good day Jalisa — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Hey Jamehia — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks so much!</t>
+          <t>Jamehia, hi, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 12807 Crystal Cove Dr, Houston, TX 77044. Is the seller open to a cash as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Hi there JAMES, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 6528 MITFORD Road, Jacksonville, FL 32210. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hey JAMES. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 6528 MITFORD Road, Jacksonville, FL 32210. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Hi JAMES, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi there JAMES, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2203 SHERRINGTON Street, Jacksonville, FL 32209 for cash. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Hello James — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
+          <t>Hi James. Charles here with Paragon Government Solutions, and I'm reaching out about 9433 S Michigan Ave, Chicago, IL 60619 — a cash purchase. Open to a discounted cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>James, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks!</t>
+          <t>Hello James, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Hey James — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi James. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 9261 Camley St, Detroit, MI 48224. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Hi JAMES, I'm Charles with Paragon Government Solutions. I'm reaching out about 736 Tobermory Rd, Fayetteville, NC 28306 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
+          <t>Good day JAMES, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 736 Tobermory Rd, Fayetteville, NC 28306. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Hello Jami. Charles here with Paragon Government Solutions, and interested in buying 10339 Limestone Dr, Dallas, TX 75217 for cash. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks much!</t>
+          <t>Good day Jami — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Hello Jamie, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 3010 Hartwick Rd, Houston, TX 77093. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Jamie, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 3010 Hartwick Rd, Houston, TX 77093. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Hey Jamie. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 2229 W 60th St, Indianapolis, IN 46228 — a cash purchase. Would the owner entertain a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
+          <t>Good day Jamie — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Hi there Jamila. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 12607 Oakfield Ave, Cleveland, OH 44105 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi there Jamila, Charles here with Paragon Government Solutions. I'm a cash investor looking at 12607 Oakfield Ave, Cleveland, OH 44105. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Good day Janina — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Janina. Charles here with Paragon Government Solutions, and I'm reaching out about 7324 S Blackstone Ave, Chicago, IL 60619 — a cash purchase. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Hi there Jasmin — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
+          <t>Hello Jasmin — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Jasmine, hi, Charles here with Paragon Government Solutions. I'm reaching out about 6433 S Talman Ave, Chicago, IL 60629 — a cash purchase. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
+          <t>Good day Jasmine, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6433 S Talman Ave, Chicago, IL 60629. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Hey Jason. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1009 Poplar Grove St, Baltimore, MD 21216. Open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Jason. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 1009 Poplar Grove St, Baltimore, MD 21216. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Hello Jason — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks!</t>
+          <t>Hello Jason, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 5732 Wood Dr SW, Albuquerque, NM 87105. Open to a discounted cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Hi Jason. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 2600 Brookside Dr APT 41, Bakersfield, CA 93311. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Jason, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2600 Brookside Dr APT 41, Bakersfield, CA 93311 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Hey Jason. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 106 N Briscoe Blvd, Dallas, TX 75211. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hey Jason, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 106 N Briscoe Blvd, Dallas, TX 75211. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Hi Jason. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1921 W WHITTON Avenue, Phoenix, AZ 85015. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
+          <t>Hello Jason, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1921 W WHITTON Avenue, Phoenix, AZ 85015. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Hi Jay. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 19300 Berg Rd, Detroit, MI 48219. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
+          <t>Good day Jay. I'm Charles with Paragon Government Solutions, and I'm reaching out about 19300 Berg Rd, Detroit, MI 48219 — a cash purchase. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Hello Jay, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 4909 Falls St, Houston, TX 77026. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey Jay, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 4909 Falls St, Houston, TX 77026. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Hello JC. I'm Charles with Paragon Government Solutions, and interested in buying 5009 W Chicago Ave, Chicago, IL 60651 for cash. Would the seller consider a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello JC, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 5009 W Chicago Ave, Chicago, IL 60651. Open to a discounted cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Hi there JD. Charles here with Paragon Government Solutions, and interested in buying 6810 Satchel Ford Rd, Columbia, SC 29206 for cash. Is the seller open to a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi JD, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6810 Satchel Ford Rd, Columbia, SC 29206. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Hi there Jean, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 10032 S Calumet Ave, Chicago, IL 60628. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Much appreciated!</t>
+          <t>Good day Jean. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 10032 S Calumet Ave, Chicago, IL 60628. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Hi there Jeff, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3218 College St, Slidell, LA 70458 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day Jeff. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 3218 College St, Slidell, LA 70458. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Hi Jeff, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi Jeff. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 116 Clay Ridge Rd, Columbia, SC 29223 — a cash purchase. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Good day Jeffrey, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 109 Kingston Trace Rd, Columbia, SC 29229. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi there Jeffrey. I'm Charles with Paragon Government Solutions, and I'm reaching out about 109 Kingston Trace Rd, Columbia, SC 29229 — a cash purchase. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Good day Jeffrey, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks!</t>
+          <t>Hi there Jeffrey, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 4137 Shorecrest Dr, Columbia, SC 29209. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Jeffrey, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Good day Jeffrey. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 8622 Othello St, Houston, TX 77029. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Good day Jeffrey. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 3196 W 116th St, Cleveland, OH 44111. Is the seller open to a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks so much!</t>
+          <t>Jeffrey, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>Hi there JELISSA, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there JELISSA, Charles here with Paragon Government Solutions. interested in buying 4173 DAVIE Court, Jacksonville, FL 32210 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Good day JENNIFER, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello JENNIFER. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 9720 STEAD Court, Jacksonville, FL 32221 for cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Jennifer, hi. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 618 E 89th St, Chicago, IL 60619. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
+          <t>Good day Jennifer. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 618 E 89th St, Chicago, IL 60619. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Jenny, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 1639 Mustang Canyon Way, Houston, TX 77049 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Good day Jenny, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1639 Mustang Canyon Way, Houston, TX 77049. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Jenya, hi — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Jenya. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 1075 Belmont Green Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Hey Jerelyn — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
+          <t>Hi there Jerelyn. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 409 Sheridan Dr, Columbia, SC 29223. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Hi Jerry. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 3012 Skyview Dr, Lakeland, FL 33801. Is the seller open to a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
+          <t>Hey Jerry, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 3012 Skyview Dr, Lakeland, FL 33801. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Hey Jesse, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1037 Lexington St, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
+          <t>Good day Jesse, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1037 Lexington St, Lakeland, FL 33801 — a cash purchase. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>Hello Jesse — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
+          <t>Hi Jesse, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 33 Heritage Village Ln, Columbia, SC 29212. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Hi Jessica — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Jessica. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 3929 Trotter Rd, Columbia, SC 29209. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Hi there Jessica — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks so much!</t>
+          <t>Good day Jessica, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 8752 Woodcastle Dr, Dallas, TX 75217 — a cash purchase. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Hi Jessica. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1521 Hamilton Ave, Hamilton, NJ 08629. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi Jessica, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Hi Jessica, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 5250 Alter Rd, Detroit, MI 48224. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi there Jessica, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>Hello JESSICA, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 994 Wayside Rd, Fayetteville, NC 28314. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Good day JESSICA — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Jill, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Jill, hi, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Hi Jim, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 5303 S Winchester Ave, Chicago, IL 60609. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
+          <t>Hello Jim. Charles Pleasant, Paragon Government Solutions, and interested in buying 5303 S Winchester Ave, Chicago, IL 60609 for cash. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>Hi Jimish — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day Jimish, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 8443 S Manistee Ave, Chicago, IL 60617. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>Hey Jimmy — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
+          <t>Jimmy, hi, Charles here with Paragon Government Solutions. interested in buying 8101 Howard Dr, Houston, TX 77017 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>Good day JoAnn — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
+          <t>Good day JoAnn, Charles here with Paragon Government Solutions. I'm reaching out about 16503 Wisconsin St, Detroit, MI 48221 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Joe, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
+          <t>Good day Joe. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in Lots 23-25 Cargill St, Houston, TX 77029. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Hi there Joel — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
+          <t>Hello Joel. Charles Pleasant, Paragon Government Solutions, and interested in buying 12126 Garner Mill Ln, Houston, TX 77089 for cash. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Good day Joel — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
+          <t>Hi there Joel. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 6502 Leedale St, Houston, TX 77016. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Good day Joey, this is Charles Pleasant with Paragon Government Solutions. interested in buying 8614 Fringewood Dr, Houston, TX 77028 for cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Joey — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Hello John — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
+          <t>Hello John — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>Hello John, I'm Charles with Paragon Government Solutions. interested in buying 4386 W 48th St, Cleveland, OH 44144 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hey John, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 4386 W 48th St, Cleveland, OH 44144. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>Hi there John — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
+          <t>Hello John — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>Hi there John, this is Charles Pleasant with Paragon Government Solutions. interested in buying 10431 Kinslow Dr, Dallas, TX 75217 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Good day John. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 10431 Kinslow Dr, Dallas, TX 75217. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Good day John. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 169 Fox Grove Cir, Columbia, SC 29229 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks much!</t>
+          <t>Hello John, this is Charles Pleasant with Paragon Government Solutions. interested in buying 169 Fox Grove Cir, Columbia, SC 29229 for cash. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Hello John, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there John — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>John, hi, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on Leadmine Rd, Gaffney, SC 29340. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey John — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Hey JOHN, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3554 BROCKWAY Road, Jacksonville, FL 32250. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
+          <t>Hi there JOHN. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 3554 BROCKWAY Road, Jacksonville, FL 32250. Open to a discounted cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Hi Johnny. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 9016 Harris Ave, Cleveland, OH 44104. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there Johnny, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>Hello JON — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
+          <t>Hi JON — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Hi there Jonathan, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 4329 S Wood St, Chicago, IL 60609. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day Jonathan, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Hello Jonathan, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hello Jonathan. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 18866 Hull Ave, Detroit, MI 48203. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Good day Jose, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Jose. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 9137 Meyers Rd, Detroit, MI 48228 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Jose, hi, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hey Jose, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Hi there Jose — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Jose — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Hi Joseph — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
+          <t>Hi there Joseph — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Hello JOSEPH — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks!</t>
+          <t>Hi JOSEPH, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12752,7 +12752,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Hi Joseph, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Hi Joseph, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Hey JOSEPH — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks!</t>
+          <t>Good day JOSEPH. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1334 W 32ND Street, Jacksonville, FL 32209. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Hey Joshua. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2021 Morninglo Ln, Columbia, SC 29223. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi Joshua, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 2021 Morninglo Ln, Columbia, SC 29223. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Good day Joshua — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks!</t>
+          <t>Hello Joshua, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 3403 Alabama Ave, Dallas, TX 75216. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Hey Joshua — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hello Joshua, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Good day Joy — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Much appreciated!</t>
+          <t>Hi Joy, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 2138 Minnesota St, Baton Rouge, LA 70802. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>JOYOUS, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
+          <t>Hey JOYOUS — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Good day Ju'Vonne, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1523 E Nevada St, Detroit, MI 48203 — a cash purchase. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Ju'Vonne, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 1523 E Nevada St, Detroit, MI 48203 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Hi there Juanita, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Juanita, hi — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Hello Judith, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 12125 Angelus Ave, Cleveland, OH 44105. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day Judith. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 12125 Angelus Ave, Cleveland, OH 44105 for cash. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Hi Judith — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Judith, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 306 SW 29th St, Cape Coral, FL 33914. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Hi there Juliana. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 155 Locust Ave W, Hamilton, NJ 08610 for cash. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
+          <t>Good day Juliana, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 155 Locust Ave W, Hamilton, NJ 08610. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Hello Julie, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 178 Vermillion Dr, Columbia, SC 29209 — a cash purchase. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks so much!</t>
+          <t>Hey Julie. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 178 Vermillion Dr, Columbia, SC 29209. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13077,7 +13077,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Good day Julio — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
+          <t>Hey Julio — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>Hi Justin — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Appreciate it!</t>
+          <t>Hey Justin. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 1246 Junction St, Detroit, MI 48209. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Hi there Justin. I'm Charles with Paragon Government Solutions, and I'm reaching out about 4701 Morris St NE APT 2604, Albuquerque, NM 87111 — a cash purchase. Would the seller consider a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Justin, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Hey Justine, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 3309 Crownover St, Austin, TX 78725. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Justine — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Good day KALICA. Charles here with Paragon Government Solutions, and interested in buying 2846 YELLOW PINE Drive, Jacksonville, FL 32277 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey KALICA — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Hey Kara, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Kara, hi. Charles here with Paragon Government Solutions, and interested in buying 846 W Carole St, Lakeland, FL 33803 for cash. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Hey Karelin. I'm Charles with Paragon Government Solutions, and I'm reaching out about 4535 W 157th St, Cleveland, OH 44135 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Karelin, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 4535 W 157th St, Cleveland, OH 44135. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Hey Karen, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello Karen, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 226 Curvewood Rd, Columbia, SC 29229. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Good day Karen, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1040 Kentucky St SE, Albuquerque, NM 87108 — a cash purchase. Would the seller consider a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks so much!</t>
+          <t>Good day Karen, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Hello KAREN, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks much!</t>
+          <t>Hey KAREN, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 6929 ROLLO Road, Jacksonville, FL 32205. Open to a discounted cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Hi there Karina, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 4030 W MARICOPA Street, Phoenix, AZ 85009. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
+          <t>Good day Karina — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Good day Karina. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 7641 Delavan Dr, Houston, TX 77028 for cash. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi Karina — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Good day Karla, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 11827 Gaston Pkwy, Dallas, TX 75218. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks much!</t>
+          <t>Hi Karla. I'm Charles with Paragon Government Solutions, and interested in buying 11827 Gaston Pkwy, Dallas, TX 75218 for cash. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Karmen, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 10210 S Prairie Ave, Chicago, IL 60628. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Good day Karmen, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 10210 S Prairie Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Kashmir, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 7305 Tremper St, Houston, TX 77020 — a cash purchase. Open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Kashmir. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 7305 Tremper St, Houston, TX 77020. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Hi Katie, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Katie, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Hi there Katy, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Katy. Charles Pleasant, Paragon Government Solutions, and interested in buying 2319 Kathleen Ave, Dallas, TX 75216 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Keith, hi. Charles here with Paragon Government Solutions, and I'm reaching out about 112 Willow Branch Dr, West Monroe, LA 71291 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Keith, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 112 Willow Branch Dr, West Monroe, LA 71291 — a cash purchase. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Hi KEITH, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi KEITH, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 4507 TRENTON Drive S, Jacksonville, FL 32209. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13552,7 +13552,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Hey Kelley, I'm Charles with Paragon Government Solutions. I'm reaching out about 1630 E ADAMS Street, Phoenix, AZ 85034 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
+          <t>Good day Kelley — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Hello Kelly — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Kelly, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 11825 Rosemary St N, Detroit, MI 48213 — a cash purchase. Open to a discounted cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Hello Keneitra, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 109 Christian St, Columbia, SC 29203 — a cash purchase. Is the seller open to a cash as-is offer, fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Keneitra, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Good day Kenisha. I'm Charles with Paragon Government Solutions, and I'm reaching out about 2324 Alpine Rd, Columbia, SC 29223 — a cash purchase. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thank you!</t>
+          <t>Good day Kenisha. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 2324 Alpine Rd, Columbia, SC 29223 — a cash purchase. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Hi there KENNETH, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1113 Branson St, Fayetteville, NC 28305. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey KENNETH. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 1113 Branson St, Fayetteville, NC 28305 for cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>Hello Kerry. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 1065 Blanchard Pl, Shreveport, LA 71104. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi Kerry. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 1065 Blanchard Pl, Shreveport, LA 71104 for cash. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Hey KEVIN — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks so much!</t>
+          <t>Hi KEVIN. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 7321 Tollhouse Dr, Fayetteville, NC 28314 — a cash purchase. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Hi Kevin — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
+          <t>Kevin, hi. I'm Charles with Paragon Government Solutions, and I'm reaching out about 6127 Pontotoc St, Baton Rouge, LA 70812 — a cash purchase. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>Kevin, hi — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Kevin. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1223 Harvey St, Columbia, SC 29201. Open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Hey Kevin. Charles Pleasant, Paragon Government Solutions, and interested in buying 11632 Laing St, Detroit, MI 48224 for cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
+          <t>Kevin, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>Khaula, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Khaula, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 3718 Barbara Ave, Bakersfield, CA 93309. Could the seller look at a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Good day Kim. Charles here with Paragon Government Solutions, and I'm reaching out about 3428 W Banff Ln, Phoenix, AZ 85053 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thank you!</t>
+          <t>Hello Kim — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>KIM, hi, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello KIM, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 752 ACOSTA Street, Jacksonville, FL 32204. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Hi Kim. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 3338 Taylor St, Detroit, MI 48206. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Kim, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Hi Kimberley. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 20 Doreen Rd, Hamilton, NJ 08690 for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
+          <t>Hello Kimberley — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Hey Kimberly, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi Kimberly. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 2056 Persimmon Ct, Cincinnati, OH 45231 for cash. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Good day Kimberly, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Good day Kimberly, Charles here with Paragon Government Solutions. I'm a cash investor looking at 204 Philip St, Detroit, MI 48215. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Hey Kira — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Kira — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Good day Kodee, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 311 Lockner Rd, Columbia, SC 29212. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Kodee, Charles here with Paragon Government Solutions. interested in buying 311 Lockner Rd, Columbia, SC 29212 for cash. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Good day KONT — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
+          <t>Hello KONT. I'm Charles with Paragon Government Solutions, and I'm reaching out about 4104 LEONARD Circle E, Jacksonville, FL 32209 — a cash purchase. Open to a discounted cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Hello Koty — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Koty, Charles here with Paragon Government Solutions. interested in buying 1208 31st St SW, Birmingham, AL 35221 for cash. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Hi Kristen, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Kristen, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 12018 Texana Cv, San Antonio, TX 78253. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Hi Kristi, Charles here with Paragon Government Solutions. interested in buying 12966 Trail Hollow Dr #2960, Houston, TX 77079 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
+          <t>Good day Kristi, Charles here with Paragon Government Solutions. I'm reaching out about 12966 Trail Hollow Dr #2960, Houston, TX 77079 — a cash purchase. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Hello Kristian — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
+          <t>Hello Kristian, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 4114 Averill St, Houston, TX 77009. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Hello Kristofer — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks!</t>
+          <t>Good day Kristofer, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Kya, hi, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Kya, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5505 Hamlet Ave, Baltimore, MD 21214. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>KYLE, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 725 W 16 Street, Jacksonville, FL 32206. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>KYLE, hi, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Lache, hi. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 4103 Sablemist Ct, Houston, TX 77014. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
+          <t>Hello Lache, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>LaCretia, hi — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thank you!</t>
+          <t>Hey LaCretia — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Hello Landon. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 8723 S Eggleston Ave, Chicago, IL 60620. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
+          <t>Landon, hi, I'm Charles with Paragon Government Solutions. interested in buying 8723 S Eggleston Ave, Chicago, IL 60620 for cash. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Hi Lara. Charles here with Paragon Government Solutions, and interested in buying 5003 Gleneagles Ct, Houston, TX 77084 for cash. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
+          <t>Hey Lara — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Hello Lara — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Lara. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 113 Wescott Pl, Columbia, SC 29229. Would the seller consider a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Hello LASHAWN. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1730 AUDUBON Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi there LASHAWN — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14377,7 +14377,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Hey LaToya — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day LaToya. Charles here with Paragon Government Solutions, and I'm reaching out about 16525 Prevost St, Detroit, MI 48235 — a cash purchase. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Hey Laura, Charles here with Paragon Government Solutions. I'm reaching out about 2705 Warren Ave, Dallas, TX 75215 — a cash purchase. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Laura, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2705 Warren Ave, Dallas, TX 75215. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Hello Laura. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 806 Homestead St, Baltimore, MD 21218. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Laura. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 806 Homestead St, Baltimore, MD 21218 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Hi there Lauran, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Hello Lauran, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Good day Lauren, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 2009 Bancroft St, Lake Charles, LA 70607. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Lauren — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Hi there Lauren — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks!</t>
+          <t>Hi Lauren — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Lawrence, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 6526 Heyden St, Detroit, MI 48228. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello Lawrence, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 6526 Heyden St, Detroit, MI 48228 for cash. Open to a discounted cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14552,7 +14552,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>Hello LEANA. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 4633 SUFFOLK Avenue, Jacksonville, FL 32208. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
+          <t>LEANA, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Lee, hi, Charles here with Paragon Government Solutions. I'm reaching out about 9 Vicky Ct, Hamilton, NJ 08610 — a cash purchase. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day Lee, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Hi Leilani, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hey Leilani — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>Hi there Leonel — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
+          <t>Hi there Leonel, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Hello Leontra, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Leontra, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 11981 Whitehill St, Detroit, MI 48224. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14677,7 +14677,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>Good day Lesa, I'm Charles with Paragon Government Solutions. I'm reaching out about 146 Dunham Rd, Columbia, SC 29209 — a cash purchase. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi there Lesa, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>Hey Lesa, Charles here with Paragon Government Solutions. I'm reaching out about 2054 Elmridge Rd, Columbia, SC 29209 — a cash purchase. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
+          <t>Good day Lesa. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2054 Elmridge Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>Hi LeTanya. I'm Charles with Paragon Government Solutions, and I'm reaching out about 2043 Parker Ranch Rd SE, Atlanta, GA 30316 — a cash purchase. Is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>LeTanya, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 2043 Parker Ranch Rd SE, Atlanta, GA 30316. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>LETICIA, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
+          <t>LETICIA, hi, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Hello Liliana, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 530 Utah St SE Trailer 14A, Albuquerque, NM 87108. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Hello Liliana, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 530 Utah St SE Trailer 14A, Albuquerque, NM 87108. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>Lily, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 1027 Hollywood Ave, Dallas, TX 75208. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
+          <t>Hey Lily, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>Linda, hi, I'm Charles with Paragon Government Solutions. I'm reaching out about 15779 Wabash St, Detroit, MI 48238 — a cash purchase. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Linda — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>LINDA, hi, Charles Pleasant, Paragon Government Solutions. interested in buying 4815 LYNBROOK Drive, Jacksonville, FL 32207 for cash. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
+          <t>LINDA, hi — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Linda, hi — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Linda. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 10 Stacey Ave, Trenton, NJ 08618. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Hey Lindsey, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Lindsey. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 5525 E THOMAS Road #R9, Phoenix, AZ 85018 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Hello Lisa, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 131 Elm Rd, Pittsburgh, PA 15237. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Lisa, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Lisa, hi. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 1910 Greenoaks Rd APT A, Columbia, SC 29206. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
+          <t>Hi Lisa, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1910 Greenoaks Rd APT A, Columbia, SC 29206. Is the seller open to a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Hello Liz — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
+          <t>Liz, hi — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Hi Liz — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thank you!</t>
+          <t>Hi Liz. Charles Pleasant, Paragon Government Solutions, and interested in buying 1607 Elrino St, Baltimore, MD 21224 for cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Lora, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Lora — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Hey Lori — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there Lori — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Louis, hi, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 600 Stirrup Ave, Bakersfield, CA 93307. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Louis, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 600 Stirrup Ave, Bakersfield, CA 93307. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>LOURDES, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hello LOURDES. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 72 E 32 Street, Jacksonville, FL 32206. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Hi there Luan, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Luan, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Luciano, hi. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 5930 Guadalupe St, Houston, TX 77016. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi there Luciano, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Good day LUCIE, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 162 E 54TH Street, Jacksonville, FL 32208. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks so much!</t>
+          <t>Hi there LUCIE, Charles Pleasant, Paragon Government Solutions. interested in buying 162 E 54TH Street, Jacksonville, FL 32208 for cash. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Hey Luis — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
+          <t>Hi Luis, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Hi there Lydia — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
+          <t>Hey Lydia. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 13515 S Baltimore Ave, Chicago, IL 60633 for cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Hi MAE. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 1412 Morganton Rd, Fayetteville, NC 28305. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi there MAE. Charles Pleasant, Paragon Government Solutions, and interested in buying 1412 Morganton Rd, Fayetteville, NC 28305 for cash. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Good day Maico, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1638 W MOHAVE Street, Phoenix, AZ 85007. Would the seller consider a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Maico — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Good day Makia, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there Makia — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Hi Malaka. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 10731 Roxbury St, Detroit, MI 48224. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
+          <t>Hi there Malaka — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Hello Malwina. I'm Charles with Paragon Government Solutions, and interested in buying 8252 S Marshfield Ave, Chicago, IL 60620 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Malwina, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Hello Mamie. Charles Pleasant, Paragon Government Solutions, and interested in buying 216 W 10th St, Lakeland, FL 33805 for cash. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Mamie, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Hello Marc, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6003 Glenoak Ave, Baltimore, MD 21214. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
+          <t>Marc, hi, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Hi Marc, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Marc, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Hi Marc — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
+          <t>Good day Marc — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Good day Marc, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks!</t>
+          <t>Hi Marc, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 8313 S Wabash Ave, Chicago, IL 60619. Is the seller open to a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Good day Marcela — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Marcela, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 3712 W Cold Spring Ln, Baltimore, MD 21215 for cash. Open to a discounted cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15527,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Hi Marcelo, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Marcelo — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Hi there Marcia, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 90 Grandview Ave, Hamilton, NJ 08620. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
+          <t>Hey Marcia. Charles here with Paragon Government Solutions, and I'm reaching out about 90 Grandview Ave, Hamilton, NJ 08620 — a cash purchase. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Hi there Marcia, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 2627 Carmel St, Houston, TX 77091. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hey Marcia. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 2627 Carmel St, Houston, TX 77091. Open to a discounted cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Hi Marcy, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 1115 Belmont Green Rd, Columbia, SC 29209. Is the seller open to a cash as-is offer, close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hello Marcy, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1115 Belmont Green Rd, Columbia, SC 29209. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Hello Margarita, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2526 Exline St, Dallas, TX 75215 for cash. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Margarita — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Good day Maria, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Maria, hi, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Good day Maria — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
+          <t>Good day Maria, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 4541 S Laporte Ave, Chicago, IL 60638. Open to a discounted cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Good day Maria — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi there Maria. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 1015 Barelas St SW, Albuquerque, NM 87102. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Good day Maria, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 618 Dolores St, Bakersfield, CA 93305. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Maria, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Hi Maria. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 19355 Alcoy St, Detroit, MI 48205. Would the owner entertain a cash as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Maria. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 19355 Alcoy St, Detroit, MI 48205 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Hello MARIA, Charles here with Paragon Government Solutions. I'm reaching out about 5974 CHARLES D EVERS Drive, Jacksonville, FL 32219 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
+          <t>Hello MARIA, I'm Charles with Paragon Government Solutions. interested in buying 5974 CHARLES D EVERS Drive, Jacksonville, FL 32219 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Mariah, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks so much!</t>
+          <t>Mariah, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 9042 S Ellis Ave, Chicago, IL 60619 — a cash purchase. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Hi Maribel, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 16560 La Salle Ave, Detroit, MI 48221. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
+          <t>Maribel, hi, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Hi Maricela — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there Maricela — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Good day Maricela. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 124 Harriet Dr, San Antonio, TX 78216. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Maricela. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 124 Harriet Dr, San Antonio, TX 78216. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Good day Maricela, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Maricela, hi — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Hi there Marie — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
+          <t>Hi there Marie, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 11927 Horse Canyon, San Antonio, TX 78254. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Hey Marisela, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hello Marisela — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Hi Mariusz. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 8153 S Stewart Ave, Chicago, IL 60620. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Mariusz. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 8153 S Stewart Ave, Chicago, IL 60620. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16002,7 +16002,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>Hi there Mark, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Mark — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Good day Mark — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
+          <t>Good day Mark. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1010 N 18TH Street, Phoenix, AZ 85006. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Good day Marketta, Charles here with Paragon Government Solutions. I'm reaching out about 16241 E State Fair St, Detroit, MI 48205 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
+          <t>Hello Marketta. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 16241 E State Fair St, Detroit, MI 48205. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Hi Marshon — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks!</t>
+          <t>Hello Marshon. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 11841 S Union Ave, Chicago, IL 60628 — a cash purchase. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Hi Martha. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 10356 Shelburne Dr, Dallas, TX 75227. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>Martha, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Hi Martha, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Martha, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>Martina, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 6826 Larkstone St, Houston, TX 77028. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Martina, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Hi Mary, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Mary. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 1803 Cermack St, Columbia, SC 29223. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Hi Mary. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 511 Solar Dr, San Antonio, TX 78227. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
+          <t>Hey Mary, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Hi Matt, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 24 Merrymount Rd, Baltimore, MD 21210. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Matt — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Hi there Matthew, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1816 N 37th Avenue, Phoenix, AZ 85009. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Matthew, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>Hello MATTHEW, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi MATTHEW. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 4840 COLONIAL Avenue, Jacksonville, FL 32210. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Good day Mauricio. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3523 Edgewood St, Dallas, TX 75215. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
+          <t>Hello Mauricio, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3523 Edgewood St, Dallas, TX 75215. Is the seller open to a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Hey Mauricio, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5242 W Monroe St, Chicago, IL 60644. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi there Mauricio. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5242 W Monroe St, Chicago, IL 60644. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Good day Maya. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 5936 Hillcrest St, Detroit, MI 48236 — a cash purchase. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Maya. I'm Charles with Paragon Government Solutions, and interested in buying 5936 Hillcrest St, Detroit, MI 48236 for cash. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Hey MELISSA, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 2007 LAMBERT Street, Jacksonville, FL 32206. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
+          <t>MELISSA, hi. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 2007 LAMBERT Street, Jacksonville, FL 32206. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Good day Melody — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thank you!</t>
+          <t>Melody, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 353 E 90th St, Chicago, IL 60619. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Hi there Meredith, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 8511 Little River Rd, Houston, TX 77064. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Meredith, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16452,7 +16452,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Hey Michael, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 6463 Crane St, Detroit, MI 48213. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
+          <t>Hey Michael, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 6463 Crane St, Detroit, MI 48213. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>Hi there Michael, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 120 Curvewood Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day Michael. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 120 Curvewood Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>MICHAEL, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1204 Patrick Dr, Fayetteville, NC 28314 — a cash purchase. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
+          <t>MICHAEL, hi, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Hey Michael — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks!</t>
+          <t>Michael, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Hello Michael, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey Michael, Charles Pleasant, Paragon Government Solutions. interested in buying 228 Haybert Ct, Bakersfield, CA 93304 for cash. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 2637 Marbella Ln, Dallas, TX 75228. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Michael, hi — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hey Michael — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Michael, hi — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
+          <t>Hi there Michael — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Hey Michael, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Michael, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 9960 S Van Vlissingen Rd, Chicago, IL 60617 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Good day Michelle, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there Michelle. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5601 Howell St, Houston, TX 77032. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Good day Michelle — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
+          <t>Michelle, hi, I'm Charles with Paragon Government Solutions. interested in buying 16438 Vermillion Dr, Baton Rouge, LA 70819 for cash. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Hi there Michelle, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 16438 Vermillion Dr, Baton Rouge, LA 70819. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Michelle — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Hi there Michelle, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 13350 Tacoma St, Detroit, MI 48205. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
+          <t>Michelle, hi, Charles here with Paragon Government Solutions. interested in buying 13350 Tacoma St, Detroit, MI 48205 for cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Mike, hi, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3065 Noble St, Houston, TX 77026. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
+          <t>Hi Mike, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 3065 Noble St, Houston, TX 77026. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>Hi there MIKE, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1928 Crestview Dr, Fayetteville, NC 28304 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
+          <t>Good day MIKE, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Hi Mike, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 4337 Algonquin St, Detroit, MI 48215 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
+          <t>Mike, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Mike, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 8243 N 34TH Drive, Phoenix, AZ 85051. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Mike — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Hello MILDRED. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 10460 GAILWOOD Circle E, Jacksonville, FL 32218. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there MILDRED, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 10460 GAILWOOD Circle E, Jacksonville, FL 32218 — a cash purchase. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>Hi there Milton, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 10707 Carvel Ln, Houston, TX 77072 — a cash purchase. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Milton, hi — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Hello Milton — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Much appreciated!</t>
+          <t>Good day Milton, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1038 Canal Dr W, Lakeland, FL 33801 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>Hi Milton — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Appreciate it!</t>
+          <t>Good day Milton — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>Hi there MINNA — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
+          <t>Hello MINNA, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>Mitchell, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Mitchell, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 342 Ishmeal St, Houston, TX 77091 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Hi MITZIE, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1912 Blake St, Fayetteville, NC 28301. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thanks so much!</t>
+          <t>Good day MITZIE. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 1912 Blake St, Fayetteville, NC 28301. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Hey Moe, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 11409 Manor St, Detroit, MI 48204. Would the seller consider a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey Moe. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 11409 Manor St, Detroit, MI 48204. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Mohammad, hi, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3502 Goodhope St, Houston, TX 77021. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Mohammad. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 3502 Goodhope St, Houston, TX 77021. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>Good day MORGAN, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 525 W 66TH Street, Jacksonville, FL 32208. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Much appreciated!</t>
+          <t>MORGAN, hi, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 525 W 66TH Street, Jacksonville, FL 32208 for cash. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Good day Mr.. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 131 Hoffman Ave, Trenton, NJ 08618. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi there Mr., Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Good day Ms — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thank you!</t>
+          <t>Hi there Ms — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>Good day Mwood, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 18982 Joann St, Detroit, MI 48205. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi there Mwood — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Hi there Nader. Charles here with Paragon Government Solutions, and I'm reaching out about 12400 Lansdowne St, Grosse Pointe, MI 48224 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Good day Nader, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Hi Nadia — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thank you!</t>
+          <t>Hello Nadia. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 1333 W 71st St, Chicago, IL 60636. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Najah, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 17160 Northlawn St, Detroit, MI 48221 for cash. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
+          <t>Good day Najah, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 17160 Northlawn St, Detroit, MI 48221. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17277,7 +17277,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Good day Nakashia — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
+          <t>Hello Nakashia. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 9937 Golden Gate Ave, Baton Rouge, LA 70818. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Hi there Nameer. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2510 Sturtevant St, Detroit, MI 48206. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Nameer. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 2510 Sturtevant St, Detroit, MI 48206. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Hi there Nanci — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
+          <t>Nanci, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 4500 Norfolk Ave, Baltimore, MD 21216. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>Good day Nancy, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 4217 NW 32nd Ter, Cape Coral, FL 33993. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
+          <t>Hello Nancy. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 4217 NW 32nd Ter, Cape Coral, FL 33993 for cash. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Hi Nancy — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks much!</t>
+          <t>Hey Nancy — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Hi there Nardu, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3250 Elm Dr, Baton Rouge, LA 70805 — a cash purchase. Is the seller open to a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Nardu, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Hi NARENDRA, Charles Pleasant, Paragon Government Solutions. interested in buying 7007 LUCKY Drive E, Jacksonville, FL 32208 for cash. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
+          <t>Good day NARENDRA. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 7007 LUCKY Drive E, Jacksonville, FL 32208. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Hi there Natalie — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks much!</t>
+          <t>Hello Natalie, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 4009 W ORANGE Drive #36, Phoenix, AZ 85019. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Good day Nataly, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi Nataly. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 20260 Dean St, Detroit, MI 48234. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Hi Neeta. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 19024 Riverview St, Detroit, MI 48219. Is the seller open to a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hello Neeta, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Nelly, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 315 Gober St, Houston, TX 77017 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
+          <t>Hi Nelly. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 315 Gober St, Houston, TX 77017. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Good day Nichol, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks!</t>
+          <t>Nichol, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 125 Cedar Glen Ln, Columbia, SC 29223. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>Hey Nicholas, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hey Nicholas. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 3952 Bluehill St, Detroit, MI 48224. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>Hi Nick. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 129 Pond Oak Ln, Columbia, SC 29212. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Nick, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 129 Pond Oak Ln, Columbia, SC 29212 for cash. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Hi Nick, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Nick, hi, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Hey NICOLE. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 322 E 6TH Street, Jacksonville, FL 32206. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day NICOLE, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 322 E 6TH Street, Jacksonville, FL 32206. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17677,7 +17677,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Good day Nikhil, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi Nikhil, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 408 Longfellow Blvd, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>Hey Nikole. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 3450 Minnesota Ave, St. Louis, MO 63118. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Nikole, hi. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 3450 Minnesota Ave, St. Louis, MO 63118 for cash. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17727,7 +17727,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Nilsa, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 703 Monterey Ave, Cape Coral, FL 33904. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
+          <t>Hey Nilsa — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>Hello Nima — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Nima — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>Hey NM — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there NM, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>Hi there Noah — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there Noah — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17827,7 +17827,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Hello Norma, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 1810 Atlas Dr, Dallas, TX 75216. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Norma. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1810 Atlas Dr, Dallas, TX 75216 — a cash purchase. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Good day Norma, this is Charles Pleasant with Paragon Government Solutions. interested in buying 11326 S Union Ave, Chicago, IL 60628 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
+          <t>Good day Norma. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 11326 S Union Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17877,7 +17877,7 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Hey Olivia, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1434 N Leamington Ave, Chicago, IL 60651. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Good day Olivia — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Hey Orlando, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks much!</t>
+          <t>Hi there Orlando. Charles here with Paragon Government Solutions, and I'm reaching out about 13420 Chico Rd NE, Albuquerque, NM 87123 — a cash purchase. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Hello Oscar — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hello Oscar. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 10939 S Avenue F, Chicago, IL 60617 for cash. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17952,7 +17952,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Good day Otis. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 7221 S Bennett Ave, Chicago, IL 60649. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Hi there Otis, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Hi Pablo, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 213 Hogan St, Houston, TX 77009. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Pablo — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Hey PAIGE, this is Charles Pleasant with Paragon Government Solutions. interested in buying 3821 OLYMPIC Lane, Jacksonville, FL 32223 for cash. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thank you!</t>
+          <t>Hi PAIGE — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Hello Pamela, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 520 W CLARENDON Avenue #C3, Phoenix, AZ 85013. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day Pamela — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18052,7 +18052,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Hi Pamela, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 11401 S Morgan St, Chicago, IL 60643. Open to a discounted cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day Pamela. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 11401 S Morgan St, Chicago, IL 60643. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>Hello Pamela, I'm Charles with Paragon Government Solutions. interested in buying 3714 Hydrangea St, Columbia, SC 29205 for cash. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thank you!</t>
+          <t>Hi there Pamela. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 3714 Hydrangea St, Columbia, SC 29205 — a cash purchase. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Patricia, hi — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day Patricia — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18127,7 +18127,7 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>PATRICIA, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 1934 N Pearl St, Fayetteville, NC 28303. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi PATRICIA, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 1934 N Pearl St, Fayetteville, NC 28303. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Hello Patrick, I'm Charles with Paragon Government Solutions. interested in buying 609 Chestnut Ave, Trenton, NJ 08611 for cash. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Patrick — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Good day Patti, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Patti. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 218 Florien St, Pittsburgh, PA 15204 — a cash purchase. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>Hey Paul, I'm Charles with Paragon Government Solutions. I'm reaching out about 4629 Larkspur St, Houston, TX 77051 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thank you!</t>
+          <t>Hello Paul — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>PEPPER, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Good day PEPPER, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2185 MOREHOUSE Road, Jacksonville, FL 32209 for cash. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18252,7 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>Hi PETER. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 919 OBSERVATORY Parkway, Jacksonville, FL 32218 — a cash purchase. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
+          <t>PETER, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Hey Phil, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hey Phil, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18302,7 +18302,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Hi there Phyllis, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Phyllis — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Ponce, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 12 Sea Hawk Ct, Columbia, SC 29203 for cash. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks!</t>
+          <t>Good day Ponce — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>QUINNEICE, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day QUINNEICE. Charles here with Paragon Government Solutions, and interested in buying 1921 Ashridge Dr, Fayetteville, NC 28304 for cash. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Hi there Rachel, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Rachel, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 330 Klamath Dr, Pittsburgh, PA 15205 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Hi Rae, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 7720 Smart St, Detroit, MI 48210 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Rae, I'm Charles with Paragon Government Solutions. interested in buying 7720 Smart St, Detroit, MI 48210 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Hello Randal — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi Randal, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Ray, hi, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Ray, hi — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Hey Re/Max — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks much!</t>
+          <t>Re/Max, hi — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Rebecca, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 6408 Macroom Meadows Ln, Houston, TX 77048. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there Rebecca — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>Hi Regina. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 6036 Central St, Detroit, MI 48210. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
+          <t>Hello Regina, Charles Pleasant, Paragon Government Solutions. interested in buying 6036 Central St, Detroit, MI 48210 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>Hey Reid — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
+          <t>Hello Reid, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6224 Highland Hills Dr, Dallas, TX 75241. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Good day Rene, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 7331 S Peoria St, Chicago, IL 60621. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
+          <t>Rene, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Hello Reva, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 8451 Greenview Ave, Detroit, MI 48228. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
+          <t>Hello Reva — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18627,7 +18627,7 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>Hi Rhonda — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Rhonda, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Hi there Rhonda, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 2802 W Mosher St, Baltimore, MD 21216. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Good day Rhonda — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>Good day Ricardo, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Ricardo, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>Richard, hi. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 8327 Lou Gehrig St, San Antonio, TX 78240. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Richard. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 8327 Lou Gehrig St, San Antonio, TX 78240. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>Hi there Robbie, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hello Robbie. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 33870 Perkins Crossing Rd, Walker, LA 70785. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>Hi Robert. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 8410 N 32ND Avenue, Phoenix, AZ 85051. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
+          <t>Hey Robert — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>Hello ROBERT, this is Charles Pleasant with Paragon Government Solutions. interested in buying 784 Yardville Hamilton Sq, Trenton, NJ 08691 for cash. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello ROBERT. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 784 Yardville Hamilton Sq, Trenton, NJ 08691 for cash. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>Hey Robert. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 321 Crawford Rd, Columbia, SC 29203. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Robert, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>Hi there Robert, Charles here with Paragon Government Solutions. I'm a cash investor looking at 6235 Leaf Arbor Dr, Houston, TX 77092. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Robert, I'm Charles with Paragon Government Solutions. I'm reaching out about 6235 Leaf Arbor Dr, Houston, TX 77092 — a cash purchase. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>Hi there Roberto. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 11881 Saint Patrick St, Detroit, MI 48205 — a cash purchase. Would the owner entertain a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi Roberto, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>Hi there Roberto. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3226 Decatur Ave, Lakeland, FL 33805. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks!</t>
+          <t>Hello Roberto. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 3226 Decatur Ave, Lakeland, FL 33805. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>Hi there Robin. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 17003 Tireman St, Detroit, MI 48228. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Good day Robin. Charles Pleasant, Paragon Government Solutions, and interested in buying 17003 Tireman St, Detroit, MI 48228 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>Hey Robyn — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
+          <t>Hi Robyn, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>Good day Rodney — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Rodney, Charles Pleasant, Paragon Government Solutions. interested in buying 14035 Kentfield St, Detroit, MI 48223 for cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>Good day Rohn, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1614 Kayouche St, Lake Charles, LA 70601. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Rohn. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1614 Kayouche St, Lake Charles, LA 70601. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>Good day Ross, this is Charles Pleasant with Paragon Government Solutions. interested in buying 2507 Parktrail Rd, Baltimore, MD 21234 for cash. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day Ross, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19027,7 +19027,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>Hey Rosy — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Rosy — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>Hi there Roxanne, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Good day Roxanne, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 1316 E Applegate Dr, Austin, TX 78753. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>Hello Rubi — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks!</t>
+          <t>Hi Rubi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 4600 Ireland St, Houston, TX 77016. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19102,7 +19102,7 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>Good day Ryan, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Hi there Ryan — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>Hello RYAN. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 3318 NOLAN Street, Jacksonville, FL 32254. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
+          <t>RYAN, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3318 NOLAN Street, Jacksonville, FL 32254. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>Hi Ryan — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
+          <t>Hi Ryan — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>Hello Ryan. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 2258 Hawthorne Ave, Pittsburgh, PA 15218. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi Ryan — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>Good day S. — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thank you!</t>
+          <t>S., hi, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>Hey Samantha, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hey Samantha, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6159 Lyndhurst Dr, Houston, TX 77033. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19252,7 +19252,7 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>Hey Sara, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hey Sara, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 6537 S 15th Dr, Phoenix, AZ 85041. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>Hey Sarah. I'm Charles with Paragon Government Solutions, and interested in buying 5953 S Throop St, Chicago, IL 60636 for cash. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Sarah, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19302,7 +19302,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>Hello Schlanda, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thank you!</t>
+          <t>Hello Schlanda, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1319 Reynes St, New Orleans, LA 70117 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>Hello Schylbea — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks much!</t>
+          <t>Hello Schylbea. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 13123 Indiana St, Detroit, MI 48238. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19352,7 +19352,7 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>Hi there Scott. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 7607 Dobel St, Detroit, MI 48234. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there Scott, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>Hi Scott, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Scott, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>Hello SCOTT, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Hi SCOTT — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>Hi Scott, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi there Scott — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>Hello Sean, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there Sean, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 8605 Fireside Dr, Austin, TX 78757. Could the seller look at a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>Hello Sean. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 8506 McDade St, Houston, TX 77080. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there Sean — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>Sebastian, hi. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5730 S Hoyne Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
+          <t>Hi Sebastian — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>Good day Sergio. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 16203 Barbarossa Dr, Houston, TX 77083. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
+          <t>Sergio, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>Sergio, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hi Sergio. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 10841 S Vernon Ave, Chicago, IL 60628. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>Hello SETH, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi SETH, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>Hello Shakena. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 130 Brandon Hall Rd, Columbia, SC 29229. Is the seller open to a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hello Shakena. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 130 Brandon Hall Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>Hey Shane. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 889 E 128th St, Cleveland, OH 44108. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hello Shane, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>Shannon, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 8710 Files St, Dallas, TX 75217. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
+          <t>Hello Shannon, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>Hi there Shannon — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi Shannon, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 134 Palmetto Park Cir, Columbia, SC 29229. Would the owner entertain a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>Hi Sharon — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Sharon, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 516 Lakeside Ave, Columbia, SC 29203. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>Hey Sharon, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 515 W Main St, Gonzales, LA 70737. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Much appreciated!</t>
+          <t>Sharon, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>Shauntell, hi — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Shauntell. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 337 W 110th Pl, Chicago, IL 60628. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>Good day SHAWANA — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
+          <t>Hi SHAWANA, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>Hi Shawn, Charles here with Paragon Government Solutions. interested in buying 5404 Dixie Ln, Alexandria, LA 71301 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks!</t>
+          <t>Hi Shawn, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5404 Dixie Ln, Alexandria, LA 71301. Is the seller open to a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>Hey SHAWN. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3862 ORLANDO Circle W, Jacksonville, FL 32207. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi SHAWN — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>Hello Shay — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day Shay — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>Shelby, hi, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Good day Shelby, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 4235 Elmwood St, Houston, TX 77051. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19902,7 +19902,7 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>Hi Shelly — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
+          <t>Hi there Shelly, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>Hello Shemika — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
+          <t>Good day Shemika, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>Hello Shemika — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Appreciate it!</t>
+          <t>Good day Shemika, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 2764 Dalton St, Baton Rouge, LA 70805. Is the seller open to a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>Hi there Sherrease, Charles here with Paragon Government Solutions. I'm reaching out about 14216 Kentucky St, Detroit, MI 48238 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
+          <t>Hey Sherrease, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 14216 Kentucky St, Detroit, MI 48238 — a cash purchase. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20002,7 +20002,7 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>Hello Sherri, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hello Sherri — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20027,7 +20027,7 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>Hi Sherri, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 8091 Kenney St, Detroit, MI 48234. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
+          <t>Hey Sherri — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20052,7 +20052,7 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>SHINESHA, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Appreciate it!</t>
+          <t>Hello SHINESHA — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>Hi Shirley, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Shirley, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>Hi Shoaib, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5093 Garland St, Detroit, MI 48213. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Shoaib, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 5093 Garland St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>Good day Shoaib — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
+          <t>Hi there Shoaib, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>Good day Shon, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Shon, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>Hi Shonda. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 218 Sanhican Dr, Trenton, NJ 08618. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
+          <t>Shonda, hi — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>Hey Sidra — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Sidra. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 7106 Tierwester St, Houston, TX 77021 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>Hey Sonia, this is Charles Pleasant with Paragon Government Solutions. interested in buying 514 L St, Bakersfield, CA 93304 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
+          <t>Sonia, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 514 L St, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>Hi there Sonia — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks!</t>
+          <t>Good day Sonia, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 11315 Raincove Dr, Houston, TX 77016. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>Hi STACEY, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there STACEY. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 6811 LANGFORD Street, Jacksonville, FL 32219. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>Hello Stacie, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 4400 Norfolk Ave, Baltimore, MD 21216. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi Stacie, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 4400 Norfolk Ave, Baltimore, MD 21216. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20327,7 +20327,7 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>Hello Stacy — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there Stacy, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 11833 Beachberry Dr, Houston, TX 77034. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hello Stephanie. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 6541 W OSBORN Road, Phoenix, AZ 85033 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>Good day Stephanie, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Stephanie — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20402,7 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>Hi Stephanie, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi there Stephanie. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1404 SE 34th Ter, Cape Coral, FL 33904 — a cash purchase. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>STEPHANIE, hi — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks!</t>
+          <t>Hey STEPHANIE, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 2205 COMMONWEALTH Avenue, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20452,7 +20452,7 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>Hey STEPHANIE — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks!</t>
+          <t>Good day STEPHANIE. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 115 Brookwood Ave, Fayetteville, NC 28301. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>Good day Stephanie, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 6106 Sandy Creek Ln, Zachary, LA 70791. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>Hi there Stephanie, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Stephanie, hi — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20527,7 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>Hey STEPHEN — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Much appreciated!</t>
+          <t>STEPHEN, hi — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20552,7 +20552,7 @@
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>Hello Steve — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Steve. I'm Charles with Paragon Government Solutions, and interested in buying 6831 S Emerald Ave, Chicago, IL 60621 for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>Steve, hi. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 2666 Olympia Ave, North Charleston, SC 29405 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Hi there Steve. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2666 Olympia Ave, North Charleston, SC 29405. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>Hi there Steven, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi Steven, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 2514 W Ramsey Ave, Milwaukee, WI 53221. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20627,7 +20627,7 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>Hi Steven, Charles here with Paragon Government Solutions. I'm a cash investor looking at 408 W Montana Ave, Dallas, TX 75224. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
+          <t>Hey Steven — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20652,7 +20652,7 @@
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>Hey Steven, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 12008 Vista Nogal St, San Antonio, TX 78213 — a cash purchase. Would the owner entertain a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Thank you!</t>
+          <t>Hi Steven — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20677,7 +20677,7 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>Hey Steven, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3061 Horse Ranch Rd, San Antonio, TX 78264. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
+          <t>Good day Steven. I'm Charles with Paragon Government Solutions, and interested in buying 3061 Horse Ranch Rd, San Antonio, TX 78264 for cash. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>Hi Summer — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi Summer, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1201 Willow Dr, Lake Charles, LA 70611. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>Hi there Susan, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 3419 SE 5th Ave, Cape Coral, FL 33904. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
+          <t>Hey Susan — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>Hey Susan — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Susan — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>Hi there Suzy. I'm Charles with Paragon Government Solutions, and I'm reaching out about 13050 N 19TH Street #50, Phoenix, AZ 85022 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day Suzy — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>Hi there Sylvia, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Good day Sylvia. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 4401 Hughes Ln Space 200, Bakersfield, CA 93304. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20832,7 +20832,7 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>Hi there T'Keyah, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey T'Keyah, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>Good day Tai, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Tai — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20882,7 +20882,7 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>Hello Tal, Charles Pleasant, Paragon Government Solutions. interested in buying 2166 W 93rd St, Cleveland, OH 44102 for cash. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
+          <t>Tal, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 2166 W 93rd St, Cleveland, OH 44102. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>Hi Tamara, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi Tamara, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 5151 S Denley Dr, Dallas, TX 75241. Would the seller consider a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20932,7 +20932,7 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>Hi Tamara, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Good day Tamara, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1991 Lawrence St, Detroit, MI 48206. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20957,7 +20957,7 @@
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>Tamara, hi — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
+          <t>Good day Tamara, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>Hi there Tamesha. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 12323 Misty Laurel Dr, Houston, TX 77014. Would the seller consider a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Good day Tamesha, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Hi there Tami. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 6243 S 31st West Ave, Tulsa, OK 74132 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Tami, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 6243 S 31st West Ave, Tulsa, OK 74132. Would the seller consider a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21032,7 +21032,7 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Good day Tamie — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Tamie, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 24 Evans Ave, Trenton, NJ 08638. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21057,7 +21057,7 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>Tamika, hi. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 10118 S Luella Ave, Chicago, IL 60617. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey Tamika, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21082,7 +21082,7 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Hi Tammi, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Tammi, I'm Charles with Paragon Government Solutions. I'm reaching out about 323 Belle Winds Ct, Shreveport, LA 71106 — a cash purchase. Open to a discounted cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21107,7 +21107,7 @@
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Good day Tammy, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Tammy, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 12011 Doubleday Dr, Houston, TX 77089 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>Hi there TANA. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2425 HOLMES Street, Jacksonville, FL 32207. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello TANA, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>Hi Tanisha, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 19953 Hull St, Detroit, MI 48203. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
+          <t>Tanisha, hi, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>Hi Tara, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Tara, hi, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 1430 Dahlia Rd, Columbia, SC 29205. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>TASHELE, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 9656 FLECHETTE Avenue, Jacksonville, FL 32208 — a cash purchase. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks!</t>
+          <t>Hey TASHELE, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 9656 FLECHETTE Avenue, Jacksonville, FL 32208. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>Hi Tashia — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Tashia, Charles Pleasant, Paragon Government Solutions. interested in buying 2433 W Tonto St, Phoenix, AZ 85009 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>Tawanda, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 4410 Greenwood Ln, Baker, LA 70714. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
+          <t>Hi there Tawanda, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21282,7 +21282,7 @@
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>Hey Taz, Charles here with Paragon Government Solutions. I'm reaching out about 10615 Kirkdale Dr, Houston, TX 77089 — a cash purchase. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Taz, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 10615 Kirkdale Dr, Houston, TX 77089. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>Hey Teal, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day Teal, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2831 Lawrence St, Denver, CO 80205. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>Hello Tene', Charles here with Paragon Government Solutions. I'm a cash investor looking at 6845 S Chappel Ave, Chicago, IL 60649. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
+          <t>Hey Tene', Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>Tera, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2222 Detroit Ave APT 504, Cleveland, OH 44113. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
+          <t>Tera, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 2222 Detroit Ave APT 504, Cleveland, OH 44113 for cash. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>Hi Terence — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Terence, Charles here with Paragon Government Solutions. I'm reaching out about 389 Northwood St, Columbia, SC 29201 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21407,7 +21407,7 @@
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>Hey Teresa — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
+          <t>Teresa, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 189 Regina Ave, Hamilton, NJ 08619 — a cash purchase. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>Hi there Teresa. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2602 Falls Dr, Dallas, TX 75211. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
+          <t>Hey Teresa. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2602 Falls Dr, Dallas, TX 75211. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>Hi there Terry. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 609 Lufkin Circle, Fayetteville, NC 28311. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Terry, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 609 Lufkin Circle, Fayetteville, NC 28311. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>Hello Terry — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
+          <t>Hi there Terry, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>Hi there Thalia, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 12699 Greenlawn St, Detroit, MI 48238. Would the seller consider a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Thalia — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>Thao, hi — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Thao. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1263 James St, Baltimore, MD 21223. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21557,7 +21557,7 @@
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>Hello Thao. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 9303 Kingsflower Cir, Houston, TX 77075. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Thao — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>Hey Thomas, I'm Charles with Paragon Government Solutions. I'm reaching out about 8656 &amp; 8560 Farmbrook St, Detroit, MI 48224 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
+          <t>Hi Thomas, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>Hi there THOMAS, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hello THOMAS — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21632,7 @@
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>Hey TIER, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 621 Ashboro St, Fayetteville, NC 28311. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
+          <t>Hello TIER, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>Hi there Tiffany. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 10320 S Indiana Ave, Chicago, IL 60628. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Tiffany, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 10320 S Indiana Ave, Chicago, IL 60628. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>Good day Tiffany, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 11744 Wade St, Detroit, MI 48213. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
+          <t>Tiffany, hi — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21707,7 +21707,7 @@
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>Hi TIM. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 7940 EATON Avenue, Jacksonville, FL 32211. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>Good day TIM, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21732,7 +21732,7 @@
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>Hey Timothy, I'm Charles with Paragon Government Solutions. I'm reaching out about 230 Sterling Rd, Bakersfield, CA 93307 — a cash purchase. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
+          <t>Timothy, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 230 Sterling Rd, Bakersfield, CA 93307 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21757,7 +21757,7 @@
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>Timothy, hi, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thank you!</t>
+          <t>Timothy, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 20260 Patton St, Detroit, MI 48219 — a cash purchase. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>TJ, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks!</t>
+          <t>Hello TJ. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 1809 Manteo St, Fayetteville, NC 28303. Open to a discounted cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21807,7 +21807,7 @@
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>Hello TLeice — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks!</t>
+          <t>Hello TLeice, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2684 Iroquois St, Baton Rouge, LA 70805. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>TLeice, hi, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there TLeice — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>Tom, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 83 Bryn Mawr Ave, Trenton, NJ 08618. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
+          <t>Good day Tom, this is Charles Pleasant with Paragon Government Solutions. interested in buying 83 Bryn Mawr Ave, Trenton, NJ 08618 for cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>TONY, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 3252 THOMAS Street, Jacksonville, FL 32254. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
+          <t>Hi TONY. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3252 THOMAS Street, Jacksonville, FL 32254. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>Hey TONYA, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there TONYA. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5466 Maplewood Ct, Fayetteville, NC 28314. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21932,7 +21932,7 @@
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>Hey Tonya. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 12746 Woodland Dr, Jacksonville, FL 32218 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks much!</t>
+          <t>Hello Tonya, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21957,7 +21957,7 @@
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>Hi TORANIQUE. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1354 Worstead Dr, Fayetteville, NC 28314 — a cash purchase. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey TORANIQUE — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21982,7 +21982,7 @@
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>Hi there Tosh, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Tosh — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>Hey TRACEY — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
+          <t>Hi TRACEY, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>Transit, hi — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hello Transit — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22057,7 +22057,7 @@
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>Hi there Tricia, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hi there Tricia. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 129 Kings Parish Ct, Columbia, SC 29209. Would the owner entertain a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22082,7 +22082,7 @@
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>Hi Trinh. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 255 Sorrel Tree Dr, Columbia, SC 29223. Open to a discounted cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day Trinh, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>Hi TRINITY. Charles here with Paragon Government Solutions, and I'm reaching out about 6559 Amanda Cir, Fayetteville, NC 28304 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks much!</t>
+          <t>Hi there TRINITY. I'm Charles with Paragon Government Solutions, and I'm reaching out about 6559 Amanda Cir, Fayetteville, NC 28304 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22132,7 +22132,7 @@
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>Good day Tucker, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 4538 Larkspur St, Houston, TX 77051. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Tucker, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>Tyjuan, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 29 Battery Walk Ct, Columbia, SC 29212. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
+          <t>Hi Tyjuan, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22182,7 +22182,7 @@
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>Hello Tyler, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hello Tyler, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22207,7 +22207,7 @@
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>Hi Tyreeta, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hey Tyreeta — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>Hi there Tyrone, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 7137 S Winchester Ave, Chicago, IL 60636. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Hello Tyrone. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 7137 S Winchester Ave, Chicago, IL 60636. Is the seller open to a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22257,7 +22257,7 @@
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>Valerie, hi. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 3698 Menlo Rd, Shaker Heights, OH 44120. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
+          <t>Valerie, hi, Charles here with Paragon Government Solutions. interested in buying 3698 Menlo Rd, Shaker Heights, OH 44120 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22282,7 +22282,7 @@
       </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>Hey Vanessa, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Vanessa, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22307,7 +22307,7 @@
       </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>Good day Vanessa, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 2248 Cooper St, Dallas, TX 75215. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Vanessa — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>Hi there Vanessa. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 8043 Wier Dr, Houston, TX 77017. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Vanessa — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>Hey Vanessa, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 133 Cornwall Ave, Trenton, NJ 08618. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
+          <t>Hello Vanessa — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22382,7 @@
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>Hello Vanessa, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 11265 S May St, Chicago, IL 60643 — a cash purchase. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Vanessa — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>Hi VANETTA — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Much appreciated!</t>
+          <t>Hello VANETTA. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 4022 TYNDALE Drive, Jacksonville, FL 32210. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>Vanity, hi — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
+          <t>Good day Vanity — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>Hi there Veronica — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
+          <t>Hi there Veronica, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 213 T St, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>Hello Vickie. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in your listing. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
+          <t>Hey Vickie, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>Good day Victoria, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Victoria, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2127 Coelum Ct, Dallas TX 75253. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22532,7 +22532,7 @@
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>Hello Victoria, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 7538 Bywood St, Houston, TX 77028. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
+          <t>Victoria, hi, Charles Pleasant, Paragon Government Solutions. interested in buying 7538 Bywood St, Houston, TX 77028 for cash. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>Good day Vince — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
+          <t>Vince, hi. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 517 Windjammer Ln, Columbia, SC 29229. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>Good day Vinh, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Vinh — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22607,7 +22607,7 @@
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>Hi Viveka. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 8028 S Ada St, Chicago, IL 60620 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
+          <t>Good day Viveka, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>Good day Wally, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 5604 Creekmore Dr, Oklahoma City, OK 73179. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>Hi there Wally. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 5604 Creekmore Dr, Oklahoma City, OK 73179 — a cash purchase. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22657,7 +22657,7 @@
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>Good day Wayne, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hello Wayne. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 2011 Lake Carolina Dr, Columbia, SC 29229. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>Hi WELCOME, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 603 Faison Ave, Fayetteville, NC 28304. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
+          <t>Good day WELCOME, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 603 Faison Ave, Fayetteville, NC 28304. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>Hey Wendy, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 16878 Lilac St, Detroit, MI 48221. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hello Wendy — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22732,7 +22732,7 @@
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>Hello Wes. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 1013 N Ruth Ave, Lakeland, FL 33805. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello Wes, Charles here with Paragon Government Solutions. I'm reaching out about 1013 N Ruth Ave, Lakeland, FL 33805 — a cash purchase. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>Hi there William — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
+          <t>Hi William, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22782,7 +22782,7 @@
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>William, hi — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey William, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22807,7 +22807,7 @@
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>Hi WILLIAM, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day WILLIAM — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22832,7 +22832,7 @@
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>Hey William, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 14711 Lappin St, Detroit, MI 48205 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
+          <t>William, hi. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 14711 Lappin St, Detroit, MI 48205. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>Good day William. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 2640 Cypress Ave, Dallas, TX 75227. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hey William. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 2640 Cypress Ave, Dallas, TX 75227 — a cash purchase. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>Hello Willie, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Good day Willie, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 8367 Howton St #A/B, Houston, TX 77028. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>Hello Xiaochen. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 20315 Goulburn St, Detroit, MI 48205. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
+          <t>Hi there Xiaochen — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22932,7 +22932,7 @@
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>Yu, hi, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Yu — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22957,7 +22957,7 @@
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>Hi there Yurika, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Yurika. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 9551 Gonzales Dr, Dallas, TX 75227 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>Yvette, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hi Yvette, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>Zachary, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
+          <t>Good day Zachary — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23032,7 @@
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>Hey Zena, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Zena — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>

--- a/GV_Campaign_NoEmail_20260620.xlsx
+++ b/GV_Campaign_NoEmail_20260620.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hi Keelie — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi Keelie, Charles here with Paragon Government Solutions. I came across 10319 Violetlawn St, Detroit, MI 48204 and buy cash; could the seller look at a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hi there Greg, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Good day Greg. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 125 Deer Hound Trl, Columbia, SC 29223. could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hi there Amar — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
+          <t>Hey Amar, I'm Charles with Paragon Government Solutions. I'm interested in buying 10504 Olympic St NW, Albuquerque, NM 87114 for cash; would the owner entertain a cash as-is offer, fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Good day Tyjuan — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thank you!</t>
+          <t>Good day Tyjuan. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 108 Malisa Dr, Columbia, SC 29229. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hi Julie, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1146 Castle Pinckney Rd, Columbia, SC 29223. Could the seller look at a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
+          <t>Hi Julie — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1146 Castle Pinckney Rd, Columbia, SC 29223 for cash. open to a discounted cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hello Jasmine — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Jasmine. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 13 Gatewood Way, Columbia, SC 29229. open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hello John. Charles Pleasant, Paragon Government Solutions, and interested in buying 11718 Coachfield Ln, Houston, TX 77035 for cash. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
+          <t>Hey John, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 11718 Coachfield Ln, Houston, TX 77035; could the seller look at a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hi Lauren — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
+          <t>Hey Lauren — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 1531 Alma Rd, Columbia, SC 29209. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Good day Tricia, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Tricia. my name's Charles Pleasant, Paragon Government Solutions, and I came across 116 Patio Pl, Columbia, SC 29212 and buy cash. could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hello Wendy — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
+          <t>Wendy, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 117 Lambeth Dr, Columbia, SC 29209 — open to a discounted cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Good day Brad, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Brad, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1143 Owens Rd, Columbia, SC 29203 — open to a discounted cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hey Joey. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 1515 Rushmore Rd, Columbia, SC 29210. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Joey, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 1515 Rushmore Rd, Columbia, SC 29210. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Good day Nina. Charles here with Paragon Government Solutions, and I'm reaching out about 106 Rolling Knoll Dr, Columbia, SC 29229 — a cash purchase. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi there Nina, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 106 Rolling Knoll Dr, Columbia, SC 29229 — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hi Austin. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 1246 Rabon Pond Dr, Columbia, SC 29223. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Hello Austin, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1246 Rabon Pond Dr, Columbia, SC 29223 — open to a discounted cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Good day Bonni, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hey Bonni, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 145 Patio Pl, Columbia, SC 29212 — any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hey Daleik — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
+          <t>Daleik, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1163 Atkinson St, Detroit, MI 48202 — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hey Jamila. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 103 Village Way, Columbia, SC 29209. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Jamila. Charles here with Paragon Government Solutions, and I'm interested in buying 103 Village Way, Columbia, SC 29209 for cash. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hello Mark. Charles Pleasant, Paragon Government Solutions, and interested in buying 12717 Indiana St, Detroit, MI 48238 for cash. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
+          <t>Hello Mark, this is Charles Pleasant with Paragon Government Solutions. I came across 12717 Indiana St, Detroit, MI 48238 and buy cash; is the seller open to a cash as-is offer, fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hello Shayla — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks much!</t>
+          <t>Hello Shayla, I'm Charles with Paragon Government Solutions. I'm reaching out about 133 Heritage Village Ln, Columbia, SC 29212; any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hi Tracy, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Tracy, hi, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 126 Burnsdowne Rd, Columbia, SC 29210; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hi Becky. I'm Charles with Paragon Government Solutions, and interested in buying 115 Mulberry Ln, Columbia, SC 29201 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Becky, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 115 Mulberry Ln, Columbia, SC 29201. would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hey Brandon, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Hey Brandon, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 13161 Monica St, Detroit, MI 48238; could the seller look at a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hi there Bryant, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1111 Cloister Pl, Columbia, SC 29210. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Bryant — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1111 Cloister Pl, Columbia, SC 29210. open to a discounted cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hey Jamie. I'm Charles with Paragon Government Solutions, and interested in buying 2018 Hallmark Ct, Lakeland, FL 33803 for cash. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
+          <t>Good day Jamie. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2018 Hallmark Ct, Lakeland, FL 33803. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hi there Nadia — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thank you!</t>
+          <t>Hey Nadia, this is Charles Pleasant with Paragon Government Solutions. I came across 1009 Gardendale Dr, Columbia, SC 29210 and buy cash — is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Renee, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hi there Renee, I'm Charles with Paragon Government Solutions. I came across 228 Rolling Rock Rd, Columbia, SC 29212 and buy cash; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Good day Sheila. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 124 Farrow Pointe Ln, Columbia, SC 29203 — a cash purchase. Is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks!</t>
+          <t>Hey Sheila, Charles here with Paragon Government Solutions. I'm a cash investor looking at 124 Farrow Pointe Ln, Columbia, SC 29203; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hello Amber, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thank you!</t>
+          <t>Hey Amber. Charles Pleasant, Paragon Government Solutions, and I came across 314 Leton Dr, Columbia, SC 29210 and buy cash. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hey ANDREA. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 3736 ROSE Street, Jacksonville, FL 32208. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
+          <t>Hi there ANDREA, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3736 ROSE Street, Jacksonville, FL 32208 — would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hi there Andrew, I'm Charles with Paragon Government Solutions. I'm reaching out about 10201 S Princeton Ave, Chicago, IL 60628 — a cash purchase. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Andrew, I'm Charles with Paragon Government Solutions. I'm reaching out about 10201 S Princeton Ave, Chicago, IL 60628; would the owner entertain a cash as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Good day Angela, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Angela — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1024 Price Ave, Columbia, SC 29201. would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anthony, hi. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 11439 Ohio St, Detroit, MI 48204. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Anthony — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 11439 Ohio St, Detroit, MI 48204. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hello Anya, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 12664 Kelly Rd, Detroit, MI 48224 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Hi Anya, my name's Charles Pleasant, Paragon Government Solutions. I came across 12664 Kelly Rd, Detroit, MI 48224 and buy cash — would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hey Avia — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thank you!</t>
+          <t>Good day Avia. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 205 Parliament Dr, Columbia, SC 29223. open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hey Billy, Charles Pleasant, Paragon Government Solutions. interested in buying 23 Braiden Manor Rd, Columbia, SC 29209 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Good day Billy — Charles here with Paragon Government Solutions. I'm a cash investor looking at 23 Braiden Manor Rd, Columbia, SC 29209. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hi Carlina — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Carlina, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2027 Leesburg Rd, Columbia, SC 29209; would the seller consider a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hi there CHAD, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 1169 WOODRUFF Avenue, Jacksonville, FL 32205 for cash. Is the seller open to a cash as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hello CHAD. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1169 WOODRUFF Avenue, Jacksonville, FL 32205. would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Good day Charles, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there Charles, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 17593 Monica St, Detroit, MI 48221; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Good day Cody, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
+          <t>Cody, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 104 Harbor Dr, Columbia, SC 29229 for cash. would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hi there Daniel, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Daniel, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1257 E 170th St, Cleveland, OH 44110; any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hey DIETCHI, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>DIETCHI, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1007 Anarine Rd, Fayetteville, NC 28303 for cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Heather, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 15385 Stansbury St, Detroit, MI 48227 — a cash purchase. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Heather. I'm Charles with Paragon Government Solutions, and I came across 15385 Stansbury St, Detroit, MI 48227 and buy cash. is the seller open to a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hey Jamie, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi Jamie, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 2518 Putnam St, Columbia, SC 29204; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hello Kristian, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 12140 Wayburn St, Detroit, MI 48224. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
+          <t>Good day Kristian, this is Charles Pleasant with Paragon Government Solutions. I came across 12140 Wayburn St, Detroit, MI 48224 and buy cash; open to a discounted cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Good day Mark — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
+          <t>Hi Mark, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1233 W 73rd Pl, Chicago, IL 60636 — would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hi there Melissa — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Melissa. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 15534 Rocco Dr, Baker, LA 70714. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Michael, hi, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Hey Michael, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1023 Crow Ct, Grand Prairie, TX 75051; is the seller open to a cash as-is offer, close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hey Nancy, this is Charles Pleasant with Paragon Government Solutions. interested in buying 10310 Mills Run Dr, Houston, TX 77070 for cash. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
+          <t>Nancy, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 10310 Mills Run Dr, Houston, TX 77070 — any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patrick, hi — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Patrick — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 135 Fox Squirrel Cir, Columbia, SC 29209. could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hey Sam, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hello Sam — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 10799 Worden St, Detroit, MI 48224. is the seller open to a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hi there, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3700 Ulmer Rd, Columbia, SC 29209. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
+          <t>Good day there — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3700 Ulmer Rd, Columbia, SC 29209. could the seller look at a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hello Albert, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Good day Albert. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 12717 Riad St, Grosse Pointe, MI 48224. could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hello Alex, Charles Pleasant, Paragon Government Solutions. interested in buying 201 Sandhurst Rd, Columbia, SC 29210 for cash. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
+          <t>Hi Alex — Charles here with Paragon Government Solutions. I'm reaching out about 201 Sandhurst Rd, Columbia, SC 29210. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hi there Alex, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Alex — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1152 Vinewood St, Detroit, MI 48216. would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hi Alexander — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks!</t>
+          <t>Hello Alexander. I'm Charles with Paragon Government Solutions, and I came across 16321 Stockbridge Ave, Cleveland, OH 44128 and buy cash. any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hi Alexandra, this is Charles Pleasant with Paragon Government Solutions. interested in buying 219 Dixon Dr, Columbia, SC 29203 for cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Alexandra. I'm Charles with Paragon Government Solutions, and I came across 219 Dixon Dr, Columbia, SC 29203 and buy cash. could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hello Amber, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Amber, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 9520 Royal Ln #104, Dallas TX 75243 for cash; would the seller consider a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hey Andy — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks much!</t>
+          <t>Good day Andy. Charles here with Paragon Government Solutions, and I'm reaching out about 6506 Christie Rd, Columbia, SC 29209. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anthony, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Anthony, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1533 S Kilbourn Ave, Chicago, IL 60623; any chance the seller would take a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anthony, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 132 Flora Springs Cir, Columbia, SC 29223. Is the seller open to a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
+          <t>Anthony, hi, my name's Charles Pleasant, Paragon Government Solutions. I came across 132 Flora Springs Cir, Columbia, SC 29223 and buy cash; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ARTHUR, hi, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 1010 KENMORE Street, Jacksonville, FL 32208. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
+          <t>Hey ARTHUR, Charles here with Paragon Government Solutions. I'm interested in buying 1010 KENMORE Street, Jacksonville, FL 32208 for cash; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hi Arthur, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Arthur, this is Charles Pleasant with Paragon Government Solutions. I came across 1987 W Melvina St, Milwaukee, WI 53206 and buy cash; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hi Bobby, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Bobby. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 14941 Littlefield St, Detroit, MI 48227. would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brad, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1253 Mosser Dr, Columbia, SC 29203. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Brad. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1253 Mosser Dr, Columbia, SC 29203. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hi there Brittany — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Brittany. Charles Pleasant, Paragon Government Solutions, and I came across 2065 Missouri St, Baton Rouge, LA 70802 and buy cash. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hey Caleb, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Good day Caleb, Charles Pleasant, Paragon Government Solutions. I came across 232 Twin Oaks Ln, Columbia, SC 29209 and buy cash; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cameron, hi — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hey Cameron — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 9175 Everts St, Detroit, MI 48224. would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hi there Chachere, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Chachere, Charles here with Paragon Government Solutions. I came across 3805 Trotter Rd, Columbia, SC 29209 and buy cash; open to a discounted cash, as-is offer, quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hello CHRISTINA, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Hi there CHRISTINA — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1602 Gardenia Ave, Fayetteville, NC 28311. is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hello Crystal, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 5648 S Sawyer Ave, Chicago, IL 60629 — a cash purchase. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hello Crystal — Charles Pleasant, Paragon Government Solutions. I came across 5648 S Sawyer Ave, Chicago, IL 60629 and buy cash. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hello Daniella — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks much!</t>
+          <t>Hello Daniella, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 22118 Ulster St, Detroit, MI 48219 — would the seller consider a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hey David. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 11532 S Harvard Ave, Chicago, IL 60628 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi David, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 11532 S Harvard Ave, Chicago, IL 60628 for cash — is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Good day Dean, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi Dean, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 19760 Rowe St, Detroit, MI 48205 — could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hi there Delaney, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2 Woodshaw Ct, Columbia, SC 29212 — a cash purchase. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Delaney, my name's Charles Pleasant, Paragon Government Solutions. I came across 2 Woodshaw Ct, Columbia, SC 29212 and buy cash; would the owner entertain a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hi there DENISE. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 7330 ELWOOD Avenue, Jacksonville, FL 32208. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi DENISE, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 7330 ELWOOD Avenue, Jacksonville, FL 32208 — could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hey Derek, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Derek, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 3814 Hardy St, Houston, TX 77009; open to a discounted cash, as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hi Ejaz, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Ejaz, hi — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 14440 Chelsea St, Detroit, MI 48213. is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Good day Evan — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Evan — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 4203 New Orleans St, Houston, TX 77020 for cash. any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Franco, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 13027 Rosemary St, Detroit, MI 48213. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
+          <t>Franco, hi — Charles here with Paragon Government Solutions. I'm a cash investor looking at 13027 Rosemary St, Detroit, MI 48213. could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hi there Gaston. I'm Charles with Paragon Government Solutions, and interested in buying 15470 Mapleridge St, Detroit, MI 48205 for cash. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks much!</t>
+          <t>Good day Gaston, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 15470 Mapleridge St, Detroit, MI 48205 — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hey Graciela, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hello Graciela, Charles here with Paragon Government Solutions. I'm interested in buying 2519 Chalk Hill Rd, Dallas, TX 75212 for cash; would the owner entertain a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hi there Greg, Charles here with Paragon Government Solutions. interested in buying 20 Shuler Cir, Columbia, SC 29212 for cash. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
+          <t>Greg, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 20 Shuler Cir, Columbia, SC 29212. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Good day Gregory — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
+          <t>Gregory, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 4440 Sexton Rd, Cleveland, OH 44105. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hi there Hassan — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hassan, hi — my name's Charles Pleasant, Paragon Government Solutions. I came across 20569 Evergreen Rd, Detroit, MI 48219 and buy cash. would the owner entertain a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hey JACQUELYN, this is Charles Pleasant with Paragon Government Solutions. interested in buying 2371 JAYSON Avenue, Jacksonville, FL 32208 for cash. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
+          <t>JACQUELYN, hi. Charles here with Paragon Government Solutions, and I'm reaching out about 2371 JAYSON Avenue, Jacksonville, FL 32208. could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hi there James, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 14045 Sussex St, Detroit, MI 48227. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello James, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 14045 Sussex St, Detroit, MI 48227; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>JANET, hi, I'm Charles with Paragon Government Solutions. I'm reaching out about 412 CHESTNUT Drive, Jacksonville, FL 32208 — a cash purchase. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there JANET, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 412 CHESTNUT Drive, Jacksonville, FL 32208 — would the seller consider a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hi Jay — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
+          <t>Hey Jay. I'm Charles with Paragon Government Solutions, and I'm reaching out about 209 Leago St, Houston, TX 77022. any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hi Jessica, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 10066 S Van Vlissingen Rd, Chicago, IL 60617 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
+          <t>Hi there Jessica, Charles here with Paragon Government Solutions. I came across 10066 S Van Vlissingen Rd, Chicago, IL 60617 and buy cash; would the owner entertain a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hey JULIANA, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
+          <t>JULIANA, hi, Charles Pleasant, Paragon Government Solutions. I came across 1546 RIVER HILLS Circle W, Jacksonville, FL 32211 and buy cash; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hey Kaila. I'm Charles with Paragon Government Solutions, and interested in buying 17184 Dresden St, Detroit, MI 48205 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Good day Kaila. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 17184 Dresden St, Detroit, MI 48205. open to a discounted cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hi there Kanaan. Charles here with Paragon Government Solutions, and interested in buying 1018 W 104th Pl, Chicago, IL 60643 for cash. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Kanaan — I'm Charles with Paragon Government Solutions. I came across 1018 W 104th Pl, Chicago, IL 60643 and buy cash. would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hey Kendall, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3819 Uncas St, Baton Rouge, LA 70805 — a cash purchase. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
+          <t>Hello Kendall, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3819 Uncas St, Baton Rouge, LA 70805; open to a discounted cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hey Keri, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Hey Keri, Charles here with Paragon Government Solutions. I'm a cash investor looking at 11000 S Normal Ave, Chicago, IL 60628; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hello KRAVIN, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Hello KRAVIN. Charles here with Paragon Government Solutions, and I'm reaching out about 2051 FRANK E Avenue, Jacksonville, FL 32208. open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Good day Kristie — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Kristie, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 7604 Edgewater Dr, Columbia, SC 29223; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Good day LaToya, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hey LaToya. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1253 Rabon Pond Dr, Columbia, SC 29223. could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Good day LaTrina, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hi there LaTrina — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 19783 Annott St, Detroit, MI 48205. would the seller consider a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hello Leo — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Leo, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 3417 Gray St, Detroit, MI 48215 for cash — would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hi Lisa, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Lisa, hi, Charles here with Paragon Government Solutions. I'm interested in buying 1506 Grand Valley Dr, Houston, TX 77090 for cash; could the seller look at a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Logan, hi. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 15220 Tacoma St, Detroit, MI 48205. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Good day Logan, I'm Charles with Paragon Government Solutions. I'm interested in buying 15220 Tacoma St, Detroit, MI 48205 for cash; any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MAIDELYS, hi — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thank you!</t>
+          <t>Hello MAIDELYS — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6978 PAUL HOWARD Drive, Jacksonville, FL 32222. would the owner entertain a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hello Marcia — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Appreciate it!</t>
+          <t>Marcia, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 367 Marshdeer Way, Columbia, SC 29229; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hey Mary — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
+          <t>Good day Mary — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 336 Byron Rd, Columbia, SC 29209. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Hi there MATT, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there MATT, Charles here with Paragon Government Solutions. I came across 1311 GRANVDIEW Drive, Jacksonville, FL 32211 and buy cash; would the seller consider a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hi there McCall, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 1204 Vickie Ln, Lake Charles, LA 70601. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day McCall, I'm Charles with Paragon Government Solutions. I came across 1204 Vickie Ln, Lake Charles, LA 70601 and buy cash — could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hi there Medina, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1800 Walter St SE, Albuquerque, NM 87102. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hey Medina, Charles Pleasant, Paragon Government Solutions. I came across 1800 Walter St SE, Albuquerque, NM 87102 and buy cash — any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hey Michael, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Good day Michael, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 13594 Grandmont Ave, Detroit, MI 48227 for cash — open to a discounted cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Good day Minhaz. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 19989 Coventry St, Highland Park, MI 48203. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Minhaz, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 19989 Coventry St, Highland Park, MI 48203; would the seller consider a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hi Mladenka, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5308 W LEWIS Avenue W, Phoenix, AZ 85035. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Mladenka — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 5308 W LEWIS Avenue W, Phoenix, AZ 85035 for cash. is the seller open to a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hey Mo, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Good day Mo — Charles here with Paragon Government Solutions. I came across 125 N Lake Pointe Dr, Columbia, SC 29229 and buy cash. is the seller open to a cash as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mohamed, hi, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Good day Mohamed — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 16610 Collingham Dr, Detroit, MI 48205. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hey Monica. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 11548 S Normal Ave, Chicago, IL 60628. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Monica, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 11548 S Normal Ave, Chicago, IL 60628; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Good day Monika. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2947 Appaloosa Dr, Dallas, TX 75237. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Monika. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2947 Appaloosa Dr, Dallas, TX 75237. is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hello MOSES, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 5926 DUNMIRE Avenue, Jacksonville, FL 32219. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there MOSES, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 5926 DUNMIRE Avenue, Jacksonville, FL 32219 — is the seller open to a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Good day Nadia, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hi there Nadia — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 17206 Fenelon St, Detroit, MI 48212. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hello NAJI — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
+          <t>Good day NAJI. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 152 W 10TH Street, Jacksonville, FL 32206. is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hi Nazareth, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 2223 Gray St, Detroit, MI 48215. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hello Nazareth — my name's Charles Pleasant, Paragon Government Solutions. I came across 2223 Gray St, Detroit, MI 48215 and buy cash. could the seller look at a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Good day Pamela — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thank you!</t>
+          <t>Hello Pamela — Charles here with Paragon Government Solutions. I'm interested in buying 2912 Chestnut St, Columbia, SC 29204 for cash. would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Good day Rachel, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2539 Cherry St, Columbia, SC 29205 — a cash purchase. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
+          <t>Rachel, hi — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2539 Cherry St, Columbia, SC 29205. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hey Raquel, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Good day Raquel — I'm Charles with Paragon Government Solutions. I'm interested in buying 1513 Dianne Ct SE, Atlanta, GA for cash. is the seller open to a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hey RYAN, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
+          <t>RYAN, hi, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 1711 30TH Street W, Jacksonville, FL 32209 for cash — is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hi Sam. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1000 Coatesdale Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>Hey Sam, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1000 Coatesdale Rd, Columbia, SC 29209; could the seller look at a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hello Soraida. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 65 W 112th Pl, Chicago, IL 60628. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
+          <t>Hey Soraida, this is Charles Pleasant with Paragon Government Solutions. I came across 65 W 112th Pl, Chicago, IL 60628 and buy cash — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hi Starr, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1086 Horne St, Houston, TX 77088. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Hey Starr, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1086 Horne St, Houston, TX 77088; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hi there Sydney. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 425 Columbia St, Shreveport, LA 71104. Open to a discounted cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello Sydney — Charles here with Paragon Government Solutions. I came across 425 Columbia St, Shreveport, LA 71104 and buy cash. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hey Tarick, Charles here with Paragon Government Solutions. I'm a cash investor looking at 3331 S Liddesdale St, Detroit, MI 48217. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
+          <t>Tarick, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3331 S Liddesdale St, Detroit, MI 48217; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Timeka, hi, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi Timeka — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 2009 Las Cruces Ln, Dallas, TX 75217. open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hey Timothy. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 12729 Grandmont Ave, Detroit, MI 48227 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Timothy, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 12729 Grandmont Ave, Detroit, MI 48227 for cash; would the owner entertain a cash as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hi there Valerie — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
+          <t>Good day Valerie, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 16 Sand Spur Rd, Columbia, SC 29223; would the owner entertain a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hi there Verdieman, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Verdieman, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 20209 Stotter St, Detroit, MI 48234; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hi Will — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
+          <t>Will, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 9426 Nyssa St, Houston, TX 77078. is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hi there WILLIAM, Charles here with Paragon Government Solutions. I'm reaching out about 957 ODESSA Drive E, Jacksonville, FL 32254 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi WILLIAM, Charles here with Paragon Government Solutions. I'm a cash investor looking at 957 ODESSA Drive E, Jacksonville, FL 32254; open to a discounted cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hello WILLIAM. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2995 Coleman Rd, Eastover, NC 28312. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi there WILLIAM — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 2995 Coleman Rd, Eastover, NC 28312. would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Good day there. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1700 Grays Inn Rd, Columbia, SC 29210 — a cash purchase. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day there, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 1700 Grays Inn Rd, Columbia, SC 29210; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hi there — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 2412 E MARMORA Street, Phoenix, AZ 85032 — open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hey there. Charles here with Paragon Government Solutions, and I'm reaching out about 2737 Bristol Pl, New Orleans, LA 70131 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
+          <t>Good day there. this is Charles Pleasant with Paragon Government Solutions, and I came across 2737 Bristol Pl, New Orleans, LA 70131 and buy cash. could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hi there, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>there, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3109 Downes Grove Rd, Columbia, SC 29209; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hey there — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
+          <t>Good day there — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 950 W ROMA Avenue, Phoenix, AZ 85013. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Aaron, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 7535 S Vernon Ave, Chicago, IL 60619. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
+          <t>Hello Aaron, I'm Charles with Paragon Government Solutions. I'm reaching out about 7535 S Vernon Ave, Chicago, IL 60619 — could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Abe, hi, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 12621 Hirst Ave, Cleveland, OH 44135. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Abe, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 12621 Hirst Ave, Cleveland, OH 44135; could the seller look at a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Hi Acencion — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
+          <t>Acencion, hi — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 16643 Seawolf Dr, Houston, TX 77062. would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hi there Adam, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Hello Adam — Charles Pleasant, Paragon Government Solutions. I came across 15394 Freeland St, Detroit, MI 48227 and buy cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Adam, hi — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Adam, Charles here with Paragon Government Solutions. I'm reaching out about 195 Pomeroy Dr, Shreveport, LA 71115; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Good day Adekunle — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
+          <t>Good day Adekunle. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 11722 S Parnell Ave, Chicago, IL 60628. would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hi there Adrian, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Hi Adrian, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 2923 SW 11th Ct, Cape Coral, FL 33914; open to a discounted cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hey Adrian, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 15003 Manor St, Detroit, MI 48238. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
+          <t>Hi Adrian. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 15003 Manor St, Detroit, MI 48238. is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hi there Adrienne. Charles here with Paragon Government Solutions, and I'm reaching out about 18402 Revere St, Detroit, MI 48234 — a cash purchase. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
+          <t>Good day Adrienne — I'm Charles with Paragon Government Solutions. I'm interested in buying 18402 Revere St, Detroit, MI 48234 for cash. any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hi there Alana, this is Charles Pleasant with Paragon Government Solutions. interested in buying 4144 E 120th St, Cleveland, OH 44105 for cash. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Hello Alana, I'm Charles with Paragon Government Solutions. I came across 4144 E 120th St, Cleveland, OH 44105 and buy cash; is the seller open to a cash as-is offer, close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Good day Alannah — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Alannah. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 1314 Red Ridge Ter, Columbia, SC 29203. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hi Albert, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
+          <t>Hi Albert, Charles here with Paragon Government Solutions. I'm interested in buying 2321 Shadowbrook Dr, Baton Rouge, LA 70816 for cash; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hi Alejandro. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 919 Christine St, Houston, TX 77017. Would the seller consider a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks!</t>
+          <t>Hi Alejandro — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 919 Christine St, Houston, TX 77017. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Alex, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
+          <t>Hey Alex — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3906 Metropolitan Ave, Dallas, TX 75210. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Hello Alex. I'm Charles with Paragon Government Solutions, and interested in buying 8049 Wetherby St, Detroit, MI 48204 for cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
+          <t>Hello Alex, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 8049 Wetherby St, Detroit, MI 48204 — open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Hi Alex, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Alex, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 423 Exchange St, Houston, TX 77020 for cash. would the seller consider a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hi Alexander, I'm Charles with Paragon Government Solutions. I'm reaching out about 2317 NW 30th Ter, Cape Coral, FL 33993 — a cash purchase. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Alexander — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2317 NW 30th Ter, Cape Coral, FL 33993. open to a discounted cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Alexandria, hi — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Much appreciated!</t>
+          <t>Alexandria, hi. I'm Charles with Paragon Government Solutions, and I'm interested in buying 5981 Arapaho Rd #1607, Dallas TX 75248 for cash. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Hi Alexis, this is Charles Pleasant with Paragon Government Solutions. interested in buying 17360 Mansfield St, Detroit, MI 48235 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
+          <t>Good day Alexis. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 17360 Mansfield St, Detroit, MI 48235. would the seller consider a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hey Ali, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hi Ali — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 11718 Plainview Ave, Detroit, MI 48228. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hi there Ali, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Ali. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 9030 Plainview Ave, Detroit, MI 48228 for cash. is the seller open to a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Good day Alicia. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 4111 Mehalia Dr, Dallas, TX 75241 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Hi there Alicia, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 4111 Mehalia Dr, Dallas, TX 75241 — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Hello Allie, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 4737 Kildare Ave, Dallas, TX 75216. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day Allie, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 4737 Kildare Ave, Dallas, TX 75216 — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Good day Amanda. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 10323 Sweetbrook Dr, Houston, TX 77038. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
+          <t>Hey Amanda — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 10323 Sweetbrook Dr, Houston, TX 77038. is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Good day AMANDA. I'm Charles with Paragon Government Solutions, and I'm reaching out about 1009 Bugle Call Dr, Fayetteville, NC 28314 — a cash purchase. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
+          <t>Hello AMANDA. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1009 Bugle Call Dr, Fayetteville, NC 28314. open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Good day Amani. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 8826 Delilah St, Houston, TX 77033. Could the seller look at a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thank you!</t>
+          <t>Hello Amani, I'm Charles with Paragon Government Solutions. I'm interested in buying 8826 Delilah St, Houston, TX 77033 for cash; would the owner entertain a cash as-is offer, fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Good day AMBER. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 326 Conifer Dr, Fayetteville, NC 28314. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
+          <t>AMBER, hi, Charles here with Paragon Government Solutions. I'm a cash investor looking at 326 Conifer Dr, Fayetteville, NC 28314 — is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hi there Aminat — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks!</t>
+          <t>Good day Aminat, Charles here with Paragon Government Solutions. I'm a cash investor looking at 9404 Pinehaven Dr, Dallas, TX 75227 — is the seller open to a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hi Amy — Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Amy, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 1061 Lansing St, Detroit, MI 48209 for cash — is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hi there Amy, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hello Amy, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 2034 Lakeville Dr, Humble, TX 77339 for cash — any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>AMY, hi. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 7092 Pantego Dr, Fayetteville, NC 28314 for cash. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi AMY — Charles Pleasant, Paragon Government Solutions. I came across 7092 Pantego Dr, Fayetteville, NC 28314 and buy cash. would the owner entertain a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Andre, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 19447 Sunset St, Detroit, MI 48234. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Andre — Charles here with Paragon Government Solutions. I'm reaching out about 19447 Sunset St, Detroit, MI 48234. is the seller open to a cash as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Andrea, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Andrea, Charles Pleasant, Paragon Government Solutions. I came across 121 N 28th Ave, Phoenix, AZ 85009 and buy cash; could the seller look at a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hello Angel. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 7606 Blessing Ave, Austin, TX 78752. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Angel. this is Charles Pleasant with Paragon Government Solutions, and I came across 7606 Blessing Ave, Austin, TX 78752 and buy cash. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Angela, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 16 Carroll St, Trenton, NJ 08609 for cash. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thank you!</t>
+          <t>Hello Angela — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 16 Carroll St, Trenton, NJ 08609. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Hi there Angela. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 7748 S Langley Ave, Chicago, IL 60619. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Angela, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 7748 S Langley Ave, Chicago, IL 60619; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Hello Angela. Charles Pleasant, Paragon Government Solutions, and interested in buying 15719 Egret Field Ln, Houston, TX 77049 for cash. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
+          <t>Hello Angela, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 15719 Egret Field Ln, Houston, TX 77049 for cash — could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Good day Anthony. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 20185 Indiana St, Detroit, MI 48221. Is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Good day Anthony, Charles here with Paragon Government Solutions. I'm interested in buying 20185 Indiana St, Detroit, MI 48221 for cash; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Hello Anthony, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Anthony, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 19189 Appleton St, Detroit, MI 48219; is the seller open to a cash as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Hello Anthony, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 4141 Country Hill Dr, Baton Rouge, LA 70816 — a cash purchase. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Anthony, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 4141 Country Hill Dr, Baton Rouge, LA 70816 for cash — would the owner entertain a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hi there ANTHONY. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 2917 PARR Court E, Jacksonville, FL 32216. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks!</t>
+          <t>Hi there ANTHONY. Charles here with Paragon Government Solutions, and I came across 2917 PARR Court E, Jacksonville, FL 32216 and buy cash. would the seller consider a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Antisha, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 3677 Theodore St, Detroit, MI 48211. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi there Antisha, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3677 Theodore St, Detroit, MI 48211; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Good day ANTOINETTE — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks much!</t>
+          <t>Good day ANTOINETTE — Charles here with Paragon Government Solutions. I'm interested in buying 9419 SCADLOCKE Road, Jacksonville, FL 32208 for cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hey April, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 6510 Portsmouth Dr, Fayetteville, NC 28314. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Hey April — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 6510 Portsmouth Dr, Fayetteville, NC 28314. is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>APRYL, hi, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Good day APRYL — my name's Charles Pleasant, Paragon Government Solutions. I came across 2225 THIERVY Drive, Jacksonville, FL 32210 and buy cash. is the seller open to a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Good day Aram, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Aram, hi, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 7407 S May St, Chicago, IL 60621; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Hi Arianna, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hey Arianna. my name's Charles Pleasant, Paragon Government Solutions, and I came across 4153 Concord St, Detroit, MI 48207 and buy cash. would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Hi there Arianne, I'm Charles with Paragon Government Solutions. interested in buying 9823 S Drexel Ave, Chicago, IL 60628 for cash. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
+          <t>Arianne, hi, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 9823 S Drexel Ave, Chicago, IL 60628 for cash — is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hi Arkadiusz — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Arkadiusz, my name's Charles Pleasant, Paragon Government Solutions. I came across 2459 E 74th St, Chicago, IL 60649 and buy cash — is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>ARMANDO, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 153 Knapp Ave, Hamilton, NJ 08610. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
+          <t>Hello ARMANDO — Charles here with Paragon Government Solutions. I'm a cash investor looking at 153 Knapp Ave, Hamilton, NJ 08610. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Hello Asa. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 18310 La Salle Ave, Cleveland, OH 44119. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
+          <t>Asa, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 18310 La Salle Ave, Cleveland, OH 44119; would the owner entertain a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Good day Ashley, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3879 W 21st St, Cleveland, OH 44109. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Ashley — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3879 W 21st St, Cleveland, OH 44109. any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hey Ashley — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Appreciate it!</t>
+          <t>Hello Ashley — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 414 Angel Grove Ln, Columbia, SC 29210. open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Hi Ashley — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
+          <t>Hi Ashley. my name's Charles Pleasant, Paragon Government Solutions, and I came across 1008 Walnut Ave, Baltimore, MD 21229 and buy cash. is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Hi there Ashley, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 19261 Mitchell St, Detroit, MI 48234. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi Ashley — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 19261 Mitchell St, Detroit, MI 48234. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>ATIFA, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hello ATIFA, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 6819 N PEARL Street, Jacksonville, FL 32208 — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Hi Austin, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Austin, hi, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 4220-22 S Miro St, New Orleans, LA 70125 — is the seller open to a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Hello Babajide, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey Babajide — I'm Charles with Paragon Government Solutions. I came across 317 E 134th St, Chicago, IL 60827 and buy cash. is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Good day Bailee, Charles here with Paragon Government Solutions. I'm reaching out about 11144 Sanford St, Detroit, MI 48205 — a cash purchase. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Hi Bailee. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 11144 Sanford St, Detroit, MI 48205. would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hi there Barbara, I'm Charles with Paragon Government Solutions. interested in buying 2336 Albert St, Alexandria, LA 71301 for cash. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hello Barbara — Charles here with Paragon Government Solutions. I'm a cash investor looking at 2336 Albert St, Alexandria, LA 71301. would the seller consider a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Hi BARBARA, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 1603 W 14TH Street, Jacksonville, FL 32209. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
+          <t>Hey BARBARA — my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1603 W 14TH Street, Jacksonville, FL 32209. open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Hello BARD, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 651 W 46TH Street, Jacksonville, FL 32208. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi there BARD, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 651 W 46TH Street, Jacksonville, FL 32208 — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Hi Becky, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there Becky, Charles here with Paragon Government Solutions. I'm interested in buying 3830 E LAKEWOOD Parkway E #2057, Phoenix, AZ 85048 for cash — open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Good day Belle. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 413 Seton Hall Dr, Columbia, SC 29223 — a cash purchase. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Hello Belle — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 413 Seton Hall Dr, Columbia, SC 29223. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Hi there Benjamin. I'm Charles with Paragon Government Solutions, and I'm reaching out about 1005 Wildwood Ave, Columbia, SC 29203 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
+          <t>Hi Benjamin — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1005 Wildwood Ave, Columbia, SC 29203. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Hey Benjamin — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks!</t>
+          <t>Good day Benjamin, this is Charles Pleasant with Paragon Government Solutions. I came across 15668 Tacoma St, Detroit, MI 48205 and buy cash — would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Good day Bianca. I'm Charles with Paragon Government Solutions, and interested in buying 2609 Foerster Ave, Baltimore, MD 21230 for cash. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hello Bianca, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 2609 Foerster Ave, Baltimore, MD 21230 — any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Blodgie, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hey Blodgie, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1215 Oregon St, Bakersfield, CA 93305 — would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Hey Brad, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi Brad, Charles Pleasant, Paragon Government Solutions. I came across 5765 Kleinpeter Rd, Baton Rouge, LA 70811 and buy cash; open to a discounted cash, as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Good day Brandon, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Brandon, I'm Charles with Paragon Government Solutions. I came across 4384 Stumberg Ln, Baton Rouge, LA 70816 and buy cash; would the owner entertain a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Brandon, hi. Charles Pleasant, Paragon Government Solutions, and interested in buying 15237 Carlisle St, Detroit, MI 48205 for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Brandon. Charles here with Paragon Government Solutions, and I'm interested in buying 15237 Carlisle St, Detroit, MI 48205 for cash. is the seller open to a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Hi Brandt, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Brandt, I'm Charles with Paragon Government Solutions. I'm reaching out about 12610 S Coast Dr, Houston, TX 77047; open to a discounted cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Hey Brian, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hey Brian. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 30 Ward Ct, Columbia, SC 29223. would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Hi there Brian — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
+          <t>Hi there Brian. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 1648 Tampa Bay Dr, Dallas, TX 75217. would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hi Brianna. Charles here with Paragon Government Solutions, and I'm reaching out about 6015 N 32nd Dr, Phoenix, AZ 85017 — a cash purchase. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi Brianna — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 6015 N 32nd Dr, Phoenix, AZ 85017 for cash. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hi Bridget — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
+          <t>Hi Bridget, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 7522 S Vernon Ave, Chicago, IL 60619 for cash — is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Good day BRIGIDA. Charles Pleasant, Paragon Government Solutions, and interested in buying 156 Washington St, Trenton, NJ 08611 for cash. Open to a discounted cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Hello BRIGIDA, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 156 Washington St, Trenton, NJ 08611 — is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Brittany, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 7400 Vanderkloot Ave, New Orleans, LA 70127. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thank you!</t>
+          <t>Hey Brittany, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 7400 Vanderkloot Ave, New Orleans, LA 70127; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Good day Bryton, Charles here with Paragon Government Solutions. I'm a cash investor looking at 8215 Leather Market St, Houston, TX 77064. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
+          <t>Bryton, hi — Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 8215 Leather Market St, Houston, TX 77064. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hi there Camellia, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Hello Camellia, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 1141 E 140th St, Cleveland, OH 44110 — would the seller consider a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Hi there Carlton, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Carlton, hi, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 911 S Stadium Rd #A-31, Columbia, SC 29201; could the seller look at a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Hi Carly, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 10316 Ridge Oak St, Dallas, TX 75227. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Carly. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 10316 Ridge Oak St, Dallas, TX 75227. any chance the seller would take a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Hello Carmen — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Carmen, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 3883 Turtle Creek Blvd #1603, Dallas TX 75219 for cash; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Carmen, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Carmen. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 7216 OAKWOOD Drive, Jacksonville, FL 32211. is the seller open to a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Good day Carmen. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 7419 Lake June Rd, Dallas, TX 75217 — a cash purchase. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hey Carmen, Charles here with Paragon Government Solutions. I came across 7419 Lake June Rd, Dallas, TX 75217 and buy cash; could the seller look at a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Good day Carolinas, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 4723 Linden St, Columbia, SC 29203. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day Carolinas — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 4723 Linden St, Columbia, SC 29203. would the seller consider a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Good day Carolyn, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Carolyn, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 7201 S Vernon Ave, Chicago, IL 60619. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Hello Carolyn, I'm Charles with Paragon Government Solutions. interested in buying 2755 Palmyra St, New Orleans, LA 70119 for cash. Would the owner entertain a cash as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
+          <t>Carolyn, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2755 Palmyra St, New Orleans, LA 70119; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Good day Carolyn, Charles here with Paragon Government Solutions. I'm a cash investor looking at 6702 Tierwester St, Houston, TX 77021. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
+          <t>Good day Carolyn, Charles here with Paragon Government Solutions. I'm interested in buying 6702 Tierwester St, Houston, TX 77021 for cash — open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hi there Carrie — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks!</t>
+          <t>Carrie, hi. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1663 W 30th St, Jacksonville, FL 32209. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Carrie, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 4243 Mandel Dr, Columbia, SC 29210 — a cash purchase. Is the seller open to a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
+          <t>Hello Carrie — this is Charles Pleasant with Paragon Government Solutions. I came across 4243 Mandel Dr, Columbia, SC 29210 and buy cash. could the seller look at a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Caryn, hi, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Caryn — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 10017 Morocco Rd, Houston, TX 77041. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Hi there Casey. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 3414 Maybank St, Columbia, SC 29204. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi there Casey — Charles here with Paragon Government Solutions. I came across 3414 Maybank St, Columbia, SC 29204 and buy cash. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Hey Casey, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 2610 Brandon St, Dallas, TX 75211 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Casey, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 2610 Brandon St, Dallas, TX 75211 — would the owner entertain a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hi Cassandra. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 314 Capehill Dr, Webster, TX 77598. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
+          <t>Hi Cassandra, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 314 Capehill Dr, Webster, TX 77598; could the seller look at a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hello CATHLEEN, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 339 METZ Street, Jacksonville, FL 32211. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks much!</t>
+          <t>Good day CATHLEEN, Charles here with Paragon Government Solutions. I'm interested in buying 339 METZ Street, Jacksonville, FL 32211 for cash — open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Hey CC, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hey CC — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 5418 MINOSA Court, Jacksonville, FL 32209. could the seller look at a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Hello Celia — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there Celia, my name's Charles Pleasant, Paragon Government Solutions. I came across 2530 Marling Dr, Columbia, SC 29204 and buy cash; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Good day Century. I'm Charles with Paragon Government Solutions, and interested in buying 1033 Glencroft Drive, Columbia, SC 29210 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
+          <t>Good day Century — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1033 Glencroft Drive, Columbia, SC 29210. open to a discounted cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Hey Century — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hello Century, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 5411 Cabot Ave, Columbia, SC 29203 for cash — open to a discounted cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Good day Cerita, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 528 1st St SW, Birmingham, AL 35211. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Hey Cerita. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 528 1st St SW, Birmingham, AL 35211. open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Hello Chad, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi Chad. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 2426 Dora Ave NW, Albuquerque, NM 87104 for cash. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Hi there Chad, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
+          <t>Hello Chad, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 4012 Shady Hollow Ln, Dallas, TX 75233 for cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hi there CHARLEEN, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey CHARLEEN, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3821 MIRUELO Circle N, Jacksonville, FL 32217 — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Hi there Charles, this is Charles Pleasant with Paragon Government Solutions. interested in buying 217 Stockmoor Rd, Columbia, SC 29212 for cash. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
+          <t>Hi there Charles, I'm Charles with Paragon Government Solutions. I'm interested in buying 217 Stockmoor Rd, Columbia, SC 29212 for cash — would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Hi Charles, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 334 Carver St, Lafayette, LA 70501. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Good day Charles. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 334 Carver St, Lafayette, LA 70501. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Good day Cherie, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 4731 Stokes St, Dallas, TX 75216 for cash. Could the seller look at a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
+          <t>Cherie, hi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 4731 Stokes St, Dallas, TX 75216; could the seller look at a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Hey CHERYL, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hello CHERYL. Charles here with Paragon Government Solutions, and I'm interested in buying 9711 SKYDIVE Court, Jacksonville, FL 32221 for cash. open to a discounted cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Good day Chip, Charles Pleasant, Paragon Government Solutions. interested in buying 329 Shagbark Ave, Columbia, SC 29209 for cash. Is the seller open to a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
+          <t>Hello Chip — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 329 Shagbark Ave, Columbia, SC 29209. is the seller open to a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Hi Chip — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Chip. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 329 Shagbark Ave, Columbia, SC 29209. any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Hello Chip — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Chip, Charles here with Paragon Government Solutions. I'm reaching out about 1905 E Kings Hwy, Shreveport, LA 71105; would the owner entertain a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Hello Chris — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
+          <t>Hello Chris, I'm Charles with Paragon Government Solutions. I came across 106 Harbor Dr, Columbia, SC 29229 and buy cash — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Chris, hi — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
+          <t>Hey Chris — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3405 Gwynns Falls Pkwy, Baltimore, MD 21216. could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hi CHRIS, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>CHRIS, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 2332 BUTTONWOOD Drive, Jacksonville, FL 32216 for cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Good day Chris, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Chris — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 3804 Park Heights Ave, Baltimore, MD 21215. open to a discounted cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Hi Chris. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 8315 Westbourne Dr, Charlotte, NC 28216. Would the owner entertain a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
+          <t>Hello Chris, I'm Charles with Paragon Government Solutions. I came across 8315 Westbourne Dr, Charlotte, NC 28216 and buy cash — open to a discounted cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Hello Christina, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Christina, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2776 Prince Charles Ct, Columbia, SC 29209; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Hi there Christine. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2633 W Grand Blvd, Detroit, MI 48208. Open to a discounted cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thank you!</t>
+          <t>Hi there Christine — I'm Charles with Paragon Government Solutions. I'm reaching out about 2633 W Grand Blvd, Detroit, MI 48208. any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hello CHRISTOPHER — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
+          <t>CHRISTOPHER, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 1404 Valencia Dr, Fayetteville, NC 28303. could the seller look at a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hello Christopher, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 7741 S Chappel Ave, Chicago, IL 60649 for cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
+          <t>Hey Christopher, Charles Pleasant, Paragon Government Solutions. I came across 7741 S Chappel Ave, Chicago, IL 60649 and buy cash — would the seller consider a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hello Chuck. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 711 S Montclair Ave, Dallas, TX 75208. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
+          <t>Good day Chuck — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 711 S Montclair Ave, Dallas, TX 75208. is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Good day Cindy — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
+          <t>Cindy, hi — I'm Charles with Paragon Government Solutions. I'm interested in buying 2237 Kingswood Dr, Columbia, SC 29205 for cash. could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Hi Cindy — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Cindy, Charles here with Paragon Government Solutions. I'm reaching out about 11349 S Saint Lawrence Ave, Chicago, IL 60628; could the seller look at a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Hello Cindy, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 1703 Alba Dr, Columbia, SC 29209. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Cindy, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 1703 Alba Dr, Columbia, SC 29209. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Good day Cindy, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 10527 Cayuga Dr, Dallas, TX 75228. Open to a discounted cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thank you!</t>
+          <t>Hi there Cindy, Charles here with Paragon Government Solutions. I'm a cash investor looking at 10527 Cayuga Dr, Dallas, TX 75228; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Hi Clarence, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Clarence — Charles here with Paragon Government Solutions. I'm a cash investor looking at 7707 Candlegreen Ln, Houston, TX 77071. would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Hi there Claudia. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 20495 Mendota St, Detroit, MI 48221. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Claudia. I'm Charles with Paragon Government Solutions, and I'm interested in buying 20495 Mendota St, Detroit, MI 48221 for cash. any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Hi there Clay. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1522 W Taylor St, Phoenix, AZ 85007. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi Clay — this is Charles Pleasant with Paragon Government Solutions. I came across 1522 W Taylor St, Phoenix, AZ 85007 and buy cash. is the seller open to a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Cliff, hi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 11604 Tuscora Ave, Cleveland, OH 44108. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
+          <t>Good day Cliff. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 11604 Tuscora Ave, Cleveland, OH 44108. would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Coby, hi. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 5906 Bower Ave, Cleveland, OH 44127. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
+          <t>Hi there Coby — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 5906 Bower Ave, Cleveland, OH 44127. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Good day Cody, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6348 S Rhodes Ave, Chicago, IL 60637. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Cody, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 6348 S Rhodes Ave, Chicago, IL 60637 — would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Hey Cole. I'm Charles with Paragon Government Solutions, and interested in buying 417 W Brooklyn Ave, Dallas, TX 75208 for cash. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
+          <t>Cole, hi, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 417 W Brooklyn Ave, Dallas, TX 75208; could the seller look at a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Hi Colleen. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3945 Liberty Ave, Pittsburgh, PA 15224. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
+          <t>Colleen, hi — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3945 Liberty Ave, Pittsburgh, PA 15224. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Hello Comeiko, this is Charles Pleasant with Paragon Government Solutions. interested in buying 4971 Brigadoon Ln, Dallas, TX 75216 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
+          <t>Hello Comeiko. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 4971 Brigadoon Ln, Dallas, TX 75216. could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Hi there Compass. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 1011 Ormewood Ave SE, Atlanta, GA 30316. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Compass, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1011 Ormewood Ave SE, Atlanta, GA 30316 — would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Hi Connie — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
+          <t>Hey Connie, I'm Charles with Paragon Government Solutions. I came across 8133 Cavalier Cir, Dallas TX 75227 and buy cash — would the owner entertain a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Conor, hi, Charles here with Paragon Government Solutions. I'm a cash investor looking at 937 Avenue S, Birmingham, AL 35214. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks!</t>
+          <t>Hey Conor — this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 937 Avenue S, Birmingham, AL 35214 for cash. is the seller open to a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Hi there Corey, my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
+          <t>Corey, hi, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3503 Oakmont Ave, Baltimore, MD 21215 — open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Hey Corey. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 16410 Novara St, Detroit, MI 48205. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Corey, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 16410 Novara St, Detroit, MI 48205; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Cory, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 5747 Easthampton Dr Unit D, Houston, TX 77039. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Cory — I'm Charles with Paragon Government Solutions. I'm reaching out about 5747 Easthampton Dr Unit D, Houston, TX 77039. would the owner entertain a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Hello Crystal. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 4010 Copeland St, Dallas, TX 75210. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Crystal — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 4010 Copeland St, Dallas, TX 75210. open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Hey Crystal, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 5201 W Camelback Rd Lot A174, Phoenix, AZ 85031. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
+          <t>Good day Crystal, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 5201 W Camelback Rd Lot A174, Phoenix, AZ 85031 — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CYNDI, hi. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1722 Berriedale Dr, Fayetteville, NC 28304. Is the seller open to a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day CYNDI, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1722 Berriedale Dr, Fayetteville, NC 28304 for cash; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Good day D.R. — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
+          <t>Good day D.R. — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying Ledoux Plan, Trivento, Baker, LA 70714 for cash. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Good day D.R., my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi D.R. — I'm Charles with Paragon Government Solutions. I came across Ledoux Plan, Zachary Trails at Meadow View, Zachary, LA 70791 and buy cash. any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Hello Daisy, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day Daisy. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 4534 S Honore St, Chicago, IL 60609. would the owner entertain a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Hello Dan, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1401 Kirby St NE, Albuquerque, NM 87112 — a cash purchase. Is the seller open to a cash as-is offer, close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Dan. I'm Charles with Paragon Government Solutions, and I came across 1401 Kirby St NE, Albuquerque, NM 87112 and buy cash. could the seller look at a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Hi DANA, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey DANA, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 8064 KILWINNING Lane, Jacksonville, FL 32244 — would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Good day Dana. I'm Charles with Paragon Government Solutions, and interested in buying 11831 Bee Ln, Houston, TX 77067 for cash. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Dana — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 11831 Bee Ln, Houston, TX 77067. would the owner entertain a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>DANIEL, hi — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thank you!</t>
+          <t>Hi DANIEL, Charles here with Paragon Government Solutions. I'm reaching out about 5050 SAN JUAN Avenue, Jacksonville, FL 32210; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>DANIEL, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day DANIEL. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 22 MONTE Street, Jacksonville, FL 32254 for cash. is the seller open to a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Daniel, hi, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hello Daniel — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 20489 Andover St, Highland Park, MI 48203. would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Hi DANIELE. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1494 8TH Street W, Jacksonville, FL 32209 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there DANIELE, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1494 8TH Street W, Jacksonville, FL 32209; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Hey Danielle. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 18281 Lancashire St, Detroit, MI 48223 — a cash purchase. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Danielle — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 18281 Lancashire St, Detroit, MI 48223. would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Hi there DANYELLE, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>DANYELLE, hi, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3053 RAY Road, Jacksonville, FL 32209; would the owner entertain a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Hi Darius, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1825 N 17th St, Baton Rouge, LA 70802. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
+          <t>Hi Darius. Charles here with Paragon Government Solutions, and I'm reaching out about 1825 N 17th St, Baton Rouge, LA 70802. is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Hi there Darrin, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hi Darrin — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3507 E SANDRA Terrace, Phoenix, AZ 85032. could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Hi there Darryl, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Hi Darryl, I'm Charles with Paragon Government Solutions. I'm reaching out about 7809 Capitol St, Houston, TX 77012; open to a discounted cash, as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Hello Darryl, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 19151 Rowe St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello Darryl, Charles here with Paragon Government Solutions. I'm a cash investor looking at 19151 Rowe St, Detroit, MI 48205 — open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Darryl, hi — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
+          <t>Darryl, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 184 Springway Dr, Columbia, SC 29209 for cash; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Good day Darryn — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thank you!</t>
+          <t>Hi Darryn, I'm Charles with Paragon Government Solutions. I came across 15870 W Parkway St, Detroit, MI 48223 and buy cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Hey Daryl. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 20520 Dresden St, Detroit, MI 48205. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi Daryl, Charles here with Paragon Government Solutions. I came across 20520 Dresden St, Detroit, MI 48205 and buy cash — open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Good day David. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 116 Larchwood Dr, Columbia, SC 29203. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there David — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 116 Larchwood Dr, Columbia, SC 29203. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Good day David. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 11905 Shadeland Ave, Cleveland, OH 44108. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi David, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 11905 Shadeland Ave, Cleveland, OH 44108 for cash — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Hello David — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
+          <t>Good day David — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 712 Thaxton Ave SE, Albuquerque, NM 87102. would the owner entertain a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Hi there David — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks much!</t>
+          <t>David, hi — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 6 Crescent Ln, Columbia, SC 29212. any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Hi David, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Hi David. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 139 Spruce St, Bakersfield, CA 93304 for cash. would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Hi there David — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey David. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 2631 Mike St, Dallas, TX 75212. could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Hi there David, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi David. Charles here with Paragon Government Solutions, and I'm reaching out about 19182 Hickory St, Detroit, MI 48205. could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Good day DAVID — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Much appreciated!</t>
+          <t>DAVID, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 311 Glen Canyon Dr, Fayetteville, NC 28303. would the owner entertain a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Dayton, hi. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 6338 Firestone Pkwy, San Antonio, TX 78244. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks!</t>
+          <t>Hello Dayton, I'm Charles with Paragon Government Solutions. I came across 6338 Firestone Pkwy, San Antonio, TX 78244 and buy cash; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Hey De'Chella, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3309 E 146th St, Cleveland, OH 44120. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
+          <t>De'Chella, hi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 3309 E 146th St, Cleveland, OH 44120 — would the seller consider a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Hey Dean — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
+          <t>Hi there Dean — my name's Charles Pleasant, Paragon Government Solutions. I came across 3497 W 46th St, Cleveland, OH 44102 and buy cash. would the owner entertain a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Hey Deanna, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1811 Reynoldston Ln, Dallas, TX 75232. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi Deanna, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1811 Reynoldston Ln, Dallas, TX 75232; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Hi Debbie — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
+          <t>Hi Debbie, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3508 S Mozart St, Chicago, IL 60632; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Deborah, hi — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
+          <t>Hello Deborah — Charles here with Paragon Government Solutions. I'm interested in buying 10147 S State St, Chicago, IL 60628 for cash. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Hi DEIRDRA, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 6818 MERRILL Court, Jacksonville, FL 32211. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day DEIRDRA. Charles here with Paragon Government Solutions, and I'm interested in buying 6818 MERRILL Court, Jacksonville, FL 32211 for cash. open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Hi Demetria, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi Demetria — Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 6511 Brook Ave, Baltimore, MD 21206. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Hey Dena, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Dena — I'm Charles with Paragon Government Solutions. I came across 301 Squire Rd, Columbia, SC 29223 and buy cash. would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Hey Denise, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Denise, hi, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 7613 Parker Rd, Houston, TX 77016; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Hi there DENISE — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there DENISE, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 502 Santa Fe Dr, Fayetteville, NC 28303 — is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Good day Deven, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Deven — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 7700 S Lowe Ave, Chicago, IL 60620 for cash. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Good day DEXTER, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>DEXTER, hi, Charles here with Paragon Government Solutions. I'm interested in buying 1145 E 14TH Street, Jacksonville, FL 32206 for cash; would the owner entertain a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Hi Dexter, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 639 E 90th Pl, Chicago, IL 60619. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks so much!</t>
+          <t>Hello Dexter — this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 639 E 90th Pl, Chicago, IL 60619 for cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Good day Diana, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Diana, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 18968 E Northlawn St E, Detroit, MI 48221. is the seller open to a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Hello Diane. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2024 Elmridge Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Diane, hi — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 2024 Elmridge Rd, Columbia, SC 29209. would the seller consider a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>DMITRIY, hi — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks much!</t>
+          <t>Hi there DMITRIY. Charles here with Paragon Government Solutions, and I'm interested in buying 5527 MAXINE Drive, Jacksonville, FL 32277 for cash. is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Good day Don, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 13159 Todd Ave, Baton Rouge, LA 70815. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
+          <t>Hi Don, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 13159 Todd Ave, Baton Rouge, LA 70815; would the seller consider a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Hey Donna, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 8529 S May St, Chicago, IL 60620. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thank you!</t>
+          <t>Good day Donna. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 8529 S May St, Chicago, IL 60620. would the seller consider a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Hey Donnie — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thank you!</t>
+          <t>Good day Donnie, Charles here with Paragon Government Solutions. I'm a cash investor looking at 1778 Jackson Ave, Memphis, TN 38107; any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Hello Doreen, this is Charles Pleasant with Paragon Government Solutions. interested in buying 3506 Rosedale Rd, Baltimore, MD 21215 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
+          <t>Hi Doreen, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 3506 Rosedale Rd, Baltimore, MD 21215 — open to a discounted cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Hi there Douglas — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
+          <t>Hello Douglas. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 7111 Bart Hollow, San Antonio, TX 78250. is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Hey Doxie — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
+          <t>Hi Doxie — Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 987 E 129th St, Cleveland, OH 44108. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Hey Dr. Charles Pleasant, Paragon Government Solutions, and interested in buying 7909 Sagebrook Rd, Columbia, SC 29223 for cash. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
+          <t>Hi Dr, this is Charles Pleasant with Paragon Government Solutions. I came across 7909 Sagebrook Rd, Columbia, SC 29223 and buy cash — would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Good day Drew, I'm Charles with Paragon Government Solutions. interested in buying 4137 W 157th St, Cleveland, OH 44135 for cash. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
+          <t>Good day Drew. Charles Pleasant, Paragon Government Solutions, and I came across 4137 W 157th St, Cleveland, OH 44135 and buy cash. any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Hi there Dulcey. I'm Charles with Paragon Government Solutions, and I'm reaching out about 18011 Windward Rd, Cleveland, OH 44119 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Hello Dulcey, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 18011 Windward Rd, Cleveland, OH 44119 — is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Hello Dustin, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Dustin, hi, Charles here with Paragon Government Solutions. I'm reaching out about 1861 Torbenson Dr, Cleveland, OH 44112; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Good day DWAYNE. Charles here with Paragon Government Solutions, and interested in buying 5919 SONORA Drive W, Jacksonville, FL 32244 for cash. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello DWAYNE — Charles here with Paragon Government Solutions. I came across 5919 SONORA Drive W, Jacksonville, FL 32244 and buy cash. is the seller open to a cash as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Good day Ebony. Charles here with Paragon Government Solutions, and interested in buying 3237 W 30th St, Cleveland, OH 44109 for cash. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Ebony, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 3237 W 30th St, Cleveland, OH 44109; could the seller look at a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Hey Edgardo, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 7949 S Manistee Ave, Chicago, IL 60617 — a cash purchase. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
+          <t>Edgardo, hi — I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 7949 S Manistee Ave, Chicago, IL 60617. open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Eduardo, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 5223 Heathercrest St, Houston, TX 77045. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Hi Eduardo, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5223 Heathercrest St, Houston, TX 77045 — is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Hello Eduardo — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
+          <t>Eduardo, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 6700 S Stewart Ave, Chicago, IL 60621 — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Hello Edward. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 217 S Shields Rd, Columbia, SC 29223 — a cash purchase. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Edward, hi — Charles here with Paragon Government Solutions. I'm a cash investor looking at 217 S Shields Rd, Columbia, SC 29223. open to a discounted cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Good day Edward, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 6633 Sandstone St, Houston, TX 77074. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Edward, hi — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 6633 Sandstone St, Houston, TX 77074. would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Edward, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 13 Winding Way, Trenton, NJ 08620. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Good day Edward — Charles here with Paragon Government Solutions. I'm reaching out about 13 Winding Way, Trenton, NJ 08620. would the seller consider a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Hi Edwin. Charles here with Paragon Government Solutions, and interested in buying 19338 Teppert St, Detroit, MI 48234 for cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi Edwin — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 19338 Teppert St, Detroit, MI 48234. open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Eileen, hi — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks!</t>
+          <t>Good day Eileen — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 10121 Jasper Ave, Cleveland, OH 44111. open to a discounted cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Hey ELISABETH, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello ELISABETH, this is Charles Pleasant with Paragon Government Solutions. I came across 2121 EGNER Street, Jacksonville, FL 32206 and buy cash — is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Good day Elizabeth, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Elizabeth, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1356 W 112th St, Cleveland, OH 44102 — open to a discounted cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Hi Elizabeth — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thank you!</t>
+          <t>Elizabeth, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 5308 Foxfire Road, Fayetteville, NC 28303; could the seller look at a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Hello Elizabeth — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
+          <t>Elizabeth, hi, this is Charles Pleasant with Paragon Government Solutions. I came across 2009 NE 13th PL, Cape Coral, FL 33909 and buy cash — would the owner entertain a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Hi there ELLEN, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hey ELLEN, I'm Charles with Paragon Government Solutions. I'm interested in buying 5051 LEXINGTON Avenue, Jacksonville, FL 32210 for cash — would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Hi there Elliot. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 7901 New York Ave, Cleveland, OH 44105. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
+          <t>Hi there Elliot, Charles here with Paragon Government Solutions. I'm reaching out about 7901 New York Ave, Cleveland, OH 44105; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Hey Emil — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
+          <t>Hello Emil, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 8128 S Coles Ave, Chicago, IL 60617 — any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>ERIC, hi — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks!</t>
+          <t>Hi there ERIC, I'm Charles with Paragon Government Solutions. I'm reaching out about 9324 NORFOLK Boulevard, Jacksonville, FL 32208; open to a discounted cash, as-is offer, quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Hello Erick. Charles here with Paragon Government Solutions, and interested in buying 18710 McCormick St, Detroit, MI 48224 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi there Erick. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 18710 McCormick St, Detroit, MI 48224. open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Hi there Esmeralda — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Esmeralda. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 105 Dresden St, Houston, TX 77012. is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Hey Eve. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 11224 S Stewart Ave, Chicago, IL 60628. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi Eve — this is Charles Pleasant with Paragon Government Solutions. I came across 11224 S Stewart Ave, Chicago, IL 60628 and buy cash. is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Hi there EXP, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 2012 Bolt Dr, Anderson, SC 29621. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Hi there EXP, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 2012 Bolt Dr, Anderson, SC 29621; any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Hi there Fadie — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
+          <t>Fadie, hi. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 6324 Annland St, Detroit, MI 48204. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Hey Fany — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks much!</t>
+          <t>Good day Fany, Charles here with Paragon Government Solutions. I came across 5935 Glenhurst Dr, Houston, TX 77033 and buy cash — would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Good day Felicia — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
+          <t>Hello Felicia. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 6953 S Elizabeth St, Chicago, IL 60636 for cash. is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Hello Floyd, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 6525 Palm Island St, Dallas, TX 75241. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thank you!</t>
+          <t>Good day Floyd, Charles here with Paragon Government Solutions. I'm reaching out about 6525 Palm Island St, Dallas, TX 75241 — any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Hey Francisco, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 921 S 3RD Avenue, Phoenix, AZ 85003. Is the seller open to a cash as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
+          <t>Good day Francisco — I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 921 S 3RD Avenue, Phoenix, AZ 85003. open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Francisco, hi. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 11432 S Wentworth Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Francisco, hi. I'm Charles with Paragon Government Solutions, and I'm interested in buying 11432 S Wentworth Ave, Chicago, IL 60628 for cash. any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Hi Francys. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 18433 Norwood St, Detroit, MI 48234. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks much!</t>
+          <t>Hey Francys, Charles here with Paragon Government Solutions. I'm a cash investor looking at 18433 Norwood St, Detroit, MI 48234 — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Hi there Frank, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hey Frank, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 10471 Nottingham Rd, Detroit, MI 48224; could the seller look at a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Hello Frank, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Frank, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 9137 S Essex Ave, Chicago, IL 60617; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Hey Frank. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 7800 S Kimbark Ave, Chicago, IL 60619. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
+          <t>Frank, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 7800 S Kimbark Ave, Chicago, IL 60619. open to a discounted cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Frederick, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 818 Winters St, Dallas, TX 75216. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
+          <t>Good day Frederick, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 818 Winters St, Dallas, TX 75216 — is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Funmi, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 8745 S Euclid Ave, Chicago, IL 60617. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello Funmi, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 8745 S Euclid Ave, Chicago, IL 60617 for cash; would the seller consider a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Hey Gabe — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks!</t>
+          <t>Hi Gabe — I'm Charles with Paragon Government Solutions. I came across 9601 Silk Ave, Cleveland, OH 44102 and buy cash. open to a discounted cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Good day GABRIELA, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello GABRIELA, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 12221 SAND LAKE Court, Jacksonville, FL 32218; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Hi there Gabrielle, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 203 May Oak Rd, Columbia, SC 29229. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Gabrielle, my name's Charles Pleasant, Paragon Government Solutions. I came across 203 May Oak Rd, Columbia, SC 29229 and buy cash — could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Hey GARY, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hey GARY. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 113 Starhill Ave, Fayetteville, NC 28303. open to a discounted cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Gaymon, hi, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 113 Salusbury Ln, Columbia, SC 29229. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Gaymon — this is Charles Pleasant with Paragon Government Solutions. I came across 113 Salusbury Ln, Columbia, SC 29229 and buy cash. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Hey Genaro — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
+          <t>Hi Genaro, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 8525 Oak Haven Ln, Dallas, TX 75217 for cash; any chance the seller would take a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Hi Gene. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 192 Dunham Rd, Columbia, SC 29209. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Gene — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 192 Dunham Rd, Columbia, SC 29209. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Hi Geraldine. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 16779 Greenview Ave, Detroit, MI 48219 — a cash purchase. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Geraldine, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 16779 Greenview Ave, Detroit, MI 48219; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Gerielynn, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 16770 Greenlawn St, Detroit, MI 48221. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there Gerielynn, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 16770 Greenlawn St, Detroit, MI 48221 for cash; any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Hi Gerilet. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 5147 BROKEN ARROW Drive N, Jacksonville, FL 32244. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
+          <t>Gerilet, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 5147 BROKEN ARROW Drive N, Jacksonville, FL 32244. would the seller consider a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Hi there Gershon, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi Gershon. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 8005 S Campbell Ave, Chicago, IL 60652. is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Gina, hi, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 2640 Ridgely St, Baltimore, MD 21230. Is the seller open to a cash as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there Gina — Charles Pleasant, Paragon Government Solutions. I came across 2640 Ridgely St, Baltimore, MD 21230 and buy cash. open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Good day Gino, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Gino, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 78 Liberty St, Trenton, NJ 08611. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Hey Gladys — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks!</t>
+          <t>Gladys, hi, I'm Charles with Paragon Government Solutions. I'm interested in buying 726 Helena Ave, Dallas, TX 75217 for cash; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Good day Glen. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 3194 W 95th St, Cleveland, OH 44102. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
+          <t>Hey Glen — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3194 W 95th St, Cleveland, OH 44102. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Hey GLEN. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 8456 BOYSENBERRY Lane W, Jacksonville, FL 32244. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi GLEN. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 8456 BOYSENBERRY Lane W, Jacksonville, FL 32244. would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Hi there Gonzalo — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there Gonzalo. I'm Charles with Paragon Government Solutions, and I came across 725 W SOUTHGATE Avenue W, Phoenix, AZ 85041 and buy cash. is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Gracie, hi. Charles Pleasant, Paragon Government Solutions, and interested in buying 2628 Marfa Ave, Dallas, TX 75216 for cash. Open to a discounted cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
+          <t>Hey Gracie, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2628 Marfa Ave, Dallas, TX 75216; is the seller open to a cash as-is offer, fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Hey Gracie, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 4015 Shadrack Dr, Dallas, TX 75212. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
+          <t>Gracie, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 4015 Shadrack Dr, Dallas, TX 75212. would the seller consider a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Hi there Grant, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1709 Jeffrey Bryan Dr, Charlotte, NC 28213. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Grant — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1709 Jeffrey Bryan Dr, Charlotte, NC 28213. could the seller look at a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Good day Grazyna. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3709 W 66th Pl, Chicago, IL 60629. Could the seller look at a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Grazyna — Charles Pleasant, Paragon Government Solutions. I came across 3709 W 66th Pl, Chicago, IL 60629 and buy cash. is the seller open to a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Hi Greg, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1033 Kern St, Bakersfield, CA 93305. Open to a discounted cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
+          <t>Hello Greg, Charles here with Paragon Government Solutions. I'm reaching out about 1033 Kern St, Bakersfield, CA 93305; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Hey Gregory — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there Gregory. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 10535 S Peoria St, Chicago, IL 60643. is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Hello Gregory, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 19358 Teppert St, Detroit, MI 48234. Would the owner entertain a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
+          <t>Hey Gregory — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 19358 Teppert St, Detroit, MI 48234. open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Hi there Guillermo, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 14810 Walters Rd, Houston, TX 77068. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Guillermo, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 14810 Walters Rd, Houston, TX 77068 — would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Hey Gwendolyn — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Gwendolyn, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 319 Avenue J, Dallas, TX 75203 for cash — would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10372,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>HALEY, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Much appreciated!</t>
+          <t>HALEY, hi, I'm Charles with Paragon Government Solutions. I came across 174 Bienville Dr, Fayetteville, NC 28311 and buy cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Hannah, hi, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hey Hannah — Charles here with Paragon Government Solutions. I'm a cash investor looking at 232 Fernview Dr, Columbia, SC 29229. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Hi there Hannah. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 3834 Shelley Blvd, Dallas, TX 75211. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Hannah, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 3834 Shelley Blvd, Dallas, TX 75211 for cash — open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Hey Harold — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Harold, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 2012 Lmridge Rd, Columbia, SC 29209 for cash; any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Hey Harry. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 9432 S Bishop St, Chicago, IL 60620. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Harry, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 9432 S Bishop St, Chicago, IL 60620 — could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Hassan, hi, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hassan, hi, Charles here with Paragon Government Solutions. I'm interested in buying 5698 Greenview Ave, Detroit, MI 48228 for cash — open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Heather, hi, Charles here with Paragon Government Solutions. I'm a cash investor looking at 2000 Elmridge Rd, Columbia, SC 29209. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there Heather, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 2000 Elmridge Rd, Columbia, SC 29209 — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Hey Heather, Charles here with Paragon Government Solutions. interested in buying 5235 Cumberland Cove Dr, Baton Rouge, LA 70817 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hey Heather. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 5235 Cumberland Cove Dr, Baton Rouge, LA 70817 for cash. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Heather, hi. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 6040 W Perimeter Dr, Baton Rouge, LA 70811. Could the seller look at a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Heather, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 6040 W Perimeter Dr, Baton Rouge, LA 70811 for cash — is the seller open to a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Hey Heather — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
+          <t>Heather, hi. I'm Charles with Paragon Government Solutions, and I came across 1802 E Campo Bello Drive #92, Phoenix, AZ 85022 and buy cash. would the seller consider a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Hector, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 8910 N 10TH Street, Phoenix, AZ 85020. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
+          <t>Hey Hector, Charles here with Paragon Government Solutions. I'm reaching out about 8910 N 10TH Street, Phoenix, AZ 85020; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Hi there HENRY, Charles Pleasant, Paragon Government Solutions. interested in buying 27 W 44TH Street, Jacksonville, FL 32208 for cash. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
+          <t>HENRY, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 27 W 44TH Street, Jacksonville, FL 32208. could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Hi Henry, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Henry — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6603 S Oakley Ave, Chicago, IL 60636. would the seller consider a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Hello Hermel, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hi there Hermel, Charles here with Paragon Government Solutions. I came across 13622 Vida Ln, Dallas, TX 75253 and buy cash; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Hey Hilda, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1401 El Sereno Dr, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thank you!</t>
+          <t>Hi Hilda. Charles here with Paragon Government Solutions, and I'm reaching out about 1401 El Sereno Dr, Bakersfield, CA 93304. could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Hello Ian, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
+          <t>Ian, hi. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 19479 Spencer St, Detroit, MI 48234. open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Hi there Ijella — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Ijella, hi. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 9627 Scotswood Dr, Baton Rouge, LA 70818. open to a discounted cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Hi there Ingrid — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey Ingrid — Charles Pleasant, Paragon Government Solutions. I came across 842 Meridian Ave, Lakeland, FL 33801 and buy cash. open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Hi there IRAN — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thank you!</t>
+          <t>Hi there IRAN — Charles here with Paragon Government Solutions. I'm interested in buying 2501 DOBY Street, Jacksonville, FL 32209 for cash. open to a discounted cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Good day Iris — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Iris — this is Charles Pleasant with Paragon Government Solutions. I came across 189 Mercer St, Hamilton, NJ 08690 and buy cash. would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Good day Isabella, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Isabella, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 2304 Pelican Dr, Columbia, SC 29203; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Hello Jack, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Jack. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 905 Ann Ave, Dallas, TX 75223 for cash. is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Jacob, hi, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 17360 Greenlawn St, Detroit, MI 48221 for cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Jacob, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 17360 Greenlawn St, Detroit, MI 48221 for cash. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Hi JACOBE, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 2146 LOUISE Street, Jacksonville, FL 32206. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
+          <t>Hey JACOBE, Charles Pleasant, Paragon Government Solutions. I came across 2146 LOUISE Street, Jacksonville, FL 32206 and buy cash; any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Good day Jalisa — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Jalisa, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3431 Sayers St, Houston, TX 77026; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Jamehia, hi, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 12807 Crystal Cove Dr, Houston, TX 77044. Is the seller open to a cash as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
+          <t>Good day Jamehia, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 12807 Crystal Cove Dr, Houston, TX 77044 — is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Hey JAMES. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 6528 MITFORD Road, Jacksonville, FL 32210. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
+          <t>Hi there JAMES, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 6528 MITFORD Road, Jacksonville, FL 32210; any chance the seller would take a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Hi there JAMES, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2203 SHERRINGTON Street, Jacksonville, FL 32209 for cash. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello JAMES — Charles Pleasant, Paragon Government Solutions. I came across 2203 SHERRINGTON Street, Jacksonville, FL 32209 and buy cash. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Hi James. Charles here with Paragon Government Solutions, and I'm reaching out about 9433 S Michigan Ave, Chicago, IL 60619 — a cash purchase. Open to a discounted cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi James — Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 9433 S Michigan Ave, Chicago, IL 60619. is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Hello James, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey James, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 8350 S Lafayette Ave, Chicago, IL 60620; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Hi James. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 9261 Camley St, Detroit, MI 48224. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there James. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 9261 Camley St, Detroit, MI 48224. open to a discounted cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Good day JAMES, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 736 Tobermory Rd, Fayetteville, NC 28306. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thanks so much!</t>
+          <t>Hello JAMES, I'm Charles with Paragon Government Solutions. I'm reaching out about 736 Tobermory Rd, Fayetteville, NC 28306; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Good day Jami — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Jami — this is Charles Pleasant with Paragon Government Solutions. I came across 10339 Limestone Dr, Dallas, TX 75217 and buy cash. is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Jamie, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 3010 Hartwick Rd, Houston, TX 77093. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks!</t>
+          <t>Hey Jamie — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3010 Hartwick Rd, Houston, TX 77093. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Good day Jamie — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thank you!</t>
+          <t>Hi there Jamie — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2229 W 60th St, Indianapolis, IN 46228. would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Hi there Jamila, Charles here with Paragon Government Solutions. I'm a cash investor looking at 12607 Oakfield Ave, Cleveland, OH 44105. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Jamila — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 12607 Oakfield Ave, Cleveland, OH 44105. would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Hey Janina. Charles here with Paragon Government Solutions, and I'm reaching out about 7324 S Blackstone Ave, Chicago, IL 60619 — a cash purchase. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day Janina. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 7324 S Blackstone Ave, Chicago, IL 60619. would the seller consider a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Hello Jasmin — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
+          <t>Hey Jasmin, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 240 Mason Ave, Hamilton, NJ 08610; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Good day Jasmine, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6433 S Talman Ave, Chicago, IL 60629. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Jasmine, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 6433 S Talman Ave, Chicago, IL 60629; could the seller look at a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Hello Jason. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 1009 Poplar Grove St, Baltimore, MD 21216. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Jason, hi. I'm Charles with Paragon Government Solutions, and I'm interested in buying 1009 Poplar Grove St, Baltimore, MD 21216 for cash. open to a discounted cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Hello Jason, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 5732 Wood Dr SW, Albuquerque, NM 87105. Open to a discounted cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Jason, I'm Charles with Paragon Government Solutions. I came across 5732 Wood Dr SW, Albuquerque, NM 87105 and buy cash — any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Hi Jason, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2600 Brookside Dr APT 41, Bakersfield, CA 93311 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Jason. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 2600 Brookside Dr APT 41, Bakersfield, CA 93311. would the owner entertain a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Hey Jason, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 106 N Briscoe Blvd, Dallas, TX 75211. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Jason — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 106 N Briscoe Blvd, Dallas, TX 75211. open to a discounted cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Hello Jason, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1921 W WHITTON Avenue, Phoenix, AZ 85015. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
+          <t>Hello Jason. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1921 W WHITTON Avenue, Phoenix, AZ 85015. would the owner entertain a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Good day Jay. I'm Charles with Paragon Government Solutions, and I'm reaching out about 19300 Berg Rd, Detroit, MI 48219 — a cash purchase. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
+          <t>Hi Jay, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 19300 Berg Rd, Detroit, MI 48219 — could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Hey Jay, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 4909 Falls St, Houston, TX 77026. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
+          <t>Jay, hi — I'm Charles with Paragon Government Solutions. I came across 4909 Falls St, Houston, TX 77026 and buy cash. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Hello JC, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 5009 W Chicago Ave, Chicago, IL 60651. Open to a discounted cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
+          <t>Hi JC — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 5009 W Chicago Ave, Chicago, IL 60651. open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Hi JD, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6810 Satchel Ford Rd, Columbia, SC 29206. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Appreciate it!</t>
+          <t>JD, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 6810 Satchel Ford Rd, Columbia, SC 29206. open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Good day Jean. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 10032 S Calumet Ave, Chicago, IL 60628. Would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
+          <t>Jean, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 10032 S Calumet Ave, Chicago, IL 60628 — could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Good day Jeff. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 3218 College St, Slidell, LA 70458. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks!</t>
+          <t>Hey Jeff — this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 3218 College St, Slidell, LA 70458 for cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Hi Jeff. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 116 Clay Ridge Rd, Columbia, SC 29223 — a cash purchase. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
+          <t>Jeff, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 116 Clay Ridge Rd, Columbia, SC 29223 — would the owner entertain a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Hi there Jeffrey. I'm Charles with Paragon Government Solutions, and I'm reaching out about 109 Kingston Trace Rd, Columbia, SC 29229 — a cash purchase. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Jeffrey, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 109 Kingston Trace Rd, Columbia, SC 29229 — is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Hi there Jeffrey, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 4137 Shorecrest Dr, Columbia, SC 29209. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there Jeffrey, this is Charles Pleasant with Paragon Government Solutions. I came across 4137 Shorecrest Dr, Columbia, SC 29209 and buy cash — would the seller consider a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Good day Jeffrey. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 8622 Othello St, Houston, TX 77029. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Jeffrey, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 8622 Othello St, Houston, TX 77029 for cash. would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Jeffrey, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Jeffrey, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3196 W 116th St, Cleveland, OH 44111 — would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>Hi there JELISSA, Charles here with Paragon Government Solutions. interested in buying 4173 DAVIE Court, Jacksonville, FL 32210 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thank you!</t>
+          <t>Hello JELISSA, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 4173 DAVIE Court, Jacksonville, FL 32210 for cash — any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Hello JENNIFER. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 9720 STEAD Court, Jacksonville, FL 32221 for cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thank you!</t>
+          <t>Hi there JENNIFER, I'm Charles with Paragon Government Solutions. I'm interested in buying 9720 STEAD Court, Jacksonville, FL 32221 for cash; could the seller look at a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Good day Jennifer. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 618 E 89th St, Chicago, IL 60619. Is the seller open to a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thank you!</t>
+          <t>Jennifer, hi, this is Charles Pleasant with Paragon Government Solutions. I came across 618 E 89th St, Chicago, IL 60619 and buy cash — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Good day Jenny, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1639 Mustang Canyon Way, Houston, TX 77049. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Jenny, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1639 Mustang Canyon Way, Houston, TX 77049 for cash — would the seller consider a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Hey Jenya. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 1075 Belmont Green Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
+          <t>Jenya, hi, I'm Charles with Paragon Government Solutions. I'm reaching out about 1075 Belmont Green Rd, Columbia, SC 29209 — would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Hi there Jerelyn. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 409 Sheridan Dr, Columbia, SC 29223. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Jerelyn, Charles here with Paragon Government Solutions. I'm a cash investor looking at 409 Sheridan Dr, Columbia, SC 29223; open to a discounted cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Hey Jerry, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 3012 Skyview Dr, Lakeland, FL 33801. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Good day Jerry. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3012 Skyview Dr, Lakeland, FL 33801. open to a discounted cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Good day Jesse, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1037 Lexington St, Lakeland, FL 33801 — a cash purchase. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Jesse, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 1037 Lexington St, Lakeland, FL 33801; could the seller look at a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>Hi Jesse, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 33 Heritage Village Ln, Columbia, SC 29212. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Hey Jesse, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 33 Heritage Village Ln, Columbia, SC 29212; would the owner entertain a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Hey Jessica. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 3929 Trotter Rd, Columbia, SC 29209. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hello Jessica. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 3929 Trotter Rd, Columbia, SC 29209. would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Good day Jessica, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 8752 Woodcastle Dr, Dallas, TX 75217 — a cash purchase. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Jessica — my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 8752 Woodcastle Dr, Dallas, TX 75217. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Hi Jessica, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Jessica. Charles here with Paragon Government Solutions, and I came across 1521 Hamilton Ave, Hamilton, NJ 08629 and buy cash. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Hi there Jessica, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Hello Jessica — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 5250 Alter Rd, Detroit, MI 48224 for cash. would the seller consider a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>Good day JESSICA — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks much!</t>
+          <t>Hi there JESSICA, Charles here with Paragon Government Solutions. I'm interested in buying 994 Wayside Rd, Fayetteville, NC 28314 for cash — could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Jill, hi, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi Jill, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5706 S Columbia Pl, Tulsa, OK 74105 — would the seller consider a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Hello Jim. Charles Pleasant, Paragon Government Solutions, and interested in buying 5303 S Winchester Ave, Chicago, IL 60609 for cash. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Jim — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 5303 S Winchester Ave, Chicago, IL 60609. would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>Good day Jimish, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 8443 S Manistee Ave, Chicago, IL 60617. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
+          <t>Jimish, hi, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 8443 S Manistee Ave, Chicago, IL 60617; would the owner entertain a cash as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>Jimmy, hi, Charles here with Paragon Government Solutions. interested in buying 8101 Howard Dr, Houston, TX 77017 for cash. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks much!</t>
+          <t>Jimmy, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 8101 Howard Dr, Houston, TX 77017 — is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>Good day JoAnn, Charles here with Paragon Government Solutions. I'm reaching out about 16503 Wisconsin St, Detroit, MI 48221 — a cash purchase. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thank you!</t>
+          <t>Hello JoAnn. I'm Charles with Paragon Government Solutions, and I came across 16503 Wisconsin St, Detroit, MI 48221 and buy cash. would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Good day Joe. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in Lots 23-25 Cargill St, Houston, TX 77029. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Joe, hi, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at Lots 23-25 Cargill St, Houston, TX 77029 — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Hello Joel. Charles Pleasant, Paragon Government Solutions, and interested in buying 12126 Garner Mill Ln, Houston, TX 77089 for cash. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi Joel, I'm Charles with Paragon Government Solutions. I'm interested in buying 12126 Garner Mill Ln, Houston, TX 77089 for cash — could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Hi there Joel. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 6502 Leedale St, Houston, TX 77016. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Joel, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 6502 Leedale St, Houston, TX 77016; could the seller look at a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Good day Joey — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Joey, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 8614 Fringewood Dr, Houston, TX 77028; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Hello John — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there John. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 15346 Dexter Ave, Detroit, MI 48238. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>Hey John, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 4386 W 48th St, Cleveland, OH 44144. Could the seller look at a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there John, I'm Charles with Paragon Government Solutions. I'm reaching out about 4386 W 48th St, Cleveland, OH 44144 — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>Hello John — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks!</t>
+          <t>Hi there John — I'm Charles with Paragon Government Solutions. I came across 1002 Prouty Ave, Toledo, OH 43609 and buy cash. would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>Good day John. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 10431 Kinslow Dr, Dallas, TX 75217. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi John, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 10431 Kinslow Dr, Dallas, TX 75217; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Hello John, this is Charles Pleasant with Paragon Government Solutions. interested in buying 169 Fox Grove Cir, Columbia, SC 29229 for cash. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
+          <t>John, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 169 Fox Grove Cir, Columbia, SC 29229; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Hi there John — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
+          <t>Hello John, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 7743 E Canfield St, Detroit, MI 48214 for cash; could the seller look at a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Hey John — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks!</t>
+          <t>Hello John. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on Leadmine Rd, Gaffney, SC 29340. would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Hi there JOHN. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 3554 BROCKWAY Road, Jacksonville, FL 32250. Open to a discounted cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello JOHN. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 3554 BROCKWAY Road, Jacksonville, FL 32250 for cash. could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Hi there Johnny, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there Johnny. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 9016 Harris Ave, Cleveland, OH 44104. could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>Hi JON — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks!</t>
+          <t>Hey JON, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3218 PERRY Street, Jacksonville, FL 32206; any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Good day Jonathan, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Jonathan, I'm Charles with Paragon Government Solutions. I'm reaching out about 4329 S Wood St, Chicago, IL 60609 — is the seller open to a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Hello Jonathan. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 18866 Hull Ave, Detroit, MI 48203. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Jonathan, Charles Pleasant, Paragon Government Solutions. I came across 18866 Hull Ave, Detroit, MI 48203 and buy cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Good day Jose. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 9137 Meyers Rd, Detroit, MI 48228 for cash. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
+          <t>Good day Jose — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 9137 Meyers Rd, Detroit, MI 48228. is the seller open to a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Hey Jose, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Jose, hi — I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 5921 S Sawyer Ave, Chicago, IL 60629. would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Hello Jose — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Appreciate it!</t>
+          <t>Jose, hi. I'm Charles with Paragon Government Solutions, and I'm reaching out about 9122 S La Salle St, Chicago, IL 60620. any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Hi there Joseph — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Joseph — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 20505 Hamburg St, Detroit, MI 48205. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Hi JOSEPH, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day JOSEPH — I'm Charles with Paragon Government Solutions. I'm reaching out about 5250 SANTA MONICA Boulevard S, Jacksonville, FL 32207. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -12752,7 +12752,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Hi Joseph, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Joseph, hi — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 2856 E 79th St, Chicago, IL 60649. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Good day JOSEPH. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1334 W 32ND Street, Jacksonville, FL 32209. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
+          <t>Hey JOSEPH — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1334 W 32ND Street, Jacksonville, FL 32209. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Hi Joshua, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 2021 Morninglo Ln, Columbia, SC 29223. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks!</t>
+          <t>Hey Joshua, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 2021 Morninglo Ln, Columbia, SC 29223 for cash; open to a discounted cash, as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Hello Joshua, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 3403 Alabama Ave, Dallas, TX 75216. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hello Joshua. I'm Charles with Paragon Government Solutions, and I'm reaching out about 3403 Alabama Ave, Dallas, TX 75216. open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Hello Joshua, Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hi Joshua — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 20017 Hawthorne St, Detroit, MI 48203 for cash. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Hi Joy, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 2138 Minnesota St, Baton Rouge, LA 70802. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Joy, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2138 Minnesota St, Baton Rouge, LA 70802; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Hey JOYOUS — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
+          <t>JOYOUS, hi — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 5227 BUNCHE Drive, Jacksonville, FL 32209. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Hey Ju'Vonne, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 1523 E Nevada St, Detroit, MI 48203 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Ju'Vonne, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1523 E Nevada St, Detroit, MI 48203; any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Juanita, hi — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks much!</t>
+          <t>Hello Juanita, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 3423 Texas Dr, Dallas, TX 75211 — is the seller open to a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Good day Judith. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 12125 Angelus Ave, Cleveland, OH 44105 for cash. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Judith, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 12125 Angelus Ave, Cleveland, OH 44105 for cash. open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Hi there Judith, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 306 SW 29th St, Cape Coral, FL 33914. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Hi there Judith, my name's Charles Pleasant, Paragon Government Solutions. I came across 306 SW 29th St, Cape Coral, FL 33914 and buy cash — is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Good day Juliana, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 155 Locust Ave W, Hamilton, NJ 08610. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Juliana, hi — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 155 Locust Ave W, Hamilton, NJ 08610. is the seller open to a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Hey Julie. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 178 Vermillion Dr, Columbia, SC 29209. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Hey Julie — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 178 Vermillion Dr, Columbia, SC 29209. could the seller look at a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13077,7 +13077,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Hey Julio — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there Julio, I'm Charles with Paragon Government Solutions. I'm interested in buying 5626 Tranquil Cv, San Antonio, TX 78244 for cash — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>Hey Justin. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 1246 Junction St, Detroit, MI 48209. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
+          <t>Hello Justin — my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1246 Junction St, Detroit, MI 48209. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Justin, hi, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Justin, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 4701 Morris St NE APT 2604, Albuquerque, NM 87111. open to a discounted cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Hi Justine — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi Justine, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 3309 Crownover St, Austin, TX 78725 — would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Hey KALICA — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
+          <t>Hi there KALICA. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 2846 YELLOW PINE Drive, Jacksonville, FL 32277 for cash. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Kara, hi. Charles here with Paragon Government Solutions, and interested in buying 846 W Carole St, Lakeland, FL 33803 for cash. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
+          <t>Hello Kara, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 846 W Carole St, Lakeland, FL 33803 for cash — open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Hi Karelin, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 4535 W 157th St, Cleveland, OH 44135. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Karelin, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 4535 W 157th St, Cleveland, OH 44135; would the seller consider a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Hello Karen, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 226 Curvewood Rd, Columbia, SC 29229. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Karen. Charles Pleasant, Paragon Government Solutions, and I came across 226 Curvewood Rd, Columbia, SC 29229 and buy cash. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Good day Karen, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi Karen — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1040 Kentucky St SE, Albuquerque, NM 87108. could the seller look at a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Hey KAREN, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 6929 ROLLO Road, Jacksonville, FL 32205. Open to a discounted cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi KAREN. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 6929 ROLLO Road, Jacksonville, FL 32205. would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Good day Karina — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thank you!</t>
+          <t>Hi Karina. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 4030 W MARICOPA Street, Phoenix, AZ 85009 for cash. is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Hi Karina — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks!</t>
+          <t>Hi there Karina, I'm Charles with Paragon Government Solutions. I came across 7641 Delavan Dr, Houston, TX 77028 and buy cash; open to a discounted cash, as-is offer, close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Hi Karla. I'm Charles with Paragon Government Solutions, and interested in buying 11827 Gaston Pkwy, Dallas, TX 75218 for cash. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Karla, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 11827 Gaston Pkwy, Dallas, TX 75218 — open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Good day Karmen, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 10210 S Prairie Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
+          <t>Hey Karmen — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 10210 S Prairie Ave, Chicago, IL 60628. would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Hi there Kashmir. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 7305 Tremper St, Houston, TX 77020. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Much appreciated!</t>
+          <t>Good day Kashmir. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 7305 Tremper St, Houston, TX 77020. any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Katie, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Katie, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 8855 Stout St, Detroit, MI 48228 — is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Hi there Katy. Charles Pleasant, Paragon Government Solutions, and interested in buying 2319 Kathleen Ave, Dallas, TX 75216 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
+          <t>Katy, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 2319 Kathleen Ave, Dallas, TX 75216. open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Hello Keith, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 112 Willow Branch Dr, West Monroe, LA 71291 — a cash purchase. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thank you!</t>
+          <t>Hi Keith — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 112 Willow Branch Dr, West Monroe, LA 71291. would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Hi KEITH, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 4507 TRENTON Drive S, Jacksonville, FL 32209. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi KEITH. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 4507 TRENTON Drive S, Jacksonville, FL 32209. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13552,7 +13552,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Good day Kelley — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
+          <t>Hi Kelley. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1630 E ADAMS Street, Phoenix, AZ 85034. open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Good day Kelly, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 11825 Rosemary St N, Detroit, MI 48213 — a cash purchase. Open to a discounted cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi Kelly, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 11825 Rosemary St N, Detroit, MI 48213; open to a discounted cash, as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Hello Keneitra, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Keneitra, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 109 Christian St, Columbia, SC 29203 — is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Good day Kenisha. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 2324 Alpine Rd, Columbia, SC 29223 — a cash purchase. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there Kenisha. I'm Charles with Paragon Government Solutions, and I'm reaching out about 2324 Alpine Rd, Columbia, SC 29223. is the seller open to a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Hey KENNETH. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 1113 Branson St, Fayetteville, NC 28305 for cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
+          <t>Hello KENNETH — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1113 Branson St, Fayetteville, NC 28305. could the seller look at a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>Hi Kerry. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 1065 Blanchard Pl, Shreveport, LA 71104 for cash. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Kerry, I'm Charles with Paragon Government Solutions. I came across 1065 Blanchard Pl, Shreveport, LA 71104 and buy cash — would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Hi KEVIN. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 7321 Tollhouse Dr, Fayetteville, NC 28314 — a cash purchase. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi KEVIN, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 7321 Tollhouse Dr, Fayetteville, NC 28314; any chance the seller would take a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Kevin, hi. I'm Charles with Paragon Government Solutions, and I'm reaching out about 6127 Pontotoc St, Baton Rouge, LA 70812 — a cash purchase. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
+          <t>Kevin, hi, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 6127 Pontotoc St, Baton Rouge, LA 70812; would the owner entertain a cash as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>Hello Kevin. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1223 Harvey St, Columbia, SC 29201. Open to a discounted cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi there Kevin — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1223 Harvey St, Columbia, SC 29201. is the seller open to a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Kevin, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Good day Kevin, my name's Charles Pleasant, Paragon Government Solutions. I came across 11632 Laing St, Detroit, MI 48224 and buy cash; would the seller consider a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>Khaula, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 3718 Barbara Ave, Bakersfield, CA 93309. Could the seller look at a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Khaula. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 3718 Barbara Ave, Bakersfield, CA 93309 for cash. any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Hello Kim — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thank you!</t>
+          <t>Hey Kim, this is Charles Pleasant with Paragon Government Solutions. I came across 3428 W Banff Ln, Phoenix, AZ 85053 and buy cash — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>Hello KIM, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 752 ACOSTA Street, Jacksonville, FL 32204. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
+          <t>Good day KIM. Charles here with Paragon Government Solutions, and I'm interested in buying 752 ACOSTA Street, Jacksonville, FL 32204 for cash. open to a discounted cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Hi Kim, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hello Kim. I'm Charles with Paragon Government Solutions, and I'm reaching out about 3338 Taylor St, Detroit, MI 48206. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Hello Kimberley — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
+          <t>Good day Kimberley, my name's Charles Pleasant, Paragon Government Solutions. I came across 20 Doreen Rd, Hamilton, NJ 08690 and buy cash — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Hi Kimberly. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 2056 Persimmon Ct, Cincinnati, OH 45231 for cash. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
+          <t>Hey Kimberly, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 2056 Persimmon Ct, Cincinnati, OH 45231 — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Good day Kimberly, Charles here with Paragon Government Solutions. I'm a cash investor looking at 204 Philip St, Detroit, MI 48215. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day Kimberly, I'm Charles with Paragon Government Solutions. I came across 204 Philip St, Detroit, MI 48215 and buy cash; would the seller consider a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Hi Kira — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Kira, Charles Pleasant, Paragon Government Solutions. I came across 420 Pitchling Dr, Columbia, SC 29223 and buy cash — could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Hey Kodee, Charles here with Paragon Government Solutions. interested in buying 311 Lockner Rd, Columbia, SC 29212 for cash. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
+          <t>Good day Kodee — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 311 Lockner Rd, Columbia, SC 29212. open to a discounted cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Hello KONT. I'm Charles with Paragon Government Solutions, and I'm reaching out about 4104 LEONARD Circle E, Jacksonville, FL 32209 — a cash purchase. Open to a discounted cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
+          <t>Hi KONT — Charles Pleasant, Paragon Government Solutions. I came across 4104 LEONARD Circle E, Jacksonville, FL 32209 and buy cash. could the seller look at a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Hi Koty, Charles here with Paragon Government Solutions. interested in buying 1208 31st St SW, Birmingham, AL 35221 for cash. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello Koty, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1208 31st St SW, Birmingham, AL 35221 — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Hello Kristen, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 12018 Texana Cv, San Antonio, TX 78253. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks much!</t>
+          <t>Hello Kristen, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 12018 Texana Cv, San Antonio, TX 78253; could the seller look at a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Good day Kristi, Charles here with Paragon Government Solutions. I'm reaching out about 12966 Trail Hollow Dr #2960, Houston, TX 77079 — a cash purchase. Is the seller open to a cash as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day Kristi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 12966 Trail Hollow Dr #2960, Houston, TX 77079 — would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Hello Kristian, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 4114 Averill St, Houston, TX 77009. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi Kristian — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 4114 Averill St, Houston, TX 77009. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Good day Kristofer, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thank you!</t>
+          <t>Kristofer, hi, I'm Charles with Paragon Government Solutions. I came across 602 Lightstone Dr, San Antonio, TX 78258 and buy cash — would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Hey Kya, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5505 Hamlet Ave, Baltimore, MD 21214. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
+          <t>Hi there Kya. my name's Charles Pleasant, Paragon Government Solutions, and I came across 5505 Hamlet Ave, Baltimore, MD 21214 and buy cash. any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>KYLE, hi, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey KYLE, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 725 W 16 Street, Jacksonville, FL 32206 — could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Hello Lache, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Hello Lache — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 4103 Sablemist Ct, Houston, TX 77014. would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Hey LaCretia — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
+          <t>LaCretia, hi — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 17694 Avon Ave, Detroit, MI 48219. could the seller look at a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Landon, hi, I'm Charles with Paragon Government Solutions. interested in buying 8723 S Eggleston Ave, Chicago, IL 60620 for cash. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
+          <t>Landon, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 8723 S Eggleston Ave, Chicago, IL 60620 — would the owner entertain a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Hey Lara — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
+          <t>Hi there Lara. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 5003 Gleneagles Ct, Houston, TX 77084. any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Good day Lara. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 113 Wescott Pl, Columbia, SC 29229. Would the seller consider a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
+          <t>Lara, hi. Charles here with Paragon Government Solutions, and I'm interested in buying 113 Wescott Pl, Columbia, SC 29229 for cash. open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Hi there LASHAWN — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
+          <t>Hello LASHAWN. this is Charles Pleasant with Paragon Government Solutions, and I came across 1730 AUDUBON Street, Jacksonville, FL 32208 and buy cash. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14377,7 +14377,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Good day LaToya. Charles here with Paragon Government Solutions, and I'm reaching out about 16525 Prevost St, Detroit, MI 48235 — a cash purchase. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello LaToya. my name's Charles Pleasant, Paragon Government Solutions, and I came across 16525 Prevost St, Detroit, MI 48235 and buy cash. would the owner entertain a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Hi Laura, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2705 Warren Ave, Dallas, TX 75215. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Laura, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 2705 Warren Ave, Dallas, TX 75215 — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Hello Laura. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 806 Homestead St, Baltimore, MD 21218 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Hey Laura — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 806 Homestead St, Baltimore, MD 21218. would the owner entertain a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Hello Lauran, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Lauran, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2512 E Stassney Ln, Austin, TX 78744; would the seller consider a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Hey Lauren — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
+          <t>Hi Lauren. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 2009 Bancroft St, Lake Charles, LA 70607. would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Hi Lauren — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Lauren. Charles here with Paragon Government Solutions, and I'm interested in buying 6526 Oak Garden Dr, Baton Rouge, LA 70817 for cash. could the seller look at a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Hello Lawrence, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 6526 Heyden St, Detroit, MI 48228 for cash. Open to a discounted cash, as-is offer, close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Hello Lawrence, my name's Charles Pleasant, Paragon Government Solutions. I came across 6526 Heyden St, Detroit, MI 48228 and buy cash; could the seller look at a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14552,7 +14552,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>LEANA, hi, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>LEANA, hi, my name's Charles Pleasant, Paragon Government Solutions. I came across 4633 SUFFOLK Avenue, Jacksonville, FL 32208 and buy cash; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Good day Lee, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi there Lee. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 9 Vicky Ct, Hamilton, NJ 08610. could the seller look at a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Hey Leilani — my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks much!</t>
+          <t>Leilani, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 10712 Grantwood Ave, Cleveland, OH 44108. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>Hi there Leonel, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
+          <t>Hey Leonel, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 903 Cameron Ave, Dallas, TX 75223 — would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Leontra, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 11981 Whitehill St, Detroit, MI 48224. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
+          <t>Hello Leontra, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 11981 Whitehill St, Detroit, MI 48224 — would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14677,7 +14677,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>Hi there Lesa, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there Lesa — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 146 Dunham Rd, Columbia, SC 29209. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>Good day Lesa. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 2054 Elmridge Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
+          <t>Lesa, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2054 Elmridge Rd, Columbia, SC 29209; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>LeTanya, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 2043 Parker Ranch Rd SE, Atlanta, GA 30316. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
+          <t>Hi there LeTanya. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2043 Parker Ranch Rd SE, Atlanta, GA 30316. could the seller look at a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>LETICIA, hi, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hello LETICIA, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3072 BESSENT Road, Jacksonville, FL 32218 — could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Hello Liliana, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 530 Utah St SE Trailer 14A, Albuquerque, NM 87108. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
+          <t>Good day Liliana, I'm Charles with Paragon Government Solutions. I came across 530 Utah St SE Trailer 14A, Albuquerque, NM 87108 and buy cash; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>Hey Lily, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hey Lily, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 1027 Hollywood Ave, Dallas, TX 75208 for cash; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>Hi Linda — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
+          <t>Hello Linda, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 15779 Wabash St, Detroit, MI 48238 for cash; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>LINDA, hi — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
+          <t>Hi LINDA, my name's Charles Pleasant, Paragon Government Solutions. I came across 4815 LYNBROOK Drive, Jacksonville, FL 32207 and buy cash — would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Hello Linda. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 10 Stacey Ave, Trenton, NJ 08618. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
+          <t>Linda, hi — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 10 Stacey Ave, Trenton, NJ 08618. open to a discounted cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Hey Lindsey. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 5525 E THOMAS Road #R9, Phoenix, AZ 85018 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks much!</t>
+          <t>Lindsey, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 5525 E THOMAS Road #R9, Phoenix, AZ 85018. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Lisa, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Lisa, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 131 Elm Rd, Pittsburgh, PA 15237 — any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Hi Lisa, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1910 Greenoaks Rd APT A, Columbia, SC 29206. Is the seller open to a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there Lisa, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1910 Greenoaks Rd APT A, Columbia, SC 29206 for cash — would the seller consider a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Liz, hi — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Appreciate it!</t>
+          <t>Good day Liz, I'm Charles with Paragon Government Solutions. I came across 1200 Bluff Rd #198, Columbia, SC 29201 and buy cash; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Hi Liz. Charles Pleasant, Paragon Government Solutions, and interested in buying 1607 Elrino St, Baltimore, MD 21224 for cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
+          <t>Hey Liz, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1607 Elrino St, Baltimore, MD 21224 — is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Hey Lora — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi Lora, Charles here with Paragon Government Solutions. I'm reaching out about 2434 Paxton St, Columbia, SC 29204; is the seller open to a cash as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Hi there Lori — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
+          <t>Lori, hi. my name's Charles Pleasant, Paragon Government Solutions, and I came across 12346 Elmdale St, Detroit, MI 48213 and buy cash. would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Good day Louis, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 600 Stirrup Ave, Bakersfield, CA 93307. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Louis, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 600 Stirrup Ave, Bakersfield, CA 93307 — open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Hello LOURDES. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 72 E 32 Street, Jacksonville, FL 32206. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
+          <t>LOURDES, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 72 E 32 Street, Jacksonville, FL 32206; any chance the seller would take a cash, as-is offer, close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Hey Luan, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day Luan. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 3220 Plymouth Pl, New Orleans, LA 70131. could the seller look at a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Hi there Luciano, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Luciano, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 5930 Guadalupe St, Houston, TX 77016 — is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Hi there LUCIE, Charles Pleasant, Paragon Government Solutions. interested in buying 162 E 54TH Street, Jacksonville, FL 32208 for cash. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Hi there LUCIE. Charles here with Paragon Government Solutions, and I'm interested in buying 162 E 54TH Street, Jacksonville, FL 32208 for cash. would the owner entertain a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Hi Luis, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hi Luis. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 342 Creekwood Run, Lakeland, FL 33809. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Hey Lydia. my name's Charles Pleasant, Paragon Government Solutions, and interested in buying 13515 S Baltimore Ave, Chicago, IL 60633 for cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
+          <t>Hello Lydia. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 13515 S Baltimore Ave, Chicago, IL 60633. open to a discounted cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Hi there MAE. Charles Pleasant, Paragon Government Solutions, and interested in buying 1412 Morganton Rd, Fayetteville, NC 28305 for cash. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
+          <t>Good day MAE, my name's Charles Pleasant, Paragon Government Solutions. I came across 1412 Morganton Rd, Fayetteville, NC 28305 and buy cash — would the seller consider a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Hello Maico — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thank you!</t>
+          <t>Hello Maico — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1638 W MOHAVE Street, Phoenix, AZ 85007. would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Hi there Makia — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Makia. I'm Charles with Paragon Government Solutions, and I'm reaching out about 8357 Navy St, Detroit, MI 48209. would the seller consider a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Hi there Malaka — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Malaka. this is Charles Pleasant with Paragon Government Solutions, and I came across 10731 Roxbury St, Detroit, MI 48224 and buy cash. any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Good day Malwina, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
+          <t>Malwina, hi. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 8252 S Marshfield Ave, Chicago, IL 60620. open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Hey Mamie, Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Mamie, Charles here with Paragon Government Solutions. I'm interested in buying 216 W 10th St, Lakeland, FL 33805 for cash — would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Marc, hi, this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Good day Marc — Charles Pleasant, Paragon Government Solutions. I came across 6003 Glenoak Ave, Baltimore, MD 21214 and buy cash. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Marc, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there Marc — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 3010 NE 6th Place Cpe, Coral, FL 33909. could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Good day Marc — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Marc, I'm Charles with Paragon Government Solutions. I'm interested in buying 2744 Briarhurst Dr APT 51, Houston, TX 77057 for cash — is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Hi Marc, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 8313 S Wabash Ave, Chicago, IL 60619. Is the seller open to a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Marc — I'm Charles with Paragon Government Solutions. I'm interested in buying 8313 S Wabash Ave, Chicago, IL 60619 for cash. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Hi there Marcela, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 3712 W Cold Spring Ln, Baltimore, MD 21215 for cash. Open to a discounted cash, as-is offer, quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Marcela. this is Charles Pleasant with Paragon Government Solutions, and I'm interested in buying 3712 W Cold Spring Ln, Baltimore, MD 21215 for cash. any chance the seller would take a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15527,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Hello Marcelo — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
+          <t>Hi there Marcelo. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 1918 Michigan Ave, Dallas, TX 75216. open to a discounted cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Hey Marcia. Charles here with Paragon Government Solutions, and I'm reaching out about 90 Grandview Ave, Hamilton, NJ 08620 — a cash purchase. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>Hi Marcia, Charles here with Paragon Government Solutions. I'm a cash investor looking at 90 Grandview Ave, Hamilton, NJ 08620; any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Hey Marcia. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 2627 Carmel St, Houston, TX 77091. Open to a discounted cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Marcia, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2627 Carmel St, Houston, TX 77091 — would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Hello Marcy, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1115 Belmont Green Rd, Columbia, SC 29209. Open to a discounted cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Marcy. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1115 Belmont Green Rd, Columbia, SC 29209. is the seller open to a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Good day Margarita — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
+          <t>Hello Margarita, Charles here with Paragon Government Solutions. I came across 2526 Exline St, Dallas, TX 75215 and buy cash — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Maria, hi, I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there Maria, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 1250 W 49th Pl, Chicago, IL 60609 — open to a discounted cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Good day Maria, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 4541 S Laporte Ave, Chicago, IL 60638. Open to a discounted cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
+          <t>Maria, hi. I'm Charles with Paragon Government Solutions, and I'm reaching out about 4541 S Laporte Ave, Chicago, IL 60638. would the owner entertain a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Hi there Maria. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 1015 Barelas St SW, Albuquerque, NM 87102. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Maria, hi, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 1015 Barelas St SW, Albuquerque, NM 87102; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Hi there Maria, Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello Maria, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 618 Dolores St, Bakersfield, CA 93305; any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Hey Maria. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 19355 Alcoy St, Detroit, MI 48205 — a cash purchase. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
+          <t>Good day Maria. this is Charles Pleasant with Paragon Government Solutions, and I came across 19355 Alcoy St, Detroit, MI 48205 and buy cash. open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Hello MARIA, I'm Charles with Paragon Government Solutions. interested in buying 5974 CHARLES D EVERS Drive, Jacksonville, FL 32219 for cash. Is the seller open to a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Hey MARIA, I'm Charles with Paragon Government Solutions. I'm reaching out about 5974 CHARLES D EVERS Drive, Jacksonville, FL 32219 — open to a discounted cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Mariah, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 9042 S Ellis Ave, Chicago, IL 60619 — a cash purchase. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
+          <t>Mariah, hi, this is Charles Pleasant with Paragon Government Solutions. I came across 9042 S Ellis Ave, Chicago, IL 60619 and buy cash — any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Maribel, hi, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Maribel, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 16560 La Salle Ave, Detroit, MI 48221 — would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Hi there Maricela — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there Maricela, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 15008 Strathmoor St, Detroit, MI 48227 — would the seller consider a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Hey Maricela. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 124 Harriet Dr, San Antonio, TX 78216. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Good day Maricela — I'm Charles with Paragon Government Solutions. I'm reaching out about 124 Harriet Dr, San Antonio, TX 78216. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Maricela, hi — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Maricela — Charles here with Paragon Government Solutions. I'm reaching out about 7667 Ellsworth St, Detroit, MI 48238. open to a discounted cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Hi there Marie, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 11927 Horse Canyon, San Antonio, TX 78254. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
+          <t>Hey Marie, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 11927 Horse Canyon, San Antonio, TX 78254 — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Hello Marisela — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Marisela, hi, Charles Pleasant, Paragon Government Solutions. I came across 5819 S Fairfield Ave, Chicago, IL 60629 and buy cash; could the seller look at a cash, as-is offer, quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Good day Mariusz. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 8153 S Stewart Ave, Chicago, IL 60620. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Mariusz, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 8153 S Stewart Ave, Chicago, IL 60620 — would the owner entertain a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16002,7 +16002,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>Hey Mark — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks!</t>
+          <t>Mark, hi. Charles Pleasant, Paragon Government Solutions, and I came across 7039 Sheffield Dr, Lakeland, FL 33810 and buy cash. open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Good day Mark. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 1010 N 18TH Street, Phoenix, AZ 85006. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hey Mark — I'm Charles with Paragon Government Solutions. I came across 1010 N 18TH Street, Phoenix, AZ 85006 and buy cash. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Hello Marketta. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 16241 E State Fair St, Detroit, MI 48205. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks!</t>
+          <t>Hey Marketta. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 16241 E State Fair St, Detroit, MI 48205. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Hello Marshon. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 11841 S Union Ave, Chicago, IL 60628 — a cash purchase. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Marshon, Charles here with Paragon Government Solutions. I came across 11841 S Union Ave, Chicago, IL 60628 and buy cash — is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Martha, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hi there Martha, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 10356 Shelburne Dr, Dallas, TX 75227 — would the owner entertain a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Hi Martha, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Martha — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 4403 Allen St, Houston, TX 77007. open to a discounted cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>Martina, hi — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Martina, Charles Pleasant, Paragon Government Solutions. I came across 6826 Larkstone St, Houston, TX 77028 and buy cash — is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Hi Mary. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 1803 Cermack St, Columbia, SC 29223. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Mary, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1803 Cermack St, Columbia, SC 29223 — would the seller consider a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Hey Mary, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi there Mary — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 511 Solar Dr, San Antonio, TX 78227. would the owner entertain a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Hi Matt — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Matt — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 24 Merrymount Rd, Baltimore, MD 21210. is the seller open to a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Hi Matthew, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Good day Matthew, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 1816 N 37th Avenue, Phoenix, AZ 85009; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>Hi MATTHEW. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 4840 COLONIAL Avenue, Jacksonville, FL 32210. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
+          <t>Good day MATTHEW — Charles here with Paragon Government Solutions. I'm interested in buying 4840 COLONIAL Avenue, Jacksonville, FL 32210 for cash. would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Hello Mauricio, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3523 Edgewood St, Dallas, TX 75215. Is the seller open to a cash as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Mauricio, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3523 Edgewood St, Dallas, TX 75215; any chance the seller would take a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Hi there Mauricio. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5242 W Monroe St, Chicago, IL 60644. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
+          <t>Hello Mauricio. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 5242 W Monroe St, Chicago, IL 60644. would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Hi there Maya. I'm Charles with Paragon Government Solutions, and interested in buying 5936 Hillcrest St, Detroit, MI 48236 for cash. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey Maya. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 5936 Hillcrest St, Detroit, MI 48236. is the seller open to a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>MELISSA, hi. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 2007 LAMBERT Street, Jacksonville, FL 32206. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi there MELISSA, I'm Charles with Paragon Government Solutions. I'm interested in buying 2007 LAMBERT Street, Jacksonville, FL 32206 for cash; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Melody, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 353 E 90th St, Chicago, IL 60619. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
+          <t>Hey Melody, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 353 E 90th St, Chicago, IL 60619 — is the seller open to a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Hey Meredith, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Meredith, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 8511 Little River Rd, Houston, TX 77064 — is the seller open to a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16452,7 +16452,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Hey Michael, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 6463 Crane St, Detroit, MI 48213. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Michael, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6463 Crane St, Detroit, MI 48213; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>Good day Michael. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 120 Curvewood Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Michael — Charles here with Paragon Government Solutions. I'm a cash investor looking at 120 Curvewood Rd, Columbia, SC 29229. open to a discounted cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>MICHAEL, hi, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi MICHAEL, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1204 Patrick Dr, Fayetteville, NC 28314 — open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Michael, hi — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
+          <t>Good day Michael — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 7939 S Kingston Ave, Chicago, IL 60617. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Hey Michael, Charles Pleasant, Paragon Government Solutions. interested in buying 228 Haybert Ct, Bakersfield, CA 93304 for cash. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hey Michael, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 228 Haybert Ct, Bakersfield, CA 93304 — would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Hi Michael, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
+          <t>Good day Michael, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 2637 Marbella Ln, Dallas, TX 75228 for cash — would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Hey Michael — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Michael, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5950 S Marshfield Ave, Chicago, IL 60636 — open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Hi there Michael — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey Michael, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 10318 Hammerly Blvd #172, Houston, TX 77043 — would the seller consider a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Hi there Michael, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 9960 S Van Vlissingen Rd, Chicago, IL 60617 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Michael, Charles here with Paragon Government Solutions. I'm interested in buying 9960 S Van Vlissingen Rd, Chicago, IL 60617 for cash; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Hi there Michelle. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5601 Howell St, Houston, TX 77032. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
+          <t>Hello Michelle — my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 5601 Howell St, Houston, TX 77032. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Michelle, hi, I'm Charles with Paragon Government Solutions. interested in buying 16438 Vermillion Dr, Baton Rouge, LA 70819 for cash. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
+          <t>Good day Michelle — my name's Charles Pleasant, Paragon Government Solutions. I came across 16438 Vermillion Dr, Baton Rouge, LA 70819 and buy cash. would the owner entertain a cash as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Hello Michelle — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Good day Michelle — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 16438 Vermillion Dr, Baton Rouge, LA 70819. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Michelle, hi, Charles here with Paragon Government Solutions. interested in buying 13350 Tacoma St, Detroit, MI 48205 for cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
+          <t>Hi Michelle — I'm Charles with Paragon Government Solutions. I'm reaching out about 13350 Tacoma St, Detroit, MI 48205. would the seller consider a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Hi Mike, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 3065 Noble St, Houston, TX 77026. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Mike, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 3065 Noble St, Houston, TX 77026 — would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>Good day MIKE, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>MIKE, hi, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 1928 Crestview Dr, Fayetteville, NC 28304 for cash — would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Mike, hi, Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Mike, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 4337 Algonquin St, Detroit, MI 48215 — open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Hi Mike — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Mike, I'm Charles with Paragon Government Solutions. I'm reaching out about 8243 N 34TH Drive, Phoenix, AZ 85051; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Hi there MILDRED, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 10460 GAILWOOD Circle E, Jacksonville, FL 32218 — a cash purchase. Open to a discounted cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Appreciate it!</t>
+          <t>Good day MILDRED, Charles here with Paragon Government Solutions. I'm interested in buying 10460 GAILWOOD Circle E, Jacksonville, FL 32218 for cash; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>Milton, hi — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Appreciate it!</t>
+          <t>Milton, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 10707 Carvel Ln, Houston, TX 77072; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Good day Milton, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1038 Canal Dr W, Lakeland, FL 33801 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks!</t>
+          <t>Milton, hi — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1038 Canal Dr W, Lakeland, FL 33801 for cash. would the seller consider a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>Good day Milton — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Milton — Charles here with Paragon Government Solutions. I'm interested in buying 628 E 131st St, Cleveland, OH 44108 for cash. is the seller open to a cash as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>Hello MINNA, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thank you!</t>
+          <t>Hi MINNA. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 9852 OLIVIA Street, Jacksonville, FL 32219. could the seller look at a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>Hey Mitchell, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 342 Ishmeal St, Houston, TX 77091 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Mitchell, hi, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 342 Ishmeal St, Houston, TX 77091 for cash — any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Good day MITZIE. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 1912 Blake St, Fayetteville, NC 28301. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
+          <t>Hey MITZIE, I'm Charles with Paragon Government Solutions. I'm interested in buying 1912 Blake St, Fayetteville, NC 28301 for cash — would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Hey Moe. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 11409 Manor St, Detroit, MI 48204. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
+          <t>Good day Moe. my name's Charles Pleasant, Paragon Government Solutions, and I came across 11409 Manor St, Detroit, MI 48204 and buy cash. open to a discounted cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Hello Mohammad. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 3502 Goodhope St, Houston, TX 77021. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Mohammad — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 3502 Goodhope St, Houston, TX 77021. any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>MORGAN, hi, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 525 W 66TH Street, Jacksonville, FL 32208 for cash. Could the seller look at a cash, as-is offer, close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
+          <t>MORGAN, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 525 W 66TH Street, Jacksonville, FL 32208; would the owner entertain a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Hi there Mr., Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Good day Mr., my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 131 Hoffman Ave, Trenton, NJ 08618; could the seller look at a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Hi there Ms — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Ms — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 635 Marilyn Dr, Baton Rouge, LA 70815 for cash. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>Hi there Mwood — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
+          <t>Hello Mwood — Charles here with Paragon Government Solutions. I'm interested in buying 18982 Joann St, Detroit, MI 48205 for cash. open to a discounted cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Good day Nader, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Hello Nader, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 12400 Lansdowne St, Grosse Pointe, MI 48224 for cash; would the owner entertain a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Hello Nadia. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 1333 W 71st St, Chicago, IL 60636. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello Nadia — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1333 W 71st St, Chicago, IL 60636. is the seller open to a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Good day Najah, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 17160 Northlawn St, Detroit, MI 48221. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Najah, Charles here with Paragon Government Solutions. I'm a cash investor looking at 17160 Northlawn St, Detroit, MI 48221 — could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17277,7 +17277,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Hello Nakashia. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 9937 Golden Gate Ave, Baton Rouge, LA 70818. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
+          <t>Hey Nakashia — I'm Charles with Paragon Government Solutions. I came across 9937 Golden Gate Ave, Baton Rouge, LA 70818 and buy cash. could the seller look at a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Hello Nameer. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 2510 Sturtevant St, Detroit, MI 48206. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi there Nameer, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2510 Sturtevant St, Detroit, MI 48206; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Nanci, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 4500 Norfolk Ave, Baltimore, MD 21216. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
+          <t>Nanci, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 4500 Norfolk Ave, Baltimore, MD 21216. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>Hello Nancy. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 4217 NW 32nd Ter, Cape Coral, FL 33993 for cash. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hello Nancy. I'm Charles with Paragon Government Solutions, and I came across 4217 NW 32nd Ter, Cape Coral, FL 33993 and buy cash. is the seller open to a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Hey Nancy — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
+          <t>Hey Nancy — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 4903 Canal St, Houston, TX 77011. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Good day Nardu, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Nardu, hi, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 3250 Elm Dr, Baton Rouge, LA 70805 — is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Good day NARENDRA. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 7007 LUCKY Drive E, Jacksonville, FL 32208. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
+          <t>Good day NARENDRA — Charles here with Paragon Government Solutions. I'm reaching out about 7007 LUCKY Drive E, Jacksonville, FL 32208. would the owner entertain a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Hello Natalie, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 4009 W ORANGE Drive #36, Phoenix, AZ 85019. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
+          <t>Natalie, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 4009 W ORANGE Drive #36, Phoenix, AZ 85019. could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Hi Nataly. Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 20260 Dean St, Detroit, MI 48234. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Nataly. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 20260 Dean St, Detroit, MI 48234. open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Hello Neeta, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day Neeta, Charles here with Paragon Government Solutions. I'm a cash investor looking at 19024 Riverview St, Detroit, MI 48219 — would the seller consider a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Hi Nelly. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 315 Gober St, Houston, TX 77017. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
+          <t>Nelly, hi. I'm Charles with Paragon Government Solutions, and I came across 315 Gober St, Houston, TX 77017 and buy cash. open to a discounted cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Nichol, hi, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 125 Cedar Glen Ln, Columbia, SC 29223. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
+          <t>Hello Nichol, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 125 Cedar Glen Ln, Columbia, SC 29223 for cash — could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>Hey Nicholas. I'm Charles with Paragon Government Solutions, and I buy cash and I'm interested in 3952 Bluehill St, Detroit, MI 48224. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
+          <t>Hey Nicholas, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 3952 Bluehill St, Detroit, MI 48224 for cash; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>Hi Nick, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 129 Pond Oak Ln, Columbia, SC 29212 for cash. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Nick, hi, Charles here with Paragon Government Solutions. I came across 129 Pond Oak Ln, Columbia, SC 29212 and buy cash — would the seller consider a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Nick, hi, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Nick, I'm Charles with Paragon Government Solutions. I came across 2407 E Cold Spring Ln, Baltimore, MD 21214 and buy cash; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Good day NICOLE, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 322 E 6TH Street, Jacksonville, FL 32206. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day NICOLE. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 322 E 6TH Street, Jacksonville, FL 32206. could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -17677,7 +17677,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Hi Nikhil, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 408 Longfellow Blvd, Lakeland, FL 33801. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi Nikhil, I'm Charles with Paragon Government Solutions. I'm reaching out about 408 Longfellow Blvd, Lakeland, FL 33801 — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>Nikole, hi. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 3450 Minnesota Ave, St. Louis, MO 63118 for cash. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Nikole, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3450 Minnesota Ave, St. Louis, MO 63118 — is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17727,7 +17727,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Hey Nilsa — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hey Nilsa. Charles here with Paragon Government Solutions, and I'm interested in buying 703 Monterey Ave, Cape Coral, FL 33904 for cash. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>Hi there Nima — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks!</t>
+          <t>Good day Nima. this is Charles Pleasant with Paragon Government Solutions, and I came across 409 Wilkes Rd, Columbia, SC 29203 and buy cash. is the seller open to a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>Hi there NM, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Hello NM — I'm Charles with Paragon Government Solutions. I came across 3809 Santa Anita Rd SW, Albuquerque, NM 87105 and buy cash. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>Hi there Noah — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
+          <t>Good day Noah, Charles here with Paragon Government Solutions. I'm a cash investor looking at 16574 Westbrook St, Detroit, MI 48219 — could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -17827,7 +17827,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Hi there Norma. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 1810 Atlas Dr, Dallas, TX 75216 — a cash purchase. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Norma, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1810 Atlas Dr, Dallas, TX 75216 — would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Good day Norma. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 11326 S Union Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thank you!</t>
+          <t>Hey Norma — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 11326 S Union Ave, Chicago, IL 60628. any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17877,7 +17877,7 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Good day Olivia — this is Charles Pleasant with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks much!</t>
+          <t>Hello Olivia, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1434 N Leamington Ave, Chicago, IL 60651 — open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Hi there Orlando. Charles here with Paragon Government Solutions, and I'm reaching out about 13420 Chico Rd NE, Albuquerque, NM 87123 — a cash purchase. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Orlando. I'm Charles with Paragon Government Solutions, and I came across 13420 Chico Rd NE, Albuquerque, NM 87123 and buy cash. open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Hello Oscar. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 10939 S Avenue F, Chicago, IL 60617 for cash. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Oscar, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 10939 S Avenue F, Chicago, IL 60617; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -17952,7 +17952,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Hi there Otis, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hello Otis, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 7221 S Bennett Ave, Chicago, IL 60649 — could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Hi there Pablo — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Pablo. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 213 Hogan St, Houston, TX 77009. any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Hi PAIGE — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi there PAIGE, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 3821 OLYMPIC Lane, Jacksonville, FL 32223 for cash; open to a discounted cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Good day Pamela — this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks so much!</t>
+          <t>Hi Pamela. my name's Charles Pleasant, Paragon Government Solutions, and I came across 520 W CLARENDON Avenue #C3, Phoenix, AZ 85013 and buy cash. open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18052,7 +18052,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Good day Pamela. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 11401 S Morgan St, Chicago, IL 60643. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Pamela, hi. this is Charles Pleasant with Paragon Government Solutions, and I came across 11401 S Morgan St, Chicago, IL 60643 and buy cash. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>Hi there Pamela. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 3714 Hydrangea St, Columbia, SC 29205 — a cash purchase. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
+          <t>Good day Pamela, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 3714 Hydrangea St, Columbia, SC 29205; any chance the seller would take a cash, as-is offer, close quickly, short inspection period? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Good day Patricia — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Patricia, hi — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 109 Oakley Dr, Columbia, SC 29223. would the owner entertain a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18127,7 +18127,7 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>Hi PATRICIA, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 1934 N Pearl St, Fayetteville, NC 28303. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
+          <t>PATRICIA, hi — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1934 N Pearl St, Fayetteville, NC 28303. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Good day Patrick — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Much appreciated!</t>
+          <t>Hi there Patrick, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 609 Chestnut Ave, Trenton, NJ 08611 — open to a discounted cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Good day Patti. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 218 Florien St, Pittsburgh, PA 15204 — a cash purchase. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Patti. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 218 Florien St, Pittsburgh, PA 15204. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>Hello Paul — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
+          <t>Hello Paul. Charles here with Paragon Government Solutions, and I came across 4629 Larkspur St, Houston, TX 77051 and buy cash. is the seller open to a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>Good day PEPPER, my name's Charles Pleasant, Paragon Government Solutions. interested in buying 2185 MOREHOUSE Road, Jacksonville, FL 32209 for cash. Could the seller look at a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day PEPPER. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2185 MOREHOUSE Road, Jacksonville, FL 32209. could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18252,7 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>PETER, hi, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hey PETER, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 919 OBSERVATORY Parkway, Jacksonville, FL 32218 — any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Hey Phil, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day Phil, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 245 Piney Grove Rd, Columbia, SC 29210; open to a discounted cash, as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18302,7 +18302,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Hey Phyllis — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
+          <t>Hi Phyllis. Charles Pleasant, Paragon Government Solutions, and I came across 847 Glenmore Ave, Baton Rouge, LA 70806 and buy cash. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Good day Ponce — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Ponce — I'm Charles with Paragon Government Solutions. I came across 12 Sea Hawk Ct, Columbia, SC 29203 and buy cash. is the seller open to a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>Good day QUINNEICE. Charles here with Paragon Government Solutions, and interested in buying 1921 Ashridge Dr, Fayetteville, NC 28304 for cash. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Thank you!</t>
+          <t>QUINNEICE, hi — I'm Charles with Paragon Government Solutions. I'm interested in buying 1921 Ashridge Dr, Fayetteville, NC 28304 for cash. would the owner entertain a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Rachel, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 330 Klamath Dr, Pittsburgh, PA 15205 — a cash purchase. Could the seller look at a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thank you!</t>
+          <t>Rachel, hi — Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 330 Klamath Dr, Pittsburgh, PA 15205. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Hey Rae, I'm Charles with Paragon Government Solutions. interested in buying 7720 Smart St, Detroit, MI 48210 for cash. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
+          <t>Hey Rae, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 7720 Smart St, Detroit, MI 48210 — would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Hi Randal, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
+          <t>Randal, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 1644 Pincushion Rd, Columbia, SC 29209 — open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Ray, hi — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day Ray. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 6627 Eastwood St, Houston, TX 77021. would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Re/Max, hi — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks much!</t>
+          <t>Hey Re/Max. Charles here with Paragon Government Solutions, and I'm reaching out about 1720 Morninghill Dr, Columbia, SC 29210. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Hi there Rebecca — my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
+          <t>Hi Rebecca. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 6408 Macroom Meadows Ln, Houston, TX 77048. any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>Hello Regina, Charles Pleasant, Paragon Government Solutions. interested in buying 6036 Central St, Detroit, MI 48210 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Much appreciated!</t>
+          <t>Regina, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6036 Central St, Detroit, MI 48210; could the seller look at a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>Hello Reid, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6224 Highland Hills Dr, Dallas, TX 75241. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Thanks!</t>
+          <t>Hello Reid — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 6224 Highland Hills Dr, Dallas, TX 75241. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Rene, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Rene. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 7331 S Peoria St, Chicago, IL 60621 for cash. could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Hello Reva — I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
+          <t>Hello Reva — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 8451 Greenview Ave, Detroit, MI 48228. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18627,7 +18627,7 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>Hi Rhonda, Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thank you!</t>
+          <t>Hi Rhonda. my name's Charles Pleasant, Paragon Government Solutions, and I came across 37985 Falcon Wood Dr, Denham Springs, LA 70706 and buy cash. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Good day Rhonda — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Rhonda — this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 2802 W Mosher St, Baltimore, MD 21216 for cash. could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>Hi Ricardo, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thank you!</t>
+          <t>Hi Ricardo, Charles here with Paragon Government Solutions. I'm a cash investor looking at 10243 Mills Run Dr, Houston, TX 77070; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>Hi there Richard. this is Charles Pleasant with Paragon Government Solutions, and I buy cash and I'm interested in 8327 Lou Gehrig St, San Antonio, TX 78240. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks much!</t>
+          <t>Hi Richard, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 8327 Lou Gehrig St, San Antonio, TX 78240; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>Hello Robbie. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 33870 Perkins Crossing Rd, Walker, LA 70785. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
+          <t>Hello Robbie — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 33870 Perkins Crossing Rd, Walker, LA 70785. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>Hey Robert — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks!</t>
+          <t>Hello Robert, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 8410 N 32ND Avenue, Phoenix, AZ 85051; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>Hello ROBERT. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 784 Yardville Hamilton Sq, Trenton, NJ 08691 for cash. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
+          <t>Hi ROBERT — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 784 Yardville Hamilton Sq, Trenton, NJ 08691. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>Hello Robert, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Robert, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 321 Crawford Rd, Columbia, SC 29203; would the owner entertain a cash as-is offer, fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>Hello Robert, I'm Charles with Paragon Government Solutions. I'm reaching out about 6235 Leaf Arbor Dr, Houston, TX 77092 — a cash purchase. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
+          <t>Hello Robert. I'm Charles with Paragon Government Solutions, and I'm interested in buying 6235 Leaf Arbor Dr, Houston, TX 77092 for cash. is the seller open to a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>Hi Roberto, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Hi Roberto, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 11881 Saint Patrick St, Detroit, MI 48205 — is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>Hello Roberto. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 3226 Decatur Ave, Lakeland, FL 33805. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
+          <t>Hi Roberto, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 3226 Decatur Ave, Lakeland, FL 33805; is the seller open to a cash as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>Good day Robin. Charles Pleasant, Paragon Government Solutions, and interested in buying 17003 Tireman St, Detroit, MI 48228 for cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hey Robin, I'm Charles with Paragon Government Solutions. I'm reaching out about 17003 Tireman St, Detroit, MI 48228; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>Hi Robyn, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks!</t>
+          <t>Robyn, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 15212 Crystal Dr, Pride, LA 70770. could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>Hi Rodney, Charles Pleasant, Paragon Government Solutions. interested in buying 14035 Kentfield St, Detroit, MI 48223 for cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hello Rodney. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 14035 Kentfield St, Detroit, MI 48223. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>Hey Rohn. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1614 Kayouche St, Lake Charles, LA 70601. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi Rohn, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1614 Kayouche St, Lake Charles, LA 70601; any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>Good day Ross, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Hi Ross — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 2507 Parktrail Rd, Baltimore, MD 21234. would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19027,7 +19027,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>Hey Rosy — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Rosy, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 205 Thelma Ln, Lake Charles, LA 70601 — open to a discounted cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>Good day Roxanne, Charles here with Paragon Government Solutions. I buy cash and I'm interested in 1316 E Applegate Dr, Austin, TX 78753. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Hello Roxanne. this is Charles Pleasant with Paragon Government Solutions, and I came across 1316 E Applegate Dr, Austin, TX 78753 and buy cash. is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>Hi Rubi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 4600 Ireland St, Houston, TX 77016. Would the owner entertain a cash as-is offer, close quickly, short inspection period. What's the best email to send it to? Thanks!</t>
+          <t>Rubi, hi, I'm Charles with Paragon Government Solutions. I came across 4600 Ireland St, Houston, TX 77016 and buy cash — is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19102,7 +19102,7 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>Hi there Ryan — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks!</t>
+          <t>Hi Ryan, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1613 S 5th St, Phoenix, AZ 85004; is the seller open to a cash as-is offer, close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>RYAN, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3318 NOLAN Street, Jacksonville, FL 32254. Could the seller look at a cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi RYAN — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 3318 NOLAN Street, Jacksonville, FL 32254. could the seller look at a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>Hi Ryan — I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
+          <t>Ryan, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 4630 Thrush Dr, Indianapolis, IN 46222 for cash — any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>Hi Ryan — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks so much!</t>
+          <t>Hey Ryan, Charles here with Paragon Government Solutions. I'm interested in buying 2258 Hawthorne Ave, Pittsburgh, PA 15218 for cash; open to a discounted cash, as-is offer, close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>S., hi, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>S., hi, I'm Charles with Paragon Government Solutions. I'm reaching out about 12828 Strathmoor St, Detroit, MI 48227; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>Hey Samantha, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 6159 Lyndhurst Dr, Houston, TX 77033. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
+          <t>Hi there Samantha. my name's Charles Pleasant, Paragon Government Solutions, and I came across 6159 Lyndhurst Dr, Houston, TX 77033 and buy cash. is the seller open to a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19252,7 +19252,7 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>Hey Sara, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 6537 S 15th Dr, Phoenix, AZ 85041. Is the seller open to a cash as-is offer, a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
+          <t>Good day Sara. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 6537 S 15th Dr, Phoenix, AZ 85041. could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>Sarah, hi — Charles here with Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hello Sarah. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 5953 S Throop St, Chicago, IL 60636. could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19302,7 +19302,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>Hello Schlanda, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 1319 Reynes St, New Orleans, LA 70117 — a cash purchase. Could the seller look at a cash, as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks much!</t>
+          <t>Good day Schlanda — this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 1319 Reynes St, New Orleans, LA 70117 for cash. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>Hello Schylbea. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 13123 Indiana St, Detroit, MI 48238. Open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hello Schylbea, Charles here with Paragon Government Solutions. I'm interested in buying 13123 Indiana St, Detroit, MI 48238 for cash — would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19352,7 +19352,7 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>Hi there Scott, I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Scott. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 7607 Dobel St, Detroit, MI 48234 for cash. open to a discounted cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>Hello Scott, Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Scott. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 6104 Franklin Villas Way, Indianapolis, IN 46237 for cash. open to a discounted cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>Hi SCOTT — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks so much!</t>
+          <t>SCOTT, hi — I'm Charles with Paragon Government Solutions. I came across 6711 CAVALIER Road, Jacksonville, FL 32208 and buy cash. is the seller open to a cash as-is offer with quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>Hi there Scott — Charles here with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi Scott, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 1021 E TAYLOR Street, Phoenix, AZ 85006 — would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>Hi there Sean, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 8605 Fireside Dr, Austin, TX 78757. Could the seller look at a cash, as-is offer, quick close and a short inspection. Best email for the formal offer? Thanks much!</t>
+          <t>Hey Sean. Charles here with Paragon Government Solutions, and I'm reaching out about 8605 Fireside Dr, Austin, TX 78757. is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>Hi there Sean — this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Sean — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 8506 McDade St, Houston, TX 77080. would the owner entertain a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>Hi Sebastian — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Sebastian, my name's Charles Pleasant, Paragon Government Solutions. I came across 5730 S Hoyne Ave, Chicago, IL 60636 and buy cash — could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>Sergio, hi, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there Sergio. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 16203 Barbarossa Dr, Houston, TX 77083. is the seller open to a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>Hi Sergio. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 10841 S Vernon Ave, Chicago, IL 60628. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
+          <t>Sergio, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 10841 S Vernon Ave, Chicago, IL 60628. would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>Hi SETH, my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>SETH, hi — Charles here with Paragon Government Solutions. I'm interested in buying 2837 LIPPIA Road, Jacksonville, FL 32209 for cash. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>Hello Shakena. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 130 Brandon Hall Rd, Columbia, SC 29229. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
+          <t>Hey Shakena. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 130 Brandon Hall Rd, Columbia, SC 29229. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>Hello Shane, I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi Shane — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 889 E 128th St, Cleveland, OH 44108. could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>Hello Shannon, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Shannon — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 8710 Files St, Dallas, TX 75217. would the seller consider a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>Hi Shannon, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 134 Palmetto Park Cir, Columbia, SC 29229. Would the owner entertain a cash as-is offer, quick close and a short inspection. Best email for the formal offer? Appreciate it!</t>
+          <t>Hi there Shannon, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 134 Palmetto Park Cir, Columbia, SC 29229 — could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>Hi there Sharon, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 516 Lakeside Ave, Columbia, SC 29203. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Sharon — I'm Charles with Paragon Government Solutions. I'm reaching out about 516 Lakeside Ave, Columbia, SC 29203. open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>Sharon, hi, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Good day Sharon — Charles here with Paragon Government Solutions. I'm reaching out about 515 W Main St, Gonzales, LA 70737. would the owner entertain a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>Hello Shauntell. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 337 W 110th Pl, Chicago, IL 60628. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks so much!</t>
+          <t>Shauntell, hi — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 337 W 110th Pl, Chicago, IL 60628. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>Hi SHAWANA, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>SHAWANA, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 8342 BARRACUDA Road, Jacksonville, FL 32244. would the owner entertain a cash as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>Hi Shawn, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 5404 Dixie Ln, Alexandria, LA 71301. Is the seller open to a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Appreciate it!</t>
+          <t>Hi Shawn — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 5404 Dixie Ln, Alexandria, LA 71301 for cash. would the owner entertain a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>Hi SHAWN — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
+          <t>Hi there SHAWN — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3862 ORLANDO Circle W, Jacksonville, FL 32207. could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>Good day Shay — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks!</t>
+          <t>Shay, hi, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 180 Crestmere Pl, Memphis, TN 38112; could the seller look at a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>Good day Shelby, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 4235 Elmwood St, Houston, TX 77051. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi there Shelby. my name's Charles Pleasant, Paragon Government Solutions, and I came across 4235 Elmwood St, Houston, TX 77051 and buy cash. open to a discounted cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19902,7 +19902,7 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>Hi there Shelly, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. What's the best email to send it to? Thanks much!</t>
+          <t>Hi Shelly — Charles Pleasant, Paragon Government Solutions. I'm reaching out about 4500 Blossom Valley Ln, Bakersfield, CA 93313. could the seller look at a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>Good day Shemika, Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's the best email to send it to? Thank you!</t>
+          <t>Good day Shemika. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2764 Dalton St, Baton Rouge, LA 70805. could the seller look at a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>Good day Shemika, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 2764 Dalton St, Baton Rouge, LA 70805. Is the seller open to a cash as-is offer, quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Shemika — my name's Charles Pleasant, Paragon Government Solutions. I came across 2764 Dalton St, Baton Rouge, LA 70805 and buy cash. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>Hey Sherrease, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 14216 Kentucky St, Detroit, MI 48238 — a cash purchase. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
+          <t>Sherrease, hi, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 14216 Kentucky St, Detroit, MI 48238 for cash — is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20002,7 +20002,7 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>Hello Sherri — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Appreciate it!</t>
+          <t>Sherri, hi — Charles here with Paragon Government Solutions. I'm interested in buying 2108 Blake Ave, Dallas, TX 75228 for cash. is the seller open to a cash as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20027,7 +20027,7 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>Hey Sherri — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
+          <t>Sherri, hi, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 8091 Kenney St, Detroit, MI 48234 — would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20052,7 +20052,7 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>Hello SHINESHA — I'm Charles with Paragon Government Solutions. Is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Much appreciated!</t>
+          <t>Hello SHINESHA — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 235 Whitney Dr, Fayetteville, NC 28314. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>Hi there Shirley, this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
+          <t>Shirley, hi, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3815 Webb Ct, Columbia, SC 29204 — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>Hello Shoaib, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 5093 Garland St, Detroit, MI 48213. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi Shoaib. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 5093 Garland St, Detroit, MI 48213. could the seller look at a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>Hi there Shoaib, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Hey Shoaib, this is Charles Pleasant with Paragon Government Solutions. I came across 5330 Longmeadow St, Houston, TX 77033 and buy cash; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>Hello Shon, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast close with a brief inspection window? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Shon, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 2091 Yulee St, Jacksonville, FL 32209; would the owner entertain a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>Shonda, hi — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? Where can I email the written terms? Much appreciated!</t>
+          <t>Hi there Shonda — Charles here with Paragon Government Solutions. I came across 218 Sanhican Dr, Trenton, NJ 08618 and buy cash. would the owner entertain a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>Hi there Sidra. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 7106 Tierwester St, Houston, TX 77021 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks much!</t>
+          <t>Sidra, hi — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 7106 Tierwester St, Houston, TX 77021. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>Sonia, hi. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 514 L St, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Sonia — Charles here with Paragon Government Solutions. I'm reaching out about 514 L St, Bakersfield, CA 93304. would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>Good day Sonia, Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 11315 Raincove Dr, Houston, TX 77016. Open to a discounted cash, as-is offer, quick close and a short inspection. Where can I email the written terms? Thanks much!</t>
+          <t>Hi Sonia, Charles Pleasant, Paragon Government Solutions. I came across 11315 Raincove Dr, Houston, TX 77016 and buy cash — any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>Hi there STACEY. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 6811 LANGFORD Street, Jacksonville, FL 32219. Open to a discounted cash, as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks!</t>
+          <t>Good day STACEY, this is Charles Pleasant with Paragon Government Solutions. I came across 6811 LANGFORD Street, Jacksonville, FL 32219 and buy cash — any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>Hi Stacie, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 4400 Norfolk Ave, Baltimore, MD 21216. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi Stacie, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 4400 Norfolk Ave, Baltimore, MD 21216; would the owner entertain a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20327,7 +20327,7 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>Hi there Stacy, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 11833 Beachberry Dr, Houston, TX 77034. Would the owner entertain a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Thanks so much!</t>
+          <t>Hello Stacy — this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 11833 Beachberry Dr, Houston, TX 77034 for cash. open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>Hello Stephanie. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 6541 W OSBORN Road, Phoenix, AZ 85033 — a cash purchase. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Stephanie, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 6541 W OSBORN Road, Phoenix, AZ 85033 — any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>Hello Stephanie — Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks much!</t>
+          <t>Hello Stephanie — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5135 S May St, Chicago, IL 60609. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20402,7 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>Hi there Stephanie. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1404 SE 34th Ter, Cape Coral, FL 33904 — a cash purchase. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
+          <t>Hi Stephanie. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 1404 SE 34th Ter, Cape Coral, FL 33904. could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>Hey STEPHANIE, Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 2205 COMMONWEALTH Avenue, Jacksonville, FL 32209. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thank you!</t>
+          <t>Hello STEPHANIE, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 2205 COMMONWEALTH Avenue, Jacksonville, FL 32209; any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20452,7 +20452,7 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>Good day STEPHANIE. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 115 Brookwood Ave, Fayetteville, NC 28301. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hey STEPHANIE. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 115 Brookwood Ave, Fayetteville, NC 28301. would the seller consider a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>Hi Stephanie, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Stephanie — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 6106 Sandy Creek Ln, Zachary, LA 70791. could the seller look at a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>Stephanie, hi — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks much!</t>
+          <t>Stephanie, hi. Charles here with Paragon Government Solutions, and I'm interested in buying 16127 Long Rd, Houston, TX 77044 for cash. is the seller open to a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20527,7 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>STEPHEN, hi — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Thanks!</t>
+          <t>Hey STEPHEN. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 4222 Woodlea Ave, Baltimore, MD 21206. open to a discounted cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20552,7 +20552,7 @@
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>Hi Steve. I'm Charles with Paragon Government Solutions, and interested in buying 6831 S Emerald Ave, Chicago, IL 60621 for cash. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi Steve — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 6831 S Emerald Ave, Chicago, IL 60621. would the seller consider a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>Hi there Steve. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2666 Olympia Ave, North Charleston, SC 29405. Open to a discounted cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Much appreciated!</t>
+          <t>Hello Steve — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2666 Olympia Ave, North Charleston, SC 29405. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>Hi Steven, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 2514 W Ramsey Ave, Milwaukee, WI 53221. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
+          <t>Steven, hi, Charles here with Paragon Government Solutions. I'm a cash investor looking at 2514 W Ramsey Ave, Milwaukee, WI 53221; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20627,7 +20627,7 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>Hey Steven — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Much appreciated!</t>
+          <t>Steven, hi, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 408 W Montana Ave, Dallas, TX 75224 — could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20652,7 +20652,7 @@
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>Hi Steven — this is Charles Pleasant with Paragon Government Solutions. Could the seller look at a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Appreciate it!</t>
+          <t>Hi Steven, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 12008 Vista Nogal St, San Antonio, TX 78213 — would the seller consider a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20677,7 +20677,7 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>Good day Steven. I'm Charles with Paragon Government Solutions, and interested in buying 3061 Horse Ranch Rd, San Antonio, TX 78264 for cash. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Hi Steven. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 3061 Horse Ranch Rd, San Antonio, TX 78264. is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>Hi Summer, my name's Charles Pleasant, Paragon Government Solutions. I buy cash and I'm interested in 1201 Willow Dr, Lake Charles, LA 70611. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Summer — Charles here with Paragon Government Solutions. I came across 1201 Willow Dr, Lake Charles, LA 70611 and buy cash. is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>Hey Susan — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
+          <t>Hello Susan. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3419 SE 5th Ave, Cape Coral, FL 33904. any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>Hi there Susan — Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks so much!</t>
+          <t>Susan, hi, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 12244 Woodmont Ave, Detroit, MI 48227 — would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>Good day Suzy — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks much!</t>
+          <t>Hello Suzy. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 13050 N 19TH Street #50, Phoenix, AZ 85022. open to a discounted cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>Good day Sylvia. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 4401 Hughes Ln Space 200, Bakersfield, CA 93304. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
+          <t>Hi Sylvia, Charles here with Paragon Government Solutions. I'm reaching out about 4401 Hughes Ln Space 200, Bakersfield, CA 93304; would the owner entertain a cash as-is offer, close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20832,7 +20832,7 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>Hey T'Keyah, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thank you!</t>
+          <t>Hello T'Keyah. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in your listing. would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>Hi there Tai — I'm Charles with Paragon Government Solutions. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thanks so much!</t>
+          <t>Tai, hi, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 7219 Avocet Ln, Houston, TX 77040 — could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20882,7 +20882,7 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>Tal, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 2166 W 93rd St, Cleveland, OH 44102. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Tal. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 2166 W 93rd St, Cleveland, OH 44102. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>Hi Tamara, I'm Charles with Paragon Government Solutions. I'd like to put in a cash offer on 5151 S Denley Dr, Dallas, TX 75241. Would the seller consider a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
+          <t>Hey Tamara, Charles here with Paragon Government Solutions. I came across 5151 S Denley Dr, Dallas, TX 75241 and buy cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20932,7 +20932,7 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>Good day Tamara, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1991 Lawrence St, Detroit, MI 48206. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence. Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Tamara, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1991 Lawrence St, Detroit, MI 48206 — could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -20957,7 +20957,7 @@
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>Good day Tamara, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — close quickly, short inspection period? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Good day Tamara — Charles here with Paragon Government Solutions. I came across 3846 W 84th Pl, Chicago, IL 60652 and buy cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>Good day Tamesha, this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Tamesha. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 12323 Misty Laurel Dr, Houston, TX 77014. open to a discounted cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Hey Tami, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 6243 S 31st West Ave, Tulsa, OK 74132. Would the seller consider a cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Appreciate it!</t>
+          <t>Tami, hi. I'm Charles with Paragon Government Solutions, and I'm interested in buying 6243 S 31st West Ave, Tulsa, OK 74132 for cash. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21032,7 +21032,7 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Hey Tamie, Charles here with Paragon Government Solutions. I'm a cash buyer interested in 24 Evans Ave, Trenton, NJ 08638. Open to a discounted cash, as-is offer, close quickly, short inspection period. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there Tamie, Charles here with Paragon Government Solutions. I came across 24 Evans Ave, Trenton, NJ 08638 and buy cash; would the seller consider a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21057,7 +21057,7 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>Hey Tamika, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Thanks!</t>
+          <t>Hey Tamika, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 10118 S Luella Ave, Chicago, IL 60617; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21082,7 +21082,7 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Hey Tammi, I'm Charles with Paragon Government Solutions. I'm reaching out about 323 Belle Winds Ct, Shreveport, LA 71106 — a cash purchase. Open to a discounted cash, as-is offer, quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
+          <t>Good day Tammi, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 323 Belle Winds Ct, Shreveport, LA 71106; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21107,7 +21107,7 @@
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Good day Tammy, this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 12011 Doubleday Dr, Houston, TX 77089 — a cash purchase. Is the seller open to a cash as-is offer, quick close and a short inspection. What's the best email to send it to? Appreciate it!</t>
+          <t>Good day Tammy, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 12011 Doubleday Dr, Houston, TX 77089 — is the seller open to a cash as-is offer, fast close with a brief inspection window? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>Hello TANA, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>TANA, hi, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2425 HOLMES Street, Jacksonville, FL 32207; open to a discounted cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>Tanisha, hi, I'm Charles with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hello Tanisha, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 19953 Hull St, Detroit, MI 48203 — could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>Tara, hi, this is Charles Pleasant with Paragon Government Solutions. I buy cash and I'm interested in 1430 Dahlia Rd, Columbia, SC 29205. Any chance the seller would take a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Tara — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 1430 Dahlia Rd, Columbia, SC 29205. would the seller consider a cash, as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>Hey TASHELE, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 9656 FLECHETTE Avenue, Jacksonville, FL 32208. Open to a discounted cash, as-is offer, fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello TASHELE, I'm Charles with Paragon Government Solutions. I came across 9656 FLECHETTE Avenue, Jacksonville, FL 32208 and buy cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>Hey Tashia, Charles Pleasant, Paragon Government Solutions. interested in buying 2433 W Tonto St, Phoenix, AZ 85009 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
+          <t>Hey Tashia. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 2433 W Tonto St, Phoenix, AZ 85009. would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>Hi there Tawanda, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
+          <t>Tawanda, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 4410 Greenwood Ln, Baker, LA 70714 — any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21282,7 +21282,7 @@
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>Hi Taz, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 10615 Kirkdale Dr, Houston, TX 77089. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
+          <t>Good day Taz. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 10615 Kirkdale Dr, Houston, TX 77089. would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>Good day Teal, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2831 Lawrence St, Denver, CO 80205. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Much appreciated!</t>
+          <t>Good day Teal, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 2831 Lawrence St, Denver, CO 80205; open to a discounted cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>Hey Tene', Charles here with Paragon Government Solutions. Would the seller consider a cash, as-is offer — a quick clean close and short due diligence? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Tene', my name's Charles Pleasant, Paragon Government Solutions. I came across 6845 S Chappel Ave, Chicago, IL 60649 and buy cash; could the seller look at a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>Tera, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 2222 Detroit Ave APT 504, Cleveland, OH 44113 for cash. Would the owner entertain a cash as-is offer, close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
+          <t>Tera, hi. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 2222 Detroit Ave APT 504, Cleveland, OH 44113. is the seller open to a cash as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>Hi there Terence, Charles here with Paragon Government Solutions. I'm reaching out about 389 Northwood St, Columbia, SC 29201 — a cash purchase. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window. What's a good email for the written offer? Thank you!</t>
+          <t>Hello Terence, I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 389 Northwood St, Columbia, SC 29201 — any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21407,7 +21407,7 @@
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>Teresa, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 189 Regina Ave, Hamilton, NJ 08619 — a cash purchase. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Teresa, hi. I'm Charles with Paragon Government Solutions, and I came across 189 Regina Ave, Hamilton, NJ 08619 and buy cash. would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>Hey Teresa. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2602 Falls Dr, Dallas, TX 75211. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi there Teresa. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2602 Falls Dr, Dallas, TX 75211. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>Hi Terry, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 609 Lufkin Circle, Fayetteville, NC 28311. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
+          <t>Terry, hi — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 609 Lufkin Circle, Fayetteville, NC 28311. could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>Hi there Terry, I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Terry, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 5214 Quarter Ln, Baton Rouge, LA 70809; would the owner entertain a cash as-is offer, fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>Good day Thalia — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thank you!</t>
+          <t>Hi there Thalia, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 12699 Greenlawn St, Detroit, MI 48238; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>Hi Thao. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 1263 James St, Baltimore, MD 21223. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Thao, hi — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 1263 James St, Baltimore, MD 21223. would the seller consider a cash, as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21557,7 +21557,7 @@
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>Good day Thao — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Much appreciated!</t>
+          <t>Hey Thao, Charles Pleasant, Paragon Government Solutions. I'm reaching out about 9303 Kingsflower Cir, Houston, TX 77075; would the owner entertain a cash as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>Hi Thomas, my name's Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hey Thomas, this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 8656 &amp; 8560 Farmbrook St, Detroit, MI 48224; would the seller consider a cash, as-is offer, quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>Hello THOMAS — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi there THOMAS, I'm Charles with Paragon Government Solutions. I'm reaching out about 1232 RENSSELAER Avenue, Jacksonville, FL 32205 — would the owner entertain a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21632,7 @@
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>Hello TIER, this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Best email for the formal offer? Thanks!</t>
+          <t>Hello TIER, my name's Charles Pleasant, Paragon Government Solutions. I came across 621 Ashboro St, Fayetteville, NC 28311 and buy cash; would the seller consider a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>Tiffany, hi, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 10320 S Indiana Ave, Chicago, IL 60628. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence. What's the best email to send it to? Much appreciated!</t>
+          <t>Hey Tiffany, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 10320 S Indiana Ave, Chicago, IL 60628; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>Tiffany, hi — I'm Charles with Paragon Government Solutions. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks so much!</t>
+          <t>Hi Tiffany. I'm Charles with Paragon Government Solutions, and I'm interested in buying 11744 Wade St, Detroit, MI 48213 for cash. any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21707,7 +21707,7 @@
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>Good day TIM, this is Charles Pleasant with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
+          <t>Hi there TIM, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 7940 EATON Avenue, Jacksonville, FL 32211 for cash; is the seller open to a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21732,7 +21732,7 @@
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>Timothy, hi, this is Charles Pleasant with Paragon Government Solutions. interested in buying 230 Sterling Rd, Bakersfield, CA 93307 for cash. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period. What's a good email for the written offer? Thanks much!</t>
+          <t>Timothy, hi — Charles here with Paragon Government Solutions. I'd like to put in a cash offer on 230 Sterling Rd, Bakersfield, CA 93307. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21757,7 +21757,7 @@
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>Timothy, hi. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 20260 Patton St, Detroit, MI 48219 — a cash purchase. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi Timothy, I'm Charles with Paragon Government Solutions. I'm interested in buying 20260 Patton St, Detroit, MI 48219 for cash; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>Hello TJ. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 1809 Manteo St, Fayetteville, NC 28303. Open to a discounted cash, as-is offer with close quickly, short inspection period. Best email for the formal offer? Thanks!</t>
+          <t>Hi TJ — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1809 Manteo St, Fayetteville, NC 28303. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21807,7 +21807,7 @@
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>Hello TLeice, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2684 Iroquois St, Baton Rouge, LA 70805. Open to a discounted cash, as-is offer, a quick clean close and short due diligence. Where can I email the written terms? Much appreciated!</t>
+          <t>Hi TLeice. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 2684 Iroquois St, Baton Rouge, LA 70805. could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>Hi there TLeice — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi TLeice, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 2684 Iroquois St, Baton Rouge, LA 70805 — open to a discounted cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>Good day Tom, this is Charles Pleasant with Paragon Government Solutions. interested in buying 83 Bryn Mawr Ave, Trenton, NJ 08618 for cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
+          <t>Hey Tom, Charles here with Paragon Government Solutions. I'm a cash investor looking at 83 Bryn Mawr Ave, Trenton, NJ 08618 — could the seller look at a cash, as-is offer, fast close with a brief inspection window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>Hi TONY. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 3252 THOMAS Street, Jacksonville, FL 32254. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Hi there TONY — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 3252 THOMAS Street, Jacksonville, FL 32254. could the seller look at a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>Hi there TONYA. my name's Charles Pleasant, Paragon Government Solutions, and I buy cash and I'm interested in 5466 Maplewood Ct, Fayetteville, NC 28314. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
+          <t>Hi TONYA, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 5466 Maplewood Ct, Fayetteville, NC 28314; is the seller open to a cash as-is offer, fast cash close, short feasibility window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21932,7 +21932,7 @@
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>Hello Tonya, this is Charles Pleasant with Paragon Government Solutions. Open to a discounted cash, as-is offer — close quickly, short inspection period? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Tonya — this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 12746 Woodland Dr, Jacksonville, FL 32218 for cash. could the seller look at a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -21957,7 +21957,7 @@
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>Hey TORANIQUE — my name's Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Appreciate it!</t>
+          <t>Good day TORANIQUE. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash investor looking at 1354 Worstead Dr, Fayetteville, NC 28314. is the seller open to a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -21982,7 +21982,7 @@
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>Hello Tosh — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
+          <t>Good day Tosh, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1735 N Sherwood Forest Dr, Baton Rouge, LA 70814; open to a discounted cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>Hi TRACEY, Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
+          <t>Good day TRACEY. Charles Pleasant, Paragon Government Solutions, and I came across 1181 Torrey Dr, Fayetteville, NC 28301 and buy cash. could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>Hello Transit — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi Transit, Charles here with Paragon Government Solutions. I'm interested in buying 699 Gladiolus Dr, Columbia, SC 29229 for cash — open to a discounted cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22057,7 +22057,7 @@
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>Hi there Tricia. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 129 Kings Parish Ct, Columbia, SC 29209. Would the owner entertain a cash as-is offer with quick close and a short inspection. What email should I send the written offer to? Thanks!</t>
+          <t>Hey Tricia, I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 129 Kings Parish Ct, Columbia, SC 29209; any chance the seller would take a cash, as-is offer, quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22082,7 +22082,7 @@
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>Good day Trinh, Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Trinh. Charles Pleasant, Paragon Government Solutions, and I came across 255 Sorrel Tree Dr, Columbia, SC 29223 and buy cash. could the seller look at a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>Hi there TRINITY. I'm Charles with Paragon Government Solutions, and I'm reaching out about 6559 Amanda Cir, Fayetteville, NC 28304 — a cash purchase. Is the seller open to a cash as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks much!</t>
+          <t>Hello TRINITY, this is Charles Pleasant with Paragon Government Solutions. I came across 6559 Amanda Cir, Fayetteville, NC 28304 and buy cash — would the seller consider a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22132,7 +22132,7 @@
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>Hi Tucker, my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer — quick close and a short inspection? I can send written terms today. Best email for the formal offer? Thank you!</t>
+          <t>Hey Tucker — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 4538 Larkspur St, Houston, TX 77051. would the owner entertain a cash as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>Hi Tyjuan, Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi there Tyjuan, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 29 Battery Walk Ct, Columbia, SC 29212 — open to a discounted cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22182,7 +22182,7 @@
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>Hello Tyler, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — quick close and a short inspection? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>Hello Tyler — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 338 Bowling Ave, Columbia, SC 29203. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22207,7 +22207,7 @@
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>Hey Tyreeta — Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks!</t>
+          <t>Hello Tyreeta. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 3628 W 83rd St, Chicago, IL 60652. open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>Hello Tyrone. Charles here with Paragon Government Solutions, and I buy cash and I'm interested in 7137 S Winchester Ave, Chicago, IL 60636. Is the seller open to a cash as-is offer with quick close and a short inspection. Where can I email the written terms? Appreciate it!</t>
+          <t>Hey Tyrone, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 7137 S Winchester Ave, Chicago, IL 60636; could the seller look at a cash, as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22257,7 +22257,7 @@
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>Valerie, hi, Charles here with Paragon Government Solutions. interested in buying 3698 Menlo Rd, Shaker Heights, OH 44120 for cash. Is the seller open to a cash as-is offer, fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
+          <t>Hi Valerie, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 3698 Menlo Rd, Shaker Heights, OH 44120 for cash — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22282,7 +22282,7 @@
       </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>Hey Vanessa, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
+          <t>Hello Vanessa. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 15560 Tiger Bend Rd, Baton Rouge, LA 70817. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22307,7 +22307,7 @@
       </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>Hello Vanessa — Charles here with Paragon Government Solutions. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Best email for the formal offer? Thanks much!</t>
+          <t>Vanessa, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 2248 Cooper St, Dallas, TX 75215 for cash. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>Hey Vanessa — this is Charles Pleasant with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks much!</t>
+          <t>Hi there Vanessa, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 8043 Wier Dr, Houston, TX 77017; could the seller look at a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>Hello Vanessa — Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Vanessa, Charles here with Paragon Government Solutions. I'm reaching out about 133 Cornwall Ave, Trenton, NJ 08618 — could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22382,7 @@
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>Hey Vanessa — this is Charles Pleasant with Paragon Government Solutions. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's a good email for the written offer? Appreciate it!</t>
+          <t>Hey Vanessa, Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 11265 S May St, Chicago, IL 60643; any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? I can send written terms today. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>Hello VANETTA. my name's Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 4022 TYNDALE Drive, Jacksonville, FL 32210. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Appreciate it!</t>
+          <t>Hey VANETTA — Charles Pleasant, Paragon Government Solutions. I came across 4022 TYNDALE Drive, Jacksonville, FL 32210 and buy cash. is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>Good day Vanity — Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Best email for the formal offer? Thank you!</t>
+          <t>Vanity, hi, my name's Charles Pleasant, Paragon Government Solutions. I came across 8926 S Lowe Ave, Chicago, IL 60620 and buy cash — would the seller consider a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>Hi there Veronica, I'm Charles with Paragon Government Solutions. I buy cash and I'm interested in 213 T St, Bakersfield, CA 93304. Would the seller consider a cash, as-is offer, quick close and a short inspection. Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hi there Veronica. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 213 T St, Bakersfield, CA 93304. would the seller consider a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>Hey Vickie, my name's Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer — fast cash close, short feasibility window? I can send written terms today. What email should I send the written offer to? Thanks much!</t>
+          <t>Hi Vickie, my name's Charles Pleasant, Paragon Government Solutions. I came across your listing and buy cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>Hello Victoria, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2127 Coelum Ct, Dallas TX 75253. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks!</t>
+          <t>Victoria, hi — my name's Charles Pleasant, Paragon Government Solutions. I came across 2127 Coelum Ct, Dallas TX 75253 and buy cash. open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22532,7 +22532,7 @@
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>Victoria, hi, Charles Pleasant, Paragon Government Solutions. interested in buying 7538 Bywood St, Houston, TX 77028 for cash. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks much!</t>
+          <t>Hi there Victoria, Charles Pleasant, Paragon Government Solutions. I'm interested in buying 7538 Bywood St, Houston, TX 77028 for cash; any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? I can send written terms today. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>Vince, hi. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 517 Windjammer Ln, Columbia, SC 29229. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hi there Vince, Charles here with Paragon Government Solutions. I came across 517 Windjammer Ln, Columbia, SC 29229 and buy cash — any chance the seller would take a cash, as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>Hello Vinh — my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Vinh, hi, Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 2503 Highland Ave, Shreveport, LA 71104 — could the seller look at a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22607,7 +22607,7 @@
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>Good day Viveka, Charles Pleasant, Paragon Government Solutions. Is the seller open to a cash as-is offer — a quick clean close and short due diligence? I can send written terms today. Where should I send the offer in writing? Thanks!</t>
+          <t>Hey Viveka — I'm Charles with Paragon Government Solutions. I'm reaching out about 8028 S Ada St, Chicago, IL 60620. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>Hi there Wally. this is Charles Pleasant with Paragon Government Solutions, and I'm reaching out about 5604 Creekmore Dr, Oklahoma City, OK 73179 — a cash purchase. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks!</t>
+          <t>Good day Wally. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 5604 Creekmore Dr, Oklahoma City, OK 73179. would the owner entertain a cash as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22657,7 +22657,7 @@
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>Hello Wayne. Charles Pleasant, Paragon Government Solutions, and I'm a cash buyer interested in 2011 Lake Carolina Dr, Columbia, SC 29229. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi there Wayne — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2011 Lake Carolina Dr, Columbia, SC 29229. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>Good day WELCOME, this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 603 Faison Ave, Fayetteville, NC 28304. Would the seller consider a cash, as-is offer, fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hi there WELCOME. Charles here with Paragon Government Solutions, and I'm interested in buying 603 Faison Ave, Fayetteville, NC 28304 for cash. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>Hello Wendy — Charles Pleasant, Paragon Government Solutions. Would the owner entertain a cash as-is offer, close quickly, short inspection period? Best email for the formal offer? Appreciate it!</t>
+          <t>Hey Wendy, I'm Charles with Paragon Government Solutions. I'm interested in buying 16878 Lilac St, Detroit, MI 48221 for cash; any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22732,7 +22732,7 @@
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>Hello Wes, Charles here with Paragon Government Solutions. I'm reaching out about 1013 N Ruth Ave, Lakeland, FL 33805 — a cash purchase. Would the owner entertain a cash as-is offer, fast close with a brief inspection window. Where can I email the written terms? Thank you!</t>
+          <t>Hello Wes — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 1013 N Ruth Ave, Lakeland, FL 33805. would the seller consider a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>Hi William, I'm Charles with Paragon Government Solutions. Would the seller consider a cash, as-is offer — fast close with a brief inspection window? I can send written terms today. What's the best email to send it to? Thanks!</t>
+          <t>William, hi, this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3713 Mary Ave, Baltimore, MD 21206 — would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22782,7 +22782,7 @@
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>Hey William, my name's Charles Pleasant, Paragon Government Solutions. Any chance the seller would take a cash, as-is offer — close quickly, short inspection period? I can send written terms today. Best email for the formal offer? Thanks much!</t>
+          <t>Hi there William, Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 6211 Fullerton Ave, Cleveland, OH 44105 — open to a discounted cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -22807,7 +22807,7 @@
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>Good day WILLIAM — my name's Charles Pleasant, Paragon Government Solutions. Open to a discounted cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
+          <t>Hey WILLIAM, Charles here with Paragon Government Solutions. I came across 10592 HAVERFORD Road, Jacksonville, FL 32218 and buy cash; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -22832,7 +22832,7 @@
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>William, hi. I'm Charles with Paragon Government Solutions, and I'm a cash buyer interested in 14711 Lappin St, Detroit, MI 48205. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks much!</t>
+          <t>Hi William. my name's Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 14711 Lappin St, Detroit, MI 48205. could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>Hey William. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 2640 Cypress Ave, Dallas, TX 75227 — a cash purchase. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Thanks so much!</t>
+          <t>Hey William. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 2640 Cypress Ave, Dallas, TX 75227. open to a discounted cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>Good day Willie, my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 8367 Howton St #A/B, Houston, TX 77028. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window. What's the best email to send it to? Thanks much!</t>
+          <t>Willie, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 8367 Howton St #A/B, Houston, TX 77028; would the owner entertain a cash as-is offer, a quick clean close and short due diligence? I can send written terms today. What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>Hi there Xiaochen — Charles here with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
+          <t>Hello Xiaochen, I'm Charles with Paragon Government Solutions. I came across 20315 Goulburn St, Detroit, MI 48205 and buy cash — would the seller consider a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22932,7 +22932,7 @@
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>Hello Yu — I'm Charles with Paragon Government Solutions. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What's a good email for the written offer? Thanks so much!</t>
+          <t>Hi Yu, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 19408 Goulburn St, Detroit, MI 48205; would the seller consider a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -22957,7 +22957,7 @@
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>Hello Yurika. this is Charles Pleasant with Paragon Government Solutions, and interested in buying 9551 Gonzales Dr, Dallas, TX 75227 for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Yurika, Charles here with Paragon Government Solutions. I'm reaching out about 9551 Gonzales Dr, Dallas, TX 75227; any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? I can send written terms today. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>Hi Yvette, Charles here with Paragon Government Solutions. Is the seller open to a cash as-is offer — quick close and a short inspection? I can send written terms today. What email should I send the written offer to? Thanks!</t>
+          <t>Hello Yvette, this is Charles Pleasant with Paragon Government Solutions. I'm interested in buying 3078 Benny Rd SW, Albuquerque, NM 87105 for cash — would the seller consider a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>Good day Zachary — Charles Pleasant, Paragon Government Solutions. Would the seller consider a cash, as-is offer, quick close and a short inspection? What's the best email to send it to? Appreciate it!</t>
+          <t>Hi there Zachary — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 2937 Seyburn St, Detroit, MI 48214. open to a discounted cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23032,7 @@
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>Hey Zena — my name's Charles Pleasant, Paragon Government Solutions. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Much appreciated!</t>
+          <t>Hi Zena, my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 15801 E State Fair St, Detroit, MI 48205 — any chance the seller would take a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>

--- a/GV_Campaign_NoEmail_20260620.xlsx
+++ b/GV_Campaign_NoEmail_20260620.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Good day Greg. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 125 Deer Hound Trl, Columbia, SC 29223. could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Appreciate it!</t>
+          <t>Good day Greg. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 125 Deer Hound Trl, Columbia, SC 29223. Could the seller look at a cash, as-is offer, quick close and a short inspection? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Good day Tyjuan. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 108 Malisa Dr, Columbia, SC 29229. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
+          <t>Good day Tyjuan. This is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 108 Malisa Dr, Columbia, SC 29229. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hi Julie — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1146 Castle Pinckney Rd, Columbia, SC 29223 for cash. open to a discounted cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi Julie — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1146 Castle Pinckney Rd, Columbia, SC 29223 for cash. Open to a discounted cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Good day Jasmine. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 13 Gatewood Way, Columbia, SC 29229. open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
+          <t>Good day Jasmine. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 13 Gatewood Way, Columbia, SC 29229. Open to a discounted cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hey Lauren — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 1531 Alma Rd, Columbia, SC 29209. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
+          <t>Hey Lauren — Charles here with Paragon Government Solutions. I'm a cash buyer interested in 1531 Alma Rd, Columbia, SC 29209. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hi Tricia. my name's Charles Pleasant, Paragon Government Solutions, and I came across 116 Patio Pl, Columbia, SC 29212 and buy cash. could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Tricia. My name's Charles Pleasant, Paragon Government Solutions, and I came across 116 Patio Pl, Columbia, SC 29212 and buy cash. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Joey, hi. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 1515 Rushmore Rd, Columbia, SC 29210. any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
+          <t>Joey, hi. This is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 1515 Rushmore Rd, Columbia, SC 29210. Any chance the seller would take a cash, as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hello Jamila. Charles here with Paragon Government Solutions, and I'm interested in buying 103 Village Way, Columbia, SC 29209 for cash. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks much!</t>
+          <t>Hello Jamila. Charles here with Paragon Government Solutions, and I'm interested in buying 103 Village Way, Columbia, SC 29209 for cash. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Becky, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 115 Mulberry Ln, Columbia, SC 29201. would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
+          <t>Becky, hi. Charles here with Paragon Government Solutions, and I'd like to put in a cash offer on 115 Mulberry Ln, Columbia, SC 29201. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hi there Bryant — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1111 Cloister Pl, Columbia, SC 29210. open to a discounted cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
+          <t>Hi there Bryant — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1111 Cloister Pl, Columbia, SC 29210. Open to a discounted cash, as-is offer with fast close with a brief inspection window. Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Good day Jamie. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2018 Hallmark Ct, Lakeland, FL 33803. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
+          <t>Good day Jamie. This is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 2018 Hallmark Ct, Lakeland, FL 33803. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hey Amber. Charles Pleasant, Paragon Government Solutions, and I came across 314 Leton Dr, Columbia, SC 29210 and buy cash. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
+          <t>Hey Amber. Charles Pleasant, Paragon Government Solutions, and I came across 314 Leton Dr, Columbia, SC 29210 and buy cash. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hi there Angela — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1024 Price Ave, Columbia, SC 29201. would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi there Angela — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 1024 Price Ave, Columbia, SC 29201. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Good day Anthony — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 11439 Ohio St, Detroit, MI 48204. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
+          <t>Good day Anthony — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 11439 Ohio St, Detroit, MI 48204. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Good day Avia. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 205 Parliament Dr, Columbia, SC 29223. open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
+          <t>Good day Avia. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 205 Parliament Dr, Columbia, SC 29223. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Good day Billy — Charles here with Paragon Government Solutions. I'm a cash investor looking at 23 Braiden Manor Rd, Columbia, SC 29209. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
+          <t>Good day Billy — Charles here with Paragon Government Solutions. I'm a cash investor looking at 23 Braiden Manor Rd, Columbia, SC 29209. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hello CHAD. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1169 WOODRUFF Avenue, Jacksonville, FL 32205. would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
+          <t>Hello CHAD. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1169 WOODRUFF Avenue, Jacksonville, FL 32205. Would the owner entertain a cash as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cody, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 104 Harbor Dr, Columbia, SC 29229 for cash. would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
+          <t>Cody, hi. My name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 104 Harbor Dr, Columbia, SC 29229 for cash. Would the owner entertain a cash as-is offer, fast cash close, short feasibility window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DIETCHI, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1007 Anarine Rd, Fayetteville, NC 28303 for cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
+          <t>DIETCHI, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 1007 Anarine Rd, Fayetteville, NC 28303 for cash. Is the seller open to a cash as-is offer with close quickly, short inspection period. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hey Heather. I'm Charles with Paragon Government Solutions, and I came across 15385 Stansbury St, Detroit, MI 48227 and buy cash. is the seller open to a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hey Heather. I'm Charles with Paragon Government Solutions, and I came across 15385 Stansbury St, Detroit, MI 48227 and buy cash. Is the seller open to a cash as-is offer, quick close and a short inspection? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hey Melissa. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 15534 Rocco Dr, Baker, LA 70714. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
+          <t>Hey Melissa. This is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 15534 Rocco Dr, Baker, LA 70714. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Good day Patrick — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 135 Fox Squirrel Cir, Columbia, SC 29209. could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Patrick — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 135 Fox Squirrel Cir, Columbia, SC 29209. Could the seller look at a cash, as-is offer with quick close and a short inspection. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hello Sam — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 10799 Worden St, Detroit, MI 48224. is the seller open to a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
+          <t>Hello Sam — this is Charles Pleasant with Paragon Government Solutions. I'm reaching out about 10799 Worden St, Detroit, MI 48224. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Good day there — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3700 Ulmer Rd, Columbia, SC 29209. could the seller look at a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
+          <t>Good day there — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 3700 Ulmer Rd, Columbia, SC 29209. Could the seller look at a cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Good day Albert. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 12717 Riad St, Grosse Pointe, MI 48224. could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks so much!</t>
+          <t>Good day Albert. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 12717 Riad St, Grosse Pointe, MI 48224. Could the seller look at a cash, as-is offer, close quickly, short inspection period? What's a good email for the written offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hi Alex — Charles here with Paragon Government Solutions. I'm reaching out about 201 Sandhurst Rd, Columbia, SC 29210. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
+          <t>Hi Alex — Charles here with Paragon Government Solutions. I'm reaching out about 201 Sandhurst Rd, Columbia, SC 29210. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hello Alex — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1152 Vinewood St, Detroit, MI 48216. would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
+          <t>Hello Alex — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 1152 Vinewood St, Detroit, MI 48216. Would the seller consider a cash, as-is offer with close quickly, short inspection period. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hello Alexander. I'm Charles with Paragon Government Solutions, and I came across 16321 Stockbridge Ave, Cleveland, OH 44128 and buy cash. any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Alexander. I'm Charles with Paragon Government Solutions, and I came across 16321 Stockbridge Ave, Cleveland, OH 44128 and buy cash. Any chance the seller would take a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Good day Alexandra. I'm Charles with Paragon Government Solutions, and I came across 219 Dixon Dr, Columbia, SC 29203 and buy cash. could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
+          <t>Good day Alexandra. I'm Charles with Paragon Government Solutions, and I came across 219 Dixon Dr, Columbia, SC 29203 and buy cash. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Good day Andy. Charles here with Paragon Government Solutions, and I'm reaching out about 6506 Christie Rd, Columbia, SC 29209. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
+          <t>Good day Andy. Charles here with Paragon Government Solutions, and I'm reaching out about 6506 Christie Rd, Columbia, SC 29209. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hi Bobby. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 14941 Littlefield St, Detroit, MI 48227. would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Appreciate it!</t>
+          <t>Hi Bobby. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 14941 Littlefield St, Detroit, MI 48227. Would the owner entertain a cash as-is offer, fast close with a brief inspection window? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hi there Brad. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1253 Mosser Dr, Columbia, SC 29203. would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
+          <t>Hi there Brad. My name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 1253 Mosser Dr, Columbia, SC 29203. Would the owner entertain a cash as-is offer, a quick clean close and short due diligence? What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hey Brittany. Charles Pleasant, Paragon Government Solutions, and I came across 2065 Missouri St, Baton Rouge, LA 70802 and buy cash. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
+          <t>Hey Brittany. Charles Pleasant, Paragon Government Solutions, and I came across 2065 Missouri St, Baton Rouge, LA 70802 and buy cash. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hey Cameron — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 9175 Everts St, Detroit, MI 48224. would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks much!</t>
+          <t>Hey Cameron — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 9175 Everts St, Detroit, MI 48224. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hi there CHRISTINA — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1602 Gardenia Ave, Fayetteville, NC 28311. is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
+          <t>Hi there CHRISTINA — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 1602 Gardenia Ave, Fayetteville, NC 28311. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hello Crystal — Charles Pleasant, Paragon Government Solutions. I came across 5648 S Sawyer Ave, Chicago, IL 60629 and buy cash. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
+          <t>Hello Crystal — Charles Pleasant, Paragon Government Solutions. I came across 5648 S Sawyer Ave, Chicago, IL 60629 and buy cash. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ejaz, hi — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 14440 Chelsea St, Detroit, MI 48213. is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Appreciate it!</t>
+          <t>Ejaz, hi — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 14440 Chelsea St, Detroit, MI 48213. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hello Evan — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 4203 New Orleans St, Houston, TX 77020 for cash. any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
+          <t>Hello Evan — my name's Charles Pleasant, Paragon Government Solutions. I'm interested in buying 4203 New Orleans St, Houston, TX 77020 for cash. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Franco, hi — Charles here with Paragon Government Solutions. I'm a cash investor looking at 13027 Rosemary St, Detroit, MI 48213. could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks much!</t>
+          <t>Franco, hi — Charles here with Paragon Government Solutions. I'm a cash investor looking at 13027 Rosemary St, Detroit, MI 48213. Could the seller look at a cash, as-is offer with fast close with a brief inspection window. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Greg, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 20 Shuler Cir, Columbia, SC 29212. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
+          <t>Greg, hi — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 20 Shuler Cir, Columbia, SC 29212. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gregory, hi. this is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 4440 Sexton Rd, Cleveland, OH 44105. is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
+          <t>Gregory, hi. This is Charles Pleasant with Paragon Government Solutions, and I'd like to put in a cash offer on 4440 Sexton Rd, Cleveland, OH 44105. Is the seller open to a cash as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hassan, hi — my name's Charles Pleasant, Paragon Government Solutions. I came across 20569 Evergreen Rd, Detroit, MI 48219 and buy cash. would the owner entertain a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Appreciate it!</t>
+          <t>Hassan, hi — my name's Charles Pleasant, Paragon Government Solutions. I came across 20569 Evergreen Rd, Detroit, MI 48219 and buy cash. Would the owner entertain a cash as-is offer with quick close and a short inspection. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JACQUELYN, hi. Charles here with Paragon Government Solutions, and I'm reaching out about 2371 JAYSON Avenue, Jacksonville, FL 32208. could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Much appreciated!</t>
+          <t>JACQUELYN, hi. Charles here with Paragon Government Solutions, and I'm reaching out about 2371 JAYSON Avenue, Jacksonville, FL 32208. Could the seller look at a cash, as-is offer, a quick clean close and short due diligence? What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hey Jay. I'm Charles with Paragon Government Solutions, and I'm reaching out about 209 Leago St, Houston, TX 77022. any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
+          <t>Hey Jay. I'm Charles with Paragon Government Solutions, and I'm reaching out about 209 Leago St, Houston, TX 77022. Any chance the seller would take a cash, as-is offer, quick close and a short inspection? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Good day Kaila. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 17184 Dresden St, Detroit, MI 48205. open to a discounted cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
+          <t>Good day Kaila. Charles here with Paragon Government Solutions, and I'm a cash buyer interested in 17184 Dresden St, Detroit, MI 48205. Open to a discounted cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hello Kanaan — I'm Charles with Paragon Government Solutions. I came across 1018 W 104th Pl, Chicago, IL 60643 and buy cash. would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks!</t>
+          <t>Hello Kanaan — I'm Charles with Paragon Government Solutions. I came across 1018 W 104th Pl, Chicago, IL 60643 and buy cash. Would the owner entertain a cash as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hello KRAVIN. Charles here with Paragon Government Solutions, and I'm reaching out about 2051 FRANK E Avenue, Jacksonville, FL 32208. open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
+          <t>Hello KRAVIN. Charles here with Paragon Government Solutions, and I'm reaching out about 2051 FRANK E Avenue, Jacksonville, FL 32208. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hey LaToya. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1253 Rabon Pond Dr, Columbia, SC 29223. could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
+          <t>Hey LaToya. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1253 Rabon Pond Dr, Columbia, SC 29223. Could the seller look at a cash, as-is offer, close quickly, short inspection period? Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hi there LaTrina — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 19783 Annott St, Detroit, MI 48205. would the seller consider a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
+          <t>Hi there LaTrina — Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 19783 Annott St, Detroit, MI 48205. Would the seller consider a cash, as-is offer with close quickly, short inspection period. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hello MAIDELYS — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6978 PAUL HOWARD Drive, Jacksonville, FL 32222. would the owner entertain a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
+          <t>Hello MAIDELYS — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 6978 PAUL HOWARD Drive, Jacksonville, FL 32222. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Good day Mary — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 336 Byron Rd, Columbia, SC 29209. any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
+          <t>Good day Mary — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 336 Byron Rd, Columbia, SC 29209. Any chance the seller would take a cash, as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hi Mladenka — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 5308 W LEWIS Avenue W, Phoenix, AZ 85035 for cash. is the seller open to a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
+          <t>Hi Mladenka — Charles Pleasant, Paragon Government Solutions. I'm interested in buying 5308 W LEWIS Avenue W, Phoenix, AZ 85035 for cash. Is the seller open to a cash as-is offer with close quickly, short inspection period. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Good day Mo — Charles here with Paragon Government Solutions. I came across 125 N Lake Pointe Dr, Columbia, SC 29229 and buy cash. is the seller open to a cash as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
+          <t>Good day Mo — Charles here with Paragon Government Solutions. I came across 125 N Lake Pointe Dr, Columbia, SC 29229 and buy cash. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Good day Mohamed — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 16610 Collingham Dr, Detroit, MI 48205. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
+          <t>Good day Mohamed — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 16610 Collingham Dr, Detroit, MI 48205. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hello Monika. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2947 Appaloosa Dr, Dallas, TX 75237. is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks so much!</t>
+          <t>Hello Monika. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 2947 Appaloosa Dr, Dallas, TX 75237. Is the seller open to a cash as-is offer, close quickly, short inspection period? Where should I send the offer in writing? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hi there Nadia — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 17206 Fenelon St, Detroit, MI 48212. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
+          <t>Hi there Nadia — Charles Pleasant, Paragon Government Solutions. I'm a cash buyer interested in 17206 Fenelon St, Detroit, MI 48212. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Good day NAJI. this is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 152 W 10TH Street, Jacksonville, FL 32206. is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
+          <t>Good day NAJI. This is Charles Pleasant with Paragon Government Solutions, and I'm a cash buyer interested in 152 W 10TH Street, Jacksonville, FL 32206. Is the seller open to a cash as-is offer, quick close and a short inspection? Best email for the formal offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hello Nazareth — my name's Charles Pleasant, Paragon Government Solutions. I came across 2223 Gray St, Detroit, MI 48215 and buy cash. could the seller look at a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
+          <t>Hello Nazareth — my name's Charles Pleasant, Paragon Government Solutions. I came across 2223 Gray St, Detroit, MI 48215 and buy cash. Could the seller look at a cash, as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hello Pamela — Charles here with Paragon Government Solutions. I'm interested in buying 2912 Chestnut St, Columbia, SC 29204 for cash. would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
+          <t>Hello Pamela — Charles here with Paragon Government Solutions. I'm interested in buying 2912 Chestnut St, Columbia, SC 29204 for cash. Would the seller consider a cash, as-is offer with a quick clean close and short due diligence. What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rachel, hi — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2539 Cherry St, Columbia, SC 29205. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
+          <t>Rachel, hi — Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 2539 Cherry St, Columbia, SC 29205. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Good day Raquel — I'm Charles with Paragon Government Solutions. I'm interested in buying 1513 Dianne Ct SE, Atlanta, GA for cash. is the seller open to a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
+          <t>Good day Raquel — I'm Charles with Paragon Government Solutions. I'm interested in buying 1513 Dianne Ct SE, Atlanta, GA for cash. Is the seller open to a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hello Sydney — Charles here with Paragon Government Solutions. I came across 425 Columbia St, Shreveport, LA 71104 and buy cash. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Sydney — Charles here with Paragon Government Solutions. I came across 425 Columbia St, Shreveport, LA 71104 and buy cash. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hi Timeka — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 2009 Las Cruces Ln, Dallas, TX 75217. open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
+          <t>Hi Timeka — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 2009 Las Cruces Ln, Dallas, TX 75217. Open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Will, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 9426 Nyssa St, Houston, TX 77078. is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
+          <t>Will, hi. My name's Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 9426 Nyssa St, Houston, TX 77078. Is the seller open to a cash as-is offer, close quickly, short inspection period? What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hi there WILLIAM — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 2995 Coleman Rd, Eastover, NC 28312. would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
+          <t>Hi there WILLIAM — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 2995 Coleman Rd, Eastover, NC 28312. Would the owner entertain a cash as-is offer with fast close with a brief inspection window. What's the best email to send it to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Good day there. this is Charles Pleasant with Paragon Government Solutions, and I came across 2737 Bristol Pl, New Orleans, LA 70131 and buy cash. could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
+          <t>Good day there. This is Charles Pleasant with Paragon Government Solutions, and I came across 2737 Bristol Pl, New Orleans, LA 70131 and buy cash. Could the seller look at a cash, as-is offer, fast close with a brief inspection window? What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>there, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3109 Downes Grove Rd, Columbia, SC 29209; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
+          <t>There, hi, my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 3109 Downes Grove Rd, Columbia, SC 29209; is the seller open to a cash as-is offer, quick close and a short inspection? I can send written terms today. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Good day there — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 950 W ROMA Avenue, Phoenix, AZ 85013. is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
+          <t>Good day there — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 950 W ROMA Avenue, Phoenix, AZ 85013. Is the seller open to a cash as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thanks!</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Acencion, hi — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 16643 Seawolf Dr, Houston, TX 77062. would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
+          <t>Acencion, hi — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 16643 Seawolf Dr, Houston, TX 77062. Would the seller consider a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hello Adam — Charles Pleasant, Paragon Government Solutions. I came across 15394 Freeland St, Detroit, MI 48227 and buy cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
+          <t>Hello Adam — Charles Pleasant, Paragon Government Solutions. I came across 15394 Freeland St, Detroit, MI 48227 and buy cash. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where can I email the written terms? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Good day Adekunle. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 11722 S Parnell Ave, Chicago, IL 60628. would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
+          <t>Good day Adekunle. Charles Pleasant, Paragon Government Solutions, and I'm a cash investor looking at 11722 S Parnell Ave, Chicago, IL 60628. Would the seller consider a cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hi Adrian. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 15003 Manor St, Detroit, MI 48238. is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
+          <t>Hi Adrian. I'm Charles with Paragon Government Solutions, and I'd like to put in a cash offer on 15003 Manor St, Detroit, MI 48238. Is the seller open to a cash as-is offer, quick close and a short inspection? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Good day Adrienne — I'm Charles with Paragon Government Solutions. I'm interested in buying 18402 Revere St, Detroit, MI 48234 for cash. any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
+          <t>Good day Adrienne — I'm Charles with Paragon Government Solutions. I'm interested in buying 18402 Revere St, Detroit, MI 48234 for cash. Any chance the seller would take a cash, as-is offer with close quickly, short inspection period. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hey Alannah. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 1314 Red Ridge Ter, Columbia, SC 29203. any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
+          <t>Hey Alannah. Charles Pleasant, Paragon Government Solutions, and I'd like to put in a cash offer on 1314 Red Ridge Ter, Columbia, SC 29203. Any chance the seller would take a cash, as-is offer, close quickly, short inspection period? What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hi Alejandro — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 919 Christine St, Houston, TX 77017. would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Alejandro — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 919 Christine St, Houston, TX 77017. Would the owner entertain a cash as-is offer with fast cash close, short feasibility window. What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Hey Alex — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3906 Metropolitan Ave, Dallas, TX 75210. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
+          <t>Hey Alex — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 3906 Metropolitan Ave, Dallas, TX 75210. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. Best email for the formal offer? Thank you!</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Alex, hi. my name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 423 Exchange St, Houston, TX 77020 for cash. would the seller consider a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks much!</t>
+          <t>Alex, hi. My name's Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 423 Exchange St, Houston, TX 77020 for cash. Would the seller consider a cash, as-is offer, quick close and a short inspection? Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hi Alexander — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2317 NW 30th Ter, Cape Coral, FL 33993. open to a discounted cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hi Alexander — this is Charles Pleasant with Paragon Government Solutions. I'm a cash investor looking at 2317 NW 30th Ter, Cape Coral, FL 33993. Open to a discounted cash, as-is offer with quick close and a short inspection. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Alexandria, hi. I'm Charles with Paragon Government Solutions, and I'm interested in buying 5981 Arapaho Rd #1607, Dallas TX 75248 for cash. could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
+          <t>Alexandria, hi. I'm Charles with Paragon Government Solutions, and I'm interested in buying 5981 Arapaho Rd #1607, Dallas TX 75248 for cash. Could the seller look at a cash, as-is offer, fast cash close, short feasibility window? What email should I send the written offer to? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Good day Alexis. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 17360 Mansfield St, Detroit, MI 48235. would the seller consider a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks!</t>
+          <t>Good day Alexis. Charles Pleasant, Paragon Government Solutions, and I'm reaching out about 17360 Mansfield St, Detroit, MI 48235. Would the seller consider a cash, as-is offer, close quickly, short inspection period? Where can I email the written terms? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hi Ali — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 11718 Plainview Ave, Detroit, MI 48228. any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
+          <t>Hi Ali — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 11718 Plainview Ave, Detroit, MI 48228. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hi Ali. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 9030 Plainview Ave, Detroit, MI 48228 for cash. is the seller open to a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
+          <t>Hi Ali. Charles Pleasant, Paragon Government Solutions, and I'm interested in buying 9030 Plainview Ave, Detroit, MI 48228 for cash. Is the seller open to a cash as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Hey Amanda — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 10323 Sweetbrook Dr, Houston, TX 77038. is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
+          <t>Hey Amanda — I'm Charles with Paragon Government Solutions. I'm a cash buyer interested in 10323 Sweetbrook Dr, Houston, TX 77038. Is the seller open to a cash as-is offer with fast close with a brief inspection window. Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hello AMANDA. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1009 Bugle Call Dr, Fayetteville, NC 28314. open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
+          <t>Hello AMANDA. I'm Charles with Paragon Government Solutions, and I'm a cash investor looking at 1009 Bugle Call Dr, Fayetteville, NC 28314. Open to a discounted cash, as-is offer, fast cash close, short feasibility window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Hi AMY — Charles Pleasant, Paragon Government Solutions. I came across 7092 Pantego Dr, Fayetteville, NC 28314 and buy cash. would the owner entertain a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
+          <t>Hi AMY — Charles Pleasant, Paragon Government Solutions. I came across 7092 Pantego Dr, Fayetteville, NC 28314 and buy cash. Would the owner entertain a cash as-is offer with quick close and a short inspection. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hello Andre — Charles here with Paragon Government Solutions. I'm reaching out about 19447 Sunset St, Detroit, MI 48234. is the seller open to a cash as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
+          <t>Hello Andre — Charles here with Paragon Government Solutions. I'm reaching out about 19447 Sunset St, Detroit, MI 48234. Is the seller open to a cash as-is offer with quick close and a short inspection. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hi Angel. this is Charles Pleasant with Paragon Government Solutions, and I came across 7606 Blessing Ave, Austin, TX 78752 and buy cash. would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Appreciate it!</t>
+          <t>Hi Angel. This is Charles Pleasant with Paragon Government Solutions, and I came across 7606 Blessing Ave, Austin, TX 78752 and buy cash. Would the seller consider a cash, as-is offer, a quick clean close and short due diligence? What's a good email for the written offer? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Hello Angela — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 16 Carroll St, Trenton, NJ 08609. any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
+          <t>Hello Angela — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 16 Carroll St, Trenton, NJ 08609. Any chance the seller would take a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hi there ANTHONY. Charles here with Paragon Government Solutions, and I came across 2917 PARR Court E, Jacksonville, FL 32216 and buy cash. would the seller consider a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
+          <t>Hi there ANTHONY. Charles here with Paragon Government Solutions, and I came across 2917 PARR Court E, Jacksonville, FL 32216 and buy cash. Would the seller consider a cash, as-is offer, close quickly, short inspection period? What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Good day ANTOINETTE — Charles here with Paragon Government Solutions. I'm interested in buying 9419 SCADLOCKE Road, Jacksonville, FL 32208 for cash. is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
+          <t>Good day ANTOINETTE — Charles here with Paragon Government Solutions. I'm interested in buying 9419 SCADLOCKE Road, Jacksonville, FL 32208 for cash. Is the seller open to a cash as-is offer with close quickly, short inspection period. Where should I send the offer in writing? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hey April — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 6510 Portsmouth Dr, Fayetteville, NC 28314. is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Appreciate it!</t>
+          <t>Hey April — my name's Charles Pleasant, Paragon Government Solutions. I'm a cash investor looking at 6510 Portsmouth Dr, Fayetteville, NC 28314. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. What's the best email to send it to? Appreciate it!</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Good day APRYL — my name's Charles Pleasant, Paragon Government Solutions. I came across 2225 THIERVY Drive, Jacksonville, FL 32210 and buy cash. is the seller open to a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
+          <t>Good day APRYL — my name's Charles Pleasant, Paragon Government Solutions. I came across 2225 THIERVY Drive, Jacksonville, FL 32210 and buy cash. Is the seller open to a cash as-is offer with close quickly, short inspection period. What's a good email for the written offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Hey Arianna. my name's Charles Pleasant, Paragon Government Solutions, and I came across 4153 Concord St, Detroit, MI 48207 and buy cash. would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
+          <t>Hey Arianna. My name's Charles Pleasant, Paragon Government Solutions, and I came across 4153 Concord St, Detroit, MI 48207 and buy cash. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? What's a good email for the written offer? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Hello ARMANDO — Charles here with Paragon Government Solutions. I'm a cash investor looking at 153 Knapp Ave, Hamilton, NJ 08610. could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
+          <t>Hello ARMANDO — Charles here with Paragon Government Solutions. I'm a cash investor looking at 153 Knapp Ave, Hamilton, NJ 08610. Could the seller look at a cash, as-is offer with fast cash close, short feasibility window. What email should I send the written offer to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Hey Ashley — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3879 W 21st St, Cleveland, OH 44109. any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thank you!</t>
+          <t>Hey Ashley — this is Charles Pleasant with Paragon Government Solutions. I'd like to put in a cash offer on 3879 W 21st St, Cleveland, OH 44109. Any chance the seller would take a cash, as-is offer with quick close and a short inspection. What's the best email to send it to? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hello Ashley — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 414 Angel Grove Ln, Columbia, SC 29210. open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
+          <t>Hello Ashley — I'm Charles with Paragon Government Solutions. I'm a cash investor looking at 414 Angel Grove Ln, Columbia, SC 29210. Open to a discounted cash, as-is offer with a quick clean close and short due diligence. What's a good email for the written offer? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Hi Ashley. my name's Charles Pleasant, Paragon Government Solutions, and I came across 1008 Walnut Ave, Baltimore, MD 21229 and buy cash. is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
+          <t>Hi Ashley. My name's Charles Pleasant, Paragon Government Solutions, and I came across 1008 Walnut Ave, Baltimore, MD 21229 and buy cash. Is the seller open to a cash as-is offer, fast close with a brief inspection window? Where can I email the written terms? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Hi Ashley — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 19261 Mitchell St, Detroit, MI 48234. would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
+          <t>Hi Ashley — my name's Charles Pleasant, Paragon Government Solutions. I'm reaching out about 19261 Mitchell St, Detroit, MI 48234. Would the seller consider a cash, as-is offer with fast cash close, short feasibility window. Best email for the formal offer? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Hey Babajide — I'm Charles with Paragon Government Solutions. I came across 317 E 134th St, Chicago, IL 60827 and buy cash. is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
+          <t>Hey Babajide — I'm Charles with Paragon Government Solutions. I came across 317 E 134th St, Chicago, IL 60827 and buy cash. Is the seller open to a cash as-is offer with a quick clean close and short due diligence. Where can I email the written terms? Thanks much!</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Hi Bailee. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 11144 Sanford St, Detroit, MI 48205. would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks so much!</t>
+          <t>Hi Bailee. Charles here with Paragon Government Solutions, and I'm a cash investor looking at 11144 Sanford St, Detroit, MI 48205. Would the seller consider a cash, as-is offer, fast close with a brief inspection window? Where can I email the written terms? Thanks so much!</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hello Barbara — Charles here with Paragon Government Solutions. I'm a cash investor looking at 2336 Albert St, Alexandria, LA 71301. would the seller consider a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
+          <t>Hello Barbara — Charles here with Paragon Government Solutions. I'm a cash investor looking at 2336 Albert St, Alexandria, LA 71301. Would the seller consider a cash, as-is offer with fast close with a brief inspection window. What email should I send the written offer to? Much appreciated!</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Hey BARBARA — my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1603 W 14TH Street, Jacksonville, FL 32209. open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
+          <t>Hey BARBARA — my name's Charles Pleasant, Paragon Government Solutions. I'd like to put in a cash offer on 1603 W 14TH Street, Jacksonville, FL 32209. Open to a discounted cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Thank you!</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Hello Belle — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 413 Seton Hall Dr, Columbia, SC 29223. could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
+          <t>Hello Belle — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 413 Seton Hall Dr, Columbia, SC 29223. Could the seller look at a cash, as-is offer with a quick clean close and short due diligence. Best email for the formal offer? Thanks!</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Hi Benjamin — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1005 Wildwood Ave, Columbia, SC 29203. any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Much appreciated!</t>
+          <t>Hi Benjamin — this is Charles Pleasant with Paragon Government Solutions. I'm a cash buyer interested in 1005 Wildwood Ave, Columbia, SC 29203. Any chance the seller would take a cash, as-is offer with fast cash close, short feasibility window. Where should I send the offer in writing? Mu